--- a/internal_doc/05.测试设计/story/事务支持RC隔离级别/事务自动化用例跟踪表.xlsx
+++ b/internal_doc/05.测试设计/story/事务支持RC隔离级别/事务自动化用例跟踪表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="RU" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="704" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="950" uniqueCount="269">
   <si>
     <t>用例编号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -844,6 +844,18 @@
   </si>
   <si>
     <t>卢伟康</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>是</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>否</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>版本问题，暂不提交</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1246,7 +1258,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" hidden="1">
       <c r="A5" t="s">
         <v>171</v>
       </c>
@@ -1257,7 +1269,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" hidden="1">
       <c r="A6" t="s">
         <v>172</v>
       </c>
@@ -1268,7 +1280,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" hidden="1">
       <c r="A7" t="s">
         <v>173</v>
       </c>
@@ -1279,7 +1291,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" hidden="1">
       <c r="A8" t="s">
         <v>174</v>
       </c>
@@ -1290,7 +1302,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" hidden="1">
       <c r="A9" t="s">
         <v>175</v>
       </c>
@@ -1301,7 +1313,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" hidden="1">
       <c r="A10" t="s">
         <v>176</v>
       </c>
@@ -1312,7 +1324,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" hidden="1">
       <c r="A11" t="s">
         <v>177</v>
       </c>
@@ -1323,7 +1335,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" hidden="1">
       <c r="A12" t="s">
         <v>178</v>
       </c>
@@ -1334,7 +1346,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" hidden="1">
       <c r="A13" t="s">
         <v>179</v>
       </c>
@@ -1345,7 +1357,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" hidden="1">
       <c r="A14" t="s">
         <v>180</v>
       </c>
@@ -1378,7 +1390,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="17" spans="1:6" hidden="1">
+    <row r="17" spans="1:7" hidden="1">
       <c r="A17" t="s">
         <v>183</v>
       </c>
@@ -1389,7 +1401,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="18" spans="1:6" hidden="1">
+    <row r="18" spans="1:7" hidden="1">
       <c r="A18" t="s">
         <v>184</v>
       </c>
@@ -1400,7 +1412,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:7" hidden="1">
       <c r="A19" t="s">
         <v>185</v>
       </c>
@@ -1411,7 +1423,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:7" hidden="1">
       <c r="A20" t="s">
         <v>186</v>
       </c>
@@ -1422,7 +1434,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:7" hidden="1">
       <c r="A21" t="s">
         <v>187</v>
       </c>
@@ -1433,7 +1445,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:7" hidden="1">
       <c r="A22" t="s">
         <v>188</v>
       </c>
@@ -1444,151 +1456,313 @@
         <v>265</v>
       </c>
     </row>
-    <row r="23" spans="1:6" hidden="1">
+    <row r="23" spans="1:7">
       <c r="A23" t="s">
         <v>189</v>
       </c>
+      <c r="B23" t="s">
+        <v>266</v>
+      </c>
+      <c r="C23" t="s">
+        <v>267</v>
+      </c>
       <c r="D23" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" hidden="1">
+      <c r="G23" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
       <c r="A24" t="s">
         <v>190</v>
       </c>
+      <c r="B24" t="s">
+        <v>266</v>
+      </c>
+      <c r="C24" t="s">
+        <v>267</v>
+      </c>
       <c r="D24" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="25" spans="1:6" hidden="1">
+      <c r="G24" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
       <c r="A25" t="s">
         <v>191</v>
       </c>
+      <c r="B25" t="s">
+        <v>266</v>
+      </c>
+      <c r="C25" t="s">
+        <v>267</v>
+      </c>
       <c r="D25" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="26" spans="1:6" hidden="1">
+      <c r="G25" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
       <c r="A26" t="s">
         <v>192</v>
       </c>
+      <c r="B26" t="s">
+        <v>266</v>
+      </c>
+      <c r="C26" t="s">
+        <v>267</v>
+      </c>
       <c r="D26" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="27" spans="1:6" hidden="1">
+      <c r="G26" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
       <c r="A27" t="s">
         <v>193</v>
       </c>
+      <c r="B27" t="s">
+        <v>266</v>
+      </c>
+      <c r="C27" t="s">
+        <v>267</v>
+      </c>
       <c r="D27" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="28" spans="1:6" hidden="1">
+      <c r="G27" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
       <c r="A28" t="s">
         <v>194</v>
       </c>
+      <c r="B28" t="s">
+        <v>266</v>
+      </c>
+      <c r="C28" t="s">
+        <v>267</v>
+      </c>
       <c r="D28" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="29" spans="1:6" hidden="1">
+      <c r="G28" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
       <c r="A29" t="s">
         <v>195</v>
       </c>
+      <c r="B29" t="s">
+        <v>266</v>
+      </c>
+      <c r="C29" t="s">
+        <v>267</v>
+      </c>
       <c r="D29" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="30" spans="1:6" hidden="1">
+      <c r="G29" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
       <c r="A30" t="s">
         <v>196</v>
       </c>
+      <c r="B30" t="s">
+        <v>266</v>
+      </c>
+      <c r="C30" t="s">
+        <v>267</v>
+      </c>
       <c r="D30" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="31" spans="1:6" hidden="1">
+      <c r="G30" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
       <c r="A31" t="s">
         <v>197</v>
       </c>
+      <c r="B31" t="s">
+        <v>266</v>
+      </c>
+      <c r="C31" t="s">
+        <v>267</v>
+      </c>
       <c r="D31" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="32" spans="1:6" hidden="1">
+      <c r="G31" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
       <c r="A32" t="s">
         <v>198</v>
       </c>
+      <c r="B32" t="s">
+        <v>266</v>
+      </c>
+      <c r="C32" t="s">
+        <v>267</v>
+      </c>
       <c r="D32" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="33" spans="1:6" hidden="1">
+      <c r="G32" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
       <c r="A33" t="s">
         <v>199</v>
       </c>
+      <c r="B33" t="s">
+        <v>266</v>
+      </c>
+      <c r="C33" t="s">
+        <v>267</v>
+      </c>
       <c r="D33" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="34" spans="1:6" hidden="1">
+      <c r="G33" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
       <c r="A34" t="s">
         <v>200</v>
       </c>
+      <c r="B34" t="s">
+        <v>266</v>
+      </c>
+      <c r="C34" t="s">
+        <v>267</v>
+      </c>
       <c r="D34" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="35" spans="1:6" hidden="1">
+      <c r="G34" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
       <c r="A35" t="s">
         <v>201</v>
       </c>
+      <c r="B35" t="s">
+        <v>266</v>
+      </c>
+      <c r="C35" t="s">
+        <v>267</v>
+      </c>
       <c r="D35" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="36" spans="1:6" hidden="1">
+      <c r="G35" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
       <c r="A36" t="s">
         <v>202</v>
       </c>
+      <c r="B36" t="s">
+        <v>266</v>
+      </c>
+      <c r="C36" t="s">
+        <v>267</v>
+      </c>
       <c r="D36" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="37" spans="1:6" hidden="1">
+      <c r="G36" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
       <c r="A37" t="s">
         <v>203</v>
       </c>
+      <c r="B37" t="s">
+        <v>266</v>
+      </c>
+      <c r="C37" t="s">
+        <v>267</v>
+      </c>
       <c r="D37" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="38" spans="1:6" hidden="1">
+      <c r="G37" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
       <c r="A38" t="s">
         <v>204</v>
       </c>
+      <c r="B38" t="s">
+        <v>266</v>
+      </c>
+      <c r="C38" t="s">
+        <v>267</v>
+      </c>
       <c r="D38" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="39" spans="1:6" hidden="1">
+      <c r="G38" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
       <c r="A39" t="s">
         <v>205</v>
       </c>
+      <c r="B39" t="s">
+        <v>266</v>
+      </c>
+      <c r="C39" t="s">
+        <v>267</v>
+      </c>
       <c r="D39" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="40" spans="1:6" hidden="1">
+      <c r="G39" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
       <c r="A40" t="s">
         <v>206</v>
       </c>
+      <c r="B40" t="s">
+        <v>266</v>
+      </c>
+      <c r="C40" t="s">
+        <v>267</v>
+      </c>
       <c r="D40" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="41" spans="1:6" hidden="1">
+      <c r="G40" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" hidden="1">
       <c r="A41" t="s">
         <v>207</v>
       </c>
@@ -1599,7 +1773,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="42" spans="1:6" hidden="1">
+    <row r="42" spans="1:7" hidden="1">
       <c r="A42" t="s">
         <v>208</v>
       </c>
@@ -1610,7 +1784,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="43" spans="1:6" hidden="1">
+    <row r="43" spans="1:7" hidden="1">
       <c r="A43" t="s">
         <v>209</v>
       </c>
@@ -1621,7 +1795,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="44" spans="1:6">
+    <row r="44" spans="1:7" hidden="1">
       <c r="A44" t="s">
         <v>210</v>
       </c>
@@ -1632,7 +1806,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="45" spans="1:6">
+    <row r="45" spans="1:7" hidden="1">
       <c r="A45" t="s">
         <v>211</v>
       </c>
@@ -1643,7 +1817,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="46" spans="1:6" hidden="1">
+    <row r="46" spans="1:7" hidden="1">
       <c r="A46" t="s">
         <v>212</v>
       </c>
@@ -1654,7 +1828,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="47" spans="1:6" hidden="1">
+    <row r="47" spans="1:7" hidden="1">
       <c r="A47" t="s">
         <v>213</v>
       </c>
@@ -1665,7 +1839,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="48" spans="1:6" hidden="1">
+    <row r="48" spans="1:7" hidden="1">
       <c r="A48" t="s">
         <v>214</v>
       </c>
@@ -1676,7 +1850,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="49" spans="1:6">
+    <row r="49" spans="1:6" hidden="1">
       <c r="A49" t="s">
         <v>215</v>
       </c>
@@ -2028,7 +2202,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="81" spans="1:6" hidden="1">
+    <row r="81" spans="1:7" hidden="1">
       <c r="A81" t="s">
         <v>246</v>
       </c>
@@ -2039,7 +2213,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="82" spans="1:6" hidden="1">
+    <row r="82" spans="1:7" hidden="1">
       <c r="A82" t="s">
         <v>247</v>
       </c>
@@ -2050,55 +2224,109 @@
         <v>264</v>
       </c>
     </row>
-    <row r="83" spans="1:6" hidden="1">
+    <row r="83" spans="1:7">
       <c r="A83" t="s">
         <v>248</v>
       </c>
+      <c r="B83" t="s">
+        <v>266</v>
+      </c>
+      <c r="C83" t="s">
+        <v>267</v>
+      </c>
       <c r="D83" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="84" spans="1:6" hidden="1">
+      <c r="G83" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7">
       <c r="A84" t="s">
         <v>249</v>
       </c>
+      <c r="B84" t="s">
+        <v>266</v>
+      </c>
+      <c r="C84" t="s">
+        <v>267</v>
+      </c>
       <c r="D84" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="85" spans="1:6" hidden="1">
+      <c r="G84" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7">
       <c r="A85" t="s">
         <v>250</v>
       </c>
+      <c r="B85" t="s">
+        <v>266</v>
+      </c>
+      <c r="C85" t="s">
+        <v>267</v>
+      </c>
       <c r="D85" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="86" spans="1:6" hidden="1">
+      <c r="G85" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7">
       <c r="A86" t="s">
         <v>251</v>
       </c>
+      <c r="B86" t="s">
+        <v>266</v>
+      </c>
+      <c r="C86" t="s">
+        <v>267</v>
+      </c>
       <c r="D86" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="87" spans="1:6" hidden="1">
+      <c r="G86" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7">
       <c r="A87" t="s">
         <v>252</v>
       </c>
+      <c r="B87" t="s">
+        <v>266</v>
+      </c>
+      <c r="C87" t="s">
+        <v>267</v>
+      </c>
       <c r="D87" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="88" spans="1:6" hidden="1">
+      <c r="G87" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7">
       <c r="A88" t="s">
         <v>253</v>
       </c>
+      <c r="B88" t="s">
+        <v>266</v>
+      </c>
+      <c r="C88" t="s">
+        <v>267</v>
+      </c>
       <c r="D88" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="89" spans="1:6" hidden="1">
+      <c r="G88" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" hidden="1">
       <c r="A89" t="s">
         <v>254</v>
       </c>
@@ -2109,7 +2337,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="90" spans="1:6" hidden="1">
+    <row r="90" spans="1:7" hidden="1">
       <c r="A90" t="s">
         <v>255</v>
       </c>
@@ -2120,7 +2348,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="91" spans="1:6" hidden="1">
+    <row r="91" spans="1:7" hidden="1">
       <c r="A91" t="s">
         <v>256</v>
       </c>
@@ -2131,35 +2359,62 @@
         <v>264</v>
       </c>
     </row>
-    <row r="92" spans="1:6" hidden="1">
+    <row r="92" spans="1:7">
       <c r="A92" t="s">
         <v>257</v>
       </c>
+      <c r="B92" t="s">
+        <v>266</v>
+      </c>
+      <c r="C92" t="s">
+        <v>267</v>
+      </c>
       <c r="D92" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="93" spans="1:6" hidden="1">
+      <c r="G92" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7">
       <c r="A93" t="s">
         <v>258</v>
       </c>
+      <c r="B93" t="s">
+        <v>266</v>
+      </c>
+      <c r="C93" t="s">
+        <v>267</v>
+      </c>
       <c r="D93" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="94" spans="1:6" hidden="1">
+      <c r="G93" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7">
       <c r="A94" t="s">
         <v>259</v>
       </c>
+      <c r="B94" t="s">
+        <v>266</v>
+      </c>
+      <c r="C94" t="s">
+        <v>267</v>
+      </c>
       <c r="D94" t="s">
         <v>262</v>
+      </c>
+      <c r="G94" t="s">
+        <v>268</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="D1:D94">
     <filterColumn colId="0">
       <filters>
-        <filter val="赵小妮"/>
+        <filter val="赵育"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -2170,6 +2425,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:G67"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
@@ -2199,7 +2455,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" hidden="1">
       <c r="A2" t="s">
         <v>101</v>
       </c>
@@ -2210,7 +2466,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" hidden="1">
       <c r="A3" t="s">
         <v>102</v>
       </c>
@@ -2221,7 +2477,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" hidden="1">
       <c r="A4" t="s">
         <v>103</v>
       </c>
@@ -2232,7 +2488,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" hidden="1">
       <c r="A5" t="s">
         <v>104</v>
       </c>
@@ -2243,7 +2499,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" hidden="1">
       <c r="A6" t="s">
         <v>105</v>
       </c>
@@ -2254,7 +2510,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" hidden="1">
       <c r="A7" t="s">
         <v>106</v>
       </c>
@@ -2265,7 +2521,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" hidden="1">
       <c r="A8" t="s">
         <v>107</v>
       </c>
@@ -2276,7 +2532,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" hidden="1">
       <c r="A9" t="s">
         <v>108</v>
       </c>
@@ -2287,7 +2543,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" hidden="1">
       <c r="A10" t="s">
         <v>109</v>
       </c>
@@ -2298,7 +2554,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" hidden="1">
       <c r="A11" t="s">
         <v>110</v>
       </c>
@@ -2309,7 +2565,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" hidden="1">
       <c r="A12" t="s">
         <v>111</v>
       </c>
@@ -2320,7 +2576,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" hidden="1">
       <c r="A13" t="s">
         <v>112</v>
       </c>
@@ -2331,7 +2587,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" hidden="1">
       <c r="A14" t="s">
         <v>113</v>
       </c>
@@ -2342,7 +2598,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" hidden="1">
       <c r="A15" t="s">
         <v>114</v>
       </c>
@@ -2353,7 +2609,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" hidden="1">
       <c r="A16" t="s">
         <v>115</v>
       </c>
@@ -2364,7 +2620,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:7" hidden="1">
       <c r="A17" t="s">
         <v>116</v>
       </c>
@@ -2375,7 +2631,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:7" hidden="1">
       <c r="A18" t="s">
         <v>117</v>
       </c>
@@ -2386,7 +2642,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:7" hidden="1">
       <c r="A19" t="s">
         <v>118</v>
       </c>
@@ -2397,7 +2653,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:7" hidden="1">
       <c r="A20" t="s">
         <v>119</v>
       </c>
@@ -2408,7 +2664,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:7" hidden="1">
       <c r="A21" t="s">
         <v>120</v>
       </c>
@@ -2419,7 +2675,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:7" hidden="1">
       <c r="A22" t="s">
         <v>121</v>
       </c>
@@ -2430,95 +2686,194 @@
         <v>264</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:7">
       <c r="A23" t="s">
         <v>122</v>
       </c>
+      <c r="B23" t="s">
+        <v>266</v>
+      </c>
+      <c r="C23" t="s">
+        <v>267</v>
+      </c>
       <c r="D23" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="24" spans="1:6">
+      <c r="G23" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
       <c r="A24" t="s">
         <v>123</v>
       </c>
+      <c r="B24" t="s">
+        <v>266</v>
+      </c>
+      <c r="C24" t="s">
+        <v>267</v>
+      </c>
       <c r="D24" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="25" spans="1:6">
+      <c r="G24" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
       <c r="A25" t="s">
         <v>124</v>
       </c>
+      <c r="B25" t="s">
+        <v>266</v>
+      </c>
+      <c r="C25" t="s">
+        <v>267</v>
+      </c>
       <c r="D25" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="26" spans="1:6">
+      <c r="G25" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
       <c r="A26" t="s">
         <v>125</v>
       </c>
+      <c r="B26" t="s">
+        <v>266</v>
+      </c>
+      <c r="C26" t="s">
+        <v>267</v>
+      </c>
       <c r="D26" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="27" spans="1:6">
+      <c r="G26" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
       <c r="A27" t="s">
         <v>126</v>
       </c>
+      <c r="B27" t="s">
+        <v>266</v>
+      </c>
+      <c r="C27" t="s">
+        <v>267</v>
+      </c>
       <c r="D27" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="28" spans="1:6">
+      <c r="G27" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
       <c r="A28" t="s">
         <v>127</v>
       </c>
+      <c r="B28" t="s">
+        <v>266</v>
+      </c>
+      <c r="C28" t="s">
+        <v>267</v>
+      </c>
       <c r="D28" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="29" spans="1:6">
+      <c r="G28" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
       <c r="A29" t="s">
         <v>128</v>
       </c>
+      <c r="B29" t="s">
+        <v>266</v>
+      </c>
+      <c r="C29" t="s">
+        <v>267</v>
+      </c>
       <c r="D29" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="30" spans="1:6">
+      <c r="G29" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
       <c r="A30" t="s">
         <v>129</v>
       </c>
+      <c r="B30" t="s">
+        <v>266</v>
+      </c>
+      <c r="C30" t="s">
+        <v>267</v>
+      </c>
       <c r="D30" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="31" spans="1:6">
+      <c r="G30" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
       <c r="A31" t="s">
         <v>130</v>
       </c>
+      <c r="B31" t="s">
+        <v>266</v>
+      </c>
+      <c r="C31" t="s">
+        <v>267</v>
+      </c>
       <c r="D31" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="32" spans="1:6">
+      <c r="G31" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
       <c r="A32" t="s">
         <v>131</v>
       </c>
+      <c r="B32" t="s">
+        <v>266</v>
+      </c>
+      <c r="C32" t="s">
+        <v>267</v>
+      </c>
       <c r="D32" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="33" spans="1:6">
+      <c r="G32" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
       <c r="A33" t="s">
         <v>132</v>
       </c>
+      <c r="B33" t="s">
+        <v>266</v>
+      </c>
+      <c r="C33" t="s">
+        <v>267</v>
+      </c>
       <c r="D33" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="34" spans="1:6">
+      <c r="G33" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" hidden="1">
       <c r="A34" t="s">
         <v>133</v>
       </c>
@@ -2529,7 +2884,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="35" spans="1:6">
+    <row r="35" spans="1:7" hidden="1">
       <c r="A35" t="s">
         <v>134</v>
       </c>
@@ -2540,7 +2895,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="36" spans="1:6">
+    <row r="36" spans="1:7" hidden="1">
       <c r="A36" t="s">
         <v>135</v>
       </c>
@@ -2551,7 +2906,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="37" spans="1:6">
+    <row r="37" spans="1:7" hidden="1">
       <c r="A37" t="s">
         <v>136</v>
       </c>
@@ -2562,7 +2917,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="38" spans="1:6">
+    <row r="38" spans="1:7" hidden="1">
       <c r="A38" t="s">
         <v>137</v>
       </c>
@@ -2573,7 +2928,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="39" spans="1:6">
+    <row r="39" spans="1:7" hidden="1">
       <c r="A39" t="s">
         <v>138</v>
       </c>
@@ -2584,7 +2939,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="40" spans="1:6">
+    <row r="40" spans="1:7" hidden="1">
       <c r="A40" t="s">
         <v>139</v>
       </c>
@@ -2595,7 +2950,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="41" spans="1:6">
+    <row r="41" spans="1:7" hidden="1">
       <c r="A41" t="s">
         <v>140</v>
       </c>
@@ -2606,63 +2961,126 @@
         <v>264</v>
       </c>
     </row>
-    <row r="42" spans="1:6">
+    <row r="42" spans="1:7">
       <c r="A42" t="s">
         <v>165</v>
       </c>
+      <c r="B42" t="s">
+        <v>266</v>
+      </c>
+      <c r="C42" t="s">
+        <v>267</v>
+      </c>
       <c r="D42" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="43" spans="1:6">
+      <c r="G42" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
       <c r="A43" t="s">
         <v>166</v>
       </c>
+      <c r="B43" t="s">
+        <v>266</v>
+      </c>
+      <c r="C43" t="s">
+        <v>267</v>
+      </c>
       <c r="D43" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="44" spans="1:6">
+      <c r="G43" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
       <c r="A44" t="s">
         <v>167</v>
       </c>
+      <c r="B44" t="s">
+        <v>266</v>
+      </c>
+      <c r="C44" t="s">
+        <v>267</v>
+      </c>
       <c r="D44" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="45" spans="1:6">
+      <c r="G44" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
       <c r="A45" t="s">
         <v>168</v>
       </c>
+      <c r="B45" t="s">
+        <v>266</v>
+      </c>
+      <c r="C45" t="s">
+        <v>267</v>
+      </c>
       <c r="D45" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="46" spans="1:6">
+      <c r="G45" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
       <c r="A46" t="s">
         <v>169</v>
       </c>
+      <c r="B46" t="s">
+        <v>266</v>
+      </c>
+      <c r="C46" t="s">
+        <v>267</v>
+      </c>
       <c r="D46" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="47" spans="1:6">
+      <c r="G46" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
       <c r="A47" t="s">
         <v>143</v>
       </c>
+      <c r="B47" t="s">
+        <v>266</v>
+      </c>
+      <c r="C47" t="s">
+        <v>267</v>
+      </c>
       <c r="D47" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="48" spans="1:6">
+      <c r="G47" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
       <c r="A48" t="s">
         <v>144</v>
       </c>
+      <c r="B48" t="s">
+        <v>266</v>
+      </c>
+      <c r="C48" t="s">
+        <v>267</v>
+      </c>
       <c r="D48" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="49" spans="1:6">
+      <c r="G48" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" hidden="1">
       <c r="A49" t="s">
         <v>145</v>
       </c>
@@ -2673,7 +3091,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="50" spans="1:6">
+    <row r="50" spans="1:7" hidden="1">
       <c r="A50" t="s">
         <v>146</v>
       </c>
@@ -2684,7 +3102,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="51" spans="1:6">
+    <row r="51" spans="1:7" hidden="1">
       <c r="A51" t="s">
         <v>147</v>
       </c>
@@ -2695,7 +3113,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="52" spans="1:6">
+    <row r="52" spans="1:7" hidden="1">
       <c r="A52" t="s">
         <v>148</v>
       </c>
@@ -2706,7 +3124,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="53" spans="1:6">
+    <row r="53" spans="1:7" hidden="1">
       <c r="A53" t="s">
         <v>149</v>
       </c>
@@ -2717,7 +3135,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="54" spans="1:6">
+    <row r="54" spans="1:7" hidden="1">
       <c r="A54" t="s">
         <v>150</v>
       </c>
@@ -2728,55 +3146,109 @@
         <v>263</v>
       </c>
     </row>
-    <row r="55" spans="1:6">
+    <row r="55" spans="1:7">
       <c r="A55" t="s">
         <v>151</v>
       </c>
+      <c r="B55" t="s">
+        <v>266</v>
+      </c>
+      <c r="C55" t="s">
+        <v>267</v>
+      </c>
       <c r="D55" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="56" spans="1:6">
+      <c r="G55" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7">
       <c r="A56" t="s">
         <v>152</v>
       </c>
+      <c r="B56" t="s">
+        <v>266</v>
+      </c>
+      <c r="C56" t="s">
+        <v>267</v>
+      </c>
       <c r="D56" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="57" spans="1:6">
+      <c r="G56" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7">
       <c r="A57" t="s">
         <v>153</v>
       </c>
+      <c r="B57" t="s">
+        <v>266</v>
+      </c>
+      <c r="C57" t="s">
+        <v>267</v>
+      </c>
       <c r="D57" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="58" spans="1:6">
+      <c r="G57" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7">
       <c r="A58" t="s">
         <v>154</v>
       </c>
+      <c r="B58" t="s">
+        <v>266</v>
+      </c>
+      <c r="C58" t="s">
+        <v>267</v>
+      </c>
       <c r="D58" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="59" spans="1:6">
+      <c r="G58" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7">
       <c r="A59" t="s">
         <v>155</v>
       </c>
+      <c r="B59" t="s">
+        <v>266</v>
+      </c>
+      <c r="C59" t="s">
+        <v>267</v>
+      </c>
       <c r="D59" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="60" spans="1:6">
+      <c r="G59" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7">
       <c r="A60" t="s">
         <v>156</v>
       </c>
+      <c r="B60" t="s">
+        <v>266</v>
+      </c>
+      <c r="C60" t="s">
+        <v>267</v>
+      </c>
       <c r="D60" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="61" spans="1:6">
+      <c r="G60" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" hidden="1">
       <c r="A61" t="s">
         <v>158</v>
       </c>
@@ -2787,7 +3259,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="62" spans="1:6">
+    <row r="62" spans="1:7" hidden="1">
       <c r="A62" t="s">
         <v>159</v>
       </c>
@@ -2798,7 +3270,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="63" spans="1:6">
+    <row r="63" spans="1:7" hidden="1">
       <c r="A63" t="s">
         <v>160</v>
       </c>
@@ -2809,40 +3281,82 @@
         <v>263</v>
       </c>
     </row>
-    <row r="64" spans="1:6">
+    <row r="64" spans="1:7">
       <c r="A64" t="s">
         <v>161</v>
       </c>
+      <c r="B64" t="s">
+        <v>266</v>
+      </c>
+      <c r="C64" t="s">
+        <v>267</v>
+      </c>
       <c r="D64" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="65" spans="1:4">
+      <c r="G64" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7">
       <c r="A65" t="s">
         <v>162</v>
       </c>
+      <c r="B65" t="s">
+        <v>266</v>
+      </c>
+      <c r="C65" t="s">
+        <v>267</v>
+      </c>
       <c r="D65" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="66" spans="1:4">
+      <c r="G65" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7">
       <c r="A66" t="s">
         <v>163</v>
       </c>
+      <c r="B66" t="s">
+        <v>266</v>
+      </c>
+      <c r="C66" t="s">
+        <v>267</v>
+      </c>
       <c r="D66" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="67" spans="1:4">
+      <c r="G66" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7">
       <c r="A67" t="s">
         <v>164</v>
       </c>
+      <c r="B67" t="s">
+        <v>266</v>
+      </c>
+      <c r="C67" t="s">
+        <v>267</v>
+      </c>
       <c r="D67" t="s">
         <v>262</v>
       </c>
+      <c r="G67" t="s">
+        <v>268</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="D1:D67"/>
+  <autoFilter ref="D1:D67">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="赵育"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2880,7 +3394,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" hidden="1">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -2891,7 +3405,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" hidden="1">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -2902,7 +3416,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" hidden="1">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -2913,7 +3427,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" hidden="1">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -2924,7 +3438,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" hidden="1">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -2935,7 +3449,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" hidden="1">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -2946,7 +3460,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" hidden="1">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -2957,7 +3471,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" hidden="1">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -2968,7 +3482,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" hidden="1">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -2979,7 +3493,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" hidden="1">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -2990,7 +3504,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" hidden="1">
       <c r="A12" t="s">
         <v>15</v>
       </c>
@@ -3001,7 +3515,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" hidden="1">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -3012,7 +3526,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" hidden="1">
       <c r="A14" t="s">
         <v>17</v>
       </c>
@@ -3023,7 +3537,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" hidden="1">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -3034,7 +3548,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" hidden="1">
       <c r="A16" t="s">
         <v>19</v>
       </c>
@@ -3045,7 +3559,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:7" hidden="1">
       <c r="A17" t="s">
         <v>20</v>
       </c>
@@ -3056,7 +3570,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:7" hidden="1">
       <c r="A18" t="s">
         <v>21</v>
       </c>
@@ -3067,7 +3581,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:7" hidden="1">
       <c r="A19" t="s">
         <v>22</v>
       </c>
@@ -3078,7 +3592,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:7" hidden="1">
       <c r="A20" t="s">
         <v>23</v>
       </c>
@@ -3089,7 +3603,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:7" hidden="1">
       <c r="A21" t="s">
         <v>24</v>
       </c>
@@ -3100,7 +3614,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:7" hidden="1">
       <c r="A22" t="s">
         <v>25</v>
       </c>
@@ -3111,151 +3625,313 @@
         <v>262</v>
       </c>
     </row>
-    <row r="23" spans="1:6" hidden="1">
+    <row r="23" spans="1:7">
       <c r="A23" t="s">
         <v>26</v>
       </c>
+      <c r="B23" t="s">
+        <v>266</v>
+      </c>
+      <c r="C23" t="s">
+        <v>267</v>
+      </c>
       <c r="D23" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" hidden="1">
+      <c r="G23" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
       <c r="A24" t="s">
         <v>27</v>
       </c>
+      <c r="B24" t="s">
+        <v>266</v>
+      </c>
+      <c r="C24" t="s">
+        <v>267</v>
+      </c>
       <c r="D24" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="25" spans="1:6" hidden="1">
+      <c r="G24" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
       <c r="A25" t="s">
         <v>28</v>
       </c>
+      <c r="B25" t="s">
+        <v>266</v>
+      </c>
+      <c r="C25" t="s">
+        <v>267</v>
+      </c>
       <c r="D25" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="26" spans="1:6" hidden="1">
+      <c r="G25" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
       <c r="A26" t="s">
         <v>29</v>
       </c>
+      <c r="B26" t="s">
+        <v>266</v>
+      </c>
+      <c r="C26" t="s">
+        <v>267</v>
+      </c>
       <c r="D26" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="27" spans="1:6" hidden="1">
+      <c r="G26" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
       <c r="A27" t="s">
         <v>30</v>
       </c>
+      <c r="B27" t="s">
+        <v>266</v>
+      </c>
+      <c r="C27" t="s">
+        <v>267</v>
+      </c>
       <c r="D27" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="28" spans="1:6" hidden="1">
+      <c r="G27" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
       <c r="A28" t="s">
         <v>31</v>
       </c>
+      <c r="B28" t="s">
+        <v>266</v>
+      </c>
+      <c r="C28" t="s">
+        <v>267</v>
+      </c>
       <c r="D28" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="29" spans="1:6" hidden="1">
+      <c r="G28" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
       <c r="A29" t="s">
         <v>32</v>
       </c>
+      <c r="B29" t="s">
+        <v>266</v>
+      </c>
+      <c r="C29" t="s">
+        <v>267</v>
+      </c>
       <c r="D29" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="30" spans="1:6" hidden="1">
+      <c r="G29" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
       <c r="A30" t="s">
         <v>33</v>
       </c>
+      <c r="B30" t="s">
+        <v>266</v>
+      </c>
+      <c r="C30" t="s">
+        <v>267</v>
+      </c>
       <c r="D30" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="31" spans="1:6" hidden="1">
+      <c r="G30" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
       <c r="A31" t="s">
         <v>34</v>
       </c>
+      <c r="B31" t="s">
+        <v>266</v>
+      </c>
+      <c r="C31" t="s">
+        <v>267</v>
+      </c>
       <c r="D31" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="32" spans="1:6" hidden="1">
+      <c r="G31" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
       <c r="A32" t="s">
         <v>35</v>
       </c>
+      <c r="B32" t="s">
+        <v>266</v>
+      </c>
+      <c r="C32" t="s">
+        <v>267</v>
+      </c>
       <c r="D32" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="33" spans="1:6" hidden="1">
+      <c r="G32" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
       <c r="A33" t="s">
         <v>36</v>
       </c>
+      <c r="B33" t="s">
+        <v>266</v>
+      </c>
+      <c r="C33" t="s">
+        <v>267</v>
+      </c>
       <c r="D33" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="34" spans="1:6" hidden="1">
+      <c r="G33" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
       <c r="A34" t="s">
         <v>37</v>
       </c>
+      <c r="B34" t="s">
+        <v>266</v>
+      </c>
+      <c r="C34" t="s">
+        <v>267</v>
+      </c>
       <c r="D34" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="35" spans="1:6" hidden="1">
+      <c r="G34" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
       <c r="A35" t="s">
         <v>38</v>
       </c>
+      <c r="B35" t="s">
+        <v>266</v>
+      </c>
+      <c r="C35" t="s">
+        <v>267</v>
+      </c>
       <c r="D35" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="36" spans="1:6" hidden="1">
+      <c r="G35" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
       <c r="A36" t="s">
         <v>39</v>
       </c>
+      <c r="B36" t="s">
+        <v>266</v>
+      </c>
+      <c r="C36" t="s">
+        <v>267</v>
+      </c>
       <c r="D36" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="37" spans="1:6" hidden="1">
+      <c r="G36" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
       <c r="A37" t="s">
         <v>40</v>
       </c>
+      <c r="B37" t="s">
+        <v>266</v>
+      </c>
+      <c r="C37" t="s">
+        <v>267</v>
+      </c>
       <c r="D37" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="38" spans="1:6" hidden="1">
+      <c r="G37" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
       <c r="A38" t="s">
         <v>41</v>
       </c>
+      <c r="B38" t="s">
+        <v>266</v>
+      </c>
+      <c r="C38" t="s">
+        <v>267</v>
+      </c>
       <c r="D38" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="39" spans="1:6" hidden="1">
+      <c r="G38" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
       <c r="A39" t="s">
         <v>42</v>
       </c>
+      <c r="B39" t="s">
+        <v>266</v>
+      </c>
+      <c r="C39" t="s">
+        <v>267</v>
+      </c>
       <c r="D39" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="40" spans="1:6" hidden="1">
+      <c r="G39" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
       <c r="A40" t="s">
         <v>43</v>
       </c>
+      <c r="B40" t="s">
+        <v>266</v>
+      </c>
+      <c r="C40" t="s">
+        <v>267</v>
+      </c>
       <c r="D40" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="41" spans="1:6">
+      <c r="G40" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" hidden="1">
       <c r="A41" t="s">
         <v>44</v>
       </c>
@@ -3266,7 +3942,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="42" spans="1:6">
+    <row r="42" spans="1:7" hidden="1">
       <c r="A42" t="s">
         <v>45</v>
       </c>
@@ -3277,7 +3953,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="43" spans="1:6">
+    <row r="43" spans="1:7" hidden="1">
       <c r="A43" t="s">
         <v>46</v>
       </c>
@@ -3288,7 +3964,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="44" spans="1:6">
+    <row r="44" spans="1:7" hidden="1">
       <c r="A44" t="s">
         <v>47</v>
       </c>
@@ -3299,7 +3975,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="45" spans="1:6">
+    <row r="45" spans="1:7" hidden="1">
       <c r="A45" t="s">
         <v>48</v>
       </c>
@@ -3310,7 +3986,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="46" spans="1:6">
+    <row r="46" spans="1:7" hidden="1">
       <c r="A46" t="s">
         <v>49</v>
       </c>
@@ -3321,7 +3997,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="47" spans="1:6">
+    <row r="47" spans="1:7" hidden="1">
       <c r="A47" t="s">
         <v>50</v>
       </c>
@@ -3332,7 +4008,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="48" spans="1:6">
+    <row r="48" spans="1:7" hidden="1">
       <c r="A48" t="s">
         <v>51</v>
       </c>
@@ -3343,7 +4019,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="49" spans="1:6">
+    <row r="49" spans="1:6" hidden="1">
       <c r="A49" t="s">
         <v>52</v>
       </c>
@@ -3354,7 +4030,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="50" spans="1:6">
+    <row r="50" spans="1:6" hidden="1">
       <c r="A50" t="s">
         <v>53</v>
       </c>
@@ -3365,7 +4041,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="51" spans="1:6">
+    <row r="51" spans="1:6" hidden="1">
       <c r="A51" t="s">
         <v>54</v>
       </c>
@@ -3376,7 +4052,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="52" spans="1:6">
+    <row r="52" spans="1:6" hidden="1">
       <c r="A52" t="s">
         <v>55</v>
       </c>
@@ -3387,7 +4063,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="53" spans="1:6">
+    <row r="53" spans="1:6" hidden="1">
       <c r="A53" t="s">
         <v>56</v>
       </c>
@@ -3398,7 +4074,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="54" spans="1:6">
+    <row r="54" spans="1:6" hidden="1">
       <c r="A54" t="s">
         <v>57</v>
       </c>
@@ -3409,7 +4085,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="55" spans="1:6">
+    <row r="55" spans="1:6" hidden="1">
       <c r="A55" t="s">
         <v>58</v>
       </c>
@@ -3420,7 +4096,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="56" spans="1:6">
+    <row r="56" spans="1:6" hidden="1">
       <c r="A56" t="s">
         <v>59</v>
       </c>
@@ -3431,7 +4107,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="57" spans="1:6">
+    <row r="57" spans="1:6" hidden="1">
       <c r="A57" t="s">
         <v>60</v>
       </c>
@@ -3442,7 +4118,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="58" spans="1:6">
+    <row r="58" spans="1:6" hidden="1">
       <c r="A58" t="s">
         <v>61</v>
       </c>
@@ -3453,7 +4129,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="59" spans="1:6">
+    <row r="59" spans="1:6" hidden="1">
       <c r="A59" t="s">
         <v>62</v>
       </c>
@@ -3464,7 +4140,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="60" spans="1:6">
+    <row r="60" spans="1:6" hidden="1">
       <c r="A60" t="s">
         <v>63</v>
       </c>
@@ -3475,7 +4151,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="61" spans="1:6">
+    <row r="61" spans="1:6" hidden="1">
       <c r="A61" t="s">
         <v>64</v>
       </c>
@@ -3486,7 +4162,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="62" spans="1:6">
+    <row r="62" spans="1:6" hidden="1">
       <c r="A62" t="s">
         <v>65</v>
       </c>
@@ -3497,7 +4173,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="63" spans="1:6">
+    <row r="63" spans="1:6" hidden="1">
       <c r="A63" t="s">
         <v>66</v>
       </c>
@@ -3508,7 +4184,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="64" spans="1:6">
+    <row r="64" spans="1:6" hidden="1">
       <c r="A64" t="s">
         <v>67</v>
       </c>
@@ -3519,7 +4195,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="65" spans="1:6">
+    <row r="65" spans="1:6" hidden="1">
       <c r="A65" t="s">
         <v>68</v>
       </c>
@@ -3530,7 +4206,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="66" spans="1:6">
+    <row r="66" spans="1:6" hidden="1">
       <c r="A66" t="s">
         <v>69</v>
       </c>
@@ -3541,7 +4217,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="67" spans="1:6">
+    <row r="67" spans="1:6" hidden="1">
       <c r="A67" t="s">
         <v>70</v>
       </c>
@@ -3552,7 +4228,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="68" spans="1:6">
+    <row r="68" spans="1:6" hidden="1">
       <c r="A68" t="s">
         <v>71</v>
       </c>
@@ -3563,7 +4239,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="69" spans="1:6">
+    <row r="69" spans="1:6" hidden="1">
       <c r="A69" t="s">
         <v>72</v>
       </c>
@@ -3574,7 +4250,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="70" spans="1:6">
+    <row r="70" spans="1:6" hidden="1">
       <c r="A70" t="s">
         <v>73</v>
       </c>
@@ -3585,7 +4261,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="71" spans="1:6">
+    <row r="71" spans="1:6" hidden="1">
       <c r="A71" t="s">
         <v>74</v>
       </c>
@@ -3596,7 +4272,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="72" spans="1:6">
+    <row r="72" spans="1:6" hidden="1">
       <c r="A72" t="s">
         <v>75</v>
       </c>
@@ -3607,7 +4283,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="73" spans="1:6">
+    <row r="73" spans="1:6" hidden="1">
       <c r="A73" t="s">
         <v>76</v>
       </c>
@@ -3618,7 +4294,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="74" spans="1:6">
+    <row r="74" spans="1:6" hidden="1">
       <c r="A74" t="s">
         <v>77</v>
       </c>
@@ -3629,7 +4305,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="75" spans="1:6">
+    <row r="75" spans="1:6" hidden="1">
       <c r="A75" t="s">
         <v>78</v>
       </c>
@@ -3640,7 +4316,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="76" spans="1:6">
+    <row r="76" spans="1:6" hidden="1">
       <c r="A76" t="s">
         <v>79</v>
       </c>
@@ -3651,7 +4327,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="77" spans="1:6">
+    <row r="77" spans="1:6" hidden="1">
       <c r="A77" t="s">
         <v>80</v>
       </c>
@@ -3662,7 +4338,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="78" spans="1:6">
+    <row r="78" spans="1:6" hidden="1">
       <c r="A78" t="s">
         <v>81</v>
       </c>
@@ -3673,7 +4349,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="79" spans="1:6">
+    <row r="79" spans="1:6" hidden="1">
       <c r="A79" t="s">
         <v>82</v>
       </c>
@@ -3684,7 +4360,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="80" spans="1:6">
+    <row r="80" spans="1:6" hidden="1">
       <c r="A80" t="s">
         <v>83</v>
       </c>
@@ -3695,7 +4371,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="81" spans="1:6">
+    <row r="81" spans="1:7" hidden="1">
       <c r="A81" t="s">
         <v>84</v>
       </c>
@@ -3706,7 +4382,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="82" spans="1:6">
+    <row r="82" spans="1:7" hidden="1">
       <c r="A82" t="s">
         <v>85</v>
       </c>
@@ -3717,7 +4393,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="83" spans="1:6">
+    <row r="83" spans="1:7" hidden="1">
       <c r="A83" t="s">
         <v>86</v>
       </c>
@@ -3728,7 +4404,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="84" spans="1:6">
+    <row r="84" spans="1:7" hidden="1">
       <c r="A84" t="s">
         <v>87</v>
       </c>
@@ -3739,55 +4415,109 @@
         <v>262</v>
       </c>
     </row>
-    <row r="85" spans="1:6" hidden="1">
+    <row r="85" spans="1:7">
       <c r="A85" t="s">
         <v>88</v>
       </c>
+      <c r="B85" t="s">
+        <v>266</v>
+      </c>
+      <c r="C85" t="s">
+        <v>267</v>
+      </c>
       <c r="D85" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="86" spans="1:6" hidden="1">
+      <c r="G85" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7">
       <c r="A86" t="s">
         <v>89</v>
       </c>
+      <c r="B86" t="s">
+        <v>266</v>
+      </c>
+      <c r="C86" t="s">
+        <v>267</v>
+      </c>
       <c r="D86" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="87" spans="1:6" hidden="1">
+      <c r="G86" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7">
       <c r="A87" t="s">
         <v>90</v>
       </c>
+      <c r="B87" t="s">
+        <v>266</v>
+      </c>
+      <c r="C87" t="s">
+        <v>267</v>
+      </c>
       <c r="D87" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="88" spans="1:6" hidden="1">
+      <c r="G87" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7">
       <c r="A88" t="s">
         <v>91</v>
       </c>
+      <c r="B88" t="s">
+        <v>266</v>
+      </c>
+      <c r="C88" t="s">
+        <v>267</v>
+      </c>
       <c r="D88" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="89" spans="1:6" hidden="1">
+      <c r="G88" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7">
       <c r="A89" t="s">
         <v>92</v>
       </c>
+      <c r="B89" t="s">
+        <v>266</v>
+      </c>
+      <c r="C89" t="s">
+        <v>267</v>
+      </c>
       <c r="D89" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="90" spans="1:6" hidden="1">
+      <c r="G89" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7">
       <c r="A90" t="s">
         <v>93</v>
       </c>
+      <c r="B90" t="s">
+        <v>266</v>
+      </c>
+      <c r="C90" t="s">
+        <v>267</v>
+      </c>
       <c r="D90" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="91" spans="1:6">
+      <c r="G90" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" hidden="1">
       <c r="A91" t="s">
         <v>94</v>
       </c>
@@ -3798,7 +4528,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="92" spans="1:6">
+    <row r="92" spans="1:7" hidden="1">
       <c r="A92" t="s">
         <v>95</v>
       </c>
@@ -3809,7 +4539,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="93" spans="1:6">
+    <row r="93" spans="1:7" hidden="1">
       <c r="A93" t="s">
         <v>96</v>
       </c>
@@ -3820,31 +4550,58 @@
         <v>262</v>
       </c>
     </row>
-    <row r="94" spans="1:6" hidden="1">
+    <row r="94" spans="1:7">
       <c r="A94" t="s">
         <v>97</v>
       </c>
+      <c r="B94" t="s">
+        <v>266</v>
+      </c>
+      <c r="C94" t="s">
+        <v>267</v>
+      </c>
       <c r="D94" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="95" spans="1:6" hidden="1">
+      <c r="G94" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7">
       <c r="A95" t="s">
         <v>98</v>
       </c>
+      <c r="B95" t="s">
+        <v>266</v>
+      </c>
+      <c r="C95" t="s">
+        <v>267</v>
+      </c>
       <c r="D95" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="96" spans="1:6" hidden="1">
+      <c r="G95" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7">
       <c r="A96" t="s">
         <v>99</v>
       </c>
+      <c r="B96" t="s">
+        <v>266</v>
+      </c>
+      <c r="C96" t="s">
+        <v>267</v>
+      </c>
       <c r="D96" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="97" spans="1:6">
+      <c r="G96" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" hidden="1">
       <c r="A97" t="s">
         <v>100</v>
       </c>
@@ -3859,9 +4616,7 @@
   <autoFilter ref="D1:D97">
     <filterColumn colId="0">
       <filters>
-        <filter val="卢伟康"/>
-        <filter val="尹臻"/>
-        <filter val="赵小妮"/>
+        <filter val="赵育"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/internal_doc/05.测试设计/story/事务支持RC隔离级别/事务自动化用例跟踪表.xlsx
+++ b/internal_doc/05.测试设计/story/事务支持RC隔离级别/事务自动化用例跟踪表.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="950" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1015" uniqueCount="276">
   <si>
     <t>用例编号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -856,6 +856,34 @@
   </si>
   <si>
     <t>版本问题，暂不提交</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>是</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>否</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>需新增自动化用例</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>资料用例</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>节点重启用例，待提交</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>配置验证，不实现自动化</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>全文索引用例，待提交</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3368,7 +3396,8 @@
   <dimension ref="A1:G97"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="7" width="20.625" customWidth="1"/>
+    <col min="1" max="6" width="20.625" customWidth="1"/>
+    <col min="7" max="7" width="26.125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -3394,34 +3423,61 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7" hidden="1">
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
         <v>5</v>
       </c>
+      <c r="B2" t="s">
+        <v>269</v>
+      </c>
+      <c r="C2" t="s">
+        <v>269</v>
+      </c>
       <c r="D2" t="s">
         <v>264</v>
       </c>
+      <c r="E2" t="s">
+        <v>269</v>
+      </c>
       <c r="F2" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="3" spans="1:7" hidden="1">
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>6</v>
       </c>
+      <c r="B3" t="s">
+        <v>269</v>
+      </c>
+      <c r="C3" t="s">
+        <v>269</v>
+      </c>
       <c r="D3" t="s">
         <v>264</v>
       </c>
+      <c r="E3" t="s">
+        <v>269</v>
+      </c>
       <c r="F3" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="4" spans="1:7" hidden="1">
+    <row r="4" spans="1:7">
       <c r="A4" t="s">
         <v>7</v>
       </c>
+      <c r="B4" t="s">
+        <v>269</v>
+      </c>
+      <c r="C4" t="s">
+        <v>269</v>
+      </c>
       <c r="D4" t="s">
         <v>264</v>
+      </c>
+      <c r="E4" t="s">
+        <v>269</v>
       </c>
       <c r="F4" t="s">
         <v>262</v>
@@ -3537,45 +3593,81 @@
         <v>262</v>
       </c>
     </row>
-    <row r="15" spans="1:7" hidden="1">
+    <row r="15" spans="1:7">
       <c r="A15" t="s">
         <v>18</v>
       </c>
+      <c r="B15" t="s">
+        <v>269</v>
+      </c>
+      <c r="C15" t="s">
+        <v>269</v>
+      </c>
       <c r="D15" t="s">
         <v>264</v>
       </c>
+      <c r="E15" t="s">
+        <v>269</v>
+      </c>
       <c r="F15" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="16" spans="1:7" hidden="1">
+    <row r="16" spans="1:7">
       <c r="A16" t="s">
         <v>19</v>
       </c>
+      <c r="B16" t="s">
+        <v>269</v>
+      </c>
+      <c r="C16" t="s">
+        <v>269</v>
+      </c>
       <c r="D16" t="s">
         <v>264</v>
       </c>
+      <c r="E16" t="s">
+        <v>269</v>
+      </c>
       <c r="F16" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="17" spans="1:7" hidden="1">
+    <row r="17" spans="1:7">
       <c r="A17" t="s">
         <v>20</v>
       </c>
+      <c r="B17" t="s">
+        <v>269</v>
+      </c>
+      <c r="C17" t="s">
+        <v>269</v>
+      </c>
       <c r="D17" t="s">
         <v>264</v>
       </c>
+      <c r="E17" t="s">
+        <v>269</v>
+      </c>
       <c r="F17" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="18" spans="1:7" hidden="1">
+    <row r="18" spans="1:7">
       <c r="A18" t="s">
         <v>21</v>
       </c>
+      <c r="B18" t="s">
+        <v>269</v>
+      </c>
+      <c r="C18" t="s">
+        <v>269</v>
+      </c>
       <c r="D18" t="s">
         <v>264</v>
+      </c>
+      <c r="E18" t="s">
+        <v>269</v>
       </c>
       <c r="F18" t="s">
         <v>262</v>
@@ -3625,7 +3717,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" hidden="1">
       <c r="A23" t="s">
         <v>26</v>
       </c>
@@ -3642,7 +3734,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" hidden="1">
       <c r="A24" t="s">
         <v>27</v>
       </c>
@@ -3659,7 +3751,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" hidden="1">
       <c r="A25" t="s">
         <v>28</v>
       </c>
@@ -3676,7 +3768,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" hidden="1">
       <c r="A26" t="s">
         <v>29</v>
       </c>
@@ -3693,7 +3785,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" hidden="1">
       <c r="A27" t="s">
         <v>30</v>
       </c>
@@ -3710,7 +3802,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" hidden="1">
       <c r="A28" t="s">
         <v>31</v>
       </c>
@@ -3727,7 +3819,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" hidden="1">
       <c r="A29" t="s">
         <v>32</v>
       </c>
@@ -3744,7 +3836,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" hidden="1">
       <c r="A30" t="s">
         <v>33</v>
       </c>
@@ -3761,7 +3853,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" hidden="1">
       <c r="A31" t="s">
         <v>34</v>
       </c>
@@ -3778,7 +3870,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" hidden="1">
       <c r="A32" t="s">
         <v>35</v>
       </c>
@@ -3795,7 +3887,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" hidden="1">
       <c r="A33" t="s">
         <v>36</v>
       </c>
@@ -3812,7 +3904,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" hidden="1">
       <c r="A34" t="s">
         <v>37</v>
       </c>
@@ -3829,7 +3921,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" hidden="1">
       <c r="A35" t="s">
         <v>38</v>
       </c>
@@ -3846,7 +3938,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" hidden="1">
       <c r="A36" t="s">
         <v>39</v>
       </c>
@@ -3863,7 +3955,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" hidden="1">
       <c r="A37" t="s">
         <v>40</v>
       </c>
@@ -3880,7 +3972,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" hidden="1">
       <c r="A38" t="s">
         <v>41</v>
       </c>
@@ -3897,7 +3989,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" hidden="1">
       <c r="A39" t="s">
         <v>42</v>
       </c>
@@ -3914,7 +4006,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:7" hidden="1">
       <c r="A40" t="s">
         <v>43</v>
       </c>
@@ -3931,67 +4023,121 @@
         <v>268</v>
       </c>
     </row>
-    <row r="41" spans="1:7" hidden="1">
+    <row r="41" spans="1:7">
       <c r="A41" t="s">
         <v>44</v>
       </c>
+      <c r="B41" t="s">
+        <v>269</v>
+      </c>
+      <c r="C41" t="s">
+        <v>269</v>
+      </c>
       <c r="D41" t="s">
         <v>264</v>
       </c>
+      <c r="E41" t="s">
+        <v>269</v>
+      </c>
       <c r="F41" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="42" spans="1:7" hidden="1">
+    <row r="42" spans="1:7">
       <c r="A42" t="s">
         <v>45</v>
       </c>
+      <c r="B42" t="s">
+        <v>269</v>
+      </c>
+      <c r="C42" t="s">
+        <v>269</v>
+      </c>
       <c r="D42" t="s">
         <v>264</v>
       </c>
+      <c r="E42" t="s">
+        <v>269</v>
+      </c>
       <c r="F42" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="43" spans="1:7" hidden="1">
+    <row r="43" spans="1:7">
       <c r="A43" t="s">
         <v>46</v>
       </c>
+      <c r="B43" t="s">
+        <v>269</v>
+      </c>
+      <c r="C43" t="s">
+        <v>269</v>
+      </c>
       <c r="D43" t="s">
         <v>264</v>
       </c>
+      <c r="E43" t="s">
+        <v>269</v>
+      </c>
       <c r="F43" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="44" spans="1:7" hidden="1">
+    <row r="44" spans="1:7">
       <c r="A44" t="s">
         <v>47</v>
       </c>
+      <c r="B44" t="s">
+        <v>269</v>
+      </c>
+      <c r="C44" t="s">
+        <v>269</v>
+      </c>
       <c r="D44" t="s">
         <v>264</v>
       </c>
+      <c r="E44" t="s">
+        <v>269</v>
+      </c>
       <c r="F44" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="45" spans="1:7" hidden="1">
+    <row r="45" spans="1:7">
       <c r="A45" t="s">
         <v>48</v>
       </c>
+      <c r="B45" t="s">
+        <v>269</v>
+      </c>
+      <c r="C45" t="s">
+        <v>269</v>
+      </c>
       <c r="D45" t="s">
         <v>264</v>
       </c>
+      <c r="E45" t="s">
+        <v>269</v>
+      </c>
       <c r="F45" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="46" spans="1:7" hidden="1">
+    <row r="46" spans="1:7">
       <c r="A46" t="s">
         <v>49</v>
       </c>
+      <c r="B46" t="s">
+        <v>269</v>
+      </c>
+      <c r="C46" t="s">
+        <v>269</v>
+      </c>
       <c r="D46" t="s">
         <v>264</v>
+      </c>
+      <c r="E46" t="s">
+        <v>269</v>
       </c>
       <c r="F46" t="s">
         <v>262</v>
@@ -4195,7 +4341,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="65" spans="1:6" hidden="1">
+    <row r="65" spans="1:7" hidden="1">
       <c r="A65" t="s">
         <v>68</v>
       </c>
@@ -4206,7 +4352,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="66" spans="1:6" hidden="1">
+    <row r="66" spans="1:7" hidden="1">
       <c r="A66" t="s">
         <v>69</v>
       </c>
@@ -4217,7 +4363,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="67" spans="1:6" hidden="1">
+    <row r="67" spans="1:7" hidden="1">
       <c r="A67" t="s">
         <v>70</v>
       </c>
@@ -4228,7 +4374,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="68" spans="1:6" hidden="1">
+    <row r="68" spans="1:7" hidden="1">
       <c r="A68" t="s">
         <v>71</v>
       </c>
@@ -4239,7 +4385,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="69" spans="1:6" hidden="1">
+    <row r="69" spans="1:7" hidden="1">
       <c r="A69" t="s">
         <v>72</v>
       </c>
@@ -4250,7 +4396,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="70" spans="1:6" hidden="1">
+    <row r="70" spans="1:7" hidden="1">
       <c r="A70" t="s">
         <v>73</v>
       </c>
@@ -4261,7 +4407,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="71" spans="1:6" hidden="1">
+    <row r="71" spans="1:7" hidden="1">
       <c r="A71" t="s">
         <v>74</v>
       </c>
@@ -4272,7 +4418,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="72" spans="1:6" hidden="1">
+    <row r="72" spans="1:7" hidden="1">
       <c r="A72" t="s">
         <v>75</v>
       </c>
@@ -4283,73 +4429,139 @@
         <v>262</v>
       </c>
     </row>
-    <row r="73" spans="1:6" hidden="1">
+    <row r="73" spans="1:7">
       <c r="A73" t="s">
         <v>76</v>
       </c>
+      <c r="B73" t="s">
+        <v>269</v>
+      </c>
+      <c r="C73" t="s">
+        <v>269</v>
+      </c>
       <c r="D73" t="s">
         <v>264</v>
       </c>
+      <c r="E73" t="s">
+        <v>269</v>
+      </c>
       <c r="F73" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="74" spans="1:6" hidden="1">
+    <row r="74" spans="1:7">
       <c r="A74" t="s">
         <v>77</v>
       </c>
+      <c r="B74" t="s">
+        <v>269</v>
+      </c>
+      <c r="C74" t="s">
+        <v>270</v>
+      </c>
       <c r="D74" t="s">
         <v>264</v>
       </c>
+      <c r="E74" t="s">
+        <v>270</v>
+      </c>
       <c r="F74" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="75" spans="1:6" hidden="1">
+      <c r="G74" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7">
       <c r="A75" t="s">
         <v>78</v>
       </c>
+      <c r="B75" t="s">
+        <v>269</v>
+      </c>
+      <c r="C75" t="s">
+        <v>270</v>
+      </c>
       <c r="D75" t="s">
         <v>264</v>
       </c>
+      <c r="E75" t="s">
+        <v>270</v>
+      </c>
       <c r="F75" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="76" spans="1:6" hidden="1">
+      <c r="G75" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7">
       <c r="A76" t="s">
         <v>79</v>
       </c>
+      <c r="B76" t="s">
+        <v>270</v>
+      </c>
+      <c r="C76" t="s">
+        <v>270</v>
+      </c>
       <c r="D76" t="s">
         <v>264</v>
       </c>
+      <c r="E76" t="s">
+        <v>270</v>
+      </c>
       <c r="F76" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="77" spans="1:6" hidden="1">
+      <c r="G76" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7">
       <c r="A77" t="s">
         <v>80</v>
       </c>
+      <c r="B77" t="s">
+        <v>270</v>
+      </c>
+      <c r="C77" t="s">
+        <v>270</v>
+      </c>
       <c r="D77" t="s">
         <v>264</v>
       </c>
+      <c r="E77" t="s">
+        <v>270</v>
+      </c>
       <c r="F77" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="78" spans="1:6" hidden="1">
+      <c r="G77" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7">
       <c r="A78" t="s">
         <v>81</v>
       </c>
+      <c r="B78" t="s">
+        <v>269</v>
+      </c>
+      <c r="C78" t="s">
+        <v>269</v>
+      </c>
       <c r="D78" t="s">
         <v>264</v>
       </c>
+      <c r="E78" t="s">
+        <v>269</v>
+      </c>
       <c r="F78" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="79" spans="1:6" hidden="1">
+    <row r="79" spans="1:7" hidden="1">
       <c r="A79" t="s">
         <v>82</v>
       </c>
@@ -4360,7 +4572,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="80" spans="1:6" hidden="1">
+    <row r="80" spans="1:7" hidden="1">
       <c r="A80" t="s">
         <v>83</v>
       </c>
@@ -4415,7 +4627,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="85" spans="1:7">
+    <row r="85" spans="1:7" hidden="1">
       <c r="A85" t="s">
         <v>88</v>
       </c>
@@ -4432,7 +4644,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="86" spans="1:7">
+    <row r="86" spans="1:7" hidden="1">
       <c r="A86" t="s">
         <v>89</v>
       </c>
@@ -4449,7 +4661,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="87" spans="1:7">
+    <row r="87" spans="1:7" hidden="1">
       <c r="A87" t="s">
         <v>90</v>
       </c>
@@ -4466,7 +4678,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="88" spans="1:7">
+    <row r="88" spans="1:7" hidden="1">
       <c r="A88" t="s">
         <v>91</v>
       </c>
@@ -4483,7 +4695,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="89" spans="1:7">
+    <row r="89" spans="1:7" hidden="1">
       <c r="A89" t="s">
         <v>92</v>
       </c>
@@ -4500,7 +4712,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="90" spans="1:7">
+    <row r="90" spans="1:7" hidden="1">
       <c r="A90" t="s">
         <v>93</v>
       </c>
@@ -4550,7 +4762,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="94" spans="1:7">
+    <row r="94" spans="1:7" hidden="1">
       <c r="A94" t="s">
         <v>97</v>
       </c>
@@ -4567,7 +4779,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="95" spans="1:7">
+    <row r="95" spans="1:7" hidden="1">
       <c r="A95" t="s">
         <v>98</v>
       </c>
@@ -4584,7 +4796,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="96" spans="1:7">
+    <row r="96" spans="1:7" hidden="1">
       <c r="A96" t="s">
         <v>99</v>
       </c>
@@ -4601,22 +4813,34 @@
         <v>268</v>
       </c>
     </row>
-    <row r="97" spans="1:6" hidden="1">
+    <row r="97" spans="1:7">
       <c r="A97" t="s">
         <v>100</v>
       </c>
+      <c r="B97" t="s">
+        <v>270</v>
+      </c>
+      <c r="C97" t="s">
+        <v>270</v>
+      </c>
       <c r="D97" t="s">
         <v>264</v>
       </c>
+      <c r="E97" t="s">
+        <v>270</v>
+      </c>
       <c r="F97" t="s">
         <v>262</v>
+      </c>
+      <c r="G97" t="s">
+        <v>271</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="D1:D97">
     <filterColumn colId="0">
       <filters>
-        <filter val="赵育"/>
+        <filter val="尹臻"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/internal_doc/05.测试设计/story/事务支持RC隔离级别/事务自动化用例跟踪表.xlsx
+++ b/internal_doc/05.测试设计/story/事务支持RC隔离级别/事务自动化用例跟踪表.xlsx
@@ -12,7 +12,7 @@
     <sheet name="RC不等锁" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">RC不等锁!$D$1:$D$97</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">RC不等锁!$A$1:$G$97</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">RC等锁!$D$1:$D$67</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">RU!$D$1:$D$94</definedName>
   </definedNames>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1015" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1069" uniqueCount="278">
   <si>
     <t>用例编号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -884,6 +884,14 @@
   </si>
   <si>
     <t>全文索引用例，待提交</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>记录长度太小，与测试点不符</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>内存不足，不实现自动化</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3423,7 +3431,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" hidden="1">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -3443,7 +3451,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" hidden="1">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -3463,7 +3471,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" hidden="1">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -3483,117 +3491,213 @@
         <v>262</v>
       </c>
     </row>
-    <row r="5" spans="1:7" hidden="1">
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
         <v>8</v>
       </c>
+      <c r="B5" t="s">
+        <v>269</v>
+      </c>
+      <c r="C5" t="s">
+        <v>269</v>
+      </c>
       <c r="D5" t="s">
         <v>263</v>
       </c>
+      <c r="E5" t="s">
+        <v>269</v>
+      </c>
       <c r="F5" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="6" spans="1:7" hidden="1">
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
         <v>9</v>
       </c>
+      <c r="B6" t="s">
+        <v>269</v>
+      </c>
+      <c r="C6" t="s">
+        <v>269</v>
+      </c>
       <c r="D6" t="s">
         <v>263</v>
       </c>
+      <c r="E6" t="s">
+        <v>269</v>
+      </c>
       <c r="F6" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="7" spans="1:7" hidden="1">
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
         <v>10</v>
       </c>
+      <c r="B7" t="s">
+        <v>269</v>
+      </c>
+      <c r="C7" t="s">
+        <v>269</v>
+      </c>
       <c r="D7" t="s">
         <v>263</v>
       </c>
+      <c r="E7" t="s">
+        <v>269</v>
+      </c>
       <c r="F7" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="8" spans="1:7" hidden="1">
+    <row r="8" spans="1:7">
       <c r="A8" t="s">
         <v>11</v>
       </c>
+      <c r="B8" t="s">
+        <v>269</v>
+      </c>
+      <c r="C8" t="s">
+        <v>269</v>
+      </c>
       <c r="D8" t="s">
         <v>263</v>
       </c>
+      <c r="E8" t="s">
+        <v>269</v>
+      </c>
       <c r="F8" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="9" spans="1:7" hidden="1">
+    <row r="9" spans="1:7">
       <c r="A9" t="s">
         <v>12</v>
       </c>
+      <c r="B9" t="s">
+        <v>269</v>
+      </c>
+      <c r="C9" t="s">
+        <v>269</v>
+      </c>
       <c r="D9" t="s">
         <v>263</v>
       </c>
+      <c r="E9" t="s">
+        <v>269</v>
+      </c>
       <c r="F9" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="10" spans="1:7" hidden="1">
+    <row r="10" spans="1:7">
       <c r="A10" t="s">
         <v>13</v>
       </c>
+      <c r="B10" t="s">
+        <v>269</v>
+      </c>
+      <c r="C10" t="s">
+        <v>269</v>
+      </c>
       <c r="D10" t="s">
         <v>263</v>
       </c>
+      <c r="E10" t="s">
+        <v>269</v>
+      </c>
       <c r="F10" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="11" spans="1:7" hidden="1">
+    <row r="11" spans="1:7">
       <c r="A11" t="s">
         <v>14</v>
       </c>
+      <c r="B11" t="s">
+        <v>269</v>
+      </c>
+      <c r="C11" t="s">
+        <v>269</v>
+      </c>
       <c r="D11" t="s">
         <v>263</v>
       </c>
+      <c r="E11" t="s">
+        <v>269</v>
+      </c>
       <c r="F11" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="12" spans="1:7" hidden="1">
+    <row r="12" spans="1:7">
       <c r="A12" t="s">
         <v>15</v>
       </c>
+      <c r="B12" t="s">
+        <v>269</v>
+      </c>
+      <c r="C12" t="s">
+        <v>269</v>
+      </c>
       <c r="D12" t="s">
         <v>263</v>
       </c>
+      <c r="E12" t="s">
+        <v>269</v>
+      </c>
       <c r="F12" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="13" spans="1:7" hidden="1">
+    <row r="13" spans="1:7">
       <c r="A13" t="s">
         <v>16</v>
       </c>
+      <c r="B13" t="s">
+        <v>269</v>
+      </c>
+      <c r="C13" t="s">
+        <v>269</v>
+      </c>
       <c r="D13" t="s">
         <v>263</v>
       </c>
+      <c r="E13" t="s">
+        <v>269</v>
+      </c>
       <c r="F13" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" hidden="1">
+      <c r="G13" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
       <c r="A14" t="s">
         <v>17</v>
       </c>
+      <c r="B14" t="s">
+        <v>269</v>
+      </c>
+      <c r="C14" t="s">
+        <v>269</v>
+      </c>
       <c r="D14" t="s">
         <v>263</v>
       </c>
+      <c r="E14" t="s">
+        <v>269</v>
+      </c>
       <c r="F14" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="15" spans="1:7">
+      <c r="G14" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" hidden="1">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -3613,7 +3717,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" hidden="1">
       <c r="A16" t="s">
         <v>19</v>
       </c>
@@ -3633,7 +3737,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" hidden="1">
       <c r="A17" t="s">
         <v>20</v>
       </c>
@@ -3653,7 +3757,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" hidden="1">
       <c r="A18" t="s">
         <v>21</v>
       </c>
@@ -3673,45 +3777,81 @@
         <v>262</v>
       </c>
     </row>
-    <row r="19" spans="1:7" hidden="1">
+    <row r="19" spans="1:7">
       <c r="A19" t="s">
         <v>22</v>
       </c>
+      <c r="B19" t="s">
+        <v>269</v>
+      </c>
+      <c r="C19" t="s">
+        <v>269</v>
+      </c>
       <c r="D19" t="s">
         <v>263</v>
       </c>
+      <c r="E19" t="s">
+        <v>269</v>
+      </c>
       <c r="F19" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="20" spans="1:7" hidden="1">
+    <row r="20" spans="1:7">
       <c r="A20" t="s">
         <v>23</v>
       </c>
+      <c r="B20" t="s">
+        <v>269</v>
+      </c>
+      <c r="C20" t="s">
+        <v>269</v>
+      </c>
       <c r="D20" t="s">
         <v>263</v>
       </c>
+      <c r="E20" t="s">
+        <v>269</v>
+      </c>
       <c r="F20" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="21" spans="1:7" hidden="1">
+    <row r="21" spans="1:7">
       <c r="A21" t="s">
         <v>24</v>
       </c>
+      <c r="B21" t="s">
+        <v>269</v>
+      </c>
+      <c r="C21" t="s">
+        <v>269</v>
+      </c>
       <c r="D21" t="s">
         <v>263</v>
       </c>
+      <c r="E21" t="s">
+        <v>269</v>
+      </c>
       <c r="F21" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="22" spans="1:7" hidden="1">
+    <row r="22" spans="1:7">
       <c r="A22" t="s">
         <v>25</v>
       </c>
+      <c r="B22" t="s">
+        <v>269</v>
+      </c>
+      <c r="C22" t="s">
+        <v>269</v>
+      </c>
       <c r="D22" t="s">
         <v>263</v>
+      </c>
+      <c r="E22" t="s">
+        <v>269</v>
       </c>
       <c r="F22" t="s">
         <v>262</v>
@@ -4023,7 +4163,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" hidden="1">
       <c r="A41" t="s">
         <v>44</v>
       </c>
@@ -4043,7 +4183,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:7" hidden="1">
       <c r="A42" t="s">
         <v>45</v>
       </c>
@@ -4063,7 +4203,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" hidden="1">
       <c r="A43" t="s">
         <v>46</v>
       </c>
@@ -4083,7 +4223,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:7" hidden="1">
       <c r="A44" t="s">
         <v>47</v>
       </c>
@@ -4103,7 +4243,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:7" hidden="1">
       <c r="A45" t="s">
         <v>48</v>
       </c>
@@ -4123,7 +4263,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:7" hidden="1">
       <c r="A46" t="s">
         <v>49</v>
       </c>
@@ -4143,40 +4283,70 @@
         <v>262</v>
       </c>
     </row>
-    <row r="47" spans="1:7" hidden="1">
+    <row r="47" spans="1:7">
       <c r="A47" t="s">
         <v>50</v>
       </c>
+      <c r="B47" t="s">
+        <v>269</v>
+      </c>
+      <c r="C47" t="s">
+        <v>269</v>
+      </c>
       <c r="D47" t="s">
         <v>263</v>
       </c>
+      <c r="E47" t="s">
+        <v>269</v>
+      </c>
       <c r="F47" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="48" spans="1:7" hidden="1">
+    <row r="48" spans="1:7">
       <c r="A48" t="s">
         <v>51</v>
       </c>
+      <c r="B48" t="s">
+        <v>269</v>
+      </c>
+      <c r="C48" t="s">
+        <v>269</v>
+      </c>
       <c r="D48" t="s">
         <v>263</v>
       </c>
+      <c r="E48" t="s">
+        <v>269</v>
+      </c>
       <c r="F48" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="49" spans="1:6" hidden="1">
+    <row r="49" spans="1:7">
       <c r="A49" t="s">
         <v>52</v>
       </c>
+      <c r="B49" t="s">
+        <v>270</v>
+      </c>
+      <c r="C49" t="s">
+        <v>270</v>
+      </c>
       <c r="D49" t="s">
         <v>263</v>
       </c>
+      <c r="E49" t="s">
+        <v>270</v>
+      </c>
       <c r="F49" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="50" spans="1:6" hidden="1">
+      <c r="G49" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" hidden="1">
       <c r="A50" t="s">
         <v>53</v>
       </c>
@@ -4187,7 +4357,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="51" spans="1:6" hidden="1">
+    <row r="51" spans="1:7" hidden="1">
       <c r="A51" t="s">
         <v>54</v>
       </c>
@@ -4198,7 +4368,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="52" spans="1:6" hidden="1">
+    <row r="52" spans="1:7" hidden="1">
       <c r="A52" t="s">
         <v>55</v>
       </c>
@@ -4209,7 +4379,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="53" spans="1:6" hidden="1">
+    <row r="53" spans="1:7" hidden="1">
       <c r="A53" t="s">
         <v>56</v>
       </c>
@@ -4220,7 +4390,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="54" spans="1:6" hidden="1">
+    <row r="54" spans="1:7" hidden="1">
       <c r="A54" t="s">
         <v>57</v>
       </c>
@@ -4231,7 +4401,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="55" spans="1:6" hidden="1">
+    <row r="55" spans="1:7" hidden="1">
       <c r="A55" t="s">
         <v>58</v>
       </c>
@@ -4242,7 +4412,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="56" spans="1:6" hidden="1">
+    <row r="56" spans="1:7" hidden="1">
       <c r="A56" t="s">
         <v>59</v>
       </c>
@@ -4253,7 +4423,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="57" spans="1:6" hidden="1">
+    <row r="57" spans="1:7" hidden="1">
       <c r="A57" t="s">
         <v>60</v>
       </c>
@@ -4264,7 +4434,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="58" spans="1:6" hidden="1">
+    <row r="58" spans="1:7" hidden="1">
       <c r="A58" t="s">
         <v>61</v>
       </c>
@@ -4275,7 +4445,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="59" spans="1:6" hidden="1">
+    <row r="59" spans="1:7" hidden="1">
       <c r="A59" t="s">
         <v>62</v>
       </c>
@@ -4286,7 +4456,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="60" spans="1:6" hidden="1">
+    <row r="60" spans="1:7" hidden="1">
       <c r="A60" t="s">
         <v>63</v>
       </c>
@@ -4297,7 +4467,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="61" spans="1:6" hidden="1">
+    <row r="61" spans="1:7" hidden="1">
       <c r="A61" t="s">
         <v>64</v>
       </c>
@@ -4308,7 +4478,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="62" spans="1:6" hidden="1">
+    <row r="62" spans="1:7" hidden="1">
       <c r="A62" t="s">
         <v>65</v>
       </c>
@@ -4319,7 +4489,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="63" spans="1:6" hidden="1">
+    <row r="63" spans="1:7" hidden="1">
       <c r="A63" t="s">
         <v>66</v>
       </c>
@@ -4330,7 +4500,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="64" spans="1:6" hidden="1">
+    <row r="64" spans="1:7" hidden="1">
       <c r="A64" t="s">
         <v>67</v>
       </c>
@@ -4429,7 +4599,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="73" spans="1:7">
+    <row r="73" spans="1:7" hidden="1">
       <c r="A73" t="s">
         <v>76</v>
       </c>
@@ -4449,7 +4619,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="74" spans="1:7">
+    <row r="74" spans="1:7" hidden="1">
       <c r="A74" t="s">
         <v>77</v>
       </c>
@@ -4472,7 +4642,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="75" spans="1:7">
+    <row r="75" spans="1:7" hidden="1">
       <c r="A75" t="s">
         <v>78</v>
       </c>
@@ -4495,7 +4665,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="76" spans="1:7">
+    <row r="76" spans="1:7" hidden="1">
       <c r="A76" t="s">
         <v>79</v>
       </c>
@@ -4518,7 +4688,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="77" spans="1:7">
+    <row r="77" spans="1:7" hidden="1">
       <c r="A77" t="s">
         <v>80</v>
       </c>
@@ -4541,7 +4711,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="78" spans="1:7">
+    <row r="78" spans="1:7" hidden="1">
       <c r="A78" t="s">
         <v>81</v>
       </c>
@@ -4813,7 +4983,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="97" spans="1:7">
+    <row r="97" spans="1:7" hidden="1">
       <c r="A97" t="s">
         <v>100</v>
       </c>
@@ -4837,10 +5007,10 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="D1:D97">
-    <filterColumn colId="0">
+  <autoFilter ref="A1:G97">
+    <filterColumn colId="3">
       <filters>
-        <filter val="尹臻"/>
+        <filter val="赵小妮"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/internal_doc/05.测试设计/story/事务支持RC隔离级别/事务自动化用例跟踪表.xlsx
+++ b/internal_doc/05.测试设计/story/事务支持RC隔离级别/事务自动化用例跟踪表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="2"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
   </bookViews>
   <sheets>
     <sheet name="RU" sheetId="1" r:id="rId1"/>
@@ -12,7 +12,7 @@
     <sheet name="RC不等锁" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">RC不等锁!$A$1:$G$97</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">RC不等锁!$D$1:$D$97</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">RC等锁!$D$1:$D$67</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">RU!$D$1:$D$94</definedName>
   </definedNames>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1069" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1089" uniqueCount="279">
   <si>
     <t>用例编号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -887,11 +887,14 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>记录长度太小，与测试点不符</t>
+    <t>是</t>
+  </si>
+  <si>
+    <t>是</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>内存不足，不实现自动化</t>
+    <t>否</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1231,7 +1234,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:G94"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
@@ -1261,40 +1263,67 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7" hidden="1">
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
         <v>170</v>
       </c>
+      <c r="B2" t="s">
+        <v>277</v>
+      </c>
+      <c r="C2" t="s">
+        <v>277</v>
+      </c>
       <c r="D2" t="s">
         <v>264</v>
       </c>
+      <c r="E2" t="s">
+        <v>277</v>
+      </c>
       <c r="F2" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="3" spans="1:7" hidden="1">
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>141</v>
       </c>
+      <c r="B3" t="s">
+        <v>276</v>
+      </c>
+      <c r="C3" t="s">
+        <v>277</v>
+      </c>
       <c r="D3" t="s">
         <v>264</v>
       </c>
+      <c r="E3" t="s">
+        <v>277</v>
+      </c>
       <c r="F3" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="4" spans="1:7" hidden="1">
+    <row r="4" spans="1:7">
       <c r="A4" t="s">
         <v>142</v>
       </c>
+      <c r="B4" t="s">
+        <v>276</v>
+      </c>
+      <c r="C4" t="s">
+        <v>277</v>
+      </c>
       <c r="D4" t="s">
         <v>264</v>
       </c>
+      <c r="E4" t="s">
+        <v>277</v>
+      </c>
       <c r="F4" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="5" spans="1:7" hidden="1">
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
         <v>171</v>
       </c>
@@ -1305,7 +1334,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="6" spans="1:7" hidden="1">
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
         <v>172</v>
       </c>
@@ -1316,7 +1345,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="7" spans="1:7" hidden="1">
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
         <v>173</v>
       </c>
@@ -1327,7 +1356,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="8" spans="1:7" hidden="1">
+    <row r="8" spans="1:7">
       <c r="A8" t="s">
         <v>174</v>
       </c>
@@ -1338,7 +1367,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="9" spans="1:7" hidden="1">
+    <row r="9" spans="1:7">
       <c r="A9" t="s">
         <v>175</v>
       </c>
@@ -1349,7 +1378,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="10" spans="1:7" hidden="1">
+    <row r="10" spans="1:7">
       <c r="A10" t="s">
         <v>176</v>
       </c>
@@ -1360,7 +1389,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="11" spans="1:7" hidden="1">
+    <row r="11" spans="1:7">
       <c r="A11" t="s">
         <v>177</v>
       </c>
@@ -1371,7 +1400,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="12" spans="1:7" hidden="1">
+    <row r="12" spans="1:7">
       <c r="A12" t="s">
         <v>178</v>
       </c>
@@ -1382,7 +1411,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="13" spans="1:7" hidden="1">
+    <row r="13" spans="1:7">
       <c r="A13" t="s">
         <v>179</v>
       </c>
@@ -1393,7 +1422,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="14" spans="1:7" hidden="1">
+    <row r="14" spans="1:7">
       <c r="A14" t="s">
         <v>180</v>
       </c>
@@ -1404,51 +1433,87 @@
         <v>265</v>
       </c>
     </row>
-    <row r="15" spans="1:7" hidden="1">
+    <row r="15" spans="1:7">
       <c r="A15" t="s">
         <v>181</v>
       </c>
+      <c r="B15" t="s">
+        <v>277</v>
+      </c>
+      <c r="C15" t="s">
+        <v>276</v>
+      </c>
       <c r="D15" t="s">
         <v>264</v>
       </c>
+      <c r="E15" t="s">
+        <v>277</v>
+      </c>
       <c r="F15" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="16" spans="1:7" hidden="1">
+    <row r="16" spans="1:7">
       <c r="A16" t="s">
         <v>182</v>
       </c>
+      <c r="B16" t="s">
+        <v>277</v>
+      </c>
+      <c r="C16" t="s">
+        <v>277</v>
+      </c>
       <c r="D16" t="s">
         <v>264</v>
       </c>
+      <c r="E16" t="s">
+        <v>277</v>
+      </c>
       <c r="F16" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="17" spans="1:7" hidden="1">
+    <row r="17" spans="1:7">
       <c r="A17" t="s">
         <v>183</v>
       </c>
+      <c r="B17" t="s">
+        <v>277</v>
+      </c>
+      <c r="C17" t="s">
+        <v>277</v>
+      </c>
       <c r="D17" t="s">
         <v>264</v>
       </c>
+      <c r="E17" t="s">
+        <v>277</v>
+      </c>
       <c r="F17" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="18" spans="1:7" hidden="1">
+    <row r="18" spans="1:7">
       <c r="A18" t="s">
         <v>184</v>
       </c>
+      <c r="B18" t="s">
+        <v>277</v>
+      </c>
+      <c r="C18" t="s">
+        <v>277</v>
+      </c>
       <c r="D18" t="s">
         <v>264</v>
       </c>
+      <c r="E18" t="s">
+        <v>277</v>
+      </c>
       <c r="F18" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="19" spans="1:7" hidden="1">
+    <row r="19" spans="1:7">
       <c r="A19" t="s">
         <v>185</v>
       </c>
@@ -1459,7 +1524,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="20" spans="1:7" hidden="1">
+    <row r="20" spans="1:7">
       <c r="A20" t="s">
         <v>186</v>
       </c>
@@ -1470,7 +1535,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="21" spans="1:7" hidden="1">
+    <row r="21" spans="1:7">
       <c r="A21" t="s">
         <v>187</v>
       </c>
@@ -1481,7 +1546,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="22" spans="1:7" hidden="1">
+    <row r="22" spans="1:7">
       <c r="A22" t="s">
         <v>188</v>
       </c>
@@ -1798,40 +1863,67 @@
         <v>268</v>
       </c>
     </row>
-    <row r="41" spans="1:7" hidden="1">
+    <row r="41" spans="1:7">
       <c r="A41" t="s">
         <v>207</v>
       </c>
+      <c r="B41" t="s">
+        <v>277</v>
+      </c>
+      <c r="C41" t="s">
+        <v>276</v>
+      </c>
       <c r="D41" t="s">
         <v>264</v>
       </c>
+      <c r="E41" t="s">
+        <v>277</v>
+      </c>
       <c r="F41" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="42" spans="1:7" hidden="1">
+    <row r="42" spans="1:7">
       <c r="A42" t="s">
         <v>208</v>
       </c>
+      <c r="B42" t="s">
+        <v>277</v>
+      </c>
+      <c r="C42" t="s">
+        <v>277</v>
+      </c>
       <c r="D42" t="s">
         <v>264</v>
       </c>
+      <c r="E42" t="s">
+        <v>277</v>
+      </c>
       <c r="F42" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="43" spans="1:7" hidden="1">
+    <row r="43" spans="1:7">
       <c r="A43" t="s">
         <v>209</v>
       </c>
+      <c r="B43" t="s">
+        <v>277</v>
+      </c>
+      <c r="C43" t="s">
+        <v>277</v>
+      </c>
       <c r="D43" t="s">
         <v>264</v>
       </c>
+      <c r="E43" t="s">
+        <v>277</v>
+      </c>
       <c r="F43" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="44" spans="1:7" hidden="1">
+    <row r="44" spans="1:7">
       <c r="A44" t="s">
         <v>210</v>
       </c>
@@ -1842,7 +1934,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="45" spans="1:7" hidden="1">
+    <row r="45" spans="1:7">
       <c r="A45" t="s">
         <v>211</v>
       </c>
@@ -1853,40 +1945,67 @@
         <v>265</v>
       </c>
     </row>
-    <row r="46" spans="1:7" hidden="1">
+    <row r="46" spans="1:7">
       <c r="A46" t="s">
         <v>212</v>
       </c>
+      <c r="B46" t="s">
+        <v>277</v>
+      </c>
+      <c r="C46" t="s">
+        <v>276</v>
+      </c>
       <c r="D46" t="s">
         <v>264</v>
       </c>
+      <c r="E46" t="s">
+        <v>277</v>
+      </c>
       <c r="F46" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="47" spans="1:7" hidden="1">
+    <row r="47" spans="1:7">
       <c r="A47" t="s">
         <v>213</v>
       </c>
+      <c r="B47" t="s">
+        <v>277</v>
+      </c>
+      <c r="C47" t="s">
+        <v>277</v>
+      </c>
       <c r="D47" t="s">
         <v>264</v>
       </c>
+      <c r="E47" t="s">
+        <v>277</v>
+      </c>
       <c r="F47" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="48" spans="1:7" hidden="1">
+    <row r="48" spans="1:7">
       <c r="A48" t="s">
         <v>214</v>
       </c>
+      <c r="B48" t="s">
+        <v>277</v>
+      </c>
+      <c r="C48" t="s">
+        <v>277</v>
+      </c>
       <c r="D48" t="s">
         <v>264</v>
       </c>
+      <c r="E48" t="s">
+        <v>277</v>
+      </c>
       <c r="F48" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="49" spans="1:6" hidden="1">
+    <row r="49" spans="1:6">
       <c r="A49" t="s">
         <v>215</v>
       </c>
@@ -1897,7 +2016,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="50" spans="1:6" hidden="1">
+    <row r="50" spans="1:6">
       <c r="A50" t="s">
         <v>216</v>
       </c>
@@ -1908,7 +2027,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="51" spans="1:6" hidden="1">
+    <row r="51" spans="1:6">
       <c r="A51" t="s">
         <v>217</v>
       </c>
@@ -1919,7 +2038,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="52" spans="1:6" hidden="1">
+    <row r="52" spans="1:6">
       <c r="A52" t="s">
         <v>218</v>
       </c>
@@ -1930,7 +2049,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="53" spans="1:6" hidden="1">
+    <row r="53" spans="1:6">
       <c r="A53" t="s">
         <v>219</v>
       </c>
@@ -1941,7 +2060,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="54" spans="1:6" hidden="1">
+    <row r="54" spans="1:6">
       <c r="A54" t="s">
         <v>220</v>
       </c>
@@ -1952,7 +2071,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="55" spans="1:6" hidden="1">
+    <row r="55" spans="1:6">
       <c r="A55" t="s">
         <v>221</v>
       </c>
@@ -1963,7 +2082,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="56" spans="1:6" hidden="1">
+    <row r="56" spans="1:6">
       <c r="A56" t="s">
         <v>222</v>
       </c>
@@ -1974,7 +2093,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="57" spans="1:6" hidden="1">
+    <row r="57" spans="1:6">
       <c r="A57" t="s">
         <v>223</v>
       </c>
@@ -1985,7 +2104,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="58" spans="1:6" hidden="1">
+    <row r="58" spans="1:6">
       <c r="A58" t="s">
         <v>224</v>
       </c>
@@ -1996,7 +2115,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="59" spans="1:6" hidden="1">
+    <row r="59" spans="1:6">
       <c r="A59" t="s">
         <v>225</v>
       </c>
@@ -2007,7 +2126,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="60" spans="1:6" hidden="1">
+    <row r="60" spans="1:6">
       <c r="A60" t="s">
         <v>226</v>
       </c>
@@ -2018,7 +2137,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="61" spans="1:6" hidden="1">
+    <row r="61" spans="1:6">
       <c r="A61" t="s">
         <v>227</v>
       </c>
@@ -2029,7 +2148,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="62" spans="1:6" hidden="1">
+    <row r="62" spans="1:6">
       <c r="A62" t="s">
         <v>228</v>
       </c>
@@ -2040,7 +2159,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="63" spans="1:6" hidden="1">
+    <row r="63" spans="1:6">
       <c r="A63" t="s">
         <v>229</v>
       </c>
@@ -2051,7 +2170,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="64" spans="1:6" hidden="1">
+    <row r="64" spans="1:6">
       <c r="A64" t="s">
         <v>230</v>
       </c>
@@ -2062,7 +2181,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="65" spans="1:6" hidden="1">
+    <row r="65" spans="1:6">
       <c r="A65" t="s">
         <v>231</v>
       </c>
@@ -2073,7 +2192,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="66" spans="1:6" hidden="1">
+    <row r="66" spans="1:6">
       <c r="A66" t="s">
         <v>232</v>
       </c>
@@ -2084,7 +2203,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="67" spans="1:6" hidden="1">
+    <row r="67" spans="1:6">
       <c r="A67" t="s">
         <v>233</v>
       </c>
@@ -2095,7 +2214,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="68" spans="1:6" hidden="1">
+    <row r="68" spans="1:6">
       <c r="A68" t="s">
         <v>234</v>
       </c>
@@ -2106,7 +2225,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="69" spans="1:6" hidden="1">
+    <row r="69" spans="1:6">
       <c r="A69" t="s">
         <v>235</v>
       </c>
@@ -2117,7 +2236,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="70" spans="1:6" hidden="1">
+    <row r="70" spans="1:6">
       <c r="A70" t="s">
         <v>236</v>
       </c>
@@ -2128,21 +2247,33 @@
         <v>264</v>
       </c>
     </row>
-    <row r="71" spans="1:6" hidden="1">
+    <row r="71" spans="1:6">
       <c r="A71" t="s">
         <v>237</v>
       </c>
+      <c r="B71" t="s">
+        <v>277</v>
+      </c>
+      <c r="C71" t="s">
+        <v>277</v>
+      </c>
       <c r="D71" t="s">
         <v>264</v>
       </c>
+      <c r="E71" t="s">
+        <v>277</v>
+      </c>
       <c r="F71" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="72" spans="1:6" hidden="1">
+    <row r="72" spans="1:6">
       <c r="A72" t="s">
         <v>238</v>
       </c>
+      <c r="C72" t="s">
+        <v>278</v>
+      </c>
       <c r="D72" t="s">
         <v>264</v>
       </c>
@@ -2150,10 +2281,13 @@
         <v>263</v>
       </c>
     </row>
-    <row r="73" spans="1:6" hidden="1">
+    <row r="73" spans="1:6">
       <c r="A73" t="s">
         <v>239</v>
       </c>
+      <c r="C73" t="s">
+        <v>278</v>
+      </c>
       <c r="D73" t="s">
         <v>264</v>
       </c>
@@ -2161,18 +2295,27 @@
         <v>263</v>
       </c>
     </row>
-    <row r="74" spans="1:6" hidden="1">
+    <row r="74" spans="1:6">
       <c r="A74" t="s">
         <v>242</v>
       </c>
+      <c r="B74" t="s">
+        <v>277</v>
+      </c>
+      <c r="C74" t="s">
+        <v>277</v>
+      </c>
       <c r="D74" t="s">
         <v>264</v>
       </c>
+      <c r="E74" t="s">
+        <v>277</v>
+      </c>
       <c r="F74" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="75" spans="1:6" hidden="1">
+    <row r="75" spans="1:6">
       <c r="A75" t="s">
         <v>240</v>
       </c>
@@ -2183,7 +2326,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="76" spans="1:6" hidden="1">
+    <row r="76" spans="1:6">
       <c r="A76" t="s">
         <v>241</v>
       </c>
@@ -2194,7 +2337,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="77" spans="1:6" hidden="1">
+    <row r="77" spans="1:6">
       <c r="A77" t="s">
         <v>243</v>
       </c>
@@ -2205,7 +2348,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="78" spans="1:6" hidden="1">
+    <row r="78" spans="1:6">
       <c r="A78" t="s">
         <v>157</v>
       </c>
@@ -2216,7 +2359,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="79" spans="1:6" hidden="1">
+    <row r="79" spans="1:6">
       <c r="A79" t="s">
         <v>244</v>
       </c>
@@ -2227,7 +2370,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="80" spans="1:6" hidden="1">
+    <row r="80" spans="1:6">
       <c r="A80" t="s">
         <v>245</v>
       </c>
@@ -2238,7 +2381,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="81" spans="1:7" hidden="1">
+    <row r="81" spans="1:7">
       <c r="A81" t="s">
         <v>246</v>
       </c>
@@ -2249,7 +2392,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="82" spans="1:7" hidden="1">
+    <row r="82" spans="1:7">
       <c r="A82" t="s">
         <v>247</v>
       </c>
@@ -2362,7 +2505,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="89" spans="1:7" hidden="1">
+    <row r="89" spans="1:7">
       <c r="A89" t="s">
         <v>254</v>
       </c>
@@ -2373,7 +2516,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="90" spans="1:7" hidden="1">
+    <row r="90" spans="1:7">
       <c r="A90" t="s">
         <v>255</v>
       </c>
@@ -2384,7 +2527,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="91" spans="1:7" hidden="1">
+    <row r="91" spans="1:7">
       <c r="A91" t="s">
         <v>256</v>
       </c>
@@ -2448,11 +2591,7 @@
     </row>
   </sheetData>
   <autoFilter ref="D1:D94">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="赵育"/>
-      </filters>
-    </filterColumn>
+    <filterColumn colId="0"/>
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2461,7 +2600,6 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:G67"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
@@ -2491,7 +2629,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7" hidden="1">
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
         <v>101</v>
       </c>
@@ -2502,7 +2640,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="3" spans="1:7" hidden="1">
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>102</v>
       </c>
@@ -2513,7 +2651,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="4" spans="1:7" hidden="1">
+    <row r="4" spans="1:7">
       <c r="A4" t="s">
         <v>103</v>
       </c>
@@ -2524,7 +2662,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="5" spans="1:7" hidden="1">
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
         <v>104</v>
       </c>
@@ -2535,7 +2673,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="6" spans="1:7" hidden="1">
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
         <v>105</v>
       </c>
@@ -2546,7 +2684,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="7" spans="1:7" hidden="1">
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
         <v>106</v>
       </c>
@@ -2557,7 +2695,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="8" spans="1:7" hidden="1">
+    <row r="8" spans="1:7">
       <c r="A8" t="s">
         <v>107</v>
       </c>
@@ -2568,7 +2706,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="9" spans="1:7" hidden="1">
+    <row r="9" spans="1:7">
       <c r="A9" t="s">
         <v>108</v>
       </c>
@@ -2579,7 +2717,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="10" spans="1:7" hidden="1">
+    <row r="10" spans="1:7">
       <c r="A10" t="s">
         <v>109</v>
       </c>
@@ -2590,7 +2728,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="11" spans="1:7" hidden="1">
+    <row r="11" spans="1:7">
       <c r="A11" t="s">
         <v>110</v>
       </c>
@@ -2601,7 +2739,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="12" spans="1:7" hidden="1">
+    <row r="12" spans="1:7">
       <c r="A12" t="s">
         <v>111</v>
       </c>
@@ -2612,7 +2750,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="13" spans="1:7" hidden="1">
+    <row r="13" spans="1:7">
       <c r="A13" t="s">
         <v>112</v>
       </c>
@@ -2623,7 +2761,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="14" spans="1:7" hidden="1">
+    <row r="14" spans="1:7">
       <c r="A14" t="s">
         <v>113</v>
       </c>
@@ -2634,7 +2772,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="15" spans="1:7" hidden="1">
+    <row r="15" spans="1:7">
       <c r="A15" t="s">
         <v>114</v>
       </c>
@@ -2645,7 +2783,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="16" spans="1:7" hidden="1">
+    <row r="16" spans="1:7">
       <c r="A16" t="s">
         <v>115</v>
       </c>
@@ -2656,7 +2794,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="17" spans="1:7" hidden="1">
+    <row r="17" spans="1:7">
       <c r="A17" t="s">
         <v>116</v>
       </c>
@@ -2667,7 +2805,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="18" spans="1:7" hidden="1">
+    <row r="18" spans="1:7">
       <c r="A18" t="s">
         <v>117</v>
       </c>
@@ -2678,7 +2816,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="19" spans="1:7" hidden="1">
+    <row r="19" spans="1:7">
       <c r="A19" t="s">
         <v>118</v>
       </c>
@@ -2689,7 +2827,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="20" spans="1:7" hidden="1">
+    <row r="20" spans="1:7">
       <c r="A20" t="s">
         <v>119</v>
       </c>
@@ -2700,7 +2838,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="21" spans="1:7" hidden="1">
+    <row r="21" spans="1:7">
       <c r="A21" t="s">
         <v>120</v>
       </c>
@@ -2711,7 +2849,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="22" spans="1:7" hidden="1">
+    <row r="22" spans="1:7">
       <c r="A22" t="s">
         <v>121</v>
       </c>
@@ -2909,7 +3047,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="34" spans="1:7" hidden="1">
+    <row r="34" spans="1:7">
       <c r="A34" t="s">
         <v>133</v>
       </c>
@@ -2920,7 +3058,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="35" spans="1:7" hidden="1">
+    <row r="35" spans="1:7">
       <c r="A35" t="s">
         <v>134</v>
       </c>
@@ -2931,7 +3069,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="36" spans="1:7" hidden="1">
+    <row r="36" spans="1:7">
       <c r="A36" t="s">
         <v>135</v>
       </c>
@@ -2942,7 +3080,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="37" spans="1:7" hidden="1">
+    <row r="37" spans="1:7">
       <c r="A37" t="s">
         <v>136</v>
       </c>
@@ -2953,7 +3091,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="38" spans="1:7" hidden="1">
+    <row r="38" spans="1:7">
       <c r="A38" t="s">
         <v>137</v>
       </c>
@@ -2964,7 +3102,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="39" spans="1:7" hidden="1">
+    <row r="39" spans="1:7">
       <c r="A39" t="s">
         <v>138</v>
       </c>
@@ -2975,7 +3113,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="40" spans="1:7" hidden="1">
+    <row r="40" spans="1:7">
       <c r="A40" t="s">
         <v>139</v>
       </c>
@@ -2986,7 +3124,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="41" spans="1:7" hidden="1">
+    <row r="41" spans="1:7">
       <c r="A41" t="s">
         <v>140</v>
       </c>
@@ -3116,67 +3254,121 @@
         <v>268</v>
       </c>
     </row>
-    <row r="49" spans="1:7" hidden="1">
+    <row r="49" spans="1:7">
       <c r="A49" t="s">
         <v>145</v>
       </c>
+      <c r="B49" t="s">
+        <v>277</v>
+      </c>
+      <c r="C49" t="s">
+        <v>277</v>
+      </c>
       <c r="D49" t="s">
         <v>265</v>
       </c>
+      <c r="E49" t="s">
+        <v>277</v>
+      </c>
       <c r="F49" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="50" spans="1:7" hidden="1">
+    <row r="50" spans="1:7">
       <c r="A50" t="s">
         <v>146</v>
       </c>
+      <c r="B50" t="s">
+        <v>277</v>
+      </c>
+      <c r="C50" t="s">
+        <v>277</v>
+      </c>
       <c r="D50" t="s">
         <v>265</v>
       </c>
+      <c r="E50" t="s">
+        <v>277</v>
+      </c>
       <c r="F50" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="51" spans="1:7" hidden="1">
+    <row r="51" spans="1:7">
       <c r="A51" t="s">
         <v>147</v>
       </c>
+      <c r="B51" t="s">
+        <v>277</v>
+      </c>
+      <c r="C51" t="s">
+        <v>277</v>
+      </c>
       <c r="D51" t="s">
         <v>265</v>
       </c>
+      <c r="E51" t="s">
+        <v>277</v>
+      </c>
       <c r="F51" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="52" spans="1:7" hidden="1">
+    <row r="52" spans="1:7">
       <c r="A52" t="s">
         <v>148</v>
       </c>
+      <c r="B52" t="s">
+        <v>277</v>
+      </c>
+      <c r="C52" t="s">
+        <v>277</v>
+      </c>
       <c r="D52" t="s">
         <v>265</v>
       </c>
+      <c r="E52" t="s">
+        <v>277</v>
+      </c>
       <c r="F52" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="53" spans="1:7" hidden="1">
+    <row r="53" spans="1:7">
       <c r="A53" t="s">
         <v>149</v>
       </c>
+      <c r="B53" t="s">
+        <v>277</v>
+      </c>
+      <c r="C53" t="s">
+        <v>277</v>
+      </c>
       <c r="D53" t="s">
         <v>265</v>
       </c>
+      <c r="E53" t="s">
+        <v>277</v>
+      </c>
       <c r="F53" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="54" spans="1:7" hidden="1">
+    <row r="54" spans="1:7">
       <c r="A54" t="s">
         <v>150</v>
       </c>
+      <c r="B54" t="s">
+        <v>277</v>
+      </c>
+      <c r="C54" t="s">
+        <v>277</v>
+      </c>
       <c r="D54" t="s">
         <v>265</v>
+      </c>
+      <c r="E54" t="s">
+        <v>277</v>
       </c>
       <c r="F54" t="s">
         <v>263</v>
@@ -3284,34 +3476,61 @@
         <v>268</v>
       </c>
     </row>
-    <row r="61" spans="1:7" hidden="1">
+    <row r="61" spans="1:7">
       <c r="A61" t="s">
         <v>158</v>
       </c>
+      <c r="B61" t="s">
+        <v>277</v>
+      </c>
+      <c r="C61" t="s">
+        <v>277</v>
+      </c>
       <c r="D61" t="s">
         <v>265</v>
       </c>
+      <c r="E61" t="s">
+        <v>277</v>
+      </c>
       <c r="F61" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="62" spans="1:7" hidden="1">
+    <row r="62" spans="1:7">
       <c r="A62" t="s">
         <v>159</v>
       </c>
+      <c r="B62" t="s">
+        <v>277</v>
+      </c>
+      <c r="C62" t="s">
+        <v>277</v>
+      </c>
       <c r="D62" t="s">
         <v>265</v>
       </c>
+      <c r="E62" t="s">
+        <v>277</v>
+      </c>
       <c r="F62" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="63" spans="1:7" hidden="1">
+    <row r="63" spans="1:7">
       <c r="A63" t="s">
         <v>160</v>
       </c>
+      <c r="B63" t="s">
+        <v>277</v>
+      </c>
+      <c r="C63" t="s">
+        <v>277</v>
+      </c>
       <c r="D63" t="s">
         <v>265</v>
+      </c>
+      <c r="E63" t="s">
+        <v>277</v>
       </c>
       <c r="F63" t="s">
         <v>263</v>
@@ -3387,11 +3606,7 @@
     </row>
   </sheetData>
   <autoFilter ref="D1:D67">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="赵育"/>
-      </filters>
-    </filterColumn>
+    <filterColumn colId="0"/>
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3400,7 +3615,6 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:G97"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
@@ -3431,7 +3645,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7" hidden="1">
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -3451,7 +3665,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="3" spans="1:7" hidden="1">
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -3471,7 +3685,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="4" spans="1:7" hidden="1">
+    <row r="4" spans="1:7">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -3495,17 +3709,8 @@
       <c r="A5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" t="s">
-        <v>269</v>
-      </c>
-      <c r="C5" t="s">
-        <v>269</v>
-      </c>
       <c r="D5" t="s">
         <v>263</v>
-      </c>
-      <c r="E5" t="s">
-        <v>269</v>
       </c>
       <c r="F5" t="s">
         <v>262</v>
@@ -3515,17 +3720,8 @@
       <c r="A6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" t="s">
-        <v>269</v>
-      </c>
-      <c r="C6" t="s">
-        <v>269</v>
-      </c>
       <c r="D6" t="s">
         <v>263</v>
-      </c>
-      <c r="E6" t="s">
-        <v>269</v>
       </c>
       <c r="F6" t="s">
         <v>262</v>
@@ -3535,17 +3731,8 @@
       <c r="A7" t="s">
         <v>10</v>
       </c>
-      <c r="B7" t="s">
-        <v>269</v>
-      </c>
-      <c r="C7" t="s">
-        <v>269</v>
-      </c>
       <c r="D7" t="s">
         <v>263</v>
-      </c>
-      <c r="E7" t="s">
-        <v>269</v>
       </c>
       <c r="F7" t="s">
         <v>262</v>
@@ -3555,17 +3742,8 @@
       <c r="A8" t="s">
         <v>11</v>
       </c>
-      <c r="B8" t="s">
-        <v>269</v>
-      </c>
-      <c r="C8" t="s">
-        <v>269</v>
-      </c>
       <c r="D8" t="s">
         <v>263</v>
-      </c>
-      <c r="E8" t="s">
-        <v>269</v>
       </c>
       <c r="F8" t="s">
         <v>262</v>
@@ -3575,17 +3753,8 @@
       <c r="A9" t="s">
         <v>12</v>
       </c>
-      <c r="B9" t="s">
-        <v>269</v>
-      </c>
-      <c r="C9" t="s">
-        <v>269</v>
-      </c>
       <c r="D9" t="s">
         <v>263</v>
-      </c>
-      <c r="E9" t="s">
-        <v>269</v>
       </c>
       <c r="F9" t="s">
         <v>262</v>
@@ -3595,17 +3764,8 @@
       <c r="A10" t="s">
         <v>13</v>
       </c>
-      <c r="B10" t="s">
-        <v>269</v>
-      </c>
-      <c r="C10" t="s">
-        <v>269</v>
-      </c>
       <c r="D10" t="s">
         <v>263</v>
-      </c>
-      <c r="E10" t="s">
-        <v>269</v>
       </c>
       <c r="F10" t="s">
         <v>262</v>
@@ -3615,17 +3775,8 @@
       <c r="A11" t="s">
         <v>14</v>
       </c>
-      <c r="B11" t="s">
-        <v>269</v>
-      </c>
-      <c r="C11" t="s">
-        <v>269</v>
-      </c>
       <c r="D11" t="s">
         <v>263</v>
-      </c>
-      <c r="E11" t="s">
-        <v>269</v>
       </c>
       <c r="F11" t="s">
         <v>262</v>
@@ -3635,17 +3786,8 @@
       <c r="A12" t="s">
         <v>15</v>
       </c>
-      <c r="B12" t="s">
-        <v>269</v>
-      </c>
-      <c r="C12" t="s">
-        <v>269</v>
-      </c>
       <c r="D12" t="s">
         <v>263</v>
-      </c>
-      <c r="E12" t="s">
-        <v>269</v>
       </c>
       <c r="F12" t="s">
         <v>262</v>
@@ -3655,49 +3797,25 @@
       <c r="A13" t="s">
         <v>16</v>
       </c>
-      <c r="B13" t="s">
-        <v>269</v>
-      </c>
-      <c r="C13" t="s">
-        <v>269</v>
-      </c>
       <c r="D13" t="s">
         <v>263</v>
       </c>
-      <c r="E13" t="s">
-        <v>269</v>
-      </c>
       <c r="F13" t="s">
         <v>262</v>
-      </c>
-      <c r="G13" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
         <v>17</v>
       </c>
-      <c r="B14" t="s">
-        <v>269</v>
-      </c>
-      <c r="C14" t="s">
-        <v>269</v>
-      </c>
       <c r="D14" t="s">
         <v>263</v>
       </c>
-      <c r="E14" t="s">
-        <v>269</v>
-      </c>
       <c r="F14" t="s">
         <v>262</v>
       </c>
-      <c r="G14" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" hidden="1">
+    </row>
+    <row r="15" spans="1:7">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -3717,7 +3835,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="16" spans="1:7" hidden="1">
+    <row r="16" spans="1:7">
       <c r="A16" t="s">
         <v>19</v>
       </c>
@@ -3737,7 +3855,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="17" spans="1:7" hidden="1">
+    <row r="17" spans="1:7">
       <c r="A17" t="s">
         <v>20</v>
       </c>
@@ -3757,7 +3875,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="18" spans="1:7" hidden="1">
+    <row r="18" spans="1:7">
       <c r="A18" t="s">
         <v>21</v>
       </c>
@@ -3781,17 +3899,8 @@
       <c r="A19" t="s">
         <v>22</v>
       </c>
-      <c r="B19" t="s">
-        <v>269</v>
-      </c>
-      <c r="C19" t="s">
-        <v>269</v>
-      </c>
       <c r="D19" t="s">
         <v>263</v>
-      </c>
-      <c r="E19" t="s">
-        <v>269</v>
       </c>
       <c r="F19" t="s">
         <v>262</v>
@@ -3801,17 +3910,8 @@
       <c r="A20" t="s">
         <v>23</v>
       </c>
-      <c r="B20" t="s">
-        <v>269</v>
-      </c>
-      <c r="C20" t="s">
-        <v>269</v>
-      </c>
       <c r="D20" t="s">
         <v>263</v>
-      </c>
-      <c r="E20" t="s">
-        <v>269</v>
       </c>
       <c r="F20" t="s">
         <v>262</v>
@@ -3821,17 +3921,8 @@
       <c r="A21" t="s">
         <v>24</v>
       </c>
-      <c r="B21" t="s">
-        <v>269</v>
-      </c>
-      <c r="C21" t="s">
-        <v>269</v>
-      </c>
       <c r="D21" t="s">
         <v>263</v>
-      </c>
-      <c r="E21" t="s">
-        <v>269</v>
       </c>
       <c r="F21" t="s">
         <v>262</v>
@@ -3841,23 +3932,14 @@
       <c r="A22" t="s">
         <v>25</v>
       </c>
-      <c r="B22" t="s">
-        <v>269</v>
-      </c>
-      <c r="C22" t="s">
-        <v>269</v>
-      </c>
       <c r="D22" t="s">
         <v>263</v>
       </c>
-      <c r="E22" t="s">
-        <v>269</v>
-      </c>
       <c r="F22" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="23" spans="1:7" hidden="1">
+    <row r="23" spans="1:7">
       <c r="A23" t="s">
         <v>26</v>
       </c>
@@ -3874,7 +3956,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="24" spans="1:7" hidden="1">
+    <row r="24" spans="1:7">
       <c r="A24" t="s">
         <v>27</v>
       </c>
@@ -3891,7 +3973,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="25" spans="1:7" hidden="1">
+    <row r="25" spans="1:7">
       <c r="A25" t="s">
         <v>28</v>
       </c>
@@ -3908,7 +3990,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="26" spans="1:7" hidden="1">
+    <row r="26" spans="1:7">
       <c r="A26" t="s">
         <v>29</v>
       </c>
@@ -3925,7 +4007,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="27" spans="1:7" hidden="1">
+    <row r="27" spans="1:7">
       <c r="A27" t="s">
         <v>30</v>
       </c>
@@ -3942,7 +4024,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="28" spans="1:7" hidden="1">
+    <row r="28" spans="1:7">
       <c r="A28" t="s">
         <v>31</v>
       </c>
@@ -3959,7 +4041,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="29" spans="1:7" hidden="1">
+    <row r="29" spans="1:7">
       <c r="A29" t="s">
         <v>32</v>
       </c>
@@ -3976,7 +4058,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="30" spans="1:7" hidden="1">
+    <row r="30" spans="1:7">
       <c r="A30" t="s">
         <v>33</v>
       </c>
@@ -3993,7 +4075,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="31" spans="1:7" hidden="1">
+    <row r="31" spans="1:7">
       <c r="A31" t="s">
         <v>34</v>
       </c>
@@ -4010,7 +4092,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="32" spans="1:7" hidden="1">
+    <row r="32" spans="1:7">
       <c r="A32" t="s">
         <v>35</v>
       </c>
@@ -4027,7 +4109,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="33" spans="1:7" hidden="1">
+    <row r="33" spans="1:7">
       <c r="A33" t="s">
         <v>36</v>
       </c>
@@ -4044,7 +4126,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="34" spans="1:7" hidden="1">
+    <row r="34" spans="1:7">
       <c r="A34" t="s">
         <v>37</v>
       </c>
@@ -4061,7 +4143,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="35" spans="1:7" hidden="1">
+    <row r="35" spans="1:7">
       <c r="A35" t="s">
         <v>38</v>
       </c>
@@ -4078,7 +4160,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="36" spans="1:7" hidden="1">
+    <row r="36" spans="1:7">
       <c r="A36" t="s">
         <v>39</v>
       </c>
@@ -4095,7 +4177,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="37" spans="1:7" hidden="1">
+    <row r="37" spans="1:7">
       <c r="A37" t="s">
         <v>40</v>
       </c>
@@ -4112,7 +4194,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="38" spans="1:7" hidden="1">
+    <row r="38" spans="1:7">
       <c r="A38" t="s">
         <v>41</v>
       </c>
@@ -4129,7 +4211,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="39" spans="1:7" hidden="1">
+    <row r="39" spans="1:7">
       <c r="A39" t="s">
         <v>42</v>
       </c>
@@ -4146,7 +4228,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="40" spans="1:7" hidden="1">
+    <row r="40" spans="1:7">
       <c r="A40" t="s">
         <v>43</v>
       </c>
@@ -4163,7 +4245,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="41" spans="1:7" hidden="1">
+    <row r="41" spans="1:7">
       <c r="A41" t="s">
         <v>44</v>
       </c>
@@ -4183,7 +4265,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="42" spans="1:7" hidden="1">
+    <row r="42" spans="1:7">
       <c r="A42" t="s">
         <v>45</v>
       </c>
@@ -4203,7 +4285,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="43" spans="1:7" hidden="1">
+    <row r="43" spans="1:7">
       <c r="A43" t="s">
         <v>46</v>
       </c>
@@ -4223,7 +4305,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="44" spans="1:7" hidden="1">
+    <row r="44" spans="1:7">
       <c r="A44" t="s">
         <v>47</v>
       </c>
@@ -4243,7 +4325,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="45" spans="1:7" hidden="1">
+    <row r="45" spans="1:7">
       <c r="A45" t="s">
         <v>48</v>
       </c>
@@ -4263,7 +4345,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="46" spans="1:7" hidden="1">
+    <row r="46" spans="1:7">
       <c r="A46" t="s">
         <v>49</v>
       </c>
@@ -4287,17 +4369,8 @@
       <c r="A47" t="s">
         <v>50</v>
       </c>
-      <c r="B47" t="s">
-        <v>269</v>
-      </c>
-      <c r="C47" t="s">
-        <v>269</v>
-      </c>
       <c r="D47" t="s">
         <v>263</v>
-      </c>
-      <c r="E47" t="s">
-        <v>269</v>
       </c>
       <c r="F47" t="s">
         <v>262</v>
@@ -4307,46 +4380,25 @@
       <c r="A48" t="s">
         <v>51</v>
       </c>
-      <c r="B48" t="s">
-        <v>269</v>
-      </c>
-      <c r="C48" t="s">
-        <v>269</v>
-      </c>
       <c r="D48" t="s">
         <v>263</v>
       </c>
-      <c r="E48" t="s">
-        <v>269</v>
-      </c>
       <c r="F48" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="49" spans="1:7">
+    <row r="49" spans="1:6">
       <c r="A49" t="s">
         <v>52</v>
       </c>
-      <c r="B49" t="s">
-        <v>270</v>
-      </c>
-      <c r="C49" t="s">
-        <v>270</v>
-      </c>
       <c r="D49" t="s">
         <v>263</v>
       </c>
-      <c r="E49" t="s">
-        <v>270</v>
-      </c>
       <c r="F49" t="s">
         <v>262</v>
       </c>
-      <c r="G49" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" hidden="1">
+    </row>
+    <row r="50" spans="1:6">
       <c r="A50" t="s">
         <v>53</v>
       </c>
@@ -4357,7 +4409,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="51" spans="1:7" hidden="1">
+    <row r="51" spans="1:6">
       <c r="A51" t="s">
         <v>54</v>
       </c>
@@ -4368,7 +4420,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="52" spans="1:7" hidden="1">
+    <row r="52" spans="1:6">
       <c r="A52" t="s">
         <v>55</v>
       </c>
@@ -4379,7 +4431,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="53" spans="1:7" hidden="1">
+    <row r="53" spans="1:6">
       <c r="A53" t="s">
         <v>56</v>
       </c>
@@ -4390,7 +4442,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="54" spans="1:7" hidden="1">
+    <row r="54" spans="1:6">
       <c r="A54" t="s">
         <v>57</v>
       </c>
@@ -4401,7 +4453,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="55" spans="1:7" hidden="1">
+    <row r="55" spans="1:6">
       <c r="A55" t="s">
         <v>58</v>
       </c>
@@ -4412,7 +4464,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="56" spans="1:7" hidden="1">
+    <row r="56" spans="1:6">
       <c r="A56" t="s">
         <v>59</v>
       </c>
@@ -4423,7 +4475,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="57" spans="1:7" hidden="1">
+    <row r="57" spans="1:6">
       <c r="A57" t="s">
         <v>60</v>
       </c>
@@ -4434,7 +4486,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="58" spans="1:7" hidden="1">
+    <row r="58" spans="1:6">
       <c r="A58" t="s">
         <v>61</v>
       </c>
@@ -4445,7 +4497,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="59" spans="1:7" hidden="1">
+    <row r="59" spans="1:6">
       <c r="A59" t="s">
         <v>62</v>
       </c>
@@ -4456,7 +4508,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="60" spans="1:7" hidden="1">
+    <row r="60" spans="1:6">
       <c r="A60" t="s">
         <v>63</v>
       </c>
@@ -4467,7 +4519,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="61" spans="1:7" hidden="1">
+    <row r="61" spans="1:6">
       <c r="A61" t="s">
         <v>64</v>
       </c>
@@ -4478,7 +4530,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="62" spans="1:7" hidden="1">
+    <row r="62" spans="1:6">
       <c r="A62" t="s">
         <v>65</v>
       </c>
@@ -4489,7 +4541,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="63" spans="1:7" hidden="1">
+    <row r="63" spans="1:6">
       <c r="A63" t="s">
         <v>66</v>
       </c>
@@ -4500,7 +4552,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="64" spans="1:7" hidden="1">
+    <row r="64" spans="1:6">
       <c r="A64" t="s">
         <v>67</v>
       </c>
@@ -4511,7 +4563,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="65" spans="1:7" hidden="1">
+    <row r="65" spans="1:7">
       <c r="A65" t="s">
         <v>68</v>
       </c>
@@ -4522,7 +4574,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="66" spans="1:7" hidden="1">
+    <row r="66" spans="1:7">
       <c r="A66" t="s">
         <v>69</v>
       </c>
@@ -4533,7 +4585,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="67" spans="1:7" hidden="1">
+    <row r="67" spans="1:7">
       <c r="A67" t="s">
         <v>70</v>
       </c>
@@ -4544,7 +4596,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="68" spans="1:7" hidden="1">
+    <row r="68" spans="1:7">
       <c r="A68" t="s">
         <v>71</v>
       </c>
@@ -4555,7 +4607,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="69" spans="1:7" hidden="1">
+    <row r="69" spans="1:7">
       <c r="A69" t="s">
         <v>72</v>
       </c>
@@ -4566,7 +4618,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="70" spans="1:7" hidden="1">
+    <row r="70" spans="1:7">
       <c r="A70" t="s">
         <v>73</v>
       </c>
@@ -4577,7 +4629,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="71" spans="1:7" hidden="1">
+    <row r="71" spans="1:7">
       <c r="A71" t="s">
         <v>74</v>
       </c>
@@ -4588,7 +4640,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="72" spans="1:7" hidden="1">
+    <row r="72" spans="1:7">
       <c r="A72" t="s">
         <v>75</v>
       </c>
@@ -4599,7 +4651,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="73" spans="1:7" hidden="1">
+    <row r="73" spans="1:7">
       <c r="A73" t="s">
         <v>76</v>
       </c>
@@ -4619,7 +4671,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="74" spans="1:7" hidden="1">
+    <row r="74" spans="1:7">
       <c r="A74" t="s">
         <v>77</v>
       </c>
@@ -4642,7 +4694,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="75" spans="1:7" hidden="1">
+    <row r="75" spans="1:7">
       <c r="A75" t="s">
         <v>78</v>
       </c>
@@ -4665,7 +4717,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="76" spans="1:7" hidden="1">
+    <row r="76" spans="1:7">
       <c r="A76" t="s">
         <v>79</v>
       </c>
@@ -4688,7 +4740,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="77" spans="1:7" hidden="1">
+    <row r="77" spans="1:7">
       <c r="A77" t="s">
         <v>80</v>
       </c>
@@ -4711,7 +4763,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="78" spans="1:7" hidden="1">
+    <row r="78" spans="1:7">
       <c r="A78" t="s">
         <v>81</v>
       </c>
@@ -4731,7 +4783,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="79" spans="1:7" hidden="1">
+    <row r="79" spans="1:7">
       <c r="A79" t="s">
         <v>82</v>
       </c>
@@ -4742,7 +4794,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="80" spans="1:7" hidden="1">
+    <row r="80" spans="1:7">
       <c r="A80" t="s">
         <v>83</v>
       </c>
@@ -4753,7 +4805,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="81" spans="1:7" hidden="1">
+    <row r="81" spans="1:7">
       <c r="A81" t="s">
         <v>84</v>
       </c>
@@ -4764,7 +4816,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="82" spans="1:7" hidden="1">
+    <row r="82" spans="1:7">
       <c r="A82" t="s">
         <v>85</v>
       </c>
@@ -4775,7 +4827,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="83" spans="1:7" hidden="1">
+    <row r="83" spans="1:7">
       <c r="A83" t="s">
         <v>86</v>
       </c>
@@ -4786,7 +4838,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="84" spans="1:7" hidden="1">
+    <row r="84" spans="1:7">
       <c r="A84" t="s">
         <v>87</v>
       </c>
@@ -4797,7 +4849,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="85" spans="1:7" hidden="1">
+    <row r="85" spans="1:7">
       <c r="A85" t="s">
         <v>88</v>
       </c>
@@ -4814,7 +4866,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="86" spans="1:7" hidden="1">
+    <row r="86" spans="1:7">
       <c r="A86" t="s">
         <v>89</v>
       </c>
@@ -4831,7 +4883,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="87" spans="1:7" hidden="1">
+    <row r="87" spans="1:7">
       <c r="A87" t="s">
         <v>90</v>
       </c>
@@ -4848,7 +4900,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="88" spans="1:7" hidden="1">
+    <row r="88" spans="1:7">
       <c r="A88" t="s">
         <v>91</v>
       </c>
@@ -4865,7 +4917,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="89" spans="1:7" hidden="1">
+    <row r="89" spans="1:7">
       <c r="A89" t="s">
         <v>92</v>
       </c>
@@ -4882,7 +4934,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="90" spans="1:7" hidden="1">
+    <row r="90" spans="1:7">
       <c r="A90" t="s">
         <v>93</v>
       </c>
@@ -4899,7 +4951,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="91" spans="1:7" hidden="1">
+    <row r="91" spans="1:7">
       <c r="A91" t="s">
         <v>94</v>
       </c>
@@ -4910,7 +4962,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="92" spans="1:7" hidden="1">
+    <row r="92" spans="1:7">
       <c r="A92" t="s">
         <v>95</v>
       </c>
@@ -4921,7 +4973,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="93" spans="1:7" hidden="1">
+    <row r="93" spans="1:7">
       <c r="A93" t="s">
         <v>96</v>
       </c>
@@ -4932,7 +4984,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="94" spans="1:7" hidden="1">
+    <row r="94" spans="1:7">
       <c r="A94" t="s">
         <v>97</v>
       </c>
@@ -4949,7 +5001,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="95" spans="1:7" hidden="1">
+    <row r="95" spans="1:7">
       <c r="A95" t="s">
         <v>98</v>
       </c>
@@ -4966,7 +5018,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="96" spans="1:7" hidden="1">
+    <row r="96" spans="1:7">
       <c r="A96" t="s">
         <v>99</v>
       </c>
@@ -4983,7 +5035,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="97" spans="1:7" hidden="1">
+    <row r="97" spans="1:7">
       <c r="A97" t="s">
         <v>100</v>
       </c>
@@ -5007,12 +5059,8 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G97">
-    <filterColumn colId="3">
-      <filters>
-        <filter val="赵小妮"/>
-      </filters>
-    </filterColumn>
+  <autoFilter ref="D1:D97">
+    <filterColumn colId="0"/>
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/internal_doc/05.测试设计/story/事务支持RC隔离级别/事务自动化用例跟踪表.xlsx
+++ b/internal_doc/05.测试设计/story/事务支持RC隔离级别/事务自动化用例跟踪表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
   </bookViews>
   <sheets>
     <sheet name="RU" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1101" uniqueCount="283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1176" uniqueCount="284">
   <si>
     <t>用例编号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -912,6 +912,10 @@
   </si>
   <si>
     <t>seqDB-17102</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>是</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1583,10 +1587,13 @@
         <v>265</v>
       </c>
       <c r="C23" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D23" t="s">
         <v>261</v>
+      </c>
+      <c r="E23" t="s">
+        <v>283</v>
       </c>
       <c r="F23" t="s">
         <v>277</v>
@@ -1600,10 +1607,13 @@
         <v>265</v>
       </c>
       <c r="C24" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D24" t="s">
         <v>261</v>
+      </c>
+      <c r="E24" t="s">
+        <v>283</v>
       </c>
       <c r="F24" t="s">
         <v>277</v>
@@ -1617,10 +1627,13 @@
         <v>265</v>
       </c>
       <c r="C25" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D25" t="s">
         <v>261</v>
+      </c>
+      <c r="E25" t="s">
+        <v>283</v>
       </c>
       <c r="F25" t="s">
         <v>277</v>
@@ -1634,10 +1647,13 @@
         <v>265</v>
       </c>
       <c r="C26" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D26" t="s">
         <v>261</v>
+      </c>
+      <c r="E26" t="s">
+        <v>283</v>
       </c>
       <c r="F26" t="s">
         <v>277</v>
@@ -1651,10 +1667,13 @@
         <v>265</v>
       </c>
       <c r="C27" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D27" t="s">
         <v>261</v>
+      </c>
+      <c r="E27" t="s">
+        <v>283</v>
       </c>
       <c r="F27" t="s">
         <v>277</v>
@@ -1668,10 +1687,13 @@
         <v>265</v>
       </c>
       <c r="C28" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D28" t="s">
         <v>261</v>
+      </c>
+      <c r="E28" t="s">
+        <v>283</v>
       </c>
       <c r="F28" t="s">
         <v>277</v>
@@ -1685,10 +1707,13 @@
         <v>265</v>
       </c>
       <c r="C29" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D29" t="s">
         <v>261</v>
+      </c>
+      <c r="E29" t="s">
+        <v>283</v>
       </c>
       <c r="F29" t="s">
         <v>277</v>
@@ -1702,10 +1727,13 @@
         <v>265</v>
       </c>
       <c r="C30" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D30" t="s">
         <v>261</v>
+      </c>
+      <c r="E30" t="s">
+        <v>283</v>
       </c>
       <c r="F30" t="s">
         <v>277</v>
@@ -1719,10 +1747,13 @@
         <v>265</v>
       </c>
       <c r="C31" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D31" t="s">
         <v>261</v>
+      </c>
+      <c r="E31" t="s">
+        <v>283</v>
       </c>
       <c r="F31" t="s">
         <v>277</v>
@@ -1736,10 +1767,13 @@
         <v>265</v>
       </c>
       <c r="C32" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D32" t="s">
         <v>261</v>
+      </c>
+      <c r="E32" t="s">
+        <v>283</v>
       </c>
       <c r="F32" t="s">
         <v>277</v>
@@ -1753,10 +1787,13 @@
         <v>265</v>
       </c>
       <c r="C33" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D33" t="s">
         <v>261</v>
+      </c>
+      <c r="E33" t="s">
+        <v>283</v>
       </c>
       <c r="F33" t="s">
         <v>277</v>
@@ -1770,10 +1807,13 @@
         <v>265</v>
       </c>
       <c r="C34" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D34" t="s">
         <v>261</v>
+      </c>
+      <c r="E34" t="s">
+        <v>283</v>
       </c>
       <c r="F34" t="s">
         <v>277</v>
@@ -1787,10 +1827,13 @@
         <v>265</v>
       </c>
       <c r="C35" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D35" t="s">
         <v>261</v>
+      </c>
+      <c r="E35" t="s">
+        <v>283</v>
       </c>
       <c r="F35" t="s">
         <v>277</v>
@@ -1804,10 +1847,13 @@
         <v>265</v>
       </c>
       <c r="C36" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D36" t="s">
         <v>261</v>
+      </c>
+      <c r="E36" t="s">
+        <v>283</v>
       </c>
       <c r="F36" t="s">
         <v>277</v>
@@ -1821,10 +1867,13 @@
         <v>265</v>
       </c>
       <c r="C37" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D37" t="s">
         <v>261</v>
+      </c>
+      <c r="E37" t="s">
+        <v>283</v>
       </c>
       <c r="F37" t="s">
         <v>277</v>
@@ -1838,10 +1887,13 @@
         <v>265</v>
       </c>
       <c r="C38" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D38" t="s">
         <v>261</v>
+      </c>
+      <c r="E38" t="s">
+        <v>283</v>
       </c>
       <c r="F38" t="s">
         <v>277</v>
@@ -1855,10 +1907,13 @@
         <v>265</v>
       </c>
       <c r="C39" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D39" t="s">
         <v>261</v>
+      </c>
+      <c r="E39" t="s">
+        <v>283</v>
       </c>
       <c r="F39" t="s">
         <v>277</v>
@@ -1872,10 +1927,13 @@
         <v>265</v>
       </c>
       <c r="C40" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D40" t="s">
         <v>261</v>
+      </c>
+      <c r="E40" t="s">
+        <v>283</v>
       </c>
       <c r="F40" t="s">
         <v>277</v>
@@ -2429,10 +2487,13 @@
         <v>265</v>
       </c>
       <c r="C83" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D83" t="s">
         <v>261</v>
+      </c>
+      <c r="E83" t="s">
+        <v>283</v>
       </c>
       <c r="F83" t="s">
         <v>277</v>
@@ -2446,10 +2507,13 @@
         <v>265</v>
       </c>
       <c r="C84" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D84" t="s">
         <v>261</v>
+      </c>
+      <c r="E84" t="s">
+        <v>283</v>
       </c>
       <c r="F84" t="s">
         <v>277</v>
@@ -2463,10 +2527,13 @@
         <v>265</v>
       </c>
       <c r="C85" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D85" t="s">
         <v>261</v>
+      </c>
+      <c r="E85" t="s">
+        <v>283</v>
       </c>
       <c r="F85" t="s">
         <v>277</v>
@@ -2480,10 +2547,13 @@
         <v>265</v>
       </c>
       <c r="C86" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D86" t="s">
         <v>261</v>
+      </c>
+      <c r="E86" t="s">
+        <v>283</v>
       </c>
       <c r="F86" t="s">
         <v>277</v>
@@ -2497,10 +2567,13 @@
         <v>265</v>
       </c>
       <c r="C87" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D87" t="s">
         <v>261</v>
+      </c>
+      <c r="E87" t="s">
+        <v>283</v>
       </c>
       <c r="F87" t="s">
         <v>277</v>
@@ -2514,10 +2587,13 @@
         <v>265</v>
       </c>
       <c r="C88" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D88" t="s">
         <v>261</v>
+      </c>
+      <c r="E88" t="s">
+        <v>283</v>
       </c>
       <c r="F88" t="s">
         <v>277</v>
@@ -2564,10 +2640,13 @@
         <v>265</v>
       </c>
       <c r="C92" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D92" t="s">
         <v>261</v>
+      </c>
+      <c r="E92" t="s">
+        <v>283</v>
       </c>
       <c r="F92" t="s">
         <v>277</v>
@@ -2581,10 +2660,13 @@
         <v>265</v>
       </c>
       <c r="C93" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D93" t="s">
         <v>261</v>
+      </c>
+      <c r="E93" t="s">
+        <v>283</v>
       </c>
       <c r="F93" t="s">
         <v>277</v>
@@ -2598,10 +2680,13 @@
         <v>265</v>
       </c>
       <c r="C94" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D94" t="s">
         <v>261</v>
+      </c>
+      <c r="E94" t="s">
+        <v>283</v>
       </c>
       <c r="F94" t="s">
         <v>277</v>
@@ -2617,12 +2702,12 @@
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:G67"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
@@ -2652,7 +2737,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7" hidden="1">
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
         <v>100</v>
       </c>
@@ -2663,7 +2748,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="3" spans="1:7" hidden="1">
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>101</v>
       </c>
@@ -2674,7 +2759,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="4" spans="1:7" hidden="1">
+    <row r="4" spans="1:7">
       <c r="A4" t="s">
         <v>102</v>
       </c>
@@ -2685,117 +2770,207 @@
         <v>264</v>
       </c>
     </row>
-    <row r="5" spans="1:7" hidden="1">
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
         <v>103</v>
       </c>
+      <c r="B5" t="s">
+        <v>283</v>
+      </c>
+      <c r="C5" t="s">
+        <v>283</v>
+      </c>
       <c r="D5" t="s">
         <v>262</v>
       </c>
+      <c r="E5" t="s">
+        <v>283</v>
+      </c>
       <c r="F5" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="6" spans="1:7" hidden="1">
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
         <v>104</v>
       </c>
+      <c r="B6" t="s">
+        <v>283</v>
+      </c>
+      <c r="C6" t="s">
+        <v>283</v>
+      </c>
       <c r="D6" t="s">
         <v>262</v>
       </c>
+      <c r="E6" t="s">
+        <v>283</v>
+      </c>
       <c r="F6" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="7" spans="1:7" hidden="1">
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
         <v>105</v>
       </c>
+      <c r="B7" t="s">
+        <v>283</v>
+      </c>
+      <c r="C7" t="s">
+        <v>283</v>
+      </c>
       <c r="D7" t="s">
         <v>262</v>
       </c>
+      <c r="E7" t="s">
+        <v>283</v>
+      </c>
       <c r="F7" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="8" spans="1:7" hidden="1">
+    <row r="8" spans="1:7">
       <c r="A8" t="s">
         <v>106</v>
       </c>
+      <c r="B8" t="s">
+        <v>283</v>
+      </c>
+      <c r="C8" t="s">
+        <v>283</v>
+      </c>
       <c r="D8" t="s">
         <v>262</v>
       </c>
+      <c r="E8" t="s">
+        <v>283</v>
+      </c>
       <c r="F8" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="9" spans="1:7" hidden="1">
+    <row r="9" spans="1:7">
       <c r="A9" t="s">
         <v>107</v>
       </c>
+      <c r="B9" t="s">
+        <v>283</v>
+      </c>
+      <c r="C9" t="s">
+        <v>283</v>
+      </c>
       <c r="D9" t="s">
         <v>262</v>
       </c>
+      <c r="E9" t="s">
+        <v>283</v>
+      </c>
       <c r="F9" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="10" spans="1:7" hidden="1">
+    <row r="10" spans="1:7">
       <c r="A10" t="s">
         <v>108</v>
       </c>
+      <c r="B10" t="s">
+        <v>283</v>
+      </c>
+      <c r="C10" t="s">
+        <v>283</v>
+      </c>
       <c r="D10" t="s">
         <v>262</v>
       </c>
+      <c r="E10" t="s">
+        <v>283</v>
+      </c>
       <c r="F10" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="11" spans="1:7" hidden="1">
+    <row r="11" spans="1:7">
       <c r="A11" t="s">
         <v>109</v>
       </c>
+      <c r="B11" t="s">
+        <v>283</v>
+      </c>
+      <c r="C11" t="s">
+        <v>283</v>
+      </c>
       <c r="D11" t="s">
         <v>262</v>
       </c>
+      <c r="E11" t="s">
+        <v>283</v>
+      </c>
       <c r="F11" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="12" spans="1:7" hidden="1">
+    <row r="12" spans="1:7">
       <c r="A12" t="s">
         <v>110</v>
       </c>
+      <c r="B12" t="s">
+        <v>283</v>
+      </c>
+      <c r="C12" t="s">
+        <v>283</v>
+      </c>
       <c r="D12" t="s">
         <v>262</v>
       </c>
+      <c r="E12" t="s">
+        <v>283</v>
+      </c>
       <c r="F12" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="13" spans="1:7" hidden="1">
+    <row r="13" spans="1:7">
       <c r="A13" t="s">
         <v>111</v>
       </c>
+      <c r="B13" t="s">
+        <v>283</v>
+      </c>
+      <c r="C13" t="s">
+        <v>283</v>
+      </c>
       <c r="D13" t="s">
         <v>262</v>
       </c>
+      <c r="E13" t="s">
+        <v>283</v>
+      </c>
       <c r="F13" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="14" spans="1:7" hidden="1">
+    <row r="14" spans="1:7">
       <c r="A14" t="s">
         <v>112</v>
       </c>
+      <c r="B14" t="s">
+        <v>283</v>
+      </c>
+      <c r="C14" t="s">
+        <v>283</v>
+      </c>
       <c r="D14" t="s">
         <v>262</v>
       </c>
+      <c r="E14" t="s">
+        <v>283</v>
+      </c>
       <c r="F14" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="15" spans="1:7" hidden="1">
+    <row r="15" spans="1:7">
       <c r="A15" t="s">
         <v>113</v>
       </c>
@@ -2806,7 +2981,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="16" spans="1:7" hidden="1">
+    <row r="16" spans="1:7">
       <c r="A16" t="s">
         <v>114</v>
       </c>
@@ -2817,7 +2992,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="17" spans="1:6" hidden="1">
+    <row r="17" spans="1:6">
       <c r="A17" t="s">
         <v>115</v>
       </c>
@@ -2828,7 +3003,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="18" spans="1:6" hidden="1">
+    <row r="18" spans="1:6">
       <c r="A18" t="s">
         <v>116</v>
       </c>
@@ -2839,45 +3014,81 @@
         <v>264</v>
       </c>
     </row>
-    <row r="19" spans="1:6" hidden="1">
+    <row r="19" spans="1:6">
       <c r="A19" t="s">
         <v>117</v>
       </c>
+      <c r="B19" t="s">
+        <v>283</v>
+      </c>
+      <c r="C19" t="s">
+        <v>283</v>
+      </c>
       <c r="D19" t="s">
         <v>262</v>
       </c>
+      <c r="E19" t="s">
+        <v>283</v>
+      </c>
       <c r="F19" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="20" spans="1:6" hidden="1">
+    <row r="20" spans="1:6">
       <c r="A20" t="s">
         <v>118</v>
       </c>
+      <c r="B20" t="s">
+        <v>283</v>
+      </c>
+      <c r="C20" t="s">
+        <v>283</v>
+      </c>
       <c r="D20" t="s">
         <v>262</v>
       </c>
+      <c r="E20" t="s">
+        <v>283</v>
+      </c>
       <c r="F20" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="21" spans="1:6" hidden="1">
+    <row r="21" spans="1:6">
       <c r="A21" t="s">
         <v>119</v>
       </c>
+      <c r="B21" t="s">
+        <v>283</v>
+      </c>
+      <c r="C21" t="s">
+        <v>283</v>
+      </c>
       <c r="D21" t="s">
         <v>262</v>
       </c>
+      <c r="E21" t="s">
+        <v>283</v>
+      </c>
       <c r="F21" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="22" spans="1:6" hidden="1">
+    <row r="22" spans="1:6">
       <c r="A22" t="s">
         <v>120</v>
       </c>
+      <c r="B22" t="s">
+        <v>283</v>
+      </c>
+      <c r="C22" t="s">
+        <v>283</v>
+      </c>
       <c r="D22" t="s">
         <v>262</v>
+      </c>
+      <c r="E22" t="s">
+        <v>283</v>
       </c>
       <c r="F22" t="s">
         <v>263</v>
@@ -2888,7 +3099,7 @@
         <v>121</v>
       </c>
       <c r="B23" t="s">
-        <v>265</v>
+        <v>283</v>
       </c>
       <c r="C23" t="s">
         <v>266</v>
@@ -3070,7 +3281,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="34" spans="1:7" hidden="1">
+    <row r="34" spans="1:7">
       <c r="A34" t="s">
         <v>132</v>
       </c>
@@ -3081,7 +3292,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="35" spans="1:7" hidden="1">
+    <row r="35" spans="1:7">
       <c r="A35" t="s">
         <v>133</v>
       </c>
@@ -3092,7 +3303,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="36" spans="1:7" hidden="1">
+    <row r="36" spans="1:7">
       <c r="A36" t="s">
         <v>134</v>
       </c>
@@ -3103,7 +3314,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="37" spans="1:7" hidden="1">
+    <row r="37" spans="1:7">
       <c r="A37" t="s">
         <v>135</v>
       </c>
@@ -3114,7 +3325,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="38" spans="1:7" hidden="1">
+    <row r="38" spans="1:7">
       <c r="A38" t="s">
         <v>136</v>
       </c>
@@ -3125,7 +3336,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="39" spans="1:7" hidden="1">
+    <row r="39" spans="1:7">
       <c r="A39" t="s">
         <v>137</v>
       </c>
@@ -3136,23 +3347,41 @@
         <v>264</v>
       </c>
     </row>
-    <row r="40" spans="1:7" hidden="1">
+    <row r="40" spans="1:7">
       <c r="A40" t="s">
         <v>138</v>
       </c>
+      <c r="B40" t="s">
+        <v>283</v>
+      </c>
+      <c r="C40" t="s">
+        <v>283</v>
+      </c>
       <c r="D40" t="s">
         <v>262</v>
       </c>
+      <c r="E40" t="s">
+        <v>283</v>
+      </c>
       <c r="F40" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="41" spans="1:7" hidden="1">
+    <row r="41" spans="1:7">
       <c r="A41" t="s">
         <v>139</v>
       </c>
+      <c r="B41" t="s">
+        <v>283</v>
+      </c>
+      <c r="C41" t="s">
+        <v>283</v>
+      </c>
       <c r="D41" t="s">
         <v>262</v>
+      </c>
+      <c r="E41" t="s">
+        <v>283</v>
       </c>
       <c r="F41" t="s">
         <v>263</v>
@@ -3289,7 +3518,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="49" spans="1:7" hidden="1">
+    <row r="49" spans="1:7">
       <c r="A49" t="s">
         <v>144</v>
       </c>
@@ -3309,7 +3538,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="50" spans="1:7" hidden="1">
+    <row r="50" spans="1:7">
       <c r="A50" t="s">
         <v>145</v>
       </c>
@@ -3329,7 +3558,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="51" spans="1:7" hidden="1">
+    <row r="51" spans="1:7">
       <c r="A51" t="s">
         <v>146</v>
       </c>
@@ -3349,7 +3578,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="52" spans="1:7" hidden="1">
+    <row r="52" spans="1:7">
       <c r="A52" t="s">
         <v>147</v>
       </c>
@@ -3369,7 +3598,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="53" spans="1:7" hidden="1">
+    <row r="53" spans="1:7">
       <c r="A53" t="s">
         <v>148</v>
       </c>
@@ -3389,7 +3618,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="54" spans="1:7" hidden="1">
+    <row r="54" spans="1:7">
       <c r="A54" t="s">
         <v>149</v>
       </c>
@@ -3520,7 +3749,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="61" spans="1:7" hidden="1">
+    <row r="61" spans="1:7">
       <c r="A61" t="s">
         <v>157</v>
       </c>
@@ -3540,7 +3769,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="62" spans="1:7" hidden="1">
+    <row r="62" spans="1:7">
       <c r="A62" t="s">
         <v>158</v>
       </c>
@@ -3560,7 +3789,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="63" spans="1:7" hidden="1">
+    <row r="63" spans="1:7">
       <c r="A63" t="s">
         <v>159</v>
       </c>
@@ -3650,11 +3879,7 @@
     </row>
   </sheetData>
   <autoFilter ref="D1:D67">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="赵育"/>
-      </filters>
-    </filterColumn>
+    <filterColumn colId="0"/>
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/internal_doc/05.测试设计/story/事务支持RC隔离级别/事务自动化用例跟踪表.xlsx
+++ b/internal_doc/05.测试设计/story/事务支持RC隔离级别/事务自动化用例跟踪表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="RU" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1176" uniqueCount="284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1177" uniqueCount="284">
   <si>
     <t>用例编号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -3654,6 +3654,9 @@
       <c r="F55" t="s">
         <v>278</v>
       </c>
+      <c r="G55" t="s">
+        <v>279</v>
+      </c>
     </row>
     <row r="56" spans="1:7">
       <c r="A56" t="s">

--- a/internal_doc/05.测试设计/story/事务支持RC隔离级别/事务自动化用例跟踪表.xlsx
+++ b/internal_doc/05.测试设计/story/事务支持RC隔离级别/事务自动化用例跟踪表.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1177" uniqueCount="284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1197" uniqueCount="286">
   <si>
     <t>用例编号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -916,6 +916,14 @@
   </si>
   <si>
     <t>是</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>是</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>否</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2708,6 +2716,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:G67"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
@@ -2737,7 +2746,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" hidden="1">
       <c r="A2" t="s">
         <v>100</v>
       </c>
@@ -2748,7 +2757,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" hidden="1">
       <c r="A3" t="s">
         <v>101</v>
       </c>
@@ -2759,7 +2768,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" hidden="1">
       <c r="A4" t="s">
         <v>102</v>
       </c>
@@ -2770,7 +2779,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" hidden="1">
       <c r="A5" t="s">
         <v>103</v>
       </c>
@@ -2790,7 +2799,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" hidden="1">
       <c r="A6" t="s">
         <v>104</v>
       </c>
@@ -2810,7 +2819,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" hidden="1">
       <c r="A7" t="s">
         <v>105</v>
       </c>
@@ -2830,7 +2839,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" hidden="1">
       <c r="A8" t="s">
         <v>106</v>
       </c>
@@ -2850,7 +2859,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" hidden="1">
       <c r="A9" t="s">
         <v>107</v>
       </c>
@@ -2870,7 +2879,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" hidden="1">
       <c r="A10" t="s">
         <v>108</v>
       </c>
@@ -2890,7 +2899,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" hidden="1">
       <c r="A11" t="s">
         <v>109</v>
       </c>
@@ -2910,7 +2919,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" hidden="1">
       <c r="A12" t="s">
         <v>110</v>
       </c>
@@ -2930,7 +2939,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" hidden="1">
       <c r="A13" t="s">
         <v>111</v>
       </c>
@@ -2950,7 +2959,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" hidden="1">
       <c r="A14" t="s">
         <v>112</v>
       </c>
@@ -2970,7 +2979,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" hidden="1">
       <c r="A15" t="s">
         <v>113</v>
       </c>
@@ -2981,7 +2990,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" hidden="1">
       <c r="A16" t="s">
         <v>114</v>
       </c>
@@ -2992,7 +3001,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" hidden="1">
       <c r="A17" t="s">
         <v>115</v>
       </c>
@@ -3003,7 +3012,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" hidden="1">
       <c r="A18" t="s">
         <v>116</v>
       </c>
@@ -3014,7 +3023,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:6" hidden="1">
       <c r="A19" t="s">
         <v>117</v>
       </c>
@@ -3034,7 +3043,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:6" hidden="1">
       <c r="A20" t="s">
         <v>118</v>
       </c>
@@ -3054,7 +3063,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:6" hidden="1">
       <c r="A21" t="s">
         <v>119</v>
       </c>
@@ -3074,7 +3083,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:6" hidden="1">
       <c r="A22" t="s">
         <v>120</v>
       </c>
@@ -3102,10 +3111,13 @@
         <v>283</v>
       </c>
       <c r="C23" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D23" t="s">
         <v>261</v>
+      </c>
+      <c r="E23" t="s">
+        <v>284</v>
       </c>
       <c r="F23" t="s">
         <v>278</v>
@@ -3119,10 +3131,13 @@
         <v>265</v>
       </c>
       <c r="C24" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D24" t="s">
         <v>261</v>
+      </c>
+      <c r="E24" t="s">
+        <v>284</v>
       </c>
       <c r="F24" t="s">
         <v>278</v>
@@ -3136,10 +3151,13 @@
         <v>265</v>
       </c>
       <c r="C25" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D25" t="s">
         <v>261</v>
+      </c>
+      <c r="E25" t="s">
+        <v>284</v>
       </c>
       <c r="F25" t="s">
         <v>278</v>
@@ -3153,10 +3171,13 @@
         <v>265</v>
       </c>
       <c r="C26" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D26" t="s">
         <v>261</v>
+      </c>
+      <c r="E26" t="s">
+        <v>284</v>
       </c>
       <c r="F26" t="s">
         <v>278</v>
@@ -3170,10 +3191,13 @@
         <v>265</v>
       </c>
       <c r="C27" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D27" t="s">
         <v>261</v>
+      </c>
+      <c r="E27" t="s">
+        <v>284</v>
       </c>
       <c r="F27" t="s">
         <v>278</v>
@@ -3187,10 +3211,13 @@
         <v>265</v>
       </c>
       <c r="C28" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D28" t="s">
         <v>261</v>
+      </c>
+      <c r="E28" t="s">
+        <v>284</v>
       </c>
       <c r="F28" t="s">
         <v>278</v>
@@ -3204,10 +3231,13 @@
         <v>265</v>
       </c>
       <c r="C29" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D29" t="s">
         <v>261</v>
+      </c>
+      <c r="E29" t="s">
+        <v>284</v>
       </c>
       <c r="F29" t="s">
         <v>278</v>
@@ -3221,10 +3251,13 @@
         <v>265</v>
       </c>
       <c r="C30" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D30" t="s">
         <v>261</v>
+      </c>
+      <c r="E30" t="s">
+        <v>284</v>
       </c>
       <c r="F30" t="s">
         <v>278</v>
@@ -3238,10 +3271,13 @@
         <v>265</v>
       </c>
       <c r="C31" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D31" t="s">
         <v>261</v>
+      </c>
+      <c r="E31" t="s">
+        <v>284</v>
       </c>
       <c r="F31" t="s">
         <v>278</v>
@@ -3255,10 +3291,13 @@
         <v>265</v>
       </c>
       <c r="C32" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D32" t="s">
         <v>261</v>
+      </c>
+      <c r="E32" t="s">
+        <v>284</v>
       </c>
       <c r="F32" t="s">
         <v>278</v>
@@ -3272,16 +3311,19 @@
         <v>265</v>
       </c>
       <c r="C33" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D33" t="s">
         <v>261</v>
+      </c>
+      <c r="E33" t="s">
+        <v>284</v>
       </c>
       <c r="F33" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" hidden="1">
       <c r="A34" t="s">
         <v>132</v>
       </c>
@@ -3292,7 +3334,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" hidden="1">
       <c r="A35" t="s">
         <v>133</v>
       </c>
@@ -3303,7 +3345,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" hidden="1">
       <c r="A36" t="s">
         <v>134</v>
       </c>
@@ -3314,7 +3356,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" hidden="1">
       <c r="A37" t="s">
         <v>135</v>
       </c>
@@ -3325,7 +3367,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" hidden="1">
       <c r="A38" t="s">
         <v>136</v>
       </c>
@@ -3336,7 +3378,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" hidden="1">
       <c r="A39" t="s">
         <v>137</v>
       </c>
@@ -3347,7 +3389,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:7" hidden="1">
       <c r="A40" t="s">
         <v>138</v>
       </c>
@@ -3367,7 +3409,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" hidden="1">
       <c r="A41" t="s">
         <v>139</v>
       </c>
@@ -3395,10 +3437,13 @@
         <v>265</v>
       </c>
       <c r="C42" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D42" t="s">
         <v>261</v>
+      </c>
+      <c r="E42" t="s">
+        <v>284</v>
       </c>
       <c r="F42" t="s">
         <v>278</v>
@@ -3432,10 +3477,13 @@
         <v>265</v>
       </c>
       <c r="C44" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D44" t="s">
         <v>261</v>
+      </c>
+      <c r="E44" t="s">
+        <v>284</v>
       </c>
       <c r="F44" t="s">
         <v>278</v>
@@ -3469,10 +3517,13 @@
         <v>265</v>
       </c>
       <c r="C46" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D46" t="s">
         <v>261</v>
+      </c>
+      <c r="E46" t="s">
+        <v>284</v>
       </c>
       <c r="F46" t="s">
         <v>278</v>
@@ -3518,7 +3569,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="49" spans="1:7">
+    <row r="49" spans="1:7" hidden="1">
       <c r="A49" t="s">
         <v>144</v>
       </c>
@@ -3538,7 +3589,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="50" spans="1:7">
+    <row r="50" spans="1:7" hidden="1">
       <c r="A50" t="s">
         <v>145</v>
       </c>
@@ -3558,7 +3609,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="51" spans="1:7">
+    <row r="51" spans="1:7" hidden="1">
       <c r="A51" t="s">
         <v>146</v>
       </c>
@@ -3578,7 +3629,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="52" spans="1:7">
+    <row r="52" spans="1:7" hidden="1">
       <c r="A52" t="s">
         <v>147</v>
       </c>
@@ -3598,7 +3649,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="53" spans="1:7">
+    <row r="53" spans="1:7" hidden="1">
       <c r="A53" t="s">
         <v>148</v>
       </c>
@@ -3618,7 +3669,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="54" spans="1:7">
+    <row r="54" spans="1:7" hidden="1">
       <c r="A54" t="s">
         <v>149</v>
       </c>
@@ -3686,10 +3737,13 @@
         <v>265</v>
       </c>
       <c r="C57" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D57" t="s">
         <v>261</v>
+      </c>
+      <c r="E57" t="s">
+        <v>284</v>
       </c>
       <c r="F57" t="s">
         <v>278</v>
@@ -3723,7 +3777,7 @@
         <v>265</v>
       </c>
       <c r="C59" t="s">
-        <v>266</v>
+        <v>285</v>
       </c>
       <c r="D59" t="s">
         <v>261</v>
@@ -3743,16 +3797,19 @@
         <v>265</v>
       </c>
       <c r="C60" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D60" t="s">
         <v>261</v>
+      </c>
+      <c r="E60" t="s">
+        <v>284</v>
       </c>
       <c r="F60" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="61" spans="1:7">
+    <row r="61" spans="1:7" hidden="1">
       <c r="A61" t="s">
         <v>157</v>
       </c>
@@ -3772,7 +3829,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="62" spans="1:7">
+    <row r="62" spans="1:7" hidden="1">
       <c r="A62" t="s">
         <v>158</v>
       </c>
@@ -3792,7 +3849,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="63" spans="1:7">
+    <row r="63" spans="1:7" hidden="1">
       <c r="A63" t="s">
         <v>159</v>
       </c>
@@ -3820,10 +3877,13 @@
         <v>265</v>
       </c>
       <c r="C64" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D64" t="s">
         <v>261</v>
+      </c>
+      <c r="E64" t="s">
+        <v>284</v>
       </c>
       <c r="F64" t="s">
         <v>278</v>
@@ -3837,10 +3897,13 @@
         <v>265</v>
       </c>
       <c r="C65" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D65" t="s">
         <v>261</v>
+      </c>
+      <c r="E65" t="s">
+        <v>284</v>
       </c>
       <c r="F65" t="s">
         <v>278</v>
@@ -3854,10 +3917,13 @@
         <v>265</v>
       </c>
       <c r="C66" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D66" t="s">
         <v>261</v>
+      </c>
+      <c r="E66" t="s">
+        <v>284</v>
       </c>
       <c r="F66" t="s">
         <v>278</v>
@@ -3871,10 +3937,13 @@
         <v>265</v>
       </c>
       <c r="C67" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D67" t="s">
         <v>261</v>
+      </c>
+      <c r="E67" t="s">
+        <v>284</v>
       </c>
       <c r="F67" t="s">
         <v>278</v>
@@ -3882,7 +3951,11 @@
     </row>
   </sheetData>
   <autoFilter ref="D1:D67">
-    <filterColumn colId="0"/>
+    <filterColumn colId="0">
+      <filters>
+        <filter val="赵育"/>
+      </filters>
+    </filterColumn>
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/internal_doc/05.测试设计/story/事务支持RC隔离级别/事务自动化用例跟踪表.xlsx
+++ b/internal_doc/05.测试设计/story/事务支持RC隔离级别/事务自动化用例跟踪表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="RU" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1197" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1293" uniqueCount="287">
   <si>
     <t>用例编号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -924,6 +924,10 @@
   </si>
   <si>
     <t>否</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>是</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1263,7 +1267,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:G94"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
@@ -1293,7 +1296,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7" hidden="1">
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
         <v>169</v>
       </c>
@@ -1313,7 +1316,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="3" spans="1:7" hidden="1">
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>140</v>
       </c>
@@ -1333,7 +1336,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="4" spans="1:7" hidden="1">
+    <row r="4" spans="1:7">
       <c r="A4" t="s">
         <v>141</v>
       </c>
@@ -1353,7 +1356,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="5" spans="1:7" hidden="1">
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
         <v>170</v>
       </c>
@@ -1364,7 +1367,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="6" spans="1:7" hidden="1">
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
         <v>171</v>
       </c>
@@ -1375,7 +1378,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="7" spans="1:7" hidden="1">
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
         <v>172</v>
       </c>
@@ -1386,7 +1389,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="8" spans="1:7" hidden="1">
+    <row r="8" spans="1:7">
       <c r="A8" t="s">
         <v>173</v>
       </c>
@@ -1397,7 +1400,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="9" spans="1:7" hidden="1">
+    <row r="9" spans="1:7">
       <c r="A9" t="s">
         <v>174</v>
       </c>
@@ -1408,7 +1411,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="10" spans="1:7" hidden="1">
+    <row r="10" spans="1:7">
       <c r="A10" t="s">
         <v>175</v>
       </c>
@@ -1419,7 +1422,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="11" spans="1:7" hidden="1">
+    <row r="11" spans="1:7">
       <c r="A11" t="s">
         <v>176</v>
       </c>
@@ -1430,7 +1433,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="12" spans="1:7" hidden="1">
+    <row r="12" spans="1:7">
       <c r="A12" t="s">
         <v>177</v>
       </c>
@@ -1441,7 +1444,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="13" spans="1:7" hidden="1">
+    <row r="13" spans="1:7">
       <c r="A13" t="s">
         <v>178</v>
       </c>
@@ -1452,7 +1455,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="14" spans="1:7" hidden="1">
+    <row r="14" spans="1:7">
       <c r="A14" t="s">
         <v>179</v>
       </c>
@@ -1463,7 +1466,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="15" spans="1:7" hidden="1">
+    <row r="15" spans="1:7">
       <c r="A15" t="s">
         <v>180</v>
       </c>
@@ -1483,7 +1486,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="16" spans="1:7" hidden="1">
+    <row r="16" spans="1:7">
       <c r="A16" t="s">
         <v>181</v>
       </c>
@@ -1503,7 +1506,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="17" spans="1:6" hidden="1">
+    <row r="17" spans="1:6">
       <c r="A17" t="s">
         <v>182</v>
       </c>
@@ -1523,7 +1526,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="18" spans="1:6" hidden="1">
+    <row r="18" spans="1:6">
       <c r="A18" t="s">
         <v>183</v>
       </c>
@@ -1543,7 +1546,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="19" spans="1:6" hidden="1">
+    <row r="19" spans="1:6">
       <c r="A19" t="s">
         <v>184</v>
       </c>
@@ -1554,7 +1557,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="20" spans="1:6" hidden="1">
+    <row r="20" spans="1:6">
       <c r="A20" t="s">
         <v>185</v>
       </c>
@@ -1565,7 +1568,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="21" spans="1:6" hidden="1">
+    <row r="21" spans="1:6">
       <c r="A21" t="s">
         <v>186</v>
       </c>
@@ -1576,7 +1579,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="22" spans="1:6" hidden="1">
+    <row r="22" spans="1:6">
       <c r="A22" t="s">
         <v>187</v>
       </c>
@@ -1947,7 +1950,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="41" spans="1:6" hidden="1">
+    <row r="41" spans="1:6">
       <c r="A41" t="s">
         <v>206</v>
       </c>
@@ -1967,7 +1970,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="42" spans="1:6" hidden="1">
+    <row r="42" spans="1:6">
       <c r="A42" t="s">
         <v>207</v>
       </c>
@@ -1987,7 +1990,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="43" spans="1:6" hidden="1">
+    <row r="43" spans="1:6">
       <c r="A43" t="s">
         <v>208</v>
       </c>
@@ -2007,7 +2010,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="44" spans="1:6" hidden="1">
+    <row r="44" spans="1:6">
       <c r="A44" t="s">
         <v>209</v>
       </c>
@@ -2018,7 +2021,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="45" spans="1:6" hidden="1">
+    <row r="45" spans="1:6">
       <c r="A45" t="s">
         <v>210</v>
       </c>
@@ -2029,7 +2032,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="46" spans="1:6" hidden="1">
+    <row r="46" spans="1:6">
       <c r="A46" t="s">
         <v>211</v>
       </c>
@@ -2049,7 +2052,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="47" spans="1:6" hidden="1">
+    <row r="47" spans="1:6">
       <c r="A47" t="s">
         <v>212</v>
       </c>
@@ -2069,7 +2072,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="48" spans="1:6" hidden="1">
+    <row r="48" spans="1:6">
       <c r="A48" t="s">
         <v>213</v>
       </c>
@@ -2089,7 +2092,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="49" spans="1:6" hidden="1">
+    <row r="49" spans="1:6">
       <c r="A49" t="s">
         <v>214</v>
       </c>
@@ -2100,238 +2103,427 @@
         <v>264</v>
       </c>
     </row>
-    <row r="50" spans="1:6" hidden="1">
+    <row r="50" spans="1:6">
       <c r="A50" t="s">
         <v>215</v>
       </c>
+      <c r="B50" t="s">
+        <v>286</v>
+      </c>
+      <c r="C50" t="s">
+        <v>286</v>
+      </c>
       <c r="D50" t="s">
         <v>264</v>
       </c>
+      <c r="E50" t="s">
+        <v>286</v>
+      </c>
       <c r="F50" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="51" spans="1:6" hidden="1">
+    <row r="51" spans="1:6">
       <c r="A51" t="s">
         <v>216</v>
       </c>
+      <c r="B51" t="s">
+        <v>286</v>
+      </c>
+      <c r="C51" t="s">
+        <v>286</v>
+      </c>
       <c r="D51" t="s">
         <v>264</v>
       </c>
+      <c r="E51" t="s">
+        <v>286</v>
+      </c>
       <c r="F51" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="52" spans="1:6" hidden="1">
+    <row r="52" spans="1:6">
       <c r="A52" t="s">
         <v>217</v>
       </c>
+      <c r="B52" t="s">
+        <v>286</v>
+      </c>
+      <c r="C52" t="s">
+        <v>286</v>
+      </c>
       <c r="D52" t="s">
         <v>264</v>
       </c>
+      <c r="E52" t="s">
+        <v>286</v>
+      </c>
       <c r="F52" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="53" spans="1:6" hidden="1">
+    <row r="53" spans="1:6">
       <c r="A53" t="s">
         <v>218</v>
       </c>
+      <c r="B53" t="s">
+        <v>286</v>
+      </c>
+      <c r="C53" t="s">
+        <v>286</v>
+      </c>
       <c r="D53" t="s">
         <v>264</v>
       </c>
+      <c r="E53" t="s">
+        <v>286</v>
+      </c>
       <c r="F53" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="54" spans="1:6" hidden="1">
+    <row r="54" spans="1:6">
       <c r="A54" t="s">
         <v>219</v>
       </c>
+      <c r="B54" t="s">
+        <v>286</v>
+      </c>
+      <c r="C54" t="s">
+        <v>286</v>
+      </c>
       <c r="D54" t="s">
         <v>264</v>
       </c>
+      <c r="E54" t="s">
+        <v>286</v>
+      </c>
       <c r="F54" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="55" spans="1:6" hidden="1">
+    <row r="55" spans="1:6">
       <c r="A55" t="s">
         <v>220</v>
       </c>
+      <c r="B55" t="s">
+        <v>286</v>
+      </c>
+      <c r="C55" t="s">
+        <v>286</v>
+      </c>
       <c r="D55" t="s">
         <v>264</v>
       </c>
+      <c r="E55" t="s">
+        <v>286</v>
+      </c>
       <c r="F55" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="56" spans="1:6" hidden="1">
+    <row r="56" spans="1:6">
       <c r="A56" t="s">
         <v>221</v>
       </c>
+      <c r="B56" t="s">
+        <v>286</v>
+      </c>
+      <c r="C56" t="s">
+        <v>286</v>
+      </c>
       <c r="D56" t="s">
         <v>264</v>
       </c>
+      <c r="E56" t="s">
+        <v>286</v>
+      </c>
       <c r="F56" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="57" spans="1:6" hidden="1">
+    <row r="57" spans="1:6">
       <c r="A57" t="s">
         <v>222</v>
       </c>
+      <c r="B57" t="s">
+        <v>286</v>
+      </c>
+      <c r="C57" t="s">
+        <v>286</v>
+      </c>
       <c r="D57" t="s">
         <v>264</v>
       </c>
+      <c r="E57" t="s">
+        <v>286</v>
+      </c>
       <c r="F57" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="58" spans="1:6" hidden="1">
+    <row r="58" spans="1:6">
       <c r="A58" t="s">
         <v>223</v>
       </c>
+      <c r="B58" t="s">
+        <v>286</v>
+      </c>
+      <c r="C58" t="s">
+        <v>286</v>
+      </c>
       <c r="D58" t="s">
         <v>264</v>
       </c>
+      <c r="E58" t="s">
+        <v>286</v>
+      </c>
       <c r="F58" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="59" spans="1:6" hidden="1">
+    <row r="59" spans="1:6">
       <c r="A59" t="s">
         <v>224</v>
       </c>
+      <c r="B59" t="s">
+        <v>286</v>
+      </c>
+      <c r="C59" t="s">
+        <v>286</v>
+      </c>
       <c r="D59" t="s">
         <v>264</v>
       </c>
+      <c r="E59" t="s">
+        <v>286</v>
+      </c>
       <c r="F59" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="60" spans="1:6" hidden="1">
+    <row r="60" spans="1:6">
       <c r="A60" t="s">
         <v>225</v>
       </c>
+      <c r="B60" t="s">
+        <v>286</v>
+      </c>
+      <c r="C60" t="s">
+        <v>286</v>
+      </c>
       <c r="D60" t="s">
         <v>264</v>
       </c>
+      <c r="E60" t="s">
+        <v>286</v>
+      </c>
       <c r="F60" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="61" spans="1:6" hidden="1">
+    <row r="61" spans="1:6">
       <c r="A61" t="s">
         <v>226</v>
       </c>
+      <c r="B61" t="s">
+        <v>286</v>
+      </c>
+      <c r="C61" t="s">
+        <v>286</v>
+      </c>
       <c r="D61" t="s">
         <v>264</v>
       </c>
+      <c r="E61" t="s">
+        <v>286</v>
+      </c>
       <c r="F61" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="62" spans="1:6" hidden="1">
+    <row r="62" spans="1:6">
       <c r="A62" t="s">
         <v>227</v>
       </c>
+      <c r="B62" t="s">
+        <v>286</v>
+      </c>
+      <c r="C62" t="s">
+        <v>286</v>
+      </c>
       <c r="D62" t="s">
         <v>264</v>
       </c>
+      <c r="E62" t="s">
+        <v>286</v>
+      </c>
       <c r="F62" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="63" spans="1:6" hidden="1">
+    <row r="63" spans="1:6">
       <c r="A63" t="s">
         <v>228</v>
       </c>
+      <c r="B63" t="s">
+        <v>286</v>
+      </c>
+      <c r="C63" t="s">
+        <v>286</v>
+      </c>
       <c r="D63" t="s">
         <v>264</v>
       </c>
+      <c r="E63" t="s">
+        <v>286</v>
+      </c>
       <c r="F63" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="64" spans="1:6" hidden="1">
+    <row r="64" spans="1:6">
       <c r="A64" t="s">
         <v>229</v>
       </c>
+      <c r="B64" t="s">
+        <v>286</v>
+      </c>
+      <c r="C64" t="s">
+        <v>286</v>
+      </c>
       <c r="D64" t="s">
         <v>264</v>
       </c>
+      <c r="E64" t="s">
+        <v>286</v>
+      </c>
       <c r="F64" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="65" spans="1:6" hidden="1">
+    <row r="65" spans="1:6">
       <c r="A65" t="s">
         <v>230</v>
       </c>
+      <c r="B65" t="s">
+        <v>286</v>
+      </c>
+      <c r="C65" t="s">
+        <v>286</v>
+      </c>
       <c r="D65" t="s">
         <v>264</v>
       </c>
+      <c r="E65" t="s">
+        <v>286</v>
+      </c>
       <c r="F65" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="66" spans="1:6" hidden="1">
+    <row r="66" spans="1:6">
       <c r="A66" t="s">
         <v>231</v>
       </c>
+      <c r="B66" t="s">
+        <v>286</v>
+      </c>
+      <c r="C66" t="s">
+        <v>286</v>
+      </c>
       <c r="D66" t="s">
         <v>264</v>
       </c>
+      <c r="E66" t="s">
+        <v>286</v>
+      </c>
       <c r="F66" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="67" spans="1:6" hidden="1">
+    <row r="67" spans="1:6">
       <c r="A67" t="s">
         <v>232</v>
       </c>
+      <c r="B67" t="s">
+        <v>286</v>
+      </c>
+      <c r="C67" t="s">
+        <v>286</v>
+      </c>
       <c r="D67" t="s">
         <v>264</v>
       </c>
+      <c r="E67" t="s">
+        <v>286</v>
+      </c>
       <c r="F67" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="68" spans="1:6" hidden="1">
+    <row r="68" spans="1:6">
       <c r="A68" t="s">
         <v>233</v>
       </c>
+      <c r="B68" t="s">
+        <v>286</v>
+      </c>
+      <c r="C68" t="s">
+        <v>286</v>
+      </c>
       <c r="D68" t="s">
         <v>264</v>
       </c>
+      <c r="E68" t="s">
+        <v>286</v>
+      </c>
       <c r="F68" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="69" spans="1:6" hidden="1">
+    <row r="69" spans="1:6">
       <c r="A69" t="s">
         <v>234</v>
       </c>
+      <c r="B69" t="s">
+        <v>286</v>
+      </c>
+      <c r="C69" t="s">
+        <v>286</v>
+      </c>
       <c r="D69" t="s">
         <v>264</v>
       </c>
+      <c r="E69" t="s">
+        <v>286</v>
+      </c>
       <c r="F69" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="70" spans="1:6" hidden="1">
+    <row r="70" spans="1:6">
       <c r="A70" t="s">
         <v>235</v>
       </c>
+      <c r="B70" t="s">
+        <v>286</v>
+      </c>
+      <c r="C70" t="s">
+        <v>286</v>
+      </c>
       <c r="D70" t="s">
         <v>264</v>
       </c>
+      <c r="E70" t="s">
+        <v>286</v>
+      </c>
       <c r="F70" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="71" spans="1:6" hidden="1">
+    <row r="71" spans="1:6">
       <c r="A71" t="s">
         <v>236</v>
       </c>
@@ -2351,7 +2543,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="72" spans="1:6" hidden="1">
+    <row r="72" spans="1:6">
       <c r="A72" t="s">
         <v>237</v>
       </c>
@@ -2365,7 +2557,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="73" spans="1:6" hidden="1">
+    <row r="73" spans="1:6">
       <c r="A73" t="s">
         <v>238</v>
       </c>
@@ -2379,7 +2571,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="74" spans="1:6" hidden="1">
+    <row r="74" spans="1:6">
       <c r="A74" t="s">
         <v>241</v>
       </c>
@@ -2399,89 +2591,161 @@
         <v>262</v>
       </c>
     </row>
-    <row r="75" spans="1:6" hidden="1">
+    <row r="75" spans="1:6">
       <c r="A75" t="s">
         <v>239</v>
       </c>
+      <c r="B75" t="s">
+        <v>286</v>
+      </c>
+      <c r="C75" t="s">
+        <v>286</v>
+      </c>
       <c r="D75" t="s">
         <v>264</v>
       </c>
+      <c r="E75" t="s">
+        <v>286</v>
+      </c>
       <c r="F75" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="76" spans="1:6" hidden="1">
+    <row r="76" spans="1:6">
       <c r="A76" t="s">
         <v>240</v>
       </c>
+      <c r="B76" t="s">
+        <v>286</v>
+      </c>
+      <c r="C76" t="s">
+        <v>286</v>
+      </c>
       <c r="D76" t="s">
         <v>264</v>
       </c>
+      <c r="E76" t="s">
+        <v>286</v>
+      </c>
       <c r="F76" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="77" spans="1:6" hidden="1">
+    <row r="77" spans="1:6">
       <c r="A77" t="s">
         <v>242</v>
       </c>
+      <c r="B77" t="s">
+        <v>286</v>
+      </c>
+      <c r="C77" t="s">
+        <v>286</v>
+      </c>
       <c r="D77" t="s">
         <v>264</v>
       </c>
+      <c r="E77" t="s">
+        <v>286</v>
+      </c>
       <c r="F77" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="78" spans="1:6" hidden="1">
+    <row r="78" spans="1:6">
       <c r="A78" t="s">
         <v>156</v>
       </c>
+      <c r="B78" t="s">
+        <v>286</v>
+      </c>
+      <c r="C78" t="s">
+        <v>286</v>
+      </c>
       <c r="D78" t="s">
         <v>264</v>
       </c>
+      <c r="E78" t="s">
+        <v>286</v>
+      </c>
       <c r="F78" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="79" spans="1:6" hidden="1">
+    <row r="79" spans="1:6">
       <c r="A79" t="s">
         <v>243</v>
       </c>
+      <c r="B79" t="s">
+        <v>286</v>
+      </c>
+      <c r="C79" t="s">
+        <v>286</v>
+      </c>
       <c r="D79" t="s">
         <v>264</v>
       </c>
+      <c r="E79" t="s">
+        <v>286</v>
+      </c>
       <c r="F79" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="80" spans="1:6" hidden="1">
+    <row r="80" spans="1:6">
       <c r="A80" t="s">
         <v>244</v>
       </c>
+      <c r="B80" t="s">
+        <v>286</v>
+      </c>
+      <c r="C80" t="s">
+        <v>286</v>
+      </c>
       <c r="D80" t="s">
         <v>264</v>
       </c>
+      <c r="E80" t="s">
+        <v>286</v>
+      </c>
       <c r="F80" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="81" spans="1:6" hidden="1">
+    <row r="81" spans="1:6">
       <c r="A81" t="s">
         <v>245</v>
       </c>
+      <c r="B81" t="s">
+        <v>286</v>
+      </c>
+      <c r="C81" t="s">
+        <v>286</v>
+      </c>
       <c r="D81" t="s">
         <v>264</v>
       </c>
+      <c r="E81" t="s">
+        <v>286</v>
+      </c>
       <c r="F81" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="82" spans="1:6" hidden="1">
+    <row r="82" spans="1:6">
       <c r="A82" t="s">
         <v>246</v>
       </c>
+      <c r="B82" t="s">
+        <v>286</v>
+      </c>
+      <c r="C82" t="s">
+        <v>286</v>
+      </c>
       <c r="D82" t="s">
         <v>264</v>
+      </c>
+      <c r="E82" t="s">
+        <v>286</v>
       </c>
       <c r="F82" t="s">
         <v>263</v>
@@ -2607,34 +2871,61 @@
         <v>277</v>
       </c>
     </row>
-    <row r="89" spans="1:6" hidden="1">
+    <row r="89" spans="1:6">
       <c r="A89" t="s">
         <v>253</v>
       </c>
+      <c r="B89" t="s">
+        <v>286</v>
+      </c>
+      <c r="C89" t="s">
+        <v>286</v>
+      </c>
       <c r="D89" t="s">
         <v>264</v>
       </c>
+      <c r="E89" t="s">
+        <v>286</v>
+      </c>
       <c r="F89" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="90" spans="1:6" hidden="1">
+    <row r="90" spans="1:6">
       <c r="A90" t="s">
         <v>254</v>
       </c>
+      <c r="B90" t="s">
+        <v>286</v>
+      </c>
+      <c r="C90" t="s">
+        <v>286</v>
+      </c>
       <c r="D90" t="s">
         <v>264</v>
       </c>
+      <c r="E90" t="s">
+        <v>286</v>
+      </c>
       <c r="F90" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="91" spans="1:6" hidden="1">
+    <row r="91" spans="1:6">
       <c r="A91" t="s">
         <v>255</v>
       </c>
+      <c r="B91" t="s">
+        <v>286</v>
+      </c>
+      <c r="C91" t="s">
+        <v>286</v>
+      </c>
       <c r="D91" t="s">
         <v>264</v>
+      </c>
+      <c r="E91" t="s">
+        <v>286</v>
       </c>
       <c r="F91" t="s">
         <v>263</v>
@@ -2702,11 +2993,7 @@
     </row>
   </sheetData>
   <autoFilter ref="D1:D94">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="赵育"/>
-      </filters>
-    </filterColumn>
+    <filterColumn colId="0"/>
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2716,7 +3003,6 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:G67"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
@@ -2746,7 +3032,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7" hidden="1">
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
         <v>100</v>
       </c>
@@ -2757,7 +3043,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="3" spans="1:7" hidden="1">
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>101</v>
       </c>
@@ -2768,7 +3054,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="4" spans="1:7" hidden="1">
+    <row r="4" spans="1:7">
       <c r="A4" t="s">
         <v>102</v>
       </c>
@@ -2779,7 +3065,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="5" spans="1:7" hidden="1">
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
         <v>103</v>
       </c>
@@ -2799,7 +3085,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="6" spans="1:7" hidden="1">
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
         <v>104</v>
       </c>
@@ -2819,7 +3105,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="7" spans="1:7" hidden="1">
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
         <v>105</v>
       </c>
@@ -2839,7 +3125,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="8" spans="1:7" hidden="1">
+    <row r="8" spans="1:7">
       <c r="A8" t="s">
         <v>106</v>
       </c>
@@ -2859,7 +3145,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="9" spans="1:7" hidden="1">
+    <row r="9" spans="1:7">
       <c r="A9" t="s">
         <v>107</v>
       </c>
@@ -2879,7 +3165,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="10" spans="1:7" hidden="1">
+    <row r="10" spans="1:7">
       <c r="A10" t="s">
         <v>108</v>
       </c>
@@ -2899,7 +3185,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="11" spans="1:7" hidden="1">
+    <row r="11" spans="1:7">
       <c r="A11" t="s">
         <v>109</v>
       </c>
@@ -2919,7 +3205,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="12" spans="1:7" hidden="1">
+    <row r="12" spans="1:7">
       <c r="A12" t="s">
         <v>110</v>
       </c>
@@ -2939,7 +3225,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="13" spans="1:7" hidden="1">
+    <row r="13" spans="1:7">
       <c r="A13" t="s">
         <v>111</v>
       </c>
@@ -2959,7 +3245,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="14" spans="1:7" hidden="1">
+    <row r="14" spans="1:7">
       <c r="A14" t="s">
         <v>112</v>
       </c>
@@ -2979,7 +3265,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="15" spans="1:7" hidden="1">
+    <row r="15" spans="1:7">
       <c r="A15" t="s">
         <v>113</v>
       </c>
@@ -2990,7 +3276,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="16" spans="1:7" hidden="1">
+    <row r="16" spans="1:7">
       <c r="A16" t="s">
         <v>114</v>
       </c>
@@ -3001,7 +3287,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="17" spans="1:6" hidden="1">
+    <row r="17" spans="1:6">
       <c r="A17" t="s">
         <v>115</v>
       </c>
@@ -3012,7 +3298,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="18" spans="1:6" hidden="1">
+    <row r="18" spans="1:6">
       <c r="A18" t="s">
         <v>116</v>
       </c>
@@ -3023,7 +3309,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="19" spans="1:6" hidden="1">
+    <row r="19" spans="1:6">
       <c r="A19" t="s">
         <v>117</v>
       </c>
@@ -3043,7 +3329,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="20" spans="1:6" hidden="1">
+    <row r="20" spans="1:6">
       <c r="A20" t="s">
         <v>118</v>
       </c>
@@ -3063,7 +3349,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="21" spans="1:6" hidden="1">
+    <row r="21" spans="1:6">
       <c r="A21" t="s">
         <v>119</v>
       </c>
@@ -3083,7 +3369,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="22" spans="1:6" hidden="1">
+    <row r="22" spans="1:6">
       <c r="A22" t="s">
         <v>120</v>
       </c>
@@ -3323,7 +3609,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="34" spans="1:7" hidden="1">
+    <row r="34" spans="1:7">
       <c r="A34" t="s">
         <v>132</v>
       </c>
@@ -3334,7 +3620,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="35" spans="1:7" hidden="1">
+    <row r="35" spans="1:7">
       <c r="A35" t="s">
         <v>133</v>
       </c>
@@ -3345,7 +3631,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="36" spans="1:7" hidden="1">
+    <row r="36" spans="1:7">
       <c r="A36" t="s">
         <v>134</v>
       </c>
@@ -3356,7 +3642,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="37" spans="1:7" hidden="1">
+    <row r="37" spans="1:7">
       <c r="A37" t="s">
         <v>135</v>
       </c>
@@ -3367,7 +3653,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="38" spans="1:7" hidden="1">
+    <row r="38" spans="1:7">
       <c r="A38" t="s">
         <v>136</v>
       </c>
@@ -3378,7 +3664,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="39" spans="1:7" hidden="1">
+    <row r="39" spans="1:7">
       <c r="A39" t="s">
         <v>137</v>
       </c>
@@ -3389,7 +3675,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="40" spans="1:7" hidden="1">
+    <row r="40" spans="1:7">
       <c r="A40" t="s">
         <v>138</v>
       </c>
@@ -3409,7 +3695,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="41" spans="1:7" hidden="1">
+    <row r="41" spans="1:7">
       <c r="A41" t="s">
         <v>139</v>
       </c>
@@ -3569,7 +3855,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="49" spans="1:7" hidden="1">
+    <row r="49" spans="1:7">
       <c r="A49" t="s">
         <v>144</v>
       </c>
@@ -3589,7 +3875,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="50" spans="1:7" hidden="1">
+    <row r="50" spans="1:7">
       <c r="A50" t="s">
         <v>145</v>
       </c>
@@ -3609,7 +3895,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="51" spans="1:7" hidden="1">
+    <row r="51" spans="1:7">
       <c r="A51" t="s">
         <v>146</v>
       </c>
@@ -3629,7 +3915,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="52" spans="1:7" hidden="1">
+    <row r="52" spans="1:7">
       <c r="A52" t="s">
         <v>147</v>
       </c>
@@ -3649,7 +3935,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="53" spans="1:7" hidden="1">
+    <row r="53" spans="1:7">
       <c r="A53" t="s">
         <v>148</v>
       </c>
@@ -3669,7 +3955,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="54" spans="1:7" hidden="1">
+    <row r="54" spans="1:7">
       <c r="A54" t="s">
         <v>149</v>
       </c>
@@ -3809,7 +4095,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="61" spans="1:7" hidden="1">
+    <row r="61" spans="1:7">
       <c r="A61" t="s">
         <v>157</v>
       </c>
@@ -3829,7 +4115,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="62" spans="1:7" hidden="1">
+    <row r="62" spans="1:7">
       <c r="A62" t="s">
         <v>158</v>
       </c>
@@ -3849,7 +4135,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="63" spans="1:7" hidden="1">
+    <row r="63" spans="1:7">
       <c r="A63" t="s">
         <v>159</v>
       </c>
@@ -3951,11 +4237,7 @@
     </row>
   </sheetData>
   <autoFilter ref="D1:D67">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="赵育"/>
-      </filters>
-    </filterColumn>
+    <filterColumn colId="0"/>
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3964,7 +4246,6 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:G97"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
@@ -3995,7 +4276,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7" hidden="1">
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -4015,7 +4296,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="3" spans="1:7" hidden="1">
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -4035,7 +4316,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="4" spans="1:7" hidden="1">
+    <row r="4" spans="1:7">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -4055,7 +4336,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="5" spans="1:7" hidden="1">
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -4066,7 +4347,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="6" spans="1:7" hidden="1">
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -4077,7 +4358,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="7" spans="1:7" hidden="1">
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -4088,7 +4369,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="8" spans="1:7" hidden="1">
+    <row r="8" spans="1:7">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -4099,7 +4380,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="9" spans="1:7" hidden="1">
+    <row r="9" spans="1:7">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -4110,7 +4391,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="10" spans="1:7" hidden="1">
+    <row r="10" spans="1:7">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -4121,7 +4402,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="11" spans="1:7" hidden="1">
+    <row r="11" spans="1:7">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -4132,7 +4413,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="12" spans="1:7" hidden="1">
+    <row r="12" spans="1:7">
       <c r="A12" t="s">
         <v>15</v>
       </c>
@@ -4143,7 +4424,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="13" spans="1:7" hidden="1">
+    <row r="13" spans="1:7">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -4154,7 +4435,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="14" spans="1:7" hidden="1">
+    <row r="14" spans="1:7">
       <c r="A14" t="s">
         <v>17</v>
       </c>
@@ -4165,7 +4446,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="15" spans="1:7" hidden="1">
+    <row r="15" spans="1:7">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -4185,7 +4466,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="16" spans="1:7" hidden="1">
+    <row r="16" spans="1:7">
       <c r="A16" t="s">
         <v>19</v>
       </c>
@@ -4205,7 +4486,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="17" spans="1:7" hidden="1">
+    <row r="17" spans="1:7">
       <c r="A17" t="s">
         <v>20</v>
       </c>
@@ -4225,7 +4506,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="18" spans="1:7" hidden="1">
+    <row r="18" spans="1:7">
       <c r="A18" t="s">
         <v>21</v>
       </c>
@@ -4245,7 +4526,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="19" spans="1:7" hidden="1">
+    <row r="19" spans="1:7">
       <c r="A19" t="s">
         <v>22</v>
       </c>
@@ -4256,7 +4537,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="20" spans="1:7" hidden="1">
+    <row r="20" spans="1:7">
       <c r="A20" t="s">
         <v>23</v>
       </c>
@@ -4267,7 +4548,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="21" spans="1:7" hidden="1">
+    <row r="21" spans="1:7">
       <c r="A21" t="s">
         <v>24</v>
       </c>
@@ -4278,7 +4559,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="22" spans="1:7" hidden="1">
+    <row r="22" spans="1:7">
       <c r="A22" t="s">
         <v>25</v>
       </c>
@@ -4607,7 +4888,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="41" spans="1:7" hidden="1">
+    <row r="41" spans="1:7">
       <c r="A41" t="s">
         <v>43</v>
       </c>
@@ -4627,7 +4908,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="42" spans="1:7" hidden="1">
+    <row r="42" spans="1:7">
       <c r="A42" t="s">
         <v>44</v>
       </c>
@@ -4647,7 +4928,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="43" spans="1:7" hidden="1">
+    <row r="43" spans="1:7">
       <c r="A43" t="s">
         <v>45</v>
       </c>
@@ -4667,7 +4948,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="44" spans="1:7" hidden="1">
+    <row r="44" spans="1:7">
       <c r="A44" t="s">
         <v>46</v>
       </c>
@@ -4687,7 +4968,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="45" spans="1:7" hidden="1">
+    <row r="45" spans="1:7">
       <c r="A45" t="s">
         <v>47</v>
       </c>
@@ -4707,7 +4988,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="46" spans="1:7" hidden="1">
+    <row r="46" spans="1:7">
       <c r="A46" t="s">
         <v>48</v>
       </c>
@@ -4727,7 +5008,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="47" spans="1:7" hidden="1">
+    <row r="47" spans="1:7">
       <c r="A47" t="s">
         <v>49</v>
       </c>
@@ -4738,7 +5019,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="48" spans="1:7" hidden="1">
+    <row r="48" spans="1:7">
       <c r="A48" t="s">
         <v>50</v>
       </c>
@@ -4749,7 +5030,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="49" spans="1:6" hidden="1">
+    <row r="49" spans="1:6">
       <c r="A49" t="s">
         <v>51</v>
       </c>
@@ -4760,7 +5041,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="50" spans="1:6" hidden="1">
+    <row r="50" spans="1:6">
       <c r="A50" t="s">
         <v>52</v>
       </c>
@@ -4771,7 +5052,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="51" spans="1:6" hidden="1">
+    <row r="51" spans="1:6">
       <c r="A51" t="s">
         <v>53</v>
       </c>
@@ -4782,7 +5063,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="52" spans="1:6" hidden="1">
+    <row r="52" spans="1:6">
       <c r="A52" t="s">
         <v>54</v>
       </c>
@@ -4793,7 +5074,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="53" spans="1:6" hidden="1">
+    <row r="53" spans="1:6">
       <c r="A53" t="s">
         <v>55</v>
       </c>
@@ -4804,7 +5085,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="54" spans="1:6" hidden="1">
+    <row r="54" spans="1:6">
       <c r="A54" t="s">
         <v>56</v>
       </c>
@@ -4815,7 +5096,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="55" spans="1:6" hidden="1">
+    <row r="55" spans="1:6">
       <c r="A55" t="s">
         <v>57</v>
       </c>
@@ -4826,7 +5107,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="56" spans="1:6" hidden="1">
+    <row r="56" spans="1:6">
       <c r="A56" t="s">
         <v>58</v>
       </c>
@@ -4837,7 +5118,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="57" spans="1:6" hidden="1">
+    <row r="57" spans="1:6">
       <c r="A57" t="s">
         <v>59</v>
       </c>
@@ -4848,7 +5129,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="58" spans="1:6" hidden="1">
+    <row r="58" spans="1:6">
       <c r="A58" t="s">
         <v>60</v>
       </c>
@@ -4859,7 +5140,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="59" spans="1:6" hidden="1">
+    <row r="59" spans="1:6">
       <c r="A59" t="s">
         <v>61</v>
       </c>
@@ -4870,7 +5151,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="60" spans="1:6" hidden="1">
+    <row r="60" spans="1:6">
       <c r="A60" t="s">
         <v>62</v>
       </c>
@@ -4881,7 +5162,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="61" spans="1:6" hidden="1">
+    <row r="61" spans="1:6">
       <c r="A61" t="s">
         <v>63</v>
       </c>
@@ -4892,7 +5173,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="62" spans="1:6" hidden="1">
+    <row r="62" spans="1:6">
       <c r="A62" t="s">
         <v>64</v>
       </c>
@@ -4903,7 +5184,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="63" spans="1:6" hidden="1">
+    <row r="63" spans="1:6">
       <c r="A63" t="s">
         <v>65</v>
       </c>
@@ -4914,7 +5195,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="64" spans="1:6" hidden="1">
+    <row r="64" spans="1:6">
       <c r="A64" t="s">
         <v>66</v>
       </c>
@@ -4925,7 +5206,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="65" spans="1:7" hidden="1">
+    <row r="65" spans="1:7">
       <c r="A65" t="s">
         <v>67</v>
       </c>
@@ -4936,7 +5217,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="66" spans="1:7" hidden="1">
+    <row r="66" spans="1:7">
       <c r="A66" t="s">
         <v>68</v>
       </c>
@@ -4947,7 +5228,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="67" spans="1:7" hidden="1">
+    <row r="67" spans="1:7">
       <c r="A67" t="s">
         <v>69</v>
       </c>
@@ -4958,7 +5239,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="68" spans="1:7" hidden="1">
+    <row r="68" spans="1:7">
       <c r="A68" t="s">
         <v>70</v>
       </c>
@@ -4969,7 +5250,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="69" spans="1:7" hidden="1">
+    <row r="69" spans="1:7">
       <c r="A69" t="s">
         <v>71</v>
       </c>
@@ -4980,7 +5261,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="70" spans="1:7" hidden="1">
+    <row r="70" spans="1:7">
       <c r="A70" t="s">
         <v>72</v>
       </c>
@@ -4991,7 +5272,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="71" spans="1:7" hidden="1">
+    <row r="71" spans="1:7">
       <c r="A71" t="s">
         <v>73</v>
       </c>
@@ -5002,7 +5283,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="72" spans="1:7" hidden="1">
+    <row r="72" spans="1:7">
       <c r="A72" t="s">
         <v>74</v>
       </c>
@@ -5013,7 +5294,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="73" spans="1:7" hidden="1">
+    <row r="73" spans="1:7">
       <c r="A73" t="s">
         <v>75</v>
       </c>
@@ -5033,7 +5314,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="74" spans="1:7" hidden="1">
+    <row r="74" spans="1:7">
       <c r="A74" t="s">
         <v>76</v>
       </c>
@@ -5056,7 +5337,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="75" spans="1:7" hidden="1">
+    <row r="75" spans="1:7">
       <c r="A75" t="s">
         <v>77</v>
       </c>
@@ -5079,7 +5360,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="76" spans="1:7" hidden="1">
+    <row r="76" spans="1:7">
       <c r="A76" t="s">
         <v>78</v>
       </c>
@@ -5102,7 +5383,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="77" spans="1:7" hidden="1">
+    <row r="77" spans="1:7">
       <c r="A77" t="s">
         <v>79</v>
       </c>
@@ -5125,7 +5406,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="78" spans="1:7" hidden="1">
+    <row r="78" spans="1:7">
       <c r="A78" t="s">
         <v>80</v>
       </c>
@@ -5145,7 +5426,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="79" spans="1:7" hidden="1">
+    <row r="79" spans="1:7">
       <c r="A79" t="s">
         <v>81</v>
       </c>
@@ -5156,7 +5437,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="80" spans="1:7" hidden="1">
+    <row r="80" spans="1:7">
       <c r="A80" t="s">
         <v>82</v>
       </c>
@@ -5167,7 +5448,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="81" spans="1:7" hidden="1">
+    <row r="81" spans="1:7">
       <c r="A81" t="s">
         <v>83</v>
       </c>
@@ -5178,7 +5459,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="82" spans="1:7" hidden="1">
+    <row r="82" spans="1:7">
       <c r="A82" t="s">
         <v>84</v>
       </c>
@@ -5189,7 +5470,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="83" spans="1:7" hidden="1">
+    <row r="83" spans="1:7">
       <c r="A83" t="s">
         <v>85</v>
       </c>
@@ -5200,7 +5481,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="84" spans="1:7" hidden="1">
+    <row r="84" spans="1:7">
       <c r="A84" t="s">
         <v>86</v>
       </c>
@@ -5316,7 +5597,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="91" spans="1:7" hidden="1">
+    <row r="91" spans="1:7">
       <c r="A91" t="s">
         <v>93</v>
       </c>
@@ -5327,7 +5608,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="92" spans="1:7" hidden="1">
+    <row r="92" spans="1:7">
       <c r="A92" t="s">
         <v>94</v>
       </c>
@@ -5338,7 +5619,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="93" spans="1:7" hidden="1">
+    <row r="93" spans="1:7">
       <c r="A93" t="s">
         <v>95</v>
       </c>
@@ -5400,7 +5681,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="97" spans="1:7" hidden="1">
+    <row r="97" spans="1:7">
       <c r="A97" t="s">
         <v>99</v>
       </c>
@@ -5425,11 +5706,7 @@
     </row>
   </sheetData>
   <autoFilter ref="D1:D97">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="赵育"/>
-      </filters>
-    </filterColumn>
+    <filterColumn colId="0"/>
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/internal_doc/05.测试设计/story/事务支持RC隔离级别/事务自动化用例跟踪表.xlsx
+++ b/internal_doc/05.测试设计/story/事务支持RC隔离级别/事务自动化用例跟踪表.xlsx
@@ -13,15 +13,15 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">RC不等锁!$D$1:$D$97</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">RC等锁!$D$1:$D$67</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">RU!$D$1:$D$94</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">RC等锁!$E$1:$E$67</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">RU!$E$1:$E$94</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1293" uniqueCount="287">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1324" uniqueCount="296">
   <si>
     <t>用例编号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -928,6 +928,44 @@
   </si>
   <si>
     <t>是</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>是</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>否</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>通过问题单SEQUOIADBMAINSTREAM-4182跟踪检视任务</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>test1中transCL2不是事务连接</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>注释的用例标题有误</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>通过问题单SEQUOIADBMAINSTREAM-4113跟踪检视任务</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>通过问题单SEQUOIADBMAINSTREAM-4116跟踪检视任务</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>通过问题单SEQUOIADBMAINSTREAM-4118跟踪检视任务</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.建议并发的时间长一点，本地手工测试的时候运行超过24小时，自动化建议至少执行10分钟吧
+2.预置条件中需要插入1批记录用于更新与删除，用例貌似只更新删除了新插入的记录，没有更新删除老记录
+3.更新删除强制走索引</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -971,8 +1009,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1267,6 +1308,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:G94"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
@@ -1296,7 +1338,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" hidden="1">
       <c r="A2" t="s">
         <v>169</v>
       </c>
@@ -1316,7 +1358,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" hidden="1">
       <c r="A3" t="s">
         <v>140</v>
       </c>
@@ -1336,7 +1378,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" hidden="1">
       <c r="A4" t="s">
         <v>141</v>
       </c>
@@ -1466,7 +1508,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" hidden="1">
       <c r="A15" t="s">
         <v>180</v>
       </c>
@@ -1486,7 +1528,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" hidden="1">
       <c r="A16" t="s">
         <v>181</v>
       </c>
@@ -1506,7 +1548,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" hidden="1">
       <c r="A17" t="s">
         <v>182</v>
       </c>
@@ -1526,7 +1568,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" hidden="1">
       <c r="A18" t="s">
         <v>183</v>
       </c>
@@ -1590,7 +1632,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:6" hidden="1">
       <c r="A23" t="s">
         <v>188</v>
       </c>
@@ -1610,7 +1652,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:6" hidden="1">
       <c r="A24" t="s">
         <v>189</v>
       </c>
@@ -1630,7 +1672,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:6" hidden="1">
       <c r="A25" t="s">
         <v>190</v>
       </c>
@@ -1650,7 +1692,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:6" hidden="1">
       <c r="A26" t="s">
         <v>191</v>
       </c>
@@ -1670,7 +1712,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="27" spans="1:6">
+    <row r="27" spans="1:6" hidden="1">
       <c r="A27" t="s">
         <v>192</v>
       </c>
@@ -1690,7 +1732,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="28" spans="1:6">
+    <row r="28" spans="1:6" hidden="1">
       <c r="A28" t="s">
         <v>193</v>
       </c>
@@ -1710,7 +1752,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="29" spans="1:6">
+    <row r="29" spans="1:6" hidden="1">
       <c r="A29" t="s">
         <v>194</v>
       </c>
@@ -1730,7 +1772,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="30" spans="1:6">
+    <row r="30" spans="1:6" hidden="1">
       <c r="A30" t="s">
         <v>195</v>
       </c>
@@ -1750,7 +1792,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="31" spans="1:6">
+    <row r="31" spans="1:6" hidden="1">
       <c r="A31" t="s">
         <v>196</v>
       </c>
@@ -1770,7 +1812,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="32" spans="1:6">
+    <row r="32" spans="1:6" hidden="1">
       <c r="A32" t="s">
         <v>197</v>
       </c>
@@ -1790,7 +1832,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="33" spans="1:6">
+    <row r="33" spans="1:6" hidden="1">
       <c r="A33" t="s">
         <v>198</v>
       </c>
@@ -1810,7 +1852,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="34" spans="1:6">
+    <row r="34" spans="1:6" hidden="1">
       <c r="A34" t="s">
         <v>199</v>
       </c>
@@ -1830,7 +1872,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="35" spans="1:6">
+    <row r="35" spans="1:6" hidden="1">
       <c r="A35" t="s">
         <v>200</v>
       </c>
@@ -1850,7 +1892,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="36" spans="1:6">
+    <row r="36" spans="1:6" hidden="1">
       <c r="A36" t="s">
         <v>201</v>
       </c>
@@ -1870,7 +1912,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="37" spans="1:6">
+    <row r="37" spans="1:6" hidden="1">
       <c r="A37" t="s">
         <v>202</v>
       </c>
@@ -1890,7 +1932,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="38" spans="1:6">
+    <row r="38" spans="1:6" hidden="1">
       <c r="A38" t="s">
         <v>203</v>
       </c>
@@ -1910,7 +1952,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="39" spans="1:6">
+    <row r="39" spans="1:6" hidden="1">
       <c r="A39" t="s">
         <v>204</v>
       </c>
@@ -1930,7 +1972,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="40" spans="1:6">
+    <row r="40" spans="1:6" hidden="1">
       <c r="A40" t="s">
         <v>205</v>
       </c>
@@ -1950,7 +1992,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="41" spans="1:6">
+    <row r="41" spans="1:6" hidden="1">
       <c r="A41" t="s">
         <v>206</v>
       </c>
@@ -1970,7 +2012,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="42" spans="1:6">
+    <row r="42" spans="1:6" hidden="1">
       <c r="A42" t="s">
         <v>207</v>
       </c>
@@ -1990,7 +2032,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="43" spans="1:6">
+    <row r="43" spans="1:6" hidden="1">
       <c r="A43" t="s">
         <v>208</v>
       </c>
@@ -2032,7 +2074,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="46" spans="1:6">
+    <row r="46" spans="1:6" hidden="1">
       <c r="A46" t="s">
         <v>211</v>
       </c>
@@ -2052,7 +2094,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="47" spans="1:6">
+    <row r="47" spans="1:6" hidden="1">
       <c r="A47" t="s">
         <v>212</v>
       </c>
@@ -2072,7 +2114,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="48" spans="1:6">
+    <row r="48" spans="1:6" hidden="1">
       <c r="A48" t="s">
         <v>213</v>
       </c>
@@ -2103,7 +2145,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="50" spans="1:6">
+    <row r="50" spans="1:6" hidden="1">
       <c r="A50" t="s">
         <v>215</v>
       </c>
@@ -2123,7 +2165,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="51" spans="1:6">
+    <row r="51" spans="1:6" hidden="1">
       <c r="A51" t="s">
         <v>216</v>
       </c>
@@ -2143,7 +2185,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="52" spans="1:6">
+    <row r="52" spans="1:6" hidden="1">
       <c r="A52" t="s">
         <v>217</v>
       </c>
@@ -2163,7 +2205,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="53" spans="1:6">
+    <row r="53" spans="1:6" hidden="1">
       <c r="A53" t="s">
         <v>218</v>
       </c>
@@ -2183,7 +2225,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="54" spans="1:6">
+    <row r="54" spans="1:6" hidden="1">
       <c r="A54" t="s">
         <v>219</v>
       </c>
@@ -2203,7 +2245,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="55" spans="1:6">
+    <row r="55" spans="1:6" hidden="1">
       <c r="A55" t="s">
         <v>220</v>
       </c>
@@ -2223,7 +2265,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="56" spans="1:6">
+    <row r="56" spans="1:6" hidden="1">
       <c r="A56" t="s">
         <v>221</v>
       </c>
@@ -2243,7 +2285,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="57" spans="1:6">
+    <row r="57" spans="1:6" hidden="1">
       <c r="A57" t="s">
         <v>222</v>
       </c>
@@ -2263,7 +2305,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="58" spans="1:6">
+    <row r="58" spans="1:6" hidden="1">
       <c r="A58" t="s">
         <v>223</v>
       </c>
@@ -2283,7 +2325,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="59" spans="1:6">
+    <row r="59" spans="1:6" hidden="1">
       <c r="A59" t="s">
         <v>224</v>
       </c>
@@ -2303,7 +2345,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="60" spans="1:6">
+    <row r="60" spans="1:6" hidden="1">
       <c r="A60" t="s">
         <v>225</v>
       </c>
@@ -2323,7 +2365,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="61" spans="1:6">
+    <row r="61" spans="1:6" hidden="1">
       <c r="A61" t="s">
         <v>226</v>
       </c>
@@ -2343,7 +2385,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="62" spans="1:6">
+    <row r="62" spans="1:6" hidden="1">
       <c r="A62" t="s">
         <v>227</v>
       </c>
@@ -2363,7 +2405,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="63" spans="1:6">
+    <row r="63" spans="1:6" hidden="1">
       <c r="A63" t="s">
         <v>228</v>
       </c>
@@ -2383,7 +2425,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="64" spans="1:6">
+    <row r="64" spans="1:6" hidden="1">
       <c r="A64" t="s">
         <v>229</v>
       </c>
@@ -2403,7 +2445,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="65" spans="1:6">
+    <row r="65" spans="1:6" hidden="1">
       <c r="A65" t="s">
         <v>230</v>
       </c>
@@ -2423,7 +2465,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="66" spans="1:6">
+    <row r="66" spans="1:6" hidden="1">
       <c r="A66" t="s">
         <v>231</v>
       </c>
@@ -2443,7 +2485,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="67" spans="1:6">
+    <row r="67" spans="1:6" hidden="1">
       <c r="A67" t="s">
         <v>232</v>
       </c>
@@ -2463,7 +2505,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="68" spans="1:6">
+    <row r="68" spans="1:6" hidden="1">
       <c r="A68" t="s">
         <v>233</v>
       </c>
@@ -2483,7 +2525,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="69" spans="1:6">
+    <row r="69" spans="1:6" hidden="1">
       <c r="A69" t="s">
         <v>234</v>
       </c>
@@ -2503,7 +2545,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="70" spans="1:6">
+    <row r="70" spans="1:6" hidden="1">
       <c r="A70" t="s">
         <v>235</v>
       </c>
@@ -2523,7 +2565,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="71" spans="1:6">
+    <row r="71" spans="1:6" hidden="1">
       <c r="A71" t="s">
         <v>236</v>
       </c>
@@ -2571,7 +2613,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="74" spans="1:6">
+    <row r="74" spans="1:6" hidden="1">
       <c r="A74" t="s">
         <v>241</v>
       </c>
@@ -2591,7 +2633,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="75" spans="1:6">
+    <row r="75" spans="1:6" hidden="1">
       <c r="A75" t="s">
         <v>239</v>
       </c>
@@ -2611,7 +2653,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="76" spans="1:6">
+    <row r="76" spans="1:6" hidden="1">
       <c r="A76" t="s">
         <v>240</v>
       </c>
@@ -2631,7 +2673,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="77" spans="1:6">
+    <row r="77" spans="1:6" hidden="1">
       <c r="A77" t="s">
         <v>242</v>
       </c>
@@ -2651,7 +2693,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="78" spans="1:6">
+    <row r="78" spans="1:6" hidden="1">
       <c r="A78" t="s">
         <v>156</v>
       </c>
@@ -2671,7 +2713,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="79" spans="1:6">
+    <row r="79" spans="1:6" hidden="1">
       <c r="A79" t="s">
         <v>243</v>
       </c>
@@ -2691,7 +2733,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="80" spans="1:6">
+    <row r="80" spans="1:6" hidden="1">
       <c r="A80" t="s">
         <v>244</v>
       </c>
@@ -2711,7 +2753,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="81" spans="1:6">
+    <row r="81" spans="1:6" hidden="1">
       <c r="A81" t="s">
         <v>245</v>
       </c>
@@ -2731,7 +2773,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="82" spans="1:6">
+    <row r="82" spans="1:6" hidden="1">
       <c r="A82" t="s">
         <v>246</v>
       </c>
@@ -2751,7 +2793,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="83" spans="1:6">
+    <row r="83" spans="1:6" hidden="1">
       <c r="A83" t="s">
         <v>247</v>
       </c>
@@ -2771,7 +2813,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="84" spans="1:6">
+    <row r="84" spans="1:6" hidden="1">
       <c r="A84" t="s">
         <v>248</v>
       </c>
@@ -2791,7 +2833,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="85" spans="1:6">
+    <row r="85" spans="1:6" hidden="1">
       <c r="A85" t="s">
         <v>249</v>
       </c>
@@ -2811,7 +2853,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="86" spans="1:6">
+    <row r="86" spans="1:6" hidden="1">
       <c r="A86" t="s">
         <v>250</v>
       </c>
@@ -2831,7 +2873,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="87" spans="1:6">
+    <row r="87" spans="1:6" hidden="1">
       <c r="A87" t="s">
         <v>251</v>
       </c>
@@ -2851,7 +2893,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="88" spans="1:6">
+    <row r="88" spans="1:6" hidden="1">
       <c r="A88" t="s">
         <v>252</v>
       </c>
@@ -2871,7 +2913,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="89" spans="1:6">
+    <row r="89" spans="1:6" hidden="1">
       <c r="A89" t="s">
         <v>253</v>
       </c>
@@ -2891,7 +2933,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="90" spans="1:6">
+    <row r="90" spans="1:6" hidden="1">
       <c r="A90" t="s">
         <v>254</v>
       </c>
@@ -2911,7 +2953,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="91" spans="1:6">
+    <row r="91" spans="1:6" hidden="1">
       <c r="A91" t="s">
         <v>255</v>
       </c>
@@ -2931,7 +2973,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="92" spans="1:6">
+    <row r="92" spans="1:6" hidden="1">
       <c r="A92" t="s">
         <v>256</v>
       </c>
@@ -2951,7 +2993,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="93" spans="1:6">
+    <row r="93" spans="1:6" hidden="1">
       <c r="A93" t="s">
         <v>257</v>
       </c>
@@ -2971,7 +3013,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="94" spans="1:6">
+    <row r="94" spans="1:6" hidden="1">
       <c r="A94" t="s">
         <v>258</v>
       </c>
@@ -2992,8 +3034,10 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="D1:D94">
-    <filterColumn colId="0"/>
+  <autoFilter ref="E1:E94">
+    <filterColumn colId="0">
+      <filters blank="1"/>
+    </filterColumn>
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3003,6 +3047,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:G67"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
@@ -3065,7 +3110,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" hidden="1">
       <c r="A5" t="s">
         <v>103</v>
       </c>
@@ -3085,7 +3130,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" hidden="1">
       <c r="A6" t="s">
         <v>104</v>
       </c>
@@ -3105,7 +3150,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" hidden="1">
       <c r="A7" t="s">
         <v>105</v>
       </c>
@@ -3125,7 +3170,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" hidden="1">
       <c r="A8" t="s">
         <v>106</v>
       </c>
@@ -3145,7 +3190,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" hidden="1">
       <c r="A9" t="s">
         <v>107</v>
       </c>
@@ -3165,7 +3210,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" hidden="1">
       <c r="A10" t="s">
         <v>108</v>
       </c>
@@ -3185,7 +3230,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" hidden="1">
       <c r="A11" t="s">
         <v>109</v>
       </c>
@@ -3205,7 +3250,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" hidden="1">
       <c r="A12" t="s">
         <v>110</v>
       </c>
@@ -3225,7 +3270,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" hidden="1">
       <c r="A13" t="s">
         <v>111</v>
       </c>
@@ -3245,7 +3290,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" hidden="1">
       <c r="A14" t="s">
         <v>112</v>
       </c>
@@ -3309,7 +3354,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:6" hidden="1">
       <c r="A19" t="s">
         <v>117</v>
       </c>
@@ -3329,7 +3374,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:6" hidden="1">
       <c r="A20" t="s">
         <v>118</v>
       </c>
@@ -3349,7 +3394,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:6" hidden="1">
       <c r="A21" t="s">
         <v>119</v>
       </c>
@@ -3369,7 +3414,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:6" hidden="1">
       <c r="A22" t="s">
         <v>120</v>
       </c>
@@ -3389,7 +3434,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:6" hidden="1">
       <c r="A23" t="s">
         <v>121</v>
       </c>
@@ -3409,7 +3454,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:6" hidden="1">
       <c r="A24" t="s">
         <v>122</v>
       </c>
@@ -3429,7 +3474,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:6" hidden="1">
       <c r="A25" t="s">
         <v>123</v>
       </c>
@@ -3449,7 +3494,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:6" hidden="1">
       <c r="A26" t="s">
         <v>124</v>
       </c>
@@ -3469,7 +3514,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="27" spans="1:6">
+    <row r="27" spans="1:6" hidden="1">
       <c r="A27" t="s">
         <v>125</v>
       </c>
@@ -3489,7 +3534,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="28" spans="1:6">
+    <row r="28" spans="1:6" hidden="1">
       <c r="A28" t="s">
         <v>126</v>
       </c>
@@ -3509,7 +3554,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="29" spans="1:6">
+    <row r="29" spans="1:6" hidden="1">
       <c r="A29" t="s">
         <v>127</v>
       </c>
@@ -3529,7 +3574,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="30" spans="1:6">
+    <row r="30" spans="1:6" hidden="1">
       <c r="A30" t="s">
         <v>128</v>
       </c>
@@ -3549,7 +3594,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="31" spans="1:6">
+    <row r="31" spans="1:6" hidden="1">
       <c r="A31" t="s">
         <v>129</v>
       </c>
@@ -3569,7 +3614,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="32" spans="1:6">
+    <row r="32" spans="1:6" hidden="1">
       <c r="A32" t="s">
         <v>130</v>
       </c>
@@ -3589,7 +3634,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" hidden="1">
       <c r="A33" t="s">
         <v>131</v>
       </c>
@@ -3675,7 +3720,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:7" hidden="1">
       <c r="A40" t="s">
         <v>138</v>
       </c>
@@ -3695,7 +3740,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" hidden="1">
       <c r="A41" t="s">
         <v>139</v>
       </c>
@@ -3715,7 +3760,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:7" hidden="1">
       <c r="A42" t="s">
         <v>164</v>
       </c>
@@ -3755,7 +3800,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:7" hidden="1">
       <c r="A44" t="s">
         <v>166</v>
       </c>
@@ -3795,7 +3840,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:7" hidden="1">
       <c r="A46" t="s">
         <v>168</v>
       </c>
@@ -3855,7 +3900,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="49" spans="1:7">
+    <row r="49" spans="1:7" hidden="1">
       <c r="A49" t="s">
         <v>144</v>
       </c>
@@ -3875,7 +3920,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="50" spans="1:7">
+    <row r="50" spans="1:7" hidden="1">
       <c r="A50" t="s">
         <v>145</v>
       </c>
@@ -3895,7 +3940,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="51" spans="1:7">
+    <row r="51" spans="1:7" hidden="1">
       <c r="A51" t="s">
         <v>146</v>
       </c>
@@ -3915,7 +3960,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="52" spans="1:7">
+    <row r="52" spans="1:7" hidden="1">
       <c r="A52" t="s">
         <v>147</v>
       </c>
@@ -3935,7 +3980,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="53" spans="1:7">
+    <row r="53" spans="1:7" hidden="1">
       <c r="A53" t="s">
         <v>148</v>
       </c>
@@ -3955,7 +4000,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="54" spans="1:7">
+    <row r="54" spans="1:7" hidden="1">
       <c r="A54" t="s">
         <v>149</v>
       </c>
@@ -4015,7 +4060,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="57" spans="1:7">
+    <row r="57" spans="1:7" hidden="1">
       <c r="A57" t="s">
         <v>152</v>
       </c>
@@ -4075,7 +4120,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="60" spans="1:7">
+    <row r="60" spans="1:7" hidden="1">
       <c r="A60" t="s">
         <v>155</v>
       </c>
@@ -4095,7 +4140,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="61" spans="1:7">
+    <row r="61" spans="1:7" hidden="1">
       <c r="A61" t="s">
         <v>157</v>
       </c>
@@ -4115,7 +4160,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="62" spans="1:7">
+    <row r="62" spans="1:7" hidden="1">
       <c r="A62" t="s">
         <v>158</v>
       </c>
@@ -4135,7 +4180,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="63" spans="1:7">
+    <row r="63" spans="1:7" hidden="1">
       <c r="A63" t="s">
         <v>159</v>
       </c>
@@ -4155,7 +4200,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="64" spans="1:7">
+    <row r="64" spans="1:7" hidden="1">
       <c r="A64" t="s">
         <v>160</v>
       </c>
@@ -4175,7 +4220,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="65" spans="1:6">
+    <row r="65" spans="1:6" hidden="1">
       <c r="A65" t="s">
         <v>161</v>
       </c>
@@ -4195,7 +4240,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="66" spans="1:6">
+    <row r="66" spans="1:6" hidden="1">
       <c r="A66" t="s">
         <v>162</v>
       </c>
@@ -4215,7 +4260,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="67" spans="1:6">
+    <row r="67" spans="1:6" hidden="1">
       <c r="A67" t="s">
         <v>163</v>
       </c>
@@ -4236,8 +4281,10 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="D1:D67">
-    <filterColumn colId="0"/>
+  <autoFilter ref="E1:E67">
+    <filterColumn colId="0">
+      <filters blank="1"/>
+    </filterColumn>
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4246,11 +4293,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:G97"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="6" width="20.625" customWidth="1"/>
-    <col min="7" max="7" width="26.125" customWidth="1"/>
+    <col min="7" max="7" width="26.125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -4272,11 +4320,11 @@
       <c r="F1" t="s">
         <v>259</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" hidden="1">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -4295,8 +4343,9 @@
       <c r="F2" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="3" spans="1:7">
+      <c r="G2"/>
+    </row>
+    <row r="3" spans="1:7" hidden="1">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -4315,8 +4364,9 @@
       <c r="F3" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="4" spans="1:7">
+      <c r="G3"/>
+    </row>
+    <row r="4" spans="1:7" hidden="1">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -4335,8 +4385,9 @@
       <c r="F4" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="5" spans="1:7">
+      <c r="G4"/>
+    </row>
+    <row r="5" spans="1:7" hidden="1">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -4346,8 +4397,9 @@
       <c r="F5" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="6" spans="1:7">
+      <c r="G5"/>
+    </row>
+    <row r="6" spans="1:7" hidden="1">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -4357,8 +4409,9 @@
       <c r="F6" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="7" spans="1:7">
+      <c r="G6"/>
+    </row>
+    <row r="7" spans="1:7" hidden="1">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -4368,8 +4421,9 @@
       <c r="F7" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="8" spans="1:7">
+      <c r="G7"/>
+    </row>
+    <row r="8" spans="1:7" hidden="1">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -4379,8 +4433,9 @@
       <c r="F8" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="9" spans="1:7">
+      <c r="G8"/>
+    </row>
+    <row r="9" spans="1:7" hidden="1">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -4390,8 +4445,9 @@
       <c r="F9" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="10" spans="1:7">
+      <c r="G9"/>
+    </row>
+    <row r="10" spans="1:7" hidden="1">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -4401,8 +4457,9 @@
       <c r="F10" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="11" spans="1:7">
+      <c r="G10"/>
+    </row>
+    <row r="11" spans="1:7" hidden="1">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -4412,8 +4469,9 @@
       <c r="F11" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="12" spans="1:7">
+      <c r="G11"/>
+    </row>
+    <row r="12" spans="1:7" hidden="1">
       <c r="A12" t="s">
         <v>15</v>
       </c>
@@ -4423,8 +4481,9 @@
       <c r="F12" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="13" spans="1:7">
+      <c r="G12"/>
+    </row>
+    <row r="13" spans="1:7" hidden="1">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -4434,8 +4493,9 @@
       <c r="F13" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="14" spans="1:7">
+      <c r="G13"/>
+    </row>
+    <row r="14" spans="1:7" hidden="1">
       <c r="A14" t="s">
         <v>17</v>
       </c>
@@ -4445,8 +4505,9 @@
       <c r="F14" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="15" spans="1:7">
+      <c r="G14"/>
+    </row>
+    <row r="15" spans="1:7" hidden="1">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -4465,8 +4526,9 @@
       <c r="F15" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="16" spans="1:7">
+      <c r="G15"/>
+    </row>
+    <row r="16" spans="1:7" hidden="1">
       <c r="A16" t="s">
         <v>19</v>
       </c>
@@ -4485,8 +4547,9 @@
       <c r="F16" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="17" spans="1:7">
+      <c r="G16"/>
+    </row>
+    <row r="17" spans="1:7" hidden="1">
       <c r="A17" t="s">
         <v>20</v>
       </c>
@@ -4505,8 +4568,9 @@
       <c r="F17" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="18" spans="1:7">
+      <c r="G17"/>
+    </row>
+    <row r="18" spans="1:7" hidden="1">
       <c r="A18" t="s">
         <v>21</v>
       </c>
@@ -4525,8 +4589,9 @@
       <c r="F18" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="19" spans="1:7">
+      <c r="G18"/>
+    </row>
+    <row r="19" spans="1:7" hidden="1">
       <c r="A19" t="s">
         <v>22</v>
       </c>
@@ -4536,8 +4601,9 @@
       <c r="F19" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="20" spans="1:7">
+      <c r="G19"/>
+    </row>
+    <row r="20" spans="1:7" hidden="1">
       <c r="A20" t="s">
         <v>23</v>
       </c>
@@ -4547,8 +4613,9 @@
       <c r="F20" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="21" spans="1:7">
+      <c r="G20"/>
+    </row>
+    <row r="21" spans="1:7" hidden="1">
       <c r="A21" t="s">
         <v>24</v>
       </c>
@@ -4558,8 +4625,9 @@
       <c r="F21" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="22" spans="1:7">
+      <c r="G21"/>
+    </row>
+    <row r="22" spans="1:7" hidden="1">
       <c r="A22" t="s">
         <v>25</v>
       </c>
@@ -4569,8 +4637,9 @@
       <c r="F22" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="23" spans="1:7">
+      <c r="G22"/>
+    </row>
+    <row r="23" spans="1:7" hidden="1">
       <c r="A23" t="s">
         <v>26</v>
       </c>
@@ -4586,8 +4655,9 @@
       <c r="F23" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="24" spans="1:7">
+      <c r="G23"/>
+    </row>
+    <row r="24" spans="1:7" hidden="1">
       <c r="A24" t="s">
         <v>27</v>
       </c>
@@ -4603,8 +4673,9 @@
       <c r="F24" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="25" spans="1:7">
+      <c r="G24"/>
+    </row>
+    <row r="25" spans="1:7" hidden="1">
       <c r="A25" t="s">
         <v>28</v>
       </c>
@@ -4620,8 +4691,9 @@
       <c r="F25" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="26" spans="1:7">
+      <c r="G25"/>
+    </row>
+    <row r="26" spans="1:7" hidden="1">
       <c r="A26" t="s">
         <v>29</v>
       </c>
@@ -4637,8 +4709,9 @@
       <c r="F26" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="27" spans="1:7">
+      <c r="G26"/>
+    </row>
+    <row r="27" spans="1:7" hidden="1">
       <c r="A27" t="s">
         <v>30</v>
       </c>
@@ -4654,8 +4727,9 @@
       <c r="F27" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="28" spans="1:7">
+      <c r="G27"/>
+    </row>
+    <row r="28" spans="1:7" hidden="1">
       <c r="A28" t="s">
         <v>31</v>
       </c>
@@ -4675,7 +4749,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" hidden="1">
       <c r="A29" t="s">
         <v>32</v>
       </c>
@@ -4691,8 +4765,9 @@
       <c r="F29" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="30" spans="1:7">
+      <c r="G29"/>
+    </row>
+    <row r="30" spans="1:7" hidden="1">
       <c r="A30" t="s">
         <v>33</v>
       </c>
@@ -4708,8 +4783,9 @@
       <c r="F30" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="31" spans="1:7">
+      <c r="G30"/>
+    </row>
+    <row r="31" spans="1:7" hidden="1">
       <c r="A31" t="s">
         <v>34</v>
       </c>
@@ -4725,8 +4801,9 @@
       <c r="F31" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="32" spans="1:7">
+      <c r="G31"/>
+    </row>
+    <row r="32" spans="1:7" hidden="1">
       <c r="A32" t="s">
         <v>35</v>
       </c>
@@ -4742,8 +4819,9 @@
       <c r="F32" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="33" spans="1:7">
+      <c r="G32"/>
+    </row>
+    <row r="33" spans="1:7" hidden="1">
       <c r="A33" t="s">
         <v>282</v>
       </c>
@@ -4763,7 +4841,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" hidden="1">
       <c r="A34" t="s">
         <v>36</v>
       </c>
@@ -4779,8 +4857,9 @@
       <c r="F34" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="35" spans="1:7">
+      <c r="G34"/>
+    </row>
+    <row r="35" spans="1:7" hidden="1">
       <c r="A35" t="s">
         <v>37</v>
       </c>
@@ -4796,8 +4875,9 @@
       <c r="F35" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="36" spans="1:7">
+      <c r="G35"/>
+    </row>
+    <row r="36" spans="1:7" hidden="1">
       <c r="A36" t="s">
         <v>38</v>
       </c>
@@ -4813,8 +4893,9 @@
       <c r="F36" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="37" spans="1:7">
+      <c r="G36"/>
+    </row>
+    <row r="37" spans="1:7" hidden="1">
       <c r="A37" t="s">
         <v>39</v>
       </c>
@@ -4834,7 +4915,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" hidden="1">
       <c r="A38" t="s">
         <v>40</v>
       </c>
@@ -4850,8 +4931,9 @@
       <c r="F38" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="39" spans="1:7">
+      <c r="G38"/>
+    </row>
+    <row r="39" spans="1:7" hidden="1">
       <c r="A39" t="s">
         <v>41</v>
       </c>
@@ -4867,8 +4949,9 @@
       <c r="F39" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="40" spans="1:7">
+      <c r="G39"/>
+    </row>
+    <row r="40" spans="1:7" hidden="1">
       <c r="A40" t="s">
         <v>42</v>
       </c>
@@ -4888,7 +4971,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" hidden="1">
       <c r="A41" t="s">
         <v>43</v>
       </c>
@@ -4907,8 +4990,9 @@
       <c r="F41" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="42" spans="1:7">
+      <c r="G41"/>
+    </row>
+    <row r="42" spans="1:7" hidden="1">
       <c r="A42" t="s">
         <v>44</v>
       </c>
@@ -4927,8 +5011,9 @@
       <c r="F42" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="43" spans="1:7">
+      <c r="G42"/>
+    </row>
+    <row r="43" spans="1:7" hidden="1">
       <c r="A43" t="s">
         <v>45</v>
       </c>
@@ -4947,8 +5032,9 @@
       <c r="F43" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="44" spans="1:7">
+      <c r="G43"/>
+    </row>
+    <row r="44" spans="1:7" hidden="1">
       <c r="A44" t="s">
         <v>46</v>
       </c>
@@ -4967,8 +5053,9 @@
       <c r="F44" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="45" spans="1:7">
+      <c r="G44"/>
+    </row>
+    <row r="45" spans="1:7" hidden="1">
       <c r="A45" t="s">
         <v>47</v>
       </c>
@@ -4987,8 +5074,9 @@
       <c r="F45" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="46" spans="1:7">
+      <c r="G45"/>
+    </row>
+    <row r="46" spans="1:7" hidden="1">
       <c r="A46" t="s">
         <v>48</v>
       </c>
@@ -5007,8 +5095,9 @@
       <c r="F46" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="47" spans="1:7">
+      <c r="G46"/>
+    </row>
+    <row r="47" spans="1:7" hidden="1">
       <c r="A47" t="s">
         <v>49</v>
       </c>
@@ -5018,8 +5107,9 @@
       <c r="F47" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="48" spans="1:7">
+      <c r="G47"/>
+    </row>
+    <row r="48" spans="1:7" hidden="1">
       <c r="A48" t="s">
         <v>50</v>
       </c>
@@ -5029,8 +5119,9 @@
       <c r="F48" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="49" spans="1:6">
+      <c r="G48"/>
+    </row>
+    <row r="49" spans="1:7" hidden="1">
       <c r="A49" t="s">
         <v>51</v>
       </c>
@@ -5040,192 +5131,265 @@
       <c r="F49" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="50" spans="1:6">
+      <c r="G49"/>
+    </row>
+    <row r="50" spans="1:7">
       <c r="A50" t="s">
         <v>52</v>
       </c>
       <c r="D50" t="s">
         <v>264</v>
       </c>
+      <c r="E50" t="s">
+        <v>287</v>
+      </c>
       <c r="F50" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="51" spans="1:6">
+    <row r="51" spans="1:7">
       <c r="A51" t="s">
         <v>53</v>
       </c>
       <c r="D51" t="s">
         <v>264</v>
       </c>
+      <c r="E51" t="s">
+        <v>287</v>
+      </c>
       <c r="F51" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="52" spans="1:6">
+    <row r="52" spans="1:7">
       <c r="A52" t="s">
         <v>54</v>
       </c>
       <c r="D52" t="s">
         <v>264</v>
       </c>
+      <c r="E52" t="s">
+        <v>287</v>
+      </c>
       <c r="F52" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="53" spans="1:6">
+    <row r="53" spans="1:7" ht="40.5">
       <c r="A53" t="s">
         <v>55</v>
       </c>
       <c r="D53" t="s">
         <v>264</v>
       </c>
+      <c r="E53" t="s">
+        <v>288</v>
+      </c>
       <c r="F53" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="54" spans="1:6">
+      <c r="G53" s="1" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7">
       <c r="A54" t="s">
         <v>56</v>
       </c>
       <c r="D54" t="s">
         <v>264</v>
       </c>
+      <c r="E54" t="s">
+        <v>287</v>
+      </c>
       <c r="F54" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="55" spans="1:6">
+    <row r="55" spans="1:7" ht="27">
       <c r="A55" t="s">
         <v>57</v>
       </c>
       <c r="D55" t="s">
         <v>264</v>
       </c>
+      <c r="E55" t="s">
+        <v>287</v>
+      </c>
       <c r="F55" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="56" spans="1:6">
+      <c r="G55" s="1" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7">
       <c r="A56" t="s">
         <v>58</v>
       </c>
       <c r="D56" t="s">
         <v>264</v>
       </c>
+      <c r="E56" t="s">
+        <v>287</v>
+      </c>
       <c r="F56" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="57" spans="1:6">
+    <row r="57" spans="1:7">
       <c r="A57" t="s">
         <v>59</v>
       </c>
       <c r="D57" t="s">
         <v>264</v>
       </c>
+      <c r="E57" t="s">
+        <v>287</v>
+      </c>
       <c r="F57" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="58" spans="1:6">
+    <row r="58" spans="1:7">
       <c r="A58" t="s">
         <v>60</v>
       </c>
       <c r="D58" t="s">
         <v>264</v>
       </c>
+      <c r="E58" t="s">
+        <v>287</v>
+      </c>
       <c r="F58" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="59" spans="1:6">
+    <row r="59" spans="1:7">
       <c r="A59" t="s">
         <v>61</v>
       </c>
       <c r="D59" t="s">
         <v>264</v>
       </c>
+      <c r="E59" t="s">
+        <v>287</v>
+      </c>
       <c r="F59" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="60" spans="1:6">
+    <row r="60" spans="1:7">
       <c r="A60" t="s">
         <v>62</v>
       </c>
       <c r="D60" t="s">
         <v>264</v>
       </c>
+      <c r="E60" t="s">
+        <v>287</v>
+      </c>
       <c r="F60" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="61" spans="1:6">
+      <c r="G60" s="1" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" ht="40.5">
       <c r="A61" t="s">
         <v>63</v>
       </c>
       <c r="D61" t="s">
         <v>264</v>
       </c>
+      <c r="E61" t="s">
+        <v>288</v>
+      </c>
       <c r="F61" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="62" spans="1:6">
+      <c r="G61" s="1" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7">
       <c r="A62" t="s">
         <v>64</v>
       </c>
       <c r="D62" t="s">
         <v>264</v>
       </c>
+      <c r="E62" t="s">
+        <v>287</v>
+      </c>
       <c r="F62" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="63" spans="1:6">
+    <row r="63" spans="1:7">
       <c r="A63" t="s">
         <v>65</v>
       </c>
       <c r="D63" t="s">
         <v>264</v>
       </c>
+      <c r="E63" t="s">
+        <v>287</v>
+      </c>
       <c r="F63" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="64" spans="1:6">
+    <row r="64" spans="1:7" ht="40.5">
       <c r="A64" t="s">
         <v>66</v>
       </c>
       <c r="D64" t="s">
         <v>264</v>
       </c>
+      <c r="E64" t="s">
+        <v>288</v>
+      </c>
       <c r="F64" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="65" spans="1:7">
+      <c r="G64" s="1" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" ht="40.5">
       <c r="A65" t="s">
         <v>67</v>
       </c>
       <c r="D65" t="s">
         <v>264</v>
       </c>
+      <c r="E65" t="s">
+        <v>288</v>
+      </c>
       <c r="F65" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="66" spans="1:7">
+      <c r="G65" s="1" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" ht="40.5">
       <c r="A66" t="s">
         <v>68</v>
       </c>
       <c r="D66" t="s">
         <v>264</v>
       </c>
+      <c r="E66" t="s">
+        <v>288</v>
+      </c>
       <c r="F66" t="s">
         <v>261</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>294</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -5235,19 +5399,28 @@
       <c r="D67" t="s">
         <v>264</v>
       </c>
+      <c r="E67" t="s">
+        <v>287</v>
+      </c>
       <c r="F67" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="68" spans="1:7">
+    <row r="68" spans="1:7" ht="121.5">
       <c r="A68" t="s">
         <v>70</v>
       </c>
       <c r="D68" t="s">
         <v>264</v>
       </c>
+      <c r="E68" t="s">
+        <v>287</v>
+      </c>
       <c r="F68" t="s">
         <v>261</v>
+      </c>
+      <c r="G68" s="1" t="s">
+        <v>295</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -5257,6 +5430,9 @@
       <c r="D69" t="s">
         <v>264</v>
       </c>
+      <c r="E69" t="s">
+        <v>287</v>
+      </c>
       <c r="F69" t="s">
         <v>261</v>
       </c>
@@ -5268,6 +5444,9 @@
       <c r="D70" t="s">
         <v>264</v>
       </c>
+      <c r="E70" t="s">
+        <v>287</v>
+      </c>
       <c r="F70" t="s">
         <v>261</v>
       </c>
@@ -5279,6 +5458,9 @@
       <c r="D71" t="s">
         <v>264</v>
       </c>
+      <c r="E71" t="s">
+        <v>287</v>
+      </c>
       <c r="F71" t="s">
         <v>261</v>
       </c>
@@ -5290,11 +5472,14 @@
       <c r="D72" t="s">
         <v>264</v>
       </c>
+      <c r="E72" t="s">
+        <v>287</v>
+      </c>
       <c r="F72" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="73" spans="1:7">
+    <row r="73" spans="1:7" hidden="1">
       <c r="A73" t="s">
         <v>75</v>
       </c>
@@ -5313,8 +5498,9 @@
       <c r="F73" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="74" spans="1:7">
+      <c r="G73"/>
+    </row>
+    <row r="74" spans="1:7" hidden="1">
       <c r="A74" t="s">
         <v>76</v>
       </c>
@@ -5337,7 +5523,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="75" spans="1:7">
+    <row r="75" spans="1:7" hidden="1">
       <c r="A75" t="s">
         <v>77</v>
       </c>
@@ -5360,7 +5546,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="76" spans="1:7">
+    <row r="76" spans="1:7" hidden="1">
       <c r="A76" t="s">
         <v>78</v>
       </c>
@@ -5383,7 +5569,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="77" spans="1:7">
+    <row r="77" spans="1:7" hidden="1">
       <c r="A77" t="s">
         <v>79</v>
       </c>
@@ -5406,7 +5592,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="78" spans="1:7">
+    <row r="78" spans="1:7" hidden="1">
       <c r="A78" t="s">
         <v>80</v>
       </c>
@@ -5425,6 +5611,7 @@
       <c r="F78" t="s">
         <v>261</v>
       </c>
+      <c r="G78"/>
     </row>
     <row r="79" spans="1:7">
       <c r="A79" t="s">
@@ -5492,7 +5679,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="85" spans="1:7">
+    <row r="85" spans="1:7" hidden="1">
       <c r="A85" t="s">
         <v>87</v>
       </c>
@@ -5508,8 +5695,9 @@
       <c r="F85" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="86" spans="1:7">
+      <c r="G85"/>
+    </row>
+    <row r="86" spans="1:7" hidden="1">
       <c r="A86" t="s">
         <v>88</v>
       </c>
@@ -5525,8 +5713,9 @@
       <c r="F86" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="87" spans="1:7">
+      <c r="G86"/>
+    </row>
+    <row r="87" spans="1:7" hidden="1">
       <c r="A87" t="s">
         <v>89</v>
       </c>
@@ -5542,8 +5731,9 @@
       <c r="F87" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="88" spans="1:7">
+      <c r="G87"/>
+    </row>
+    <row r="88" spans="1:7" hidden="1">
       <c r="A88" t="s">
         <v>90</v>
       </c>
@@ -5563,7 +5753,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="89" spans="1:7">
+    <row r="89" spans="1:7" hidden="1">
       <c r="A89" t="s">
         <v>91</v>
       </c>
@@ -5579,8 +5769,9 @@
       <c r="F89" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="90" spans="1:7">
+      <c r="G89"/>
+    </row>
+    <row r="90" spans="1:7" hidden="1">
       <c r="A90" t="s">
         <v>92</v>
       </c>
@@ -5596,6 +5787,7 @@
       <c r="F90" t="s">
         <v>280</v>
       </c>
+      <c r="G90"/>
     </row>
     <row r="91" spans="1:7">
       <c r="A91" t="s">
@@ -5630,7 +5822,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="94" spans="1:7">
+    <row r="94" spans="1:7" hidden="1">
       <c r="A94" t="s">
         <v>96</v>
       </c>
@@ -5646,8 +5838,9 @@
       <c r="F94" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="95" spans="1:7">
+      <c r="G94"/>
+    </row>
+    <row r="95" spans="1:7" hidden="1">
       <c r="A95" t="s">
         <v>97</v>
       </c>
@@ -5663,8 +5856,9 @@
       <c r="F95" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="96" spans="1:7">
+      <c r="G95"/>
+    </row>
+    <row r="96" spans="1:7" hidden="1">
       <c r="A96" t="s">
         <v>98</v>
       </c>
@@ -5680,8 +5874,9 @@
       <c r="F96" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="97" spans="1:7">
+      <c r="G96"/>
+    </row>
+    <row r="97" spans="1:7" hidden="1">
       <c r="A97" t="s">
         <v>99</v>
       </c>
@@ -5706,7 +5901,11 @@
     </row>
   </sheetData>
   <autoFilter ref="D1:D97">
-    <filterColumn colId="0"/>
+    <filterColumn colId="0">
+      <filters>
+        <filter val="卢伟康"/>
+      </filters>
+    </filterColumn>
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/internal_doc/05.测试设计/story/事务支持RC隔离级别/事务自动化用例跟踪表.xlsx
+++ b/internal_doc/05.测试设计/story/事务支持RC隔离级别/事务自动化用例跟踪表.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1324" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1333" uniqueCount="296">
   <si>
     <t>用例编号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -940,10 +940,6 @@
   </si>
   <si>
     <t>通过问题单SEQUOIADBMAINSTREAM-4182跟踪检视任务</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>test1中transCL2不是事务连接</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -966,6 +962,10 @@
     <t>1.建议并发的时间长一点，本地手工测试的时候运行超过24小时，自动化建议至少执行10分钟吧
 2.预置条件中需要插入1批记录用于更新与删除，用例貌似只更新删除了新插入的记录，没有更新删除老记录
 3.更新删除强制走索引</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试点覆盖不全， 待修改后统一检视</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -5206,7 +5206,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="55" spans="1:7" ht="27">
+    <row r="55" spans="1:7">
       <c r="A55" t="s">
         <v>57</v>
       </c>
@@ -5218,9 +5218,6 @@
       </c>
       <c r="F55" t="s">
         <v>261</v>
-      </c>
-      <c r="G55" s="1" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -5293,7 +5290,7 @@
         <v>261</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="61" spans="1:7" ht="40.5">
@@ -5355,7 +5352,7 @@
         <v>261</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="65" spans="1:7" ht="40.5">
@@ -5372,7 +5369,7 @@
         <v>261</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="66" spans="1:7" ht="40.5">
@@ -5389,7 +5386,7 @@
         <v>261</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -5420,7 +5417,7 @@
         <v>261</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -5613,18 +5610,24 @@
       </c>
       <c r="G78"/>
     </row>
-    <row r="79" spans="1:7">
+    <row r="79" spans="1:7" ht="27">
       <c r="A79" t="s">
         <v>81</v>
       </c>
       <c r="D79" t="s">
         <v>264</v>
       </c>
+      <c r="E79" t="s">
+        <v>288</v>
+      </c>
       <c r="F79" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="80" spans="1:7">
+      <c r="G79" s="1" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" ht="27">
       <c r="A80" t="s">
         <v>82</v>
       </c>
@@ -5634,8 +5637,11 @@
       <c r="F80" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="81" spans="1:7">
+      <c r="G80" s="1" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" ht="27">
       <c r="A81" t="s">
         <v>83</v>
       </c>
@@ -5645,8 +5651,11 @@
       <c r="F81" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="82" spans="1:7">
+      <c r="G81" s="1" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" ht="27">
       <c r="A82" t="s">
         <v>84</v>
       </c>
@@ -5656,8 +5665,11 @@
       <c r="F82" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="83" spans="1:7">
+      <c r="G82" s="1" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" ht="27">
       <c r="A83" t="s">
         <v>85</v>
       </c>
@@ -5667,8 +5679,11 @@
       <c r="F83" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="84" spans="1:7">
+      <c r="G83" s="1" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" ht="27">
       <c r="A84" t="s">
         <v>86</v>
       </c>
@@ -5677,6 +5692,9 @@
       </c>
       <c r="F84" t="s">
         <v>261</v>
+      </c>
+      <c r="G84" s="1" t="s">
+        <v>295</v>
       </c>
     </row>
     <row r="85" spans="1:7" hidden="1">
@@ -5789,7 +5807,7 @@
       </c>
       <c r="G90"/>
     </row>
-    <row r="91" spans="1:7">
+    <row r="91" spans="1:7" ht="27">
       <c r="A91" t="s">
         <v>93</v>
       </c>
@@ -5799,8 +5817,11 @@
       <c r="F91" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="92" spans="1:7">
+      <c r="G91" s="1" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" ht="27">
       <c r="A92" t="s">
         <v>94</v>
       </c>
@@ -5810,8 +5831,11 @@
       <c r="F92" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="93" spans="1:7">
+      <c r="G92" s="1" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" ht="27">
       <c r="A93" t="s">
         <v>95</v>
       </c>
@@ -5820,6 +5844,9 @@
       </c>
       <c r="F93" t="s">
         <v>261</v>
+      </c>
+      <c r="G93" s="1" t="s">
+        <v>295</v>
       </c>
     </row>
     <row r="94" spans="1:7" hidden="1">

--- a/internal_doc/05.测试设计/story/事务支持RC隔离级别/事务自动化用例跟踪表.xlsx
+++ b/internal_doc/05.测试设计/story/事务支持RC隔离级别/事务自动化用例跟踪表.xlsx
@@ -4,12 +4,13 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="2"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="RU" sheetId="1" r:id="rId1"/>
     <sheet name="RC等锁" sheetId="2" r:id="rId2"/>
     <sheet name="RC不等锁" sheetId="3" r:id="rId3"/>
+    <sheet name="RC不等锁增加逆序索引及逆序查询任务" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">RC不等锁!$D$1:$D$97</definedName>
@@ -21,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1333" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1376" uniqueCount="304">
   <si>
     <t>用例编号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -966,6 +967,37 @@
   </si>
   <si>
     <t>测试点覆盖不全， 待修改后统一检视</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>用例编号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自动化代码是否已修改</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>备注</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-17092</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-17102</t>
+  </si>
+  <si>
+    <t>seqDB-17113</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-17358</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-17821</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -5938,4 +5970,232 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C41"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <cols>
+    <col min="1" max="1" width="18.5" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="3" max="3" width="18.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
+        <v>296</v>
+      </c>
+      <c r="B1" t="s">
+        <v>297</v>
+      </c>
+      <c r="C1" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" t="s">
+        <v>98</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/internal_doc/05.测试设计/story/事务支持RC隔离级别/事务自动化用例跟踪表.xlsx
+++ b/internal_doc/05.测试设计/story/事务支持RC隔离级别/事务自动化用例跟踪表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="3"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="RU" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1376" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1427" uniqueCount="306">
   <si>
     <t>用例编号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -998,6 +998,14 @@
   </si>
   <si>
     <t>seqDB-17821</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>是</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>否</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3079,7 +3087,6 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:G67"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
@@ -3142,7 +3149,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="5" spans="1:7" hidden="1">
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
         <v>103</v>
       </c>
@@ -3162,7 +3169,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="6" spans="1:7" hidden="1">
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
         <v>104</v>
       </c>
@@ -3182,7 +3189,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="7" spans="1:7" hidden="1">
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
         <v>105</v>
       </c>
@@ -3202,7 +3209,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="8" spans="1:7" hidden="1">
+    <row r="8" spans="1:7">
       <c r="A8" t="s">
         <v>106</v>
       </c>
@@ -3222,7 +3229,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="9" spans="1:7" hidden="1">
+    <row r="9" spans="1:7">
       <c r="A9" t="s">
         <v>107</v>
       </c>
@@ -3242,7 +3249,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="10" spans="1:7" hidden="1">
+    <row r="10" spans="1:7">
       <c r="A10" t="s">
         <v>108</v>
       </c>
@@ -3262,7 +3269,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="11" spans="1:7" hidden="1">
+    <row r="11" spans="1:7">
       <c r="A11" t="s">
         <v>109</v>
       </c>
@@ -3282,7 +3289,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="12" spans="1:7" hidden="1">
+    <row r="12" spans="1:7">
       <c r="A12" t="s">
         <v>110</v>
       </c>
@@ -3302,7 +3309,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="13" spans="1:7" hidden="1">
+    <row r="13" spans="1:7">
       <c r="A13" t="s">
         <v>111</v>
       </c>
@@ -3322,7 +3329,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="14" spans="1:7" hidden="1">
+    <row r="14" spans="1:7">
       <c r="A14" t="s">
         <v>112</v>
       </c>
@@ -3386,7 +3393,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="19" spans="1:6" hidden="1">
+    <row r="19" spans="1:6">
       <c r="A19" t="s">
         <v>117</v>
       </c>
@@ -3406,7 +3413,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="20" spans="1:6" hidden="1">
+    <row r="20" spans="1:6">
       <c r="A20" t="s">
         <v>118</v>
       </c>
@@ -3426,7 +3433,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="21" spans="1:6" hidden="1">
+    <row r="21" spans="1:6">
       <c r="A21" t="s">
         <v>119</v>
       </c>
@@ -3446,7 +3453,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="22" spans="1:6" hidden="1">
+    <row r="22" spans="1:6">
       <c r="A22" t="s">
         <v>120</v>
       </c>
@@ -3466,7 +3473,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="23" spans="1:6" hidden="1">
+    <row r="23" spans="1:6">
       <c r="A23" t="s">
         <v>121</v>
       </c>
@@ -3486,7 +3493,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="24" spans="1:6" hidden="1">
+    <row r="24" spans="1:6">
       <c r="A24" t="s">
         <v>122</v>
       </c>
@@ -3506,7 +3513,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="25" spans="1:6" hidden="1">
+    <row r="25" spans="1:6">
       <c r="A25" t="s">
         <v>123</v>
       </c>
@@ -3526,7 +3533,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="26" spans="1:6" hidden="1">
+    <row r="26" spans="1:6">
       <c r="A26" t="s">
         <v>124</v>
       </c>
@@ -3546,7 +3553,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="27" spans="1:6" hidden="1">
+    <row r="27" spans="1:6">
       <c r="A27" t="s">
         <v>125</v>
       </c>
@@ -3566,7 +3573,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="28" spans="1:6" hidden="1">
+    <row r="28" spans="1:6">
       <c r="A28" t="s">
         <v>126</v>
       </c>
@@ -3586,7 +3593,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="29" spans="1:6" hidden="1">
+    <row r="29" spans="1:6">
       <c r="A29" t="s">
         <v>127</v>
       </c>
@@ -3606,7 +3613,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="30" spans="1:6" hidden="1">
+    <row r="30" spans="1:6">
       <c r="A30" t="s">
         <v>128</v>
       </c>
@@ -3626,7 +3633,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="31" spans="1:6" hidden="1">
+    <row r="31" spans="1:6">
       <c r="A31" t="s">
         <v>129</v>
       </c>
@@ -3646,7 +3653,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="32" spans="1:6" hidden="1">
+    <row r="32" spans="1:6">
       <c r="A32" t="s">
         <v>130</v>
       </c>
@@ -3666,7 +3673,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="33" spans="1:7" hidden="1">
+    <row r="33" spans="1:7">
       <c r="A33" t="s">
         <v>131</v>
       </c>
@@ -3752,7 +3759,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="40" spans="1:7" hidden="1">
+    <row r="40" spans="1:7">
       <c r="A40" t="s">
         <v>138</v>
       </c>
@@ -3772,7 +3779,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="41" spans="1:7" hidden="1">
+    <row r="41" spans="1:7">
       <c r="A41" t="s">
         <v>139</v>
       </c>
@@ -3792,7 +3799,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="42" spans="1:7" hidden="1">
+    <row r="42" spans="1:7">
       <c r="A42" t="s">
         <v>164</v>
       </c>
@@ -3832,7 +3839,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="44" spans="1:7" hidden="1">
+    <row r="44" spans="1:7">
       <c r="A44" t="s">
         <v>166</v>
       </c>
@@ -3872,7 +3879,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="46" spans="1:7" hidden="1">
+    <row r="46" spans="1:7">
       <c r="A46" t="s">
         <v>168</v>
       </c>
@@ -3932,7 +3939,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="49" spans="1:7" hidden="1">
+    <row r="49" spans="1:7">
       <c r="A49" t="s">
         <v>144</v>
       </c>
@@ -3952,7 +3959,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="50" spans="1:7" hidden="1">
+    <row r="50" spans="1:7">
       <c r="A50" t="s">
         <v>145</v>
       </c>
@@ -3972,7 +3979,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="51" spans="1:7" hidden="1">
+    <row r="51" spans="1:7">
       <c r="A51" t="s">
         <v>146</v>
       </c>
@@ -3992,7 +3999,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="52" spans="1:7" hidden="1">
+    <row r="52" spans="1:7">
       <c r="A52" t="s">
         <v>147</v>
       </c>
@@ -4012,7 +4019,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="53" spans="1:7" hidden="1">
+    <row r="53" spans="1:7">
       <c r="A53" t="s">
         <v>148</v>
       </c>
@@ -4032,7 +4039,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="54" spans="1:7" hidden="1">
+    <row r="54" spans="1:7">
       <c r="A54" t="s">
         <v>149</v>
       </c>
@@ -4092,7 +4099,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="57" spans="1:7" hidden="1">
+    <row r="57" spans="1:7">
       <c r="A57" t="s">
         <v>152</v>
       </c>
@@ -4152,7 +4159,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="60" spans="1:7" hidden="1">
+    <row r="60" spans="1:7">
       <c r="A60" t="s">
         <v>155</v>
       </c>
@@ -4172,7 +4179,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="61" spans="1:7" hidden="1">
+    <row r="61" spans="1:7">
       <c r="A61" t="s">
         <v>157</v>
       </c>
@@ -4192,7 +4199,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="62" spans="1:7" hidden="1">
+    <row r="62" spans="1:7">
       <c r="A62" t="s">
         <v>158</v>
       </c>
@@ -4212,7 +4219,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="63" spans="1:7" hidden="1">
+    <row r="63" spans="1:7">
       <c r="A63" t="s">
         <v>159</v>
       </c>
@@ -4232,7 +4239,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="64" spans="1:7" hidden="1">
+    <row r="64" spans="1:7">
       <c r="A64" t="s">
         <v>160</v>
       </c>
@@ -4252,7 +4259,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="65" spans="1:6" hidden="1">
+    <row r="65" spans="1:6">
       <c r="A65" t="s">
         <v>161</v>
       </c>
@@ -4272,7 +4279,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="66" spans="1:6" hidden="1">
+    <row r="66" spans="1:6">
       <c r="A66" t="s">
         <v>162</v>
       </c>
@@ -4292,7 +4299,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="67" spans="1:6" hidden="1">
+    <row r="67" spans="1:6">
       <c r="A67" t="s">
         <v>163</v>
       </c>
@@ -4314,9 +4321,7 @@
     </row>
   </sheetData>
   <autoFilter ref="E1:E67">
-    <filterColumn colId="0">
-      <filters blank="1"/>
-    </filterColumn>
+    <filterColumn colId="0"/>
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4325,7 +4330,6 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:G97"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
@@ -4356,7 +4360,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7" hidden="1">
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -4377,7 +4381,7 @@
       </c>
       <c r="G2"/>
     </row>
-    <row r="3" spans="1:7" hidden="1">
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -4398,7 +4402,7 @@
       </c>
       <c r="G3"/>
     </row>
-    <row r="4" spans="1:7" hidden="1">
+    <row r="4" spans="1:7">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -4419,127 +4423,217 @@
       </c>
       <c r="G4"/>
     </row>
-    <row r="5" spans="1:7" hidden="1">
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
         <v>8</v>
       </c>
+      <c r="B5" t="s">
+        <v>304</v>
+      </c>
+      <c r="C5" t="s">
+        <v>304</v>
+      </c>
       <c r="D5" t="s">
         <v>262</v>
       </c>
+      <c r="E5" t="s">
+        <v>304</v>
+      </c>
       <c r="F5" t="s">
         <v>261</v>
       </c>
       <c r="G5"/>
     </row>
-    <row r="6" spans="1:7" hidden="1">
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
         <v>9</v>
       </c>
+      <c r="B6" t="s">
+        <v>304</v>
+      </c>
+      <c r="C6" t="s">
+        <v>304</v>
+      </c>
       <c r="D6" t="s">
         <v>262</v>
       </c>
+      <c r="E6" t="s">
+        <v>304</v>
+      </c>
       <c r="F6" t="s">
         <v>261</v>
       </c>
       <c r="G6"/>
     </row>
-    <row r="7" spans="1:7" hidden="1">
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
         <v>10</v>
       </c>
+      <c r="B7" t="s">
+        <v>304</v>
+      </c>
+      <c r="C7" t="s">
+        <v>304</v>
+      </c>
       <c r="D7" t="s">
         <v>262</v>
       </c>
+      <c r="E7" t="s">
+        <v>304</v>
+      </c>
       <c r="F7" t="s">
         <v>261</v>
       </c>
       <c r="G7"/>
     </row>
-    <row r="8" spans="1:7" hidden="1">
+    <row r="8" spans="1:7">
       <c r="A8" t="s">
         <v>11</v>
       </c>
+      <c r="B8" t="s">
+        <v>304</v>
+      </c>
+      <c r="C8" t="s">
+        <v>304</v>
+      </c>
       <c r="D8" t="s">
         <v>262</v>
       </c>
+      <c r="E8" t="s">
+        <v>304</v>
+      </c>
       <c r="F8" t="s">
         <v>261</v>
       </c>
       <c r="G8"/>
     </row>
-    <row r="9" spans="1:7" hidden="1">
+    <row r="9" spans="1:7">
       <c r="A9" t="s">
         <v>12</v>
       </c>
+      <c r="B9" t="s">
+        <v>304</v>
+      </c>
+      <c r="C9" t="s">
+        <v>304</v>
+      </c>
       <c r="D9" t="s">
         <v>262</v>
       </c>
+      <c r="E9" t="s">
+        <v>304</v>
+      </c>
       <c r="F9" t="s">
         <v>261</v>
       </c>
       <c r="G9"/>
     </row>
-    <row r="10" spans="1:7" hidden="1">
+    <row r="10" spans="1:7">
       <c r="A10" t="s">
         <v>13</v>
       </c>
+      <c r="B10" t="s">
+        <v>304</v>
+      </c>
+      <c r="C10" t="s">
+        <v>304</v>
+      </c>
       <c r="D10" t="s">
         <v>262</v>
       </c>
+      <c r="E10" t="s">
+        <v>304</v>
+      </c>
       <c r="F10" t="s">
         <v>261</v>
       </c>
       <c r="G10"/>
     </row>
-    <row r="11" spans="1:7" hidden="1">
+    <row r="11" spans="1:7">
       <c r="A11" t="s">
         <v>14</v>
       </c>
+      <c r="B11" t="s">
+        <v>304</v>
+      </c>
+      <c r="C11" t="s">
+        <v>304</v>
+      </c>
       <c r="D11" t="s">
         <v>262</v>
       </c>
+      <c r="E11" t="s">
+        <v>305</v>
+      </c>
       <c r="F11" t="s">
         <v>261</v>
       </c>
       <c r="G11"/>
     </row>
-    <row r="12" spans="1:7" hidden="1">
+    <row r="12" spans="1:7">
       <c r="A12" t="s">
         <v>15</v>
       </c>
+      <c r="B12" t="s">
+        <v>304</v>
+      </c>
+      <c r="C12" t="s">
+        <v>304</v>
+      </c>
       <c r="D12" t="s">
         <v>262</v>
       </c>
+      <c r="E12" t="s">
+        <v>305</v>
+      </c>
       <c r="F12" t="s">
         <v>261</v>
       </c>
       <c r="G12"/>
     </row>
-    <row r="13" spans="1:7" hidden="1">
+    <row r="13" spans="1:7">
       <c r="A13" t="s">
         <v>16</v>
       </c>
+      <c r="B13" t="s">
+        <v>304</v>
+      </c>
+      <c r="C13" t="s">
+        <v>304</v>
+      </c>
       <c r="D13" t="s">
         <v>262</v>
       </c>
+      <c r="E13" t="s">
+        <v>305</v>
+      </c>
       <c r="F13" t="s">
         <v>261</v>
       </c>
       <c r="G13"/>
     </row>
-    <row r="14" spans="1:7" hidden="1">
+    <row r="14" spans="1:7">
       <c r="A14" t="s">
         <v>17</v>
       </c>
+      <c r="B14" t="s">
+        <v>304</v>
+      </c>
+      <c r="C14" t="s">
+        <v>304</v>
+      </c>
       <c r="D14" t="s">
         <v>262</v>
       </c>
+      <c r="E14" t="s">
+        <v>305</v>
+      </c>
       <c r="F14" t="s">
         <v>261</v>
       </c>
       <c r="G14"/>
     </row>
-    <row r="15" spans="1:7" hidden="1">
+    <row r="15" spans="1:7">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -4560,7 +4654,7 @@
       </c>
       <c r="G15"/>
     </row>
-    <row r="16" spans="1:7" hidden="1">
+    <row r="16" spans="1:7">
       <c r="A16" t="s">
         <v>19</v>
       </c>
@@ -4581,7 +4675,7 @@
       </c>
       <c r="G16"/>
     </row>
-    <row r="17" spans="1:7" hidden="1">
+    <row r="17" spans="1:7">
       <c r="A17" t="s">
         <v>20</v>
       </c>
@@ -4602,7 +4696,7 @@
       </c>
       <c r="G17"/>
     </row>
-    <row r="18" spans="1:7" hidden="1">
+    <row r="18" spans="1:7">
       <c r="A18" t="s">
         <v>21</v>
       </c>
@@ -4623,55 +4717,91 @@
       </c>
       <c r="G18"/>
     </row>
-    <row r="19" spans="1:7" hidden="1">
+    <row r="19" spans="1:7">
       <c r="A19" t="s">
         <v>22</v>
       </c>
+      <c r="B19" t="s">
+        <v>304</v>
+      </c>
+      <c r="C19" t="s">
+        <v>304</v>
+      </c>
       <c r="D19" t="s">
         <v>262</v>
       </c>
+      <c r="E19" t="s">
+        <v>304</v>
+      </c>
       <c r="F19" t="s">
         <v>261</v>
       </c>
       <c r="G19"/>
     </row>
-    <row r="20" spans="1:7" hidden="1">
+    <row r="20" spans="1:7">
       <c r="A20" t="s">
         <v>23</v>
       </c>
+      <c r="B20" t="s">
+        <v>304</v>
+      </c>
+      <c r="C20" t="s">
+        <v>304</v>
+      </c>
       <c r="D20" t="s">
         <v>262</v>
       </c>
+      <c r="E20" t="s">
+        <v>304</v>
+      </c>
       <c r="F20" t="s">
         <v>261</v>
       </c>
       <c r="G20"/>
     </row>
-    <row r="21" spans="1:7" hidden="1">
+    <row r="21" spans="1:7">
       <c r="A21" t="s">
         <v>24</v>
       </c>
+      <c r="B21" t="s">
+        <v>304</v>
+      </c>
+      <c r="C21" t="s">
+        <v>304</v>
+      </c>
       <c r="D21" t="s">
         <v>262</v>
       </c>
+      <c r="E21" t="s">
+        <v>304</v>
+      </c>
       <c r="F21" t="s">
         <v>261</v>
       </c>
       <c r="G21"/>
     </row>
-    <row r="22" spans="1:7" hidden="1">
+    <row r="22" spans="1:7">
       <c r="A22" t="s">
         <v>25</v>
       </c>
+      <c r="B22" t="s">
+        <v>304</v>
+      </c>
+      <c r="C22" t="s">
+        <v>304</v>
+      </c>
       <c r="D22" t="s">
         <v>262</v>
       </c>
+      <c r="E22" t="s">
+        <v>304</v>
+      </c>
       <c r="F22" t="s">
         <v>261</v>
       </c>
       <c r="G22"/>
     </row>
-    <row r="23" spans="1:7" hidden="1">
+    <row r="23" spans="1:7">
       <c r="A23" t="s">
         <v>26</v>
       </c>
@@ -4689,7 +4819,7 @@
       </c>
       <c r="G23"/>
     </row>
-    <row r="24" spans="1:7" hidden="1">
+    <row r="24" spans="1:7">
       <c r="A24" t="s">
         <v>27</v>
       </c>
@@ -4707,7 +4837,7 @@
       </c>
       <c r="G24"/>
     </row>
-    <row r="25" spans="1:7" hidden="1">
+    <row r="25" spans="1:7">
       <c r="A25" t="s">
         <v>28</v>
       </c>
@@ -4725,7 +4855,7 @@
       </c>
       <c r="G25"/>
     </row>
-    <row r="26" spans="1:7" hidden="1">
+    <row r="26" spans="1:7">
       <c r="A26" t="s">
         <v>29</v>
       </c>
@@ -4743,7 +4873,7 @@
       </c>
       <c r="G26"/>
     </row>
-    <row r="27" spans="1:7" hidden="1">
+    <row r="27" spans="1:7">
       <c r="A27" t="s">
         <v>30</v>
       </c>
@@ -4761,7 +4891,7 @@
       </c>
       <c r="G27"/>
     </row>
-    <row r="28" spans="1:7" hidden="1">
+    <row r="28" spans="1:7">
       <c r="A28" t="s">
         <v>31</v>
       </c>
@@ -4781,7 +4911,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="29" spans="1:7" hidden="1">
+    <row r="29" spans="1:7">
       <c r="A29" t="s">
         <v>32</v>
       </c>
@@ -4799,7 +4929,7 @@
       </c>
       <c r="G29"/>
     </row>
-    <row r="30" spans="1:7" hidden="1">
+    <row r="30" spans="1:7">
       <c r="A30" t="s">
         <v>33</v>
       </c>
@@ -4817,7 +4947,7 @@
       </c>
       <c r="G30"/>
     </row>
-    <row r="31" spans="1:7" hidden="1">
+    <row r="31" spans="1:7">
       <c r="A31" t="s">
         <v>34</v>
       </c>
@@ -4835,7 +4965,7 @@
       </c>
       <c r="G31"/>
     </row>
-    <row r="32" spans="1:7" hidden="1">
+    <row r="32" spans="1:7">
       <c r="A32" t="s">
         <v>35</v>
       </c>
@@ -4853,7 +4983,7 @@
       </c>
       <c r="G32"/>
     </row>
-    <row r="33" spans="1:7" hidden="1">
+    <row r="33" spans="1:7">
       <c r="A33" t="s">
         <v>282</v>
       </c>
@@ -4873,7 +5003,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="34" spans="1:7" hidden="1">
+    <row r="34" spans="1:7">
       <c r="A34" t="s">
         <v>36</v>
       </c>
@@ -4891,7 +5021,7 @@
       </c>
       <c r="G34"/>
     </row>
-    <row r="35" spans="1:7" hidden="1">
+    <row r="35" spans="1:7">
       <c r="A35" t="s">
         <v>37</v>
       </c>
@@ -4909,7 +5039,7 @@
       </c>
       <c r="G35"/>
     </row>
-    <row r="36" spans="1:7" hidden="1">
+    <row r="36" spans="1:7">
       <c r="A36" t="s">
         <v>38</v>
       </c>
@@ -4927,7 +5057,7 @@
       </c>
       <c r="G36"/>
     </row>
-    <row r="37" spans="1:7" hidden="1">
+    <row r="37" spans="1:7">
       <c r="A37" t="s">
         <v>39</v>
       </c>
@@ -4947,7 +5077,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="38" spans="1:7" hidden="1">
+    <row r="38" spans="1:7">
       <c r="A38" t="s">
         <v>40</v>
       </c>
@@ -4965,7 +5095,7 @@
       </c>
       <c r="G38"/>
     </row>
-    <row r="39" spans="1:7" hidden="1">
+    <row r="39" spans="1:7">
       <c r="A39" t="s">
         <v>41</v>
       </c>
@@ -4983,7 +5113,7 @@
       </c>
       <c r="G39"/>
     </row>
-    <row r="40" spans="1:7" hidden="1">
+    <row r="40" spans="1:7">
       <c r="A40" t="s">
         <v>42</v>
       </c>
@@ -5003,7 +5133,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="41" spans="1:7" hidden="1">
+    <row r="41" spans="1:7">
       <c r="A41" t="s">
         <v>43</v>
       </c>
@@ -5024,7 +5154,7 @@
       </c>
       <c r="G41"/>
     </row>
-    <row r="42" spans="1:7" hidden="1">
+    <row r="42" spans="1:7">
       <c r="A42" t="s">
         <v>44</v>
       </c>
@@ -5045,7 +5175,7 @@
       </c>
       <c r="G42"/>
     </row>
-    <row r="43" spans="1:7" hidden="1">
+    <row r="43" spans="1:7">
       <c r="A43" t="s">
         <v>45</v>
       </c>
@@ -5066,7 +5196,7 @@
       </c>
       <c r="G43"/>
     </row>
-    <row r="44" spans="1:7" hidden="1">
+    <row r="44" spans="1:7">
       <c r="A44" t="s">
         <v>46</v>
       </c>
@@ -5087,7 +5217,7 @@
       </c>
       <c r="G44"/>
     </row>
-    <row r="45" spans="1:7" hidden="1">
+    <row r="45" spans="1:7">
       <c r="A45" t="s">
         <v>47</v>
       </c>
@@ -5108,7 +5238,7 @@
       </c>
       <c r="G45"/>
     </row>
-    <row r="46" spans="1:7" hidden="1">
+    <row r="46" spans="1:7">
       <c r="A46" t="s">
         <v>48</v>
       </c>
@@ -5129,36 +5259,63 @@
       </c>
       <c r="G46"/>
     </row>
-    <row r="47" spans="1:7" hidden="1">
+    <row r="47" spans="1:7">
       <c r="A47" t="s">
         <v>49</v>
       </c>
+      <c r="B47" t="s">
+        <v>304</v>
+      </c>
+      <c r="C47" t="s">
+        <v>304</v>
+      </c>
       <c r="D47" t="s">
         <v>262</v>
       </c>
+      <c r="E47" t="s">
+        <v>304</v>
+      </c>
       <c r="F47" t="s">
         <v>261</v>
       </c>
       <c r="G47"/>
     </row>
-    <row r="48" spans="1:7" hidden="1">
+    <row r="48" spans="1:7">
       <c r="A48" t="s">
         <v>50</v>
       </c>
+      <c r="B48" t="s">
+        <v>304</v>
+      </c>
+      <c r="C48" t="s">
+        <v>304</v>
+      </c>
       <c r="D48" t="s">
         <v>262</v>
       </c>
+      <c r="E48" t="s">
+        <v>304</v>
+      </c>
       <c r="F48" t="s">
         <v>261</v>
       </c>
       <c r="G48"/>
     </row>
-    <row r="49" spans="1:7" hidden="1">
+    <row r="49" spans="1:7">
       <c r="A49" t="s">
         <v>51</v>
       </c>
+      <c r="B49" t="s">
+        <v>305</v>
+      </c>
+      <c r="C49" t="s">
+        <v>305</v>
+      </c>
       <c r="D49" t="s">
         <v>262</v>
+      </c>
+      <c r="E49" t="s">
+        <v>304</v>
       </c>
       <c r="F49" t="s">
         <v>261</v>
@@ -5508,7 +5665,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="73" spans="1:7" hidden="1">
+    <row r="73" spans="1:7">
       <c r="A73" t="s">
         <v>75</v>
       </c>
@@ -5529,7 +5686,7 @@
       </c>
       <c r="G73"/>
     </row>
-    <row r="74" spans="1:7" hidden="1">
+    <row r="74" spans="1:7">
       <c r="A74" t="s">
         <v>76</v>
       </c>
@@ -5552,7 +5709,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="75" spans="1:7" hidden="1">
+    <row r="75" spans="1:7">
       <c r="A75" t="s">
         <v>77</v>
       </c>
@@ -5575,7 +5732,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="76" spans="1:7" hidden="1">
+    <row r="76" spans="1:7">
       <c r="A76" t="s">
         <v>78</v>
       </c>
@@ -5598,7 +5755,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="77" spans="1:7" hidden="1">
+    <row r="77" spans="1:7">
       <c r="A77" t="s">
         <v>79</v>
       </c>
@@ -5621,7 +5778,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="78" spans="1:7" hidden="1">
+    <row r="78" spans="1:7">
       <c r="A78" t="s">
         <v>80</v>
       </c>
@@ -5729,7 +5886,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="85" spans="1:7" hidden="1">
+    <row r="85" spans="1:7">
       <c r="A85" t="s">
         <v>87</v>
       </c>
@@ -5747,7 +5904,7 @@
       </c>
       <c r="G85"/>
     </row>
-    <row r="86" spans="1:7" hidden="1">
+    <row r="86" spans="1:7">
       <c r="A86" t="s">
         <v>88</v>
       </c>
@@ -5765,7 +5922,7 @@
       </c>
       <c r="G86"/>
     </row>
-    <row r="87" spans="1:7" hidden="1">
+    <row r="87" spans="1:7">
       <c r="A87" t="s">
         <v>89</v>
       </c>
@@ -5783,7 +5940,7 @@
       </c>
       <c r="G87"/>
     </row>
-    <row r="88" spans="1:7" hidden="1">
+    <row r="88" spans="1:7">
       <c r="A88" t="s">
         <v>90</v>
       </c>
@@ -5803,7 +5960,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="89" spans="1:7" hidden="1">
+    <row r="89" spans="1:7">
       <c r="A89" t="s">
         <v>91</v>
       </c>
@@ -5821,7 +5978,7 @@
       </c>
       <c r="G89"/>
     </row>
-    <row r="90" spans="1:7" hidden="1">
+    <row r="90" spans="1:7">
       <c r="A90" t="s">
         <v>92</v>
       </c>
@@ -5881,7 +6038,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="94" spans="1:7" hidden="1">
+    <row r="94" spans="1:7">
       <c r="A94" t="s">
         <v>96</v>
       </c>
@@ -5899,7 +6056,7 @@
       </c>
       <c r="G94"/>
     </row>
-    <row r="95" spans="1:7" hidden="1">
+    <row r="95" spans="1:7">
       <c r="A95" t="s">
         <v>97</v>
       </c>
@@ -5917,7 +6074,7 @@
       </c>
       <c r="G95"/>
     </row>
-    <row r="96" spans="1:7" hidden="1">
+    <row r="96" spans="1:7">
       <c r="A96" t="s">
         <v>98</v>
       </c>
@@ -5935,7 +6092,7 @@
       </c>
       <c r="G96"/>
     </row>
-    <row r="97" spans="1:7" hidden="1">
+    <row r="97" spans="1:7">
       <c r="A97" t="s">
         <v>99</v>
       </c>
@@ -5960,11 +6117,7 @@
     </row>
   </sheetData>
   <autoFilter ref="D1:D97">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="卢伟康"/>
-      </filters>
-    </filterColumn>
+    <filterColumn colId="0"/>
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/internal_doc/05.测试设计/story/事务支持RC隔离级别/事务自动化用例跟踪表.xlsx
+++ b/internal_doc/05.测试设计/story/事务支持RC隔离级别/事务自动化用例跟踪表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="RU" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1427" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1426" uniqueCount="306">
   <si>
     <t>用例编号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -945,10 +945,6 @@
   </si>
   <si>
     <t>注释的用例标题有误</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>通过问题单SEQUOIADBMAINSTREAM-4113跟踪检视任务</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1006,6 +1002,10 @@
   </si>
   <si>
     <t>否</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>是</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4330,6 +4330,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:G97"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
@@ -4360,7 +4361,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" hidden="1">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -4381,7 +4382,7 @@
       </c>
       <c r="G2"/>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" hidden="1">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -4402,7 +4403,7 @@
       </c>
       <c r="G3"/>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" hidden="1">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -4423,217 +4424,217 @@
       </c>
       <c r="G4"/>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" hidden="1">
       <c r="A5" t="s">
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C5" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D5" t="s">
         <v>262</v>
       </c>
       <c r="E5" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F5" t="s">
         <v>261</v>
       </c>
       <c r="G5"/>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" hidden="1">
       <c r="A6" t="s">
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C6" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D6" t="s">
         <v>262</v>
       </c>
       <c r="E6" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F6" t="s">
         <v>261</v>
       </c>
       <c r="G6"/>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" hidden="1">
       <c r="A7" t="s">
         <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C7" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D7" t="s">
         <v>262</v>
       </c>
       <c r="E7" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F7" t="s">
         <v>261</v>
       </c>
       <c r="G7"/>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" hidden="1">
       <c r="A8" t="s">
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C8" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D8" t="s">
         <v>262</v>
       </c>
       <c r="E8" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F8" t="s">
         <v>261</v>
       </c>
       <c r="G8"/>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" hidden="1">
       <c r="A9" t="s">
         <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C9" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D9" t="s">
         <v>262</v>
       </c>
       <c r="E9" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F9" t="s">
         <v>261</v>
       </c>
       <c r="G9"/>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" hidden="1">
       <c r="A10" t="s">
         <v>13</v>
       </c>
       <c r="B10" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C10" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D10" t="s">
         <v>262</v>
       </c>
       <c r="E10" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F10" t="s">
         <v>261</v>
       </c>
       <c r="G10"/>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" hidden="1">
       <c r="A11" t="s">
         <v>14</v>
       </c>
       <c r="B11" t="s">
+        <v>303</v>
+      </c>
+      <c r="C11" t="s">
+        <v>303</v>
+      </c>
+      <c r="D11" t="s">
+        <v>262</v>
+      </c>
+      <c r="E11" t="s">
         <v>304</v>
       </c>
-      <c r="C11" t="s">
-        <v>304</v>
-      </c>
-      <c r="D11" t="s">
-        <v>262</v>
-      </c>
-      <c r="E11" t="s">
-        <v>305</v>
-      </c>
       <c r="F11" t="s">
         <v>261</v>
       </c>
       <c r="G11"/>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" hidden="1">
       <c r="A12" t="s">
         <v>15</v>
       </c>
       <c r="B12" t="s">
+        <v>303</v>
+      </c>
+      <c r="C12" t="s">
+        <v>303</v>
+      </c>
+      <c r="D12" t="s">
+        <v>262</v>
+      </c>
+      <c r="E12" t="s">
         <v>304</v>
       </c>
-      <c r="C12" t="s">
-        <v>304</v>
-      </c>
-      <c r="D12" t="s">
-        <v>262</v>
-      </c>
-      <c r="E12" t="s">
-        <v>305</v>
-      </c>
       <c r="F12" t="s">
         <v>261</v>
       </c>
       <c r="G12"/>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" hidden="1">
       <c r="A13" t="s">
         <v>16</v>
       </c>
       <c r="B13" t="s">
+        <v>303</v>
+      </c>
+      <c r="C13" t="s">
+        <v>303</v>
+      </c>
+      <c r="D13" t="s">
+        <v>262</v>
+      </c>
+      <c r="E13" t="s">
         <v>304</v>
       </c>
-      <c r="C13" t="s">
-        <v>304</v>
-      </c>
-      <c r="D13" t="s">
-        <v>262</v>
-      </c>
-      <c r="E13" t="s">
-        <v>305</v>
-      </c>
       <c r="F13" t="s">
         <v>261</v>
       </c>
       <c r="G13"/>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" hidden="1">
       <c r="A14" t="s">
         <v>17</v>
       </c>
       <c r="B14" t="s">
+        <v>303</v>
+      </c>
+      <c r="C14" t="s">
+        <v>303</v>
+      </c>
+      <c r="D14" t="s">
+        <v>262</v>
+      </c>
+      <c r="E14" t="s">
         <v>304</v>
       </c>
-      <c r="C14" t="s">
-        <v>304</v>
-      </c>
-      <c r="D14" t="s">
-        <v>262</v>
-      </c>
-      <c r="E14" t="s">
-        <v>305</v>
-      </c>
       <c r="F14" t="s">
         <v>261</v>
       </c>
       <c r="G14"/>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" hidden="1">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -4654,7 +4655,7 @@
       </c>
       <c r="G15"/>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" hidden="1">
       <c r="A16" t="s">
         <v>19</v>
       </c>
@@ -4675,7 +4676,7 @@
       </c>
       <c r="G16"/>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" hidden="1">
       <c r="A17" t="s">
         <v>20</v>
       </c>
@@ -4696,7 +4697,7 @@
       </c>
       <c r="G17"/>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" hidden="1">
       <c r="A18" t="s">
         <v>21</v>
       </c>
@@ -4717,91 +4718,91 @@
       </c>
       <c r="G18"/>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" hidden="1">
       <c r="A19" t="s">
         <v>22</v>
       </c>
       <c r="B19" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C19" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D19" t="s">
         <v>262</v>
       </c>
       <c r="E19" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F19" t="s">
         <v>261</v>
       </c>
       <c r="G19"/>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" hidden="1">
       <c r="A20" t="s">
         <v>23</v>
       </c>
       <c r="B20" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C20" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D20" t="s">
         <v>262</v>
       </c>
       <c r="E20" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F20" t="s">
         <v>261</v>
       </c>
       <c r="G20"/>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" hidden="1">
       <c r="A21" t="s">
         <v>24</v>
       </c>
       <c r="B21" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C21" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D21" t="s">
         <v>262</v>
       </c>
       <c r="E21" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F21" t="s">
         <v>261</v>
       </c>
       <c r="G21"/>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" hidden="1">
       <c r="A22" t="s">
         <v>25</v>
       </c>
       <c r="B22" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C22" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D22" t="s">
         <v>262</v>
       </c>
       <c r="E22" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F22" t="s">
         <v>261</v>
       </c>
       <c r="G22"/>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" hidden="1">
       <c r="A23" t="s">
         <v>26</v>
       </c>
@@ -4819,7 +4820,7 @@
       </c>
       <c r="G23"/>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" hidden="1">
       <c r="A24" t="s">
         <v>27</v>
       </c>
@@ -4837,7 +4838,7 @@
       </c>
       <c r="G24"/>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" hidden="1">
       <c r="A25" t="s">
         <v>28</v>
       </c>
@@ -4855,7 +4856,7 @@
       </c>
       <c r="G25"/>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" hidden="1">
       <c r="A26" t="s">
         <v>29</v>
       </c>
@@ -4873,7 +4874,7 @@
       </c>
       <c r="G26"/>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" hidden="1">
       <c r="A27" t="s">
         <v>30</v>
       </c>
@@ -4891,7 +4892,7 @@
       </c>
       <c r="G27"/>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" hidden="1">
       <c r="A28" t="s">
         <v>31</v>
       </c>
@@ -4911,7 +4912,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" hidden="1">
       <c r="A29" t="s">
         <v>32</v>
       </c>
@@ -4929,7 +4930,7 @@
       </c>
       <c r="G29"/>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" hidden="1">
       <c r="A30" t="s">
         <v>33</v>
       </c>
@@ -4947,7 +4948,7 @@
       </c>
       <c r="G30"/>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" hidden="1">
       <c r="A31" t="s">
         <v>34</v>
       </c>
@@ -4965,7 +4966,7 @@
       </c>
       <c r="G31"/>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" hidden="1">
       <c r="A32" t="s">
         <v>35</v>
       </c>
@@ -4983,7 +4984,7 @@
       </c>
       <c r="G32"/>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" hidden="1">
       <c r="A33" t="s">
         <v>282</v>
       </c>
@@ -5003,7 +5004,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" hidden="1">
       <c r="A34" t="s">
         <v>36</v>
       </c>
@@ -5021,7 +5022,7 @@
       </c>
       <c r="G34"/>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" hidden="1">
       <c r="A35" t="s">
         <v>37</v>
       </c>
@@ -5039,7 +5040,7 @@
       </c>
       <c r="G35"/>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" hidden="1">
       <c r="A36" t="s">
         <v>38</v>
       </c>
@@ -5057,7 +5058,7 @@
       </c>
       <c r="G36"/>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" hidden="1">
       <c r="A37" t="s">
         <v>39</v>
       </c>
@@ -5077,7 +5078,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" hidden="1">
       <c r="A38" t="s">
         <v>40</v>
       </c>
@@ -5095,7 +5096,7 @@
       </c>
       <c r="G38"/>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" hidden="1">
       <c r="A39" t="s">
         <v>41</v>
       </c>
@@ -5113,7 +5114,7 @@
       </c>
       <c r="G39"/>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:7" hidden="1">
       <c r="A40" t="s">
         <v>42</v>
       </c>
@@ -5133,7 +5134,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" hidden="1">
       <c r="A41" t="s">
         <v>43</v>
       </c>
@@ -5154,7 +5155,7 @@
       </c>
       <c r="G41"/>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:7" hidden="1">
       <c r="A42" t="s">
         <v>44</v>
       </c>
@@ -5175,7 +5176,7 @@
       </c>
       <c r="G42"/>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" hidden="1">
       <c r="A43" t="s">
         <v>45</v>
       </c>
@@ -5196,7 +5197,7 @@
       </c>
       <c r="G43"/>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:7" hidden="1">
       <c r="A44" t="s">
         <v>46</v>
       </c>
@@ -5217,7 +5218,7 @@
       </c>
       <c r="G44"/>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:7" hidden="1">
       <c r="A45" t="s">
         <v>47</v>
       </c>
@@ -5238,7 +5239,7 @@
       </c>
       <c r="G45"/>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:7" hidden="1">
       <c r="A46" t="s">
         <v>48</v>
       </c>
@@ -5259,63 +5260,63 @@
       </c>
       <c r="G46"/>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" hidden="1">
       <c r="A47" t="s">
         <v>49</v>
       </c>
       <c r="B47" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C47" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D47" t="s">
         <v>262</v>
       </c>
       <c r="E47" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F47" t="s">
         <v>261</v>
       </c>
       <c r="G47"/>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:7" hidden="1">
       <c r="A48" t="s">
         <v>50</v>
       </c>
       <c r="B48" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C48" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D48" t="s">
         <v>262</v>
       </c>
       <c r="E48" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F48" t="s">
         <v>261</v>
       </c>
       <c r="G48"/>
     </row>
-    <row r="49" spans="1:7">
+    <row r="49" spans="1:7" hidden="1">
       <c r="A49" t="s">
         <v>51</v>
       </c>
       <c r="B49" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C49" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D49" t="s">
         <v>262</v>
       </c>
       <c r="E49" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F49" t="s">
         <v>261</v>
@@ -5527,7 +5528,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="64" spans="1:7" ht="40.5">
+    <row r="64" spans="1:7">
       <c r="A64" t="s">
         <v>66</v>
       </c>
@@ -5535,13 +5536,10 @@
         <v>264</v>
       </c>
       <c r="E64" t="s">
-        <v>288</v>
+        <v>305</v>
       </c>
       <c r="F64" t="s">
         <v>261</v>
-      </c>
-      <c r="G64" s="1" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="65" spans="1:7" ht="40.5">
@@ -5558,7 +5556,7 @@
         <v>261</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="66" spans="1:7" ht="40.5">
@@ -5575,7 +5573,7 @@
         <v>261</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -5606,7 +5604,7 @@
         <v>261</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -5665,7 +5663,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="73" spans="1:7">
+    <row r="73" spans="1:7" hidden="1">
       <c r="A73" t="s">
         <v>75</v>
       </c>
@@ -5686,7 +5684,7 @@
       </c>
       <c r="G73"/>
     </row>
-    <row r="74" spans="1:7">
+    <row r="74" spans="1:7" hidden="1">
       <c r="A74" t="s">
         <v>76</v>
       </c>
@@ -5709,7 +5707,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="75" spans="1:7">
+    <row r="75" spans="1:7" hidden="1">
       <c r="A75" t="s">
         <v>77</v>
       </c>
@@ -5732,7 +5730,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="76" spans="1:7">
+    <row r="76" spans="1:7" hidden="1">
       <c r="A76" t="s">
         <v>78</v>
       </c>
@@ -5755,7 +5753,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="77" spans="1:7">
+    <row r="77" spans="1:7" hidden="1">
       <c r="A77" t="s">
         <v>79</v>
       </c>
@@ -5778,7 +5776,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="78" spans="1:7">
+    <row r="78" spans="1:7" hidden="1">
       <c r="A78" t="s">
         <v>80</v>
       </c>
@@ -5813,7 +5811,7 @@
         <v>261</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="80" spans="1:7" ht="27">
@@ -5827,7 +5825,7 @@
         <v>261</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="81" spans="1:7" ht="27">
@@ -5841,7 +5839,7 @@
         <v>261</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="82" spans="1:7" ht="27">
@@ -5855,7 +5853,7 @@
         <v>261</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="83" spans="1:7" ht="27">
@@ -5869,7 +5867,7 @@
         <v>261</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="84" spans="1:7" ht="27">
@@ -5883,10 +5881,10 @@
         <v>261</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" hidden="1">
       <c r="A85" t="s">
         <v>87</v>
       </c>
@@ -5904,7 +5902,7 @@
       </c>
       <c r="G85"/>
     </row>
-    <row r="86" spans="1:7">
+    <row r="86" spans="1:7" hidden="1">
       <c r="A86" t="s">
         <v>88</v>
       </c>
@@ -5922,7 +5920,7 @@
       </c>
       <c r="G86"/>
     </row>
-    <row r="87" spans="1:7">
+    <row r="87" spans="1:7" hidden="1">
       <c r="A87" t="s">
         <v>89</v>
       </c>
@@ -5940,7 +5938,7 @@
       </c>
       <c r="G87"/>
     </row>
-    <row r="88" spans="1:7">
+    <row r="88" spans="1:7" hidden="1">
       <c r="A88" t="s">
         <v>90</v>
       </c>
@@ -5960,7 +5958,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="89" spans="1:7">
+    <row r="89" spans="1:7" hidden="1">
       <c r="A89" t="s">
         <v>91</v>
       </c>
@@ -5978,7 +5976,7 @@
       </c>
       <c r="G89"/>
     </row>
-    <row r="90" spans="1:7">
+    <row r="90" spans="1:7" hidden="1">
       <c r="A90" t="s">
         <v>92</v>
       </c>
@@ -6007,7 +6005,7 @@
         <v>261</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="92" spans="1:7" ht="27">
@@ -6021,7 +6019,7 @@
         <v>261</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="93" spans="1:7" ht="27">
@@ -6035,10 +6033,10 @@
         <v>261</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" hidden="1">
       <c r="A94" t="s">
         <v>96</v>
       </c>
@@ -6056,7 +6054,7 @@
       </c>
       <c r="G94"/>
     </row>
-    <row r="95" spans="1:7">
+    <row r="95" spans="1:7" hidden="1">
       <c r="A95" t="s">
         <v>97</v>
       </c>
@@ -6074,7 +6072,7 @@
       </c>
       <c r="G95"/>
     </row>
-    <row r="96" spans="1:7">
+    <row r="96" spans="1:7" hidden="1">
       <c r="A96" t="s">
         <v>98</v>
       </c>
@@ -6092,7 +6090,7 @@
       </c>
       <c r="G96"/>
     </row>
-    <row r="97" spans="1:7">
+    <row r="97" spans="1:7" hidden="1">
       <c r="A97" t="s">
         <v>99</v>
       </c>
@@ -6117,7 +6115,11 @@
     </row>
   </sheetData>
   <autoFilter ref="D1:D97">
-    <filterColumn colId="0"/>
+    <filterColumn colId="0">
+      <filters>
+        <filter val="卢伟康"/>
+      </filters>
+    </filterColumn>
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6137,18 +6139,18 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
+        <v>295</v>
+      </c>
+      <c r="B1" t="s">
         <v>296</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>297</v>
-      </c>
-      <c r="C1" t="s">
-        <v>298</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -6198,7 +6200,7 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -6253,12 +6255,12 @@
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="25" spans="1:1">
@@ -6318,7 +6320,7 @@
     </row>
     <row r="36" spans="1:1">
       <c r="A36" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="37" spans="1:1">

--- a/internal_doc/05.测试设计/story/事务支持RC隔离级别/事务自动化用例跟踪表.xlsx
+++ b/internal_doc/05.测试设计/story/事务支持RC隔离级别/事务自动化用例跟踪表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="2"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="RU" sheetId="1" r:id="rId1"/>
@@ -13,8 +13,8 @@
     <sheet name="RC不等锁增加逆序索引及逆序查询任务" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">RC不等锁!$D$1:$D$97</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">RC等锁!$E$1:$E$67</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">RC不等锁!$D$1:$D$102</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">RC等锁!$D$1:$D$67</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">RU!$E$1:$E$94</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1426" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1479" uniqueCount="316">
   <si>
     <t>用例编号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1006,6 +1006,46 @@
   </si>
   <si>
     <t>是</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>否</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>手工用例修改，自动化需对应做调整</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-17942</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-17943</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-17944</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-17945</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-17960</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>是</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>调试通过，待提交</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>调试不通过，问题单4245</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3087,6 +3127,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:G67"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
@@ -3116,7 +3157,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" hidden="1">
       <c r="A2" t="s">
         <v>100</v>
       </c>
@@ -3127,7 +3168,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" hidden="1">
       <c r="A3" t="s">
         <v>101</v>
       </c>
@@ -3138,7 +3179,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" hidden="1">
       <c r="A4" t="s">
         <v>102</v>
       </c>
@@ -3149,7 +3190,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" hidden="1">
       <c r="A5" t="s">
         <v>103</v>
       </c>
@@ -3169,7 +3210,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" hidden="1">
       <c r="A6" t="s">
         <v>104</v>
       </c>
@@ -3189,7 +3230,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" hidden="1">
       <c r="A7" t="s">
         <v>105</v>
       </c>
@@ -3209,7 +3250,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" hidden="1">
       <c r="A8" t="s">
         <v>106</v>
       </c>
@@ -3229,7 +3270,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" hidden="1">
       <c r="A9" t="s">
         <v>107</v>
       </c>
@@ -3249,7 +3290,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" hidden="1">
       <c r="A10" t="s">
         <v>108</v>
       </c>
@@ -3269,7 +3310,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" hidden="1">
       <c r="A11" t="s">
         <v>109</v>
       </c>
@@ -3289,7 +3330,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" hidden="1">
       <c r="A12" t="s">
         <v>110</v>
       </c>
@@ -3309,7 +3350,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" hidden="1">
       <c r="A13" t="s">
         <v>111</v>
       </c>
@@ -3329,7 +3370,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" hidden="1">
       <c r="A14" t="s">
         <v>112</v>
       </c>
@@ -3349,7 +3390,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" hidden="1">
       <c r="A15" t="s">
         <v>113</v>
       </c>
@@ -3360,7 +3401,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" hidden="1">
       <c r="A16" t="s">
         <v>114</v>
       </c>
@@ -3371,7 +3412,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" hidden="1">
       <c r="A17" t="s">
         <v>115</v>
       </c>
@@ -3382,7 +3423,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" hidden="1">
       <c r="A18" t="s">
         <v>116</v>
       </c>
@@ -3393,7 +3434,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:6" hidden="1">
       <c r="A19" t="s">
         <v>117</v>
       </c>
@@ -3413,7 +3454,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:6" hidden="1">
       <c r="A20" t="s">
         <v>118</v>
       </c>
@@ -3433,7 +3474,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:6" hidden="1">
       <c r="A21" t="s">
         <v>119</v>
       </c>
@@ -3453,7 +3494,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:6" hidden="1">
       <c r="A22" t="s">
         <v>120</v>
       </c>
@@ -3693,7 +3734,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" hidden="1">
       <c r="A34" t="s">
         <v>132</v>
       </c>
@@ -3704,7 +3745,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" hidden="1">
       <c r="A35" t="s">
         <v>133</v>
       </c>
@@ -3715,7 +3756,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" hidden="1">
       <c r="A36" t="s">
         <v>134</v>
       </c>
@@ -3726,7 +3767,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" hidden="1">
       <c r="A37" t="s">
         <v>135</v>
       </c>
@@ -3737,7 +3778,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" hidden="1">
       <c r="A38" t="s">
         <v>136</v>
       </c>
@@ -3748,7 +3789,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" hidden="1">
       <c r="A39" t="s">
         <v>137</v>
       </c>
@@ -3759,7 +3800,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:7" hidden="1">
       <c r="A40" t="s">
         <v>138</v>
       </c>
@@ -3779,7 +3820,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" hidden="1">
       <c r="A41" t="s">
         <v>139</v>
       </c>
@@ -3939,7 +3980,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="49" spans="1:7">
+    <row r="49" spans="1:7" hidden="1">
       <c r="A49" t="s">
         <v>144</v>
       </c>
@@ -3959,7 +4000,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="50" spans="1:7">
+    <row r="50" spans="1:7" hidden="1">
       <c r="A50" t="s">
         <v>145</v>
       </c>
@@ -3979,7 +4020,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="51" spans="1:7">
+    <row r="51" spans="1:7" hidden="1">
       <c r="A51" t="s">
         <v>146</v>
       </c>
@@ -3999,7 +4040,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="52" spans="1:7">
+    <row r="52" spans="1:7" hidden="1">
       <c r="A52" t="s">
         <v>147</v>
       </c>
@@ -4019,7 +4060,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="53" spans="1:7">
+    <row r="53" spans="1:7" hidden="1">
       <c r="A53" t="s">
         <v>148</v>
       </c>
@@ -4039,7 +4080,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="54" spans="1:7">
+    <row r="54" spans="1:7" hidden="1">
       <c r="A54" t="s">
         <v>149</v>
       </c>
@@ -4179,7 +4220,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="61" spans="1:7">
+    <row r="61" spans="1:7" hidden="1">
       <c r="A61" t="s">
         <v>157</v>
       </c>
@@ -4199,7 +4240,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="62" spans="1:7">
+    <row r="62" spans="1:7" hidden="1">
       <c r="A62" t="s">
         <v>158</v>
       </c>
@@ -4219,7 +4260,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="63" spans="1:7">
+    <row r="63" spans="1:7" hidden="1">
       <c r="A63" t="s">
         <v>159</v>
       </c>
@@ -4320,8 +4361,12 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="E1:E67">
-    <filterColumn colId="0"/>
+  <autoFilter ref="D1:D67">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="赵育"/>
+      </filters>
+    </filterColumn>
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4331,7 +4376,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:G97"/>
+  <dimension ref="A1:G102"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="6" width="20.625" customWidth="1"/>
@@ -4424,7 +4469,7 @@
       </c>
       <c r="G4"/>
     </row>
-    <row r="5" spans="1:7" hidden="1">
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -4445,7 +4490,7 @@
       </c>
       <c r="G5"/>
     </row>
-    <row r="6" spans="1:7" hidden="1">
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -4466,7 +4511,7 @@
       </c>
       <c r="G6"/>
     </row>
-    <row r="7" spans="1:7" hidden="1">
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -4487,7 +4532,7 @@
       </c>
       <c r="G7"/>
     </row>
-    <row r="8" spans="1:7" hidden="1">
+    <row r="8" spans="1:7">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -4508,7 +4553,7 @@
       </c>
       <c r="G8"/>
     </row>
-    <row r="9" spans="1:7" hidden="1">
+    <row r="9" spans="1:7">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -4529,7 +4574,7 @@
       </c>
       <c r="G9"/>
     </row>
-    <row r="10" spans="1:7" hidden="1">
+    <row r="10" spans="1:7">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -4550,7 +4595,7 @@
       </c>
       <c r="G10"/>
     </row>
-    <row r="11" spans="1:7" hidden="1">
+    <row r="11" spans="1:7">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -4571,7 +4616,7 @@
       </c>
       <c r="G11"/>
     </row>
-    <row r="12" spans="1:7" hidden="1">
+    <row r="12" spans="1:7">
       <c r="A12" t="s">
         <v>15</v>
       </c>
@@ -4592,7 +4637,7 @@
       </c>
       <c r="G12"/>
     </row>
-    <row r="13" spans="1:7" hidden="1">
+    <row r="13" spans="1:7">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -4613,7 +4658,7 @@
       </c>
       <c r="G13"/>
     </row>
-    <row r="14" spans="1:7" hidden="1">
+    <row r="14" spans="1:7">
       <c r="A14" t="s">
         <v>17</v>
       </c>
@@ -4718,7 +4763,7 @@
       </c>
       <c r="G18"/>
     </row>
-    <row r="19" spans="1:7" hidden="1">
+    <row r="19" spans="1:7">
       <c r="A19" t="s">
         <v>22</v>
       </c>
@@ -4739,7 +4784,7 @@
       </c>
       <c r="G19"/>
     </row>
-    <row r="20" spans="1:7" hidden="1">
+    <row r="20" spans="1:7">
       <c r="A20" t="s">
         <v>23</v>
       </c>
@@ -4760,7 +4805,7 @@
       </c>
       <c r="G20"/>
     </row>
-    <row r="21" spans="1:7" hidden="1">
+    <row r="21" spans="1:7">
       <c r="A21" t="s">
         <v>24</v>
       </c>
@@ -4781,7 +4826,7 @@
       </c>
       <c r="G21"/>
     </row>
-    <row r="22" spans="1:7" hidden="1">
+    <row r="22" spans="1:7">
       <c r="A22" t="s">
         <v>25</v>
       </c>
@@ -5260,7 +5305,7 @@
       </c>
       <c r="G46"/>
     </row>
-    <row r="47" spans="1:7" hidden="1">
+    <row r="47" spans="1:7">
       <c r="A47" t="s">
         <v>49</v>
       </c>
@@ -5274,14 +5319,16 @@
         <v>262</v>
       </c>
       <c r="E47" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="F47" t="s">
         <v>261</v>
       </c>
-      <c r="G47"/>
-    </row>
-    <row r="48" spans="1:7" hidden="1">
+      <c r="G47" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
       <c r="A48" t="s">
         <v>50</v>
       </c>
@@ -5295,14 +5342,16 @@
         <v>262</v>
       </c>
       <c r="E48" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="F48" t="s">
         <v>261</v>
       </c>
-      <c r="G48"/>
-    </row>
-    <row r="49" spans="1:7" hidden="1">
+      <c r="G48" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
       <c r="A49" t="s">
         <v>51</v>
       </c>
@@ -5323,7 +5372,7 @@
       </c>
       <c r="G49"/>
     </row>
-    <row r="50" spans="1:7">
+    <row r="50" spans="1:7" hidden="1">
       <c r="A50" t="s">
         <v>52</v>
       </c>
@@ -5337,7 +5386,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="51" spans="1:7">
+    <row r="51" spans="1:7" hidden="1">
       <c r="A51" t="s">
         <v>53</v>
       </c>
@@ -5351,7 +5400,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="52" spans="1:7">
+    <row r="52" spans="1:7" hidden="1">
       <c r="A52" t="s">
         <v>54</v>
       </c>
@@ -5365,7 +5414,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="53" spans="1:7" ht="40.5">
+    <row r="53" spans="1:7" ht="40.5" hidden="1">
       <c r="A53" t="s">
         <v>55</v>
       </c>
@@ -5382,7 +5431,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="54" spans="1:7">
+    <row r="54" spans="1:7" hidden="1">
       <c r="A54" t="s">
         <v>56</v>
       </c>
@@ -5396,7 +5445,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="55" spans="1:7">
+    <row r="55" spans="1:7" hidden="1">
       <c r="A55" t="s">
         <v>57</v>
       </c>
@@ -5410,7 +5459,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="56" spans="1:7">
+    <row r="56" spans="1:7" hidden="1">
       <c r="A56" t="s">
         <v>58</v>
       </c>
@@ -5424,7 +5473,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="57" spans="1:7">
+    <row r="57" spans="1:7" hidden="1">
       <c r="A57" t="s">
         <v>59</v>
       </c>
@@ -5438,7 +5487,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="58" spans="1:7">
+    <row r="58" spans="1:7" hidden="1">
       <c r="A58" t="s">
         <v>60</v>
       </c>
@@ -5452,7 +5501,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="59" spans="1:7">
+    <row r="59" spans="1:7" hidden="1">
       <c r="A59" t="s">
         <v>61</v>
       </c>
@@ -5466,7 +5515,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="60" spans="1:7">
+    <row r="60" spans="1:7" hidden="1">
       <c r="A60" t="s">
         <v>62</v>
       </c>
@@ -5483,7 +5532,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="61" spans="1:7" ht="40.5">
+    <row r="61" spans="1:7" ht="40.5" hidden="1">
       <c r="A61" t="s">
         <v>63</v>
       </c>
@@ -5500,7 +5549,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="62" spans="1:7">
+    <row r="62" spans="1:7" hidden="1">
       <c r="A62" t="s">
         <v>64</v>
       </c>
@@ -5514,7 +5563,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="63" spans="1:7">
+    <row r="63" spans="1:7" hidden="1">
       <c r="A63" t="s">
         <v>65</v>
       </c>
@@ -5528,7 +5577,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="64" spans="1:7">
+    <row r="64" spans="1:7" hidden="1">
       <c r="A64" t="s">
         <v>66</v>
       </c>
@@ -5542,7 +5591,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="65" spans="1:7" ht="40.5">
+    <row r="65" spans="1:7" ht="40.5" hidden="1">
       <c r="A65" t="s">
         <v>67</v>
       </c>
@@ -5559,7 +5608,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="66" spans="1:7" ht="40.5">
+    <row r="66" spans="1:7" ht="40.5" hidden="1">
       <c r="A66" t="s">
         <v>68</v>
       </c>
@@ -5576,7 +5625,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="67" spans="1:7">
+    <row r="67" spans="1:7" hidden="1">
       <c r="A67" t="s">
         <v>69</v>
       </c>
@@ -5590,7 +5639,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="68" spans="1:7" ht="121.5">
+    <row r="68" spans="1:7" ht="121.5" hidden="1">
       <c r="A68" t="s">
         <v>70</v>
       </c>
@@ -5607,7 +5656,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="69" spans="1:7">
+    <row r="69" spans="1:7" hidden="1">
       <c r="A69" t="s">
         <v>71</v>
       </c>
@@ -5621,7 +5670,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="70" spans="1:7">
+    <row r="70" spans="1:7" hidden="1">
       <c r="A70" t="s">
         <v>72</v>
       </c>
@@ -5635,7 +5684,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="71" spans="1:7">
+    <row r="71" spans="1:7" hidden="1">
       <c r="A71" t="s">
         <v>73</v>
       </c>
@@ -5649,7 +5698,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="72" spans="1:7">
+    <row r="72" spans="1:7" hidden="1">
       <c r="A72" t="s">
         <v>74</v>
       </c>
@@ -5797,7 +5846,7 @@
       </c>
       <c r="G78"/>
     </row>
-    <row r="79" spans="1:7" ht="27">
+    <row r="79" spans="1:7" ht="27" hidden="1">
       <c r="A79" t="s">
         <v>81</v>
       </c>
@@ -5814,7 +5863,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="80" spans="1:7" ht="27">
+    <row r="80" spans="1:7" ht="27" hidden="1">
       <c r="A80" t="s">
         <v>82</v>
       </c>
@@ -5828,7 +5877,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="81" spans="1:7" ht="27">
+    <row r="81" spans="1:7" ht="27" hidden="1">
       <c r="A81" t="s">
         <v>83</v>
       </c>
@@ -5842,7 +5891,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="82" spans="1:7" ht="27">
+    <row r="82" spans="1:7" ht="27" hidden="1">
       <c r="A82" t="s">
         <v>84</v>
       </c>
@@ -5856,7 +5905,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="83" spans="1:7" ht="27">
+    <row r="83" spans="1:7" ht="27" hidden="1">
       <c r="A83" t="s">
         <v>85</v>
       </c>
@@ -5870,7 +5919,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="84" spans="1:7" ht="27">
+    <row r="84" spans="1:7" ht="27" hidden="1">
       <c r="A84" t="s">
         <v>86</v>
       </c>
@@ -5994,7 +6043,7 @@
       </c>
       <c r="G90"/>
     </row>
-    <row r="91" spans="1:7" ht="27">
+    <row r="91" spans="1:7" ht="27" hidden="1">
       <c r="A91" t="s">
         <v>93</v>
       </c>
@@ -6008,7 +6057,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="92" spans="1:7" ht="27">
+    <row r="92" spans="1:7" ht="27" hidden="1">
       <c r="A92" t="s">
         <v>94</v>
       </c>
@@ -6022,7 +6071,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="93" spans="1:7" ht="27">
+    <row r="93" spans="1:7" ht="27" hidden="1">
       <c r="A93" t="s">
         <v>95</v>
       </c>
@@ -6113,11 +6162,66 @@
         <v>269</v>
       </c>
     </row>
+    <row r="98" spans="1:7" hidden="1">
+      <c r="A98" t="s">
+        <v>308</v>
+      </c>
+      <c r="E98" t="s">
+        <v>268</v>
+      </c>
+      <c r="G98" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" hidden="1">
+      <c r="A99" t="s">
+        <v>309</v>
+      </c>
+      <c r="E99" t="s">
+        <v>268</v>
+      </c>
+      <c r="G99" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" hidden="1">
+      <c r="A100" t="s">
+        <v>310</v>
+      </c>
+      <c r="E100" t="s">
+        <v>268</v>
+      </c>
+      <c r="G100" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" hidden="1">
+      <c r="A101" t="s">
+        <v>311</v>
+      </c>
+      <c r="E101" t="s">
+        <v>268</v>
+      </c>
+      <c r="G101" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" hidden="1">
+      <c r="A102" t="s">
+        <v>312</v>
+      </c>
+      <c r="E102" t="s">
+        <v>268</v>
+      </c>
+      <c r="G102" t="s">
+        <v>269</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="D1:D97">
+  <autoFilter ref="D1:D102">
     <filterColumn colId="0">
       <filters>
-        <filter val="卢伟康"/>
+        <filter val="赵小妮"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -6134,7 +6238,7 @@
   <cols>
     <col min="1" max="1" width="18.5" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="3" width="18.625" customWidth="1"/>
+    <col min="3" max="3" width="29.75" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -6223,129 +6327,237 @@
         <v>39</v>
       </c>
     </row>
-    <row r="17" spans="1:1">
+    <row r="17" spans="1:3">
       <c r="A17" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="18" spans="1:1">
+    <row r="18" spans="1:3">
       <c r="A18" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="19" spans="1:1">
+    <row r="19" spans="1:3">
       <c r="A19" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="20" spans="1:1">
+    <row r="20" spans="1:3">
       <c r="A20" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="21" spans="1:1">
+    <row r="21" spans="1:3">
       <c r="A21" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="22" spans="1:1">
+    <row r="22" spans="1:3">
       <c r="A22" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="23" spans="1:1">
+    <row r="23" spans="1:3">
       <c r="A23" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="24" spans="1:1">
+    <row r="24" spans="1:3">
       <c r="A24" t="s">
         <v>301</v>
       </c>
-    </row>
-    <row r="25" spans="1:1">
+      <c r="B24" t="s">
+        <v>313</v>
+      </c>
+      <c r="C24" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
       <c r="A25" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="26" spans="1:1">
+      <c r="B25" t="s">
+        <v>313</v>
+      </c>
+      <c r="C25" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
       <c r="A26" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="27" spans="1:1">
+      <c r="B26" t="s">
+        <v>313</v>
+      </c>
+      <c r="C26" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
       <c r="A27" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="28" spans="1:1">
+      <c r="B27" t="s">
+        <v>313</v>
+      </c>
+      <c r="C27" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
       <c r="A28" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="29" spans="1:1">
+      <c r="B28" t="s">
+        <v>313</v>
+      </c>
+      <c r="C28" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
       <c r="A29" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="30" spans="1:1">
+      <c r="B29" t="s">
+        <v>313</v>
+      </c>
+      <c r="C29" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
       <c r="A30" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="31" spans="1:1">
+      <c r="B30" t="s">
+        <v>313</v>
+      </c>
+      <c r="C30" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
       <c r="A31" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="32" spans="1:1">
+      <c r="B31" t="s">
+        <v>313</v>
+      </c>
+      <c r="C31" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
       <c r="A32" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="33" spans="1:1">
+      <c r="B32" t="s">
+        <v>313</v>
+      </c>
+      <c r="C32" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
       <c r="A33" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="34" spans="1:1">
+      <c r="B33" t="s">
+        <v>313</v>
+      </c>
+      <c r="C33" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
       <c r="A34" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="35" spans="1:1">
+      <c r="B34" t="s">
+        <v>313</v>
+      </c>
+      <c r="C34" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
       <c r="A35" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="36" spans="1:1">
+      <c r="B35" t="s">
+        <v>313</v>
+      </c>
+      <c r="C35" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
       <c r="A36" t="s">
         <v>302</v>
       </c>
-    </row>
-    <row r="37" spans="1:1">
+      <c r="B36" t="s">
+        <v>313</v>
+      </c>
+      <c r="C36" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
       <c r="A37" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="38" spans="1:1">
+      <c r="B37" t="s">
+        <v>313</v>
+      </c>
+      <c r="C37" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
       <c r="A38" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="39" spans="1:1">
+      <c r="B38" t="s">
+        <v>313</v>
+      </c>
+      <c r="C38" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
       <c r="A39" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="40" spans="1:1">
+      <c r="B39" t="s">
+        <v>313</v>
+      </c>
+      <c r="C39" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
       <c r="A40" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="41" spans="1:1">
+      <c r="B40" t="s">
+        <v>313</v>
+      </c>
+      <c r="C40" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
       <c r="A41" t="s">
         <v>98</v>
+      </c>
+      <c r="B41" t="s">
+        <v>313</v>
+      </c>
+      <c r="C41" t="s">
+        <v>315</v>
       </c>
     </row>
   </sheetData>

--- a/internal_doc/05.测试设计/story/事务支持RC隔离级别/事务自动化用例跟踪表.xlsx
+++ b/internal_doc/05.测试设计/story/事务支持RC隔离级别/事务自动化用例跟踪表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="3"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="RU" sheetId="1" r:id="rId1"/>
@@ -14,15 +14,15 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">RC不等锁!$D$1:$D$102</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">RC等锁!$D$1:$D$67</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">RU!$E$1:$E$94</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">RC等锁!$A$1:$G$67</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">RU!$D$1:$D$94</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1479" uniqueCount="316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1468" uniqueCount="313">
   <si>
     <t>用例编号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -498,9 +498,6 @@
     <t>seqDB-17770</t>
   </si>
   <si>
-    <t>seqDB-17771</t>
-  </si>
-  <si>
     <t>seqDB-17772</t>
   </si>
   <si>
@@ -849,11 +846,38 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>是</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>否</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>需新增自动化用例</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>资料用例</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>节点重启用例，待提交</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>配置验证，不实现自动化</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>全文索引用例，待提交</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>是</t>
+  </si>
+  <si>
+    <t>是</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -861,70 +885,31 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>需新增自动化用例</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>资料用例</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>节点重启用例，待提交</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>配置验证，不实现自动化</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>全文索引用例，待提交</t>
+    <t>尹臻</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>赵小妮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>版本问题，部分用例未提交</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>卢伟康</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-17102</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>是</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>是</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>否</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>尹臻</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>赵小妮</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>版本问题，部分用例未提交</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>卢伟康</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>版本问题，用例未提交</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>seqDB-17102</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>是</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>是</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>否</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1046,6 +1031,10 @@
   </si>
   <si>
     <t>调试不通过，问题单4245</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-17771</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1406,13 +1395,13 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E1" t="s">
         <v>3</v>
       </c>
       <c r="F1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="G1" t="s">
         <v>4</v>
@@ -1420,22 +1409,22 @@
     </row>
     <row r="2" spans="1:7" hidden="1">
       <c r="A2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="D2" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="3" spans="1:7" hidden="1">
@@ -1443,19 +1432,19 @@
         <v>140</v>
       </c>
       <c r="B3" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C3" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="D3" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E3" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="4" spans="1:7" hidden="1">
@@ -1463,1660 +1452,1662 @@
         <v>141</v>
       </c>
       <c r="B4" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C4" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="D4" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E4" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F4" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" hidden="1">
       <c r="A5" t="s">
+        <v>169</v>
+      </c>
+      <c r="D5" t="s">
+        <v>261</v>
+      </c>
+      <c r="F5" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" hidden="1">
+      <c r="A6" t="s">
         <v>170</v>
       </c>
-      <c r="D5" t="s">
-        <v>262</v>
-      </c>
-      <c r="F5" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" t="s">
+      <c r="D6" t="s">
+        <v>261</v>
+      </c>
+      <c r="F6" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" hidden="1">
+      <c r="A7" t="s">
         <v>171</v>
       </c>
-      <c r="D6" t="s">
-        <v>262</v>
-      </c>
-      <c r="F6" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" t="s">
+      <c r="D7" t="s">
+        <v>261</v>
+      </c>
+      <c r="F7" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" hidden="1">
+      <c r="A8" t="s">
         <v>172</v>
       </c>
-      <c r="D7" t="s">
-        <v>262</v>
-      </c>
-      <c r="F7" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" t="s">
+      <c r="D8" t="s">
+        <v>261</v>
+      </c>
+      <c r="F8" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" hidden="1">
+      <c r="A9" t="s">
         <v>173</v>
       </c>
-      <c r="D8" t="s">
-        <v>262</v>
-      </c>
-      <c r="F8" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" t="s">
+      <c r="D9" t="s">
+        <v>261</v>
+      </c>
+      <c r="F9" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" hidden="1">
+      <c r="A10" t="s">
         <v>174</v>
       </c>
-      <c r="D9" t="s">
-        <v>262</v>
-      </c>
-      <c r="F9" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" t="s">
+      <c r="D10" t="s">
+        <v>261</v>
+      </c>
+      <c r="F10" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" hidden="1">
+      <c r="A11" t="s">
         <v>175</v>
       </c>
-      <c r="D10" t="s">
-        <v>262</v>
-      </c>
-      <c r="F10" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" t="s">
+      <c r="D11" t="s">
+        <v>261</v>
+      </c>
+      <c r="F11" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" hidden="1">
+      <c r="A12" t="s">
         <v>176</v>
       </c>
-      <c r="D11" t="s">
-        <v>262</v>
-      </c>
-      <c r="F11" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" t="s">
+      <c r="D12" t="s">
+        <v>261</v>
+      </c>
+      <c r="F12" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" hidden="1">
+      <c r="A13" t="s">
         <v>177</v>
       </c>
-      <c r="D12" t="s">
-        <v>262</v>
-      </c>
-      <c r="F12" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13" t="s">
+      <c r="D13" t="s">
+        <v>261</v>
+      </c>
+      <c r="F13" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" hidden="1">
+      <c r="A14" t="s">
         <v>178</v>
       </c>
-      <c r="D13" t="s">
-        <v>262</v>
-      </c>
-      <c r="F13" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" t="s">
-        <v>179</v>
-      </c>
       <c r="D14" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="F14" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="15" spans="1:7" hidden="1">
       <c r="A15" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B15" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C15" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="D15" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E15" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F15" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="16" spans="1:7" hidden="1">
       <c r="A16" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B16" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C16" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="D16" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E16" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F16" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="17" spans="1:6" hidden="1">
       <c r="A17" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B17" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C17" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="D17" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E17" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F17" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="18" spans="1:6" hidden="1">
       <c r="A18" t="s">
+        <v>182</v>
+      </c>
+      <c r="B18" t="s">
+        <v>273</v>
+      </c>
+      <c r="C18" t="s">
+        <v>273</v>
+      </c>
+      <c r="D18" t="s">
+        <v>262</v>
+      </c>
+      <c r="E18" t="s">
+        <v>273</v>
+      </c>
+      <c r="F18" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" hidden="1">
+      <c r="A19" t="s">
         <v>183</v>
       </c>
-      <c r="B18" t="s">
+      <c r="D19" t="s">
+        <v>261</v>
+      </c>
+      <c r="F19" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" hidden="1">
+      <c r="A20" t="s">
+        <v>184</v>
+      </c>
+      <c r="D20" t="s">
+        <v>261</v>
+      </c>
+      <c r="F20" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" hidden="1">
+      <c r="A21" t="s">
+        <v>185</v>
+      </c>
+      <c r="D21" t="s">
+        <v>261</v>
+      </c>
+      <c r="F21" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" hidden="1">
+      <c r="A22" t="s">
+        <v>186</v>
+      </c>
+      <c r="D22" t="s">
+        <v>261</v>
+      </c>
+      <c r="F22" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" t="s">
+        <v>187</v>
+      </c>
+      <c r="B23" t="s">
+        <v>264</v>
+      </c>
+      <c r="C23" t="s">
+        <v>264</v>
+      </c>
+      <c r="D23" t="s">
+        <v>260</v>
+      </c>
+      <c r="E23" t="s">
+        <v>280</v>
+      </c>
+      <c r="F23" t="s">
         <v>275</v>
       </c>
-      <c r="C18" t="s">
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" t="s">
+        <v>188</v>
+      </c>
+      <c r="B24" t="s">
+        <v>264</v>
+      </c>
+      <c r="C24" t="s">
+        <v>264</v>
+      </c>
+      <c r="D24" t="s">
+        <v>260</v>
+      </c>
+      <c r="E24" t="s">
+        <v>280</v>
+      </c>
+      <c r="F24" t="s">
         <v>275</v>
       </c>
-      <c r="D18" t="s">
-        <v>263</v>
-      </c>
-      <c r="E18" t="s">
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25" t="s">
+        <v>189</v>
+      </c>
+      <c r="B25" t="s">
+        <v>264</v>
+      </c>
+      <c r="C25" t="s">
+        <v>264</v>
+      </c>
+      <c r="D25" t="s">
+        <v>260</v>
+      </c>
+      <c r="E25" t="s">
+        <v>280</v>
+      </c>
+      <c r="F25" t="s">
         <v>275</v>
       </c>
-      <c r="F18" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19" t="s">
-        <v>184</v>
-      </c>
-      <c r="D19" t="s">
-        <v>262</v>
-      </c>
-      <c r="F19" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20" t="s">
-        <v>185</v>
-      </c>
-      <c r="D20" t="s">
-        <v>262</v>
-      </c>
-      <c r="F20" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21" t="s">
-        <v>186</v>
-      </c>
-      <c r="D21" t="s">
-        <v>262</v>
-      </c>
-      <c r="F21" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22" t="s">
-        <v>187</v>
-      </c>
-      <c r="D22" t="s">
-        <v>262</v>
-      </c>
-      <c r="F22" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" hidden="1">
-      <c r="A23" t="s">
-        <v>188</v>
-      </c>
-      <c r="B23" t="s">
-        <v>265</v>
-      </c>
-      <c r="C23" t="s">
-        <v>265</v>
-      </c>
-      <c r="D23" t="s">
-        <v>261</v>
-      </c>
-      <c r="E23" t="s">
-        <v>283</v>
-      </c>
-      <c r="F23" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" hidden="1">
-      <c r="A24" t="s">
-        <v>189</v>
-      </c>
-      <c r="B24" t="s">
-        <v>265</v>
-      </c>
-      <c r="C24" t="s">
-        <v>265</v>
-      </c>
-      <c r="D24" t="s">
-        <v>261</v>
-      </c>
-      <c r="E24" t="s">
-        <v>283</v>
-      </c>
-      <c r="F24" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" hidden="1">
-      <c r="A25" t="s">
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26" t="s">
         <v>190</v>
       </c>
-      <c r="B25" t="s">
-        <v>265</v>
-      </c>
-      <c r="C25" t="s">
-        <v>265</v>
-      </c>
-      <c r="D25" t="s">
-        <v>261</v>
-      </c>
-      <c r="E25" t="s">
-        <v>283</v>
-      </c>
-      <c r="F25" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" hidden="1">
-      <c r="A26" t="s">
+      <c r="B26" t="s">
+        <v>264</v>
+      </c>
+      <c r="C26" t="s">
+        <v>264</v>
+      </c>
+      <c r="D26" t="s">
+        <v>260</v>
+      </c>
+      <c r="E26" t="s">
+        <v>280</v>
+      </c>
+      <c r="F26" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27" t="s">
         <v>191</v>
       </c>
-      <c r="B26" t="s">
-        <v>265</v>
-      </c>
-      <c r="C26" t="s">
-        <v>265</v>
-      </c>
-      <c r="D26" t="s">
-        <v>261</v>
-      </c>
-      <c r="E26" t="s">
-        <v>283</v>
-      </c>
-      <c r="F26" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" hidden="1">
-      <c r="A27" t="s">
+      <c r="B27" t="s">
+        <v>264</v>
+      </c>
+      <c r="C27" t="s">
+        <v>264</v>
+      </c>
+      <c r="D27" t="s">
+        <v>260</v>
+      </c>
+      <c r="E27" t="s">
+        <v>280</v>
+      </c>
+      <c r="F27" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28" t="s">
         <v>192</v>
       </c>
-      <c r="B27" t="s">
-        <v>265</v>
-      </c>
-      <c r="C27" t="s">
-        <v>265</v>
-      </c>
-      <c r="D27" t="s">
-        <v>261</v>
-      </c>
-      <c r="E27" t="s">
-        <v>283</v>
-      </c>
-      <c r="F27" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" hidden="1">
-      <c r="A28" t="s">
+      <c r="B28" t="s">
+        <v>264</v>
+      </c>
+      <c r="C28" t="s">
+        <v>264</v>
+      </c>
+      <c r="D28" t="s">
+        <v>260</v>
+      </c>
+      <c r="E28" t="s">
+        <v>280</v>
+      </c>
+      <c r="F28" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29" t="s">
         <v>193</v>
       </c>
-      <c r="B28" t="s">
-        <v>265</v>
-      </c>
-      <c r="C28" t="s">
-        <v>265</v>
-      </c>
-      <c r="D28" t="s">
-        <v>261</v>
-      </c>
-      <c r="E28" t="s">
-        <v>283</v>
-      </c>
-      <c r="F28" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" hidden="1">
-      <c r="A29" t="s">
+      <c r="B29" t="s">
+        <v>264</v>
+      </c>
+      <c r="C29" t="s">
+        <v>264</v>
+      </c>
+      <c r="D29" t="s">
+        <v>260</v>
+      </c>
+      <c r="E29" t="s">
+        <v>280</v>
+      </c>
+      <c r="F29" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30" t="s">
         <v>194</v>
       </c>
-      <c r="B29" t="s">
-        <v>265</v>
-      </c>
-      <c r="C29" t="s">
-        <v>265</v>
-      </c>
-      <c r="D29" t="s">
-        <v>261</v>
-      </c>
-      <c r="E29" t="s">
-        <v>283</v>
-      </c>
-      <c r="F29" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" hidden="1">
-      <c r="A30" t="s">
+      <c r="B30" t="s">
+        <v>264</v>
+      </c>
+      <c r="C30" t="s">
+        <v>264</v>
+      </c>
+      <c r="D30" t="s">
+        <v>260</v>
+      </c>
+      <c r="E30" t="s">
+        <v>280</v>
+      </c>
+      <c r="F30" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31" t="s">
         <v>195</v>
       </c>
-      <c r="B30" t="s">
-        <v>265</v>
-      </c>
-      <c r="C30" t="s">
-        <v>265</v>
-      </c>
-      <c r="D30" t="s">
-        <v>261</v>
-      </c>
-      <c r="E30" t="s">
-        <v>283</v>
-      </c>
-      <c r="F30" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" hidden="1">
-      <c r="A31" t="s">
+      <c r="B31" t="s">
+        <v>264</v>
+      </c>
+      <c r="C31" t="s">
+        <v>264</v>
+      </c>
+      <c r="D31" t="s">
+        <v>260</v>
+      </c>
+      <c r="E31" t="s">
+        <v>280</v>
+      </c>
+      <c r="F31" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32" t="s">
         <v>196</v>
       </c>
-      <c r="B31" t="s">
-        <v>265</v>
-      </c>
-      <c r="C31" t="s">
-        <v>265</v>
-      </c>
-      <c r="D31" t="s">
-        <v>261</v>
-      </c>
-      <c r="E31" t="s">
-        <v>283</v>
-      </c>
-      <c r="F31" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" hidden="1">
-      <c r="A32" t="s">
+      <c r="B32" t="s">
+        <v>264</v>
+      </c>
+      <c r="C32" t="s">
+        <v>264</v>
+      </c>
+      <c r="D32" t="s">
+        <v>260</v>
+      </c>
+      <c r="E32" t="s">
+        <v>280</v>
+      </c>
+      <c r="F32" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33" t="s">
         <v>197</v>
       </c>
-      <c r="B32" t="s">
-        <v>265</v>
-      </c>
-      <c r="C32" t="s">
-        <v>265</v>
-      </c>
-      <c r="D32" t="s">
-        <v>261</v>
-      </c>
-      <c r="E32" t="s">
-        <v>283</v>
-      </c>
-      <c r="F32" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" hidden="1">
-      <c r="A33" t="s">
+      <c r="B33" t="s">
+        <v>264</v>
+      </c>
+      <c r="C33" t="s">
+        <v>264</v>
+      </c>
+      <c r="D33" t="s">
+        <v>260</v>
+      </c>
+      <c r="E33" t="s">
+        <v>280</v>
+      </c>
+      <c r="F33" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34" t="s">
         <v>198</v>
       </c>
-      <c r="B33" t="s">
-        <v>265</v>
-      </c>
-      <c r="C33" t="s">
-        <v>265</v>
-      </c>
-      <c r="D33" t="s">
-        <v>261</v>
-      </c>
-      <c r="E33" t="s">
-        <v>283</v>
-      </c>
-      <c r="F33" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" hidden="1">
-      <c r="A34" t="s">
+      <c r="B34" t="s">
+        <v>264</v>
+      </c>
+      <c r="C34" t="s">
+        <v>264</v>
+      </c>
+      <c r="D34" t="s">
+        <v>260</v>
+      </c>
+      <c r="E34" t="s">
+        <v>280</v>
+      </c>
+      <c r="F34" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35" t="s">
         <v>199</v>
       </c>
-      <c r="B34" t="s">
-        <v>265</v>
-      </c>
-      <c r="C34" t="s">
-        <v>265</v>
-      </c>
-      <c r="D34" t="s">
-        <v>261</v>
-      </c>
-      <c r="E34" t="s">
-        <v>283</v>
-      </c>
-      <c r="F34" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" hidden="1">
-      <c r="A35" t="s">
+      <c r="B35" t="s">
+        <v>264</v>
+      </c>
+      <c r="C35" t="s">
+        <v>264</v>
+      </c>
+      <c r="D35" t="s">
+        <v>260</v>
+      </c>
+      <c r="E35" t="s">
+        <v>280</v>
+      </c>
+      <c r="F35" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
+      <c r="A36" t="s">
         <v>200</v>
       </c>
-      <c r="B35" t="s">
-        <v>265</v>
-      </c>
-      <c r="C35" t="s">
-        <v>265</v>
-      </c>
-      <c r="D35" t="s">
-        <v>261</v>
-      </c>
-      <c r="E35" t="s">
-        <v>283</v>
-      </c>
-      <c r="F35" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" hidden="1">
-      <c r="A36" t="s">
+      <c r="B36" t="s">
+        <v>264</v>
+      </c>
+      <c r="C36" t="s">
+        <v>264</v>
+      </c>
+      <c r="D36" t="s">
+        <v>260</v>
+      </c>
+      <c r="E36" t="s">
+        <v>280</v>
+      </c>
+      <c r="F36" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
+      <c r="A37" t="s">
         <v>201</v>
       </c>
-      <c r="B36" t="s">
-        <v>265</v>
-      </c>
-      <c r="C36" t="s">
-        <v>265</v>
-      </c>
-      <c r="D36" t="s">
-        <v>261</v>
-      </c>
-      <c r="E36" t="s">
-        <v>283</v>
-      </c>
-      <c r="F36" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" hidden="1">
-      <c r="A37" t="s">
+      <c r="B37" t="s">
+        <v>264</v>
+      </c>
+      <c r="C37" t="s">
+        <v>264</v>
+      </c>
+      <c r="D37" t="s">
+        <v>260</v>
+      </c>
+      <c r="E37" t="s">
+        <v>280</v>
+      </c>
+      <c r="F37" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
+      <c r="A38" t="s">
         <v>202</v>
       </c>
-      <c r="B37" t="s">
-        <v>265</v>
-      </c>
-      <c r="C37" t="s">
-        <v>265</v>
-      </c>
-      <c r="D37" t="s">
-        <v>261</v>
-      </c>
-      <c r="E37" t="s">
-        <v>283</v>
-      </c>
-      <c r="F37" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" hidden="1">
-      <c r="A38" t="s">
+      <c r="B38" t="s">
+        <v>264</v>
+      </c>
+      <c r="C38" t="s">
+        <v>264</v>
+      </c>
+      <c r="D38" t="s">
+        <v>260</v>
+      </c>
+      <c r="E38" t="s">
+        <v>280</v>
+      </c>
+      <c r="F38" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="A39" t="s">
         <v>203</v>
       </c>
-      <c r="B38" t="s">
-        <v>265</v>
-      </c>
-      <c r="C38" t="s">
-        <v>265</v>
-      </c>
-      <c r="D38" t="s">
-        <v>261</v>
-      </c>
-      <c r="E38" t="s">
-        <v>283</v>
-      </c>
-      <c r="F38" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" hidden="1">
-      <c r="A39" t="s">
+      <c r="B39" t="s">
+        <v>264</v>
+      </c>
+      <c r="C39" t="s">
+        <v>264</v>
+      </c>
+      <c r="D39" t="s">
+        <v>260</v>
+      </c>
+      <c r="E39" t="s">
+        <v>280</v>
+      </c>
+      <c r="F39" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="A40" t="s">
         <v>204</v>
       </c>
-      <c r="B39" t="s">
-        <v>265</v>
-      </c>
-      <c r="C39" t="s">
-        <v>265</v>
-      </c>
-      <c r="D39" t="s">
-        <v>261</v>
-      </c>
-      <c r="E39" t="s">
-        <v>283</v>
-      </c>
-      <c r="F39" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" hidden="1">
-      <c r="A40" t="s">
-        <v>205</v>
-      </c>
       <c r="B40" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C40" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D40" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E40" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F40" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="41" spans="1:6" hidden="1">
       <c r="A41" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B41" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C41" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="D41" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E41" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F41" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="42" spans="1:6" hidden="1">
       <c r="A42" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B42" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C42" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="D42" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E42" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F42" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="43" spans="1:6" hidden="1">
       <c r="A43" t="s">
+        <v>207</v>
+      </c>
+      <c r="B43" t="s">
+        <v>273</v>
+      </c>
+      <c r="C43" t="s">
+        <v>273</v>
+      </c>
+      <c r="D43" t="s">
+        <v>262</v>
+      </c>
+      <c r="E43" t="s">
+        <v>273</v>
+      </c>
+      <c r="F43" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" hidden="1">
+      <c r="A44" t="s">
         <v>208</v>
       </c>
-      <c r="B43" t="s">
-        <v>275</v>
-      </c>
-      <c r="C43" t="s">
-        <v>275</v>
-      </c>
-      <c r="D43" t="s">
-        <v>263</v>
-      </c>
-      <c r="E43" t="s">
-        <v>275</v>
-      </c>
-      <c r="F43" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44" t="s">
+      <c r="D44" t="s">
+        <v>261</v>
+      </c>
+      <c r="F44" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" hidden="1">
+      <c r="A45" t="s">
         <v>209</v>
       </c>
-      <c r="D44" t="s">
-        <v>262</v>
-      </c>
-      <c r="F44" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45" t="s">
-        <v>210</v>
-      </c>
       <c r="D45" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="F45" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="46" spans="1:6" hidden="1">
       <c r="A46" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B46" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C46" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="D46" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E46" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F46" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="47" spans="1:6" hidden="1">
       <c r="A47" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B47" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C47" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="D47" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E47" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F47" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="48" spans="1:6" hidden="1">
       <c r="A48" t="s">
+        <v>212</v>
+      </c>
+      <c r="B48" t="s">
+        <v>273</v>
+      </c>
+      <c r="C48" t="s">
+        <v>273</v>
+      </c>
+      <c r="D48" t="s">
+        <v>262</v>
+      </c>
+      <c r="E48" t="s">
+        <v>273</v>
+      </c>
+      <c r="F48" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" hidden="1">
+      <c r="A49" t="s">
         <v>213</v>
       </c>
-      <c r="B48" t="s">
-        <v>275</v>
-      </c>
-      <c r="C48" t="s">
-        <v>275</v>
-      </c>
-      <c r="D48" t="s">
-        <v>263</v>
-      </c>
-      <c r="E48" t="s">
-        <v>275</v>
-      </c>
-      <c r="F48" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
-      <c r="A49" t="s">
-        <v>214</v>
-      </c>
       <c r="D49" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="F49" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="50" spans="1:6" hidden="1">
       <c r="A50" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B50" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="C50" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="D50" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E50" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="F50" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="51" spans="1:6" hidden="1">
       <c r="A51" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B51" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="C51" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="D51" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E51" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="F51" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="52" spans="1:6" hidden="1">
       <c r="A52" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B52" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="C52" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="D52" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E52" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="F52" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="53" spans="1:6" hidden="1">
       <c r="A53" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B53" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="C53" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="D53" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E53" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="F53" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="54" spans="1:6" hidden="1">
       <c r="A54" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B54" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="C54" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="D54" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E54" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="F54" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="55" spans="1:6" hidden="1">
       <c r="A55" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B55" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="C55" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="D55" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E55" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="F55" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="56" spans="1:6" hidden="1">
       <c r="A56" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B56" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="C56" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="D56" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E56" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="F56" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="57" spans="1:6" hidden="1">
       <c r="A57" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B57" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="C57" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="D57" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E57" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="F57" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="58" spans="1:6" hidden="1">
       <c r="A58" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B58" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="C58" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="D58" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E58" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="F58" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="59" spans="1:6" hidden="1">
       <c r="A59" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B59" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="C59" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="D59" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E59" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="F59" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="60" spans="1:6" hidden="1">
       <c r="A60" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B60" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="C60" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="D60" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E60" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="F60" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="61" spans="1:6" hidden="1">
       <c r="A61" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B61" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="C61" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="D61" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E61" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="F61" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="62" spans="1:6" hidden="1">
       <c r="A62" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B62" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="C62" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="D62" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E62" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="F62" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="63" spans="1:6" hidden="1">
       <c r="A63" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B63" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="C63" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="D63" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E63" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="F63" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="64" spans="1:6" hidden="1">
       <c r="A64" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B64" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="C64" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="D64" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E64" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="F64" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="65" spans="1:6" hidden="1">
       <c r="A65" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B65" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="C65" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="D65" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E65" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="F65" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="66" spans="1:6" hidden="1">
       <c r="A66" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B66" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="C66" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="D66" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E66" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="F66" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="67" spans="1:6" hidden="1">
       <c r="A67" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B67" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="C67" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="D67" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E67" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="F67" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="68" spans="1:6" hidden="1">
       <c r="A68" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B68" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="C68" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="D68" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E68" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="F68" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="69" spans="1:6" hidden="1">
       <c r="A69" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B69" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="C69" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="D69" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E69" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="F69" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="70" spans="1:6" hidden="1">
       <c r="A70" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B70" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="C70" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="D70" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E70" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="F70" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="71" spans="1:6" hidden="1">
       <c r="A71" t="s">
+        <v>235</v>
+      </c>
+      <c r="B71" t="s">
+        <v>273</v>
+      </c>
+      <c r="C71" t="s">
+        <v>273</v>
+      </c>
+      <c r="D71" t="s">
+        <v>262</v>
+      </c>
+      <c r="E71" t="s">
+        <v>273</v>
+      </c>
+      <c r="F71" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" hidden="1">
+      <c r="A72" t="s">
         <v>236</v>
       </c>
-      <c r="B71" t="s">
-        <v>275</v>
-      </c>
-      <c r="C71" t="s">
-        <v>275</v>
-      </c>
-      <c r="D71" t="s">
-        <v>263</v>
-      </c>
-      <c r="E71" t="s">
-        <v>275</v>
-      </c>
-      <c r="F71" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6">
-      <c r="A72" t="s">
+      <c r="C72" t="s">
+        <v>274</v>
+      </c>
+      <c r="D72" t="s">
+        <v>262</v>
+      </c>
+      <c r="F72" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" hidden="1">
+      <c r="A73" t="s">
         <v>237</v>
       </c>
-      <c r="C72" t="s">
-        <v>276</v>
-      </c>
-      <c r="D72" t="s">
-        <v>263</v>
-      </c>
-      <c r="F72" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6">
-      <c r="A73" t="s">
-        <v>238</v>
-      </c>
       <c r="C73" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D73" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F73" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="74" spans="1:6" hidden="1">
       <c r="A74" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B74" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C74" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="D74" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E74" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F74" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="75" spans="1:6" hidden="1">
       <c r="A75" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B75" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="C75" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="D75" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E75" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="F75" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="76" spans="1:6" hidden="1">
       <c r="A76" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B76" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="C76" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="D76" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E76" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="F76" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="77" spans="1:6" hidden="1">
       <c r="A77" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B77" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="C77" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="D77" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E77" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="F77" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="78" spans="1:6" hidden="1">
       <c r="A78" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B78" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="C78" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="D78" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E78" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="F78" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="79" spans="1:6" hidden="1">
       <c r="A79" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B79" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="C79" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="D79" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E79" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="F79" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="80" spans="1:6" hidden="1">
       <c r="A80" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B80" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="C80" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="D80" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E80" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="F80" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="81" spans="1:6" hidden="1">
       <c r="A81" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B81" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="C81" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="D81" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E81" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="F81" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="82" spans="1:6" hidden="1">
       <c r="A82" t="s">
+        <v>245</v>
+      </c>
+      <c r="B82" t="s">
+        <v>282</v>
+      </c>
+      <c r="C82" t="s">
+        <v>282</v>
+      </c>
+      <c r="D82" t="s">
+        <v>263</v>
+      </c>
+      <c r="E82" t="s">
+        <v>282</v>
+      </c>
+      <c r="F82" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6">
+      <c r="A83" t="s">
         <v>246</v>
       </c>
-      <c r="B82" t="s">
-        <v>286</v>
-      </c>
-      <c r="C82" t="s">
-        <v>286</v>
-      </c>
-      <c r="D82" t="s">
-        <v>264</v>
-      </c>
-      <c r="E82" t="s">
-        <v>286</v>
-      </c>
-      <c r="F82" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6" hidden="1">
-      <c r="A83" t="s">
+      <c r="B83" t="s">
+        <v>264</v>
+      </c>
+      <c r="C83" t="s">
+        <v>264</v>
+      </c>
+      <c r="D83" t="s">
+        <v>260</v>
+      </c>
+      <c r="E83" t="s">
+        <v>280</v>
+      </c>
+      <c r="F83" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6">
+      <c r="A84" t="s">
         <v>247</v>
       </c>
-      <c r="B83" t="s">
-        <v>265</v>
-      </c>
-      <c r="C83" t="s">
-        <v>265</v>
-      </c>
-      <c r="D83" t="s">
-        <v>261</v>
-      </c>
-      <c r="E83" t="s">
-        <v>283</v>
-      </c>
-      <c r="F83" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" hidden="1">
-      <c r="A84" t="s">
+      <c r="B84" t="s">
+        <v>264</v>
+      </c>
+      <c r="C84" t="s">
+        <v>264</v>
+      </c>
+      <c r="D84" t="s">
+        <v>260</v>
+      </c>
+      <c r="E84" t="s">
+        <v>280</v>
+      </c>
+      <c r="F84" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6">
+      <c r="A85" t="s">
         <v>248</v>
       </c>
-      <c r="B84" t="s">
-        <v>265</v>
-      </c>
-      <c r="C84" t="s">
-        <v>265</v>
-      </c>
-      <c r="D84" t="s">
-        <v>261</v>
-      </c>
-      <c r="E84" t="s">
-        <v>283</v>
-      </c>
-      <c r="F84" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" hidden="1">
-      <c r="A85" t="s">
+      <c r="B85" t="s">
+        <v>264</v>
+      </c>
+      <c r="C85" t="s">
+        <v>264</v>
+      </c>
+      <c r="D85" t="s">
+        <v>260</v>
+      </c>
+      <c r="E85" t="s">
+        <v>280</v>
+      </c>
+      <c r="F85" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6">
+      <c r="A86" t="s">
         <v>249</v>
       </c>
-      <c r="B85" t="s">
-        <v>265</v>
-      </c>
-      <c r="C85" t="s">
-        <v>265</v>
-      </c>
-      <c r="D85" t="s">
-        <v>261</v>
-      </c>
-      <c r="E85" t="s">
-        <v>283</v>
-      </c>
-      <c r="F85" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" hidden="1">
-      <c r="A86" t="s">
+      <c r="B86" t="s">
+        <v>264</v>
+      </c>
+      <c r="C86" t="s">
+        <v>264</v>
+      </c>
+      <c r="D86" t="s">
+        <v>260</v>
+      </c>
+      <c r="E86" t="s">
+        <v>280</v>
+      </c>
+      <c r="F86" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6">
+      <c r="A87" t="s">
         <v>250</v>
       </c>
-      <c r="B86" t="s">
-        <v>265</v>
-      </c>
-      <c r="C86" t="s">
-        <v>265</v>
-      </c>
-      <c r="D86" t="s">
-        <v>261</v>
-      </c>
-      <c r="E86" t="s">
-        <v>283</v>
-      </c>
-      <c r="F86" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6" hidden="1">
-      <c r="A87" t="s">
+      <c r="B87" t="s">
+        <v>264</v>
+      </c>
+      <c r="C87" t="s">
+        <v>264</v>
+      </c>
+      <c r="D87" t="s">
+        <v>260</v>
+      </c>
+      <c r="E87" t="s">
+        <v>280</v>
+      </c>
+      <c r="F87" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6">
+      <c r="A88" t="s">
         <v>251</v>
       </c>
-      <c r="B87" t="s">
-        <v>265</v>
-      </c>
-      <c r="C87" t="s">
-        <v>265</v>
-      </c>
-      <c r="D87" t="s">
-        <v>261</v>
-      </c>
-      <c r="E87" t="s">
-        <v>283</v>
-      </c>
-      <c r="F87" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" hidden="1">
-      <c r="A88" t="s">
-        <v>252</v>
-      </c>
       <c r="B88" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C88" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D88" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E88" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F88" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="89" spans="1:6" hidden="1">
       <c r="A89" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B89" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="C89" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="D89" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E89" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="F89" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="90" spans="1:6" hidden="1">
       <c r="A90" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B90" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="C90" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="D90" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E90" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="F90" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="91" spans="1:6" hidden="1">
       <c r="A91" t="s">
+        <v>254</v>
+      </c>
+      <c r="B91" t="s">
+        <v>282</v>
+      </c>
+      <c r="C91" t="s">
+        <v>282</v>
+      </c>
+      <c r="D91" t="s">
+        <v>263</v>
+      </c>
+      <c r="E91" t="s">
+        <v>282</v>
+      </c>
+      <c r="F91" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6">
+      <c r="A92" t="s">
         <v>255</v>
       </c>
-      <c r="B91" t="s">
-        <v>286</v>
-      </c>
-      <c r="C91" t="s">
-        <v>286</v>
-      </c>
-      <c r="D91" t="s">
-        <v>264</v>
-      </c>
-      <c r="E91" t="s">
-        <v>286</v>
-      </c>
-      <c r="F91" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6" hidden="1">
-      <c r="A92" t="s">
+      <c r="B92" t="s">
+        <v>264</v>
+      </c>
+      <c r="C92" t="s">
+        <v>264</v>
+      </c>
+      <c r="D92" t="s">
+        <v>260</v>
+      </c>
+      <c r="E92" t="s">
+        <v>280</v>
+      </c>
+      <c r="F92" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6">
+      <c r="A93" t="s">
         <v>256</v>
       </c>
-      <c r="B92" t="s">
-        <v>265</v>
-      </c>
-      <c r="C92" t="s">
-        <v>265</v>
-      </c>
-      <c r="D92" t="s">
-        <v>261</v>
-      </c>
-      <c r="E92" t="s">
-        <v>283</v>
-      </c>
-      <c r="F92" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6" hidden="1">
-      <c r="A93" t="s">
+      <c r="B93" t="s">
+        <v>264</v>
+      </c>
+      <c r="C93" t="s">
+        <v>264</v>
+      </c>
+      <c r="D93" t="s">
+        <v>260</v>
+      </c>
+      <c r="E93" t="s">
+        <v>280</v>
+      </c>
+      <c r="F93" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6">
+      <c r="A94" t="s">
         <v>257</v>
       </c>
-      <c r="B93" t="s">
-        <v>265</v>
-      </c>
-      <c r="C93" t="s">
-        <v>265</v>
-      </c>
-      <c r="D93" t="s">
-        <v>261</v>
-      </c>
-      <c r="E93" t="s">
-        <v>283</v>
-      </c>
-      <c r="F93" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6" hidden="1">
-      <c r="A94" t="s">
-        <v>258</v>
-      </c>
       <c r="B94" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C94" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D94" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E94" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F94" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="E1:E94">
+  <autoFilter ref="D1:D94">
     <filterColumn colId="0">
-      <filters blank="1"/>
+      <filters>
+        <filter val="赵育"/>
+      </filters>
     </filterColumn>
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -3145,13 +3136,13 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E1" t="s">
         <v>3</v>
       </c>
       <c r="F1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="G1" t="s">
         <v>4</v>
@@ -3162,10 +3153,10 @@
         <v>100</v>
       </c>
       <c r="D2" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="3" spans="1:7" hidden="1">
@@ -3173,10 +3164,10 @@
         <v>101</v>
       </c>
       <c r="D3" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F3" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="4" spans="1:7" hidden="1">
@@ -3184,10 +3175,10 @@
         <v>102</v>
       </c>
       <c r="D4" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F4" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="5" spans="1:7" hidden="1">
@@ -3195,19 +3186,19 @@
         <v>103</v>
       </c>
       <c r="B5" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="C5" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="D5" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E5" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F5" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="6" spans="1:7" hidden="1">
@@ -3215,19 +3206,19 @@
         <v>104</v>
       </c>
       <c r="B6" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="C6" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="D6" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E6" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F6" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="7" spans="1:7" hidden="1">
@@ -3235,19 +3226,19 @@
         <v>105</v>
       </c>
       <c r="B7" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="C7" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="D7" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E7" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F7" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="8" spans="1:7" hidden="1">
@@ -3255,19 +3246,19 @@
         <v>106</v>
       </c>
       <c r="B8" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="C8" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="D8" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E8" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F8" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="9" spans="1:7" hidden="1">
@@ -3275,19 +3266,19 @@
         <v>107</v>
       </c>
       <c r="B9" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="C9" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="D9" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E9" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F9" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="10" spans="1:7" hidden="1">
@@ -3295,19 +3286,19 @@
         <v>108</v>
       </c>
       <c r="B10" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="C10" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="D10" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E10" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F10" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="11" spans="1:7" hidden="1">
@@ -3315,19 +3306,19 @@
         <v>109</v>
       </c>
       <c r="B11" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="C11" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="D11" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E11" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F11" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="12" spans="1:7" hidden="1">
@@ -3335,19 +3326,19 @@
         <v>110</v>
       </c>
       <c r="B12" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="C12" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="D12" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E12" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F12" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="13" spans="1:7" hidden="1">
@@ -3355,19 +3346,19 @@
         <v>111</v>
       </c>
       <c r="B13" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="C13" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="D13" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E13" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F13" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="14" spans="1:7" hidden="1">
@@ -3375,19 +3366,19 @@
         <v>112</v>
       </c>
       <c r="B14" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="C14" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="D14" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E14" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F14" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="15" spans="1:7" hidden="1">
@@ -3395,10 +3386,10 @@
         <v>113</v>
       </c>
       <c r="D15" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F15" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="16" spans="1:7" hidden="1">
@@ -3406,10 +3397,10 @@
         <v>114</v>
       </c>
       <c r="D16" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F16" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="17" spans="1:6" hidden="1">
@@ -3417,10 +3408,10 @@
         <v>115</v>
       </c>
       <c r="D17" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F17" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="18" spans="1:6" hidden="1">
@@ -3428,10 +3419,10 @@
         <v>116</v>
       </c>
       <c r="D18" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F18" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="19" spans="1:6" hidden="1">
@@ -3439,19 +3430,19 @@
         <v>117</v>
       </c>
       <c r="B19" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="C19" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="D19" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E19" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F19" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="20" spans="1:6" hidden="1">
@@ -3459,19 +3450,19 @@
         <v>118</v>
       </c>
       <c r="B20" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="C20" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="D20" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E20" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F20" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="21" spans="1:6" hidden="1">
@@ -3479,19 +3470,19 @@
         <v>119</v>
       </c>
       <c r="B21" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="C21" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="D21" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E21" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F21" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="22" spans="1:6" hidden="1">
@@ -3499,485 +3490,473 @@
         <v>120</v>
       </c>
       <c r="B22" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="C22" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="D22" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E22" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F22" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" hidden="1">
       <c r="A23" t="s">
         <v>121</v>
       </c>
       <c r="B23" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="C23" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D23" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E23" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="F23" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" hidden="1">
       <c r="A24" t="s">
         <v>122</v>
       </c>
       <c r="B24" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C24" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D24" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E24" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="F24" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" hidden="1">
       <c r="A25" t="s">
         <v>123</v>
       </c>
       <c r="B25" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C25" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D25" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E25" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="F25" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" hidden="1">
       <c r="A26" t="s">
         <v>124</v>
       </c>
       <c r="B26" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C26" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D26" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E26" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="F26" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" hidden="1">
       <c r="A27" t="s">
         <v>125</v>
       </c>
       <c r="B27" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C27" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D27" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E27" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="F27" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" hidden="1">
       <c r="A28" t="s">
         <v>126</v>
       </c>
       <c r="B28" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C28" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D28" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E28" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="F28" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" hidden="1">
       <c r="A29" t="s">
         <v>127</v>
       </c>
       <c r="B29" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C29" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D29" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E29" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="F29" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" hidden="1">
       <c r="A30" t="s">
         <v>128</v>
       </c>
       <c r="B30" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C30" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D30" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E30" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="F30" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" hidden="1">
       <c r="A31" t="s">
         <v>129</v>
       </c>
       <c r="B31" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C31" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D31" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E31" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="F31" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" hidden="1">
       <c r="A32" t="s">
         <v>130</v>
       </c>
       <c r="B32" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C32" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D32" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E32" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="F32" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" hidden="1">
       <c r="A33" t="s">
         <v>131</v>
       </c>
       <c r="B33" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C33" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D33" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E33" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="F33" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" hidden="1">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" hidden="1">
       <c r="A34" t="s">
         <v>132</v>
       </c>
       <c r="D34" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F34" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" hidden="1">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" hidden="1">
       <c r="A35" t="s">
         <v>133</v>
       </c>
       <c r="D35" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F35" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" hidden="1">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" hidden="1">
       <c r="A36" t="s">
         <v>134</v>
       </c>
       <c r="D36" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F36" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" hidden="1">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" hidden="1">
       <c r="A37" t="s">
         <v>135</v>
       </c>
       <c r="D37" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F37" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" hidden="1">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" hidden="1">
       <c r="A38" t="s">
         <v>136</v>
       </c>
       <c r="D38" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F38" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" hidden="1">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" hidden="1">
       <c r="A39" t="s">
         <v>137</v>
       </c>
       <c r="D39" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F39" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" hidden="1">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" hidden="1">
       <c r="A40" t="s">
         <v>138</v>
       </c>
       <c r="B40" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="C40" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="D40" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E40" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F40" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" hidden="1">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" hidden="1">
       <c r="A41" t="s">
         <v>139</v>
       </c>
       <c r="B41" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="C41" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="D41" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E41" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F41" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" hidden="1">
       <c r="A42" t="s">
+        <v>163</v>
+      </c>
+      <c r="B42" t="s">
+        <v>264</v>
+      </c>
+      <c r="C42" t="s">
+        <v>264</v>
+      </c>
+      <c r="D42" t="s">
+        <v>260</v>
+      </c>
+      <c r="E42" t="s">
+        <v>281</v>
+      </c>
+      <c r="F42" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6">
+      <c r="A43" t="s">
         <v>164</v>
       </c>
-      <c r="B42" t="s">
-        <v>265</v>
-      </c>
-      <c r="C42" t="s">
-        <v>265</v>
-      </c>
-      <c r="D42" t="s">
-        <v>261</v>
-      </c>
-      <c r="E42" t="s">
-        <v>284</v>
-      </c>
-      <c r="F42" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7">
-      <c r="A43" t="s">
+      <c r="B43" t="s">
+        <v>264</v>
+      </c>
+      <c r="C43" t="s">
+        <v>265</v>
+      </c>
+      <c r="D43" t="s">
+        <v>260</v>
+      </c>
+      <c r="F43" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" hidden="1">
+      <c r="A44" t="s">
         <v>165</v>
       </c>
-      <c r="B43" t="s">
-        <v>265</v>
-      </c>
-      <c r="C43" t="s">
-        <v>266</v>
-      </c>
-      <c r="D43" t="s">
-        <v>261</v>
-      </c>
-      <c r="F43" t="s">
-        <v>278</v>
-      </c>
-      <c r="G43" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7">
-      <c r="A44" t="s">
+      <c r="B44" t="s">
+        <v>264</v>
+      </c>
+      <c r="C44" t="s">
+        <v>264</v>
+      </c>
+      <c r="D44" t="s">
+        <v>260</v>
+      </c>
+      <c r="E44" t="s">
+        <v>281</v>
+      </c>
+      <c r="F44" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6">
+      <c r="A45" t="s">
         <v>166</v>
       </c>
-      <c r="B44" t="s">
-        <v>265</v>
-      </c>
-      <c r="C44" t="s">
-        <v>265</v>
-      </c>
-      <c r="D44" t="s">
-        <v>261</v>
-      </c>
-      <c r="E44" t="s">
-        <v>284</v>
-      </c>
-      <c r="F44" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7">
-      <c r="A45" t="s">
+      <c r="B45" t="s">
+        <v>264</v>
+      </c>
+      <c r="C45" t="s">
+        <v>265</v>
+      </c>
+      <c r="D45" t="s">
+        <v>260</v>
+      </c>
+      <c r="F45" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" hidden="1">
+      <c r="A46" t="s">
         <v>167</v>
       </c>
-      <c r="B45" t="s">
-        <v>265</v>
-      </c>
-      <c r="C45" t="s">
-        <v>266</v>
-      </c>
-      <c r="D45" t="s">
-        <v>261</v>
-      </c>
-      <c r="F45" t="s">
-        <v>278</v>
-      </c>
-      <c r="G45" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7">
-      <c r="A46" t="s">
-        <v>168</v>
-      </c>
       <c r="B46" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C46" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D46" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E46" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="F46" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6">
       <c r="A47" t="s">
         <v>142</v>
       </c>
       <c r="B47" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C47" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D47" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F47" t="s">
-        <v>278</v>
-      </c>
-      <c r="G47" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6">
       <c r="A48" t="s">
         <v>143</v>
       </c>
       <c r="B48" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C48" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D48" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F48" t="s">
-        <v>278</v>
-      </c>
-      <c r="G48" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="49" spans="1:7" hidden="1">
@@ -3985,19 +3964,19 @@
         <v>144</v>
       </c>
       <c r="B49" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C49" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="D49" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E49" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F49" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="50" spans="1:7" hidden="1">
@@ -4005,19 +3984,19 @@
         <v>145</v>
       </c>
       <c r="B50" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C50" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="D50" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E50" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F50" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="51" spans="1:7" hidden="1">
@@ -4025,19 +4004,19 @@
         <v>146</v>
       </c>
       <c r="B51" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C51" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="D51" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E51" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F51" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="52" spans="1:7" hidden="1">
@@ -4045,19 +4024,19 @@
         <v>147</v>
       </c>
       <c r="B52" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C52" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="D52" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E52" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F52" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="53" spans="1:7" hidden="1">
@@ -4065,19 +4044,19 @@
         <v>148</v>
       </c>
       <c r="B53" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C53" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="D53" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E53" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F53" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="54" spans="1:7" hidden="1">
@@ -4085,19 +4064,19 @@
         <v>149</v>
       </c>
       <c r="B54" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C54" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="D54" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E54" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F54" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -4105,19 +4084,16 @@
         <v>150</v>
       </c>
       <c r="B55" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C55" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D55" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F55" t="s">
-        <v>278</v>
-      </c>
-      <c r="G55" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -4125,39 +4101,36 @@
         <v>151</v>
       </c>
       <c r="B56" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C56" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D56" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F56" t="s">
-        <v>278</v>
-      </c>
-      <c r="G56" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" hidden="1">
       <c r="A57" t="s">
         <v>152</v>
       </c>
       <c r="B57" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C57" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D57" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E57" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="F57" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -4165,204 +4138,206 @@
         <v>153</v>
       </c>
       <c r="B58" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C58" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D58" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F58" t="s">
-        <v>278</v>
-      </c>
-      <c r="G58" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="59" spans="1:7">
       <c r="A59" t="s">
+        <v>312</v>
+      </c>
+      <c r="B59" t="s">
+        <v>264</v>
+      </c>
+      <c r="C59" t="s">
+        <v>265</v>
+      </c>
+      <c r="D59" t="s">
+        <v>260</v>
+      </c>
+      <c r="F59" t="s">
+        <v>276</v>
+      </c>
+      <c r="G59" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" hidden="1">
+      <c r="A60" t="s">
         <v>154</v>
       </c>
-      <c r="B59" t="s">
-        <v>265</v>
-      </c>
-      <c r="C59" t="s">
-        <v>285</v>
-      </c>
-      <c r="D59" t="s">
-        <v>261</v>
-      </c>
-      <c r="F59" t="s">
-        <v>278</v>
-      </c>
-      <c r="G59" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7">
-      <c r="A60" t="s">
-        <v>155</v>
-      </c>
       <c r="B60" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C60" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D60" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E60" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="F60" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="61" spans="1:7" hidden="1">
       <c r="A61" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B61" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C61" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="D61" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E61" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F61" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="62" spans="1:7" hidden="1">
       <c r="A62" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B62" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C62" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="D62" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E62" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F62" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="63" spans="1:7" hidden="1">
       <c r="A63" t="s">
+        <v>158</v>
+      </c>
+      <c r="B63" t="s">
+        <v>273</v>
+      </c>
+      <c r="C63" t="s">
+        <v>273</v>
+      </c>
+      <c r="D63" t="s">
+        <v>263</v>
+      </c>
+      <c r="E63" t="s">
+        <v>273</v>
+      </c>
+      <c r="F63" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" hidden="1">
+      <c r="A64" t="s">
         <v>159</v>
       </c>
-      <c r="B63" t="s">
-        <v>275</v>
-      </c>
-      <c r="C63" t="s">
-        <v>275</v>
-      </c>
-      <c r="D63" t="s">
-        <v>264</v>
-      </c>
-      <c r="E63" t="s">
-        <v>275</v>
-      </c>
-      <c r="F63" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7">
-      <c r="A64" t="s">
+      <c r="B64" t="s">
+        <v>264</v>
+      </c>
+      <c r="C64" t="s">
+        <v>264</v>
+      </c>
+      <c r="D64" t="s">
+        <v>260</v>
+      </c>
+      <c r="E64" t="s">
+        <v>281</v>
+      </c>
+      <c r="F64" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" hidden="1">
+      <c r="A65" t="s">
         <v>160</v>
       </c>
-      <c r="B64" t="s">
-        <v>265</v>
-      </c>
-      <c r="C64" t="s">
-        <v>265</v>
-      </c>
-      <c r="D64" t="s">
-        <v>261</v>
-      </c>
-      <c r="E64" t="s">
-        <v>284</v>
-      </c>
-      <c r="F64" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6">
-      <c r="A65" t="s">
+      <c r="B65" t="s">
+        <v>264</v>
+      </c>
+      <c r="C65" t="s">
+        <v>264</v>
+      </c>
+      <c r="D65" t="s">
+        <v>260</v>
+      </c>
+      <c r="E65" t="s">
+        <v>281</v>
+      </c>
+      <c r="F65" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" hidden="1">
+      <c r="A66" t="s">
         <v>161</v>
       </c>
-      <c r="B65" t="s">
-        <v>265</v>
-      </c>
-      <c r="C65" t="s">
-        <v>265</v>
-      </c>
-      <c r="D65" t="s">
-        <v>261</v>
-      </c>
-      <c r="E65" t="s">
-        <v>284</v>
-      </c>
-      <c r="F65" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6">
-      <c r="A66" t="s">
+      <c r="B66" t="s">
+        <v>264</v>
+      </c>
+      <c r="C66" t="s">
+        <v>264</v>
+      </c>
+      <c r="D66" t="s">
+        <v>260</v>
+      </c>
+      <c r="E66" t="s">
+        <v>281</v>
+      </c>
+      <c r="F66" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" hidden="1">
+      <c r="A67" t="s">
         <v>162</v>
       </c>
-      <c r="B66" t="s">
-        <v>265</v>
-      </c>
-      <c r="C66" t="s">
-        <v>265</v>
-      </c>
-      <c r="D66" t="s">
-        <v>261</v>
-      </c>
-      <c r="E66" t="s">
-        <v>284</v>
-      </c>
-      <c r="F66" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6">
-      <c r="A67" t="s">
-        <v>163</v>
-      </c>
       <c r="B67" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C67" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D67" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E67" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="F67" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="D1:D67">
-    <filterColumn colId="0">
+  <autoFilter ref="A1:G67">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="否"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="3">
       <filters>
         <filter val="赵育"/>
       </filters>
@@ -4394,13 +4369,13 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E1" t="s">
         <v>3</v>
       </c>
       <c r="F1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
@@ -4411,19 +4386,19 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="D2" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G2"/>
     </row>
@@ -4432,19 +4407,19 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C3" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="D3" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E3" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F3" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G3"/>
     </row>
@@ -4453,229 +4428,229 @@
         <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C4" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="D4" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E4" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F4" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G4"/>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" hidden="1">
       <c r="A5" t="s">
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C5" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="D5" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E5" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="F5" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G5"/>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" hidden="1">
       <c r="A6" t="s">
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C6" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="D6" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E6" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="F6" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G6"/>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" hidden="1">
       <c r="A7" t="s">
         <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C7" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="D7" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E7" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="F7" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G7"/>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" hidden="1">
       <c r="A8" t="s">
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C8" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="D8" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E8" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="F8" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G8"/>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" hidden="1">
       <c r="A9" t="s">
         <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C9" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="D9" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E9" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="F9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G9"/>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" hidden="1">
       <c r="A10" t="s">
         <v>13</v>
       </c>
       <c r="B10" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C10" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="D10" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E10" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="F10" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G10"/>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" hidden="1">
       <c r="A11" t="s">
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C11" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="D11" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E11" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="F11" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G11"/>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" hidden="1">
       <c r="A12" t="s">
         <v>15</v>
       </c>
       <c r="B12" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C12" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="D12" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E12" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="F12" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G12"/>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" hidden="1">
       <c r="A13" t="s">
         <v>16</v>
       </c>
       <c r="B13" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C13" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="D13" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E13" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="F13" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G13"/>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" hidden="1">
       <c r="A14" t="s">
         <v>17</v>
       </c>
       <c r="B14" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C14" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="D14" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E14" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="F14" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G14"/>
     </row>
@@ -4684,19 +4659,19 @@
         <v>18</v>
       </c>
       <c r="B15" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C15" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="D15" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E15" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F15" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G15"/>
     </row>
@@ -4705,19 +4680,19 @@
         <v>19</v>
       </c>
       <c r="B16" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C16" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="D16" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E16" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F16" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G16"/>
     </row>
@@ -4726,19 +4701,19 @@
         <v>20</v>
       </c>
       <c r="B17" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C17" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="D17" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E17" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F17" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G17"/>
     </row>
@@ -4747,456 +4722,448 @@
         <v>21</v>
       </c>
       <c r="B18" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C18" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="D18" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E18" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F18" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G18"/>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" hidden="1">
       <c r="A19" t="s">
         <v>22</v>
       </c>
       <c r="B19" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C19" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="D19" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E19" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="F19" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G19"/>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" hidden="1">
       <c r="A20" t="s">
         <v>23</v>
       </c>
       <c r="B20" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C20" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="D20" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E20" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="F20" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G20"/>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" hidden="1">
       <c r="A21" t="s">
         <v>24</v>
       </c>
       <c r="B21" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C21" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="D21" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E21" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="F21" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G21"/>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" hidden="1">
       <c r="A22" t="s">
         <v>25</v>
       </c>
       <c r="B22" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C22" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="D22" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E22" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="F22" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G22"/>
     </row>
-    <row r="23" spans="1:7" hidden="1">
+    <row r="23" spans="1:7">
       <c r="A23" t="s">
         <v>26</v>
       </c>
       <c r="B23" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C23" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D23" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F23" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="G23"/>
     </row>
-    <row r="24" spans="1:7" hidden="1">
+    <row r="24" spans="1:7">
       <c r="A24" t="s">
         <v>27</v>
       </c>
       <c r="B24" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C24" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D24" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F24" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="G24"/>
     </row>
-    <row r="25" spans="1:7" hidden="1">
+    <row r="25" spans="1:7">
       <c r="A25" t="s">
         <v>28</v>
       </c>
       <c r="B25" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C25" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D25" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F25" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="G25"/>
     </row>
-    <row r="26" spans="1:7" hidden="1">
+    <row r="26" spans="1:7">
       <c r="A26" t="s">
         <v>29</v>
       </c>
       <c r="B26" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C26" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D26" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F26" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="G26"/>
     </row>
-    <row r="27" spans="1:7" hidden="1">
+    <row r="27" spans="1:7">
       <c r="A27" t="s">
         <v>30</v>
       </c>
       <c r="B27" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C27" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D27" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F27" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="G27"/>
     </row>
-    <row r="28" spans="1:7" hidden="1">
+    <row r="28" spans="1:7">
       <c r="A28" t="s">
         <v>31</v>
       </c>
       <c r="B28" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C28" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D28" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F28" t="s">
-        <v>280</v>
-      </c>
-      <c r="G28" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" hidden="1">
+        <v>278</v>
+      </c>
+      <c r="G28"/>
+    </row>
+    <row r="29" spans="1:7">
       <c r="A29" t="s">
         <v>32</v>
       </c>
       <c r="B29" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C29" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D29" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F29" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="G29"/>
     </row>
-    <row r="30" spans="1:7" hidden="1">
+    <row r="30" spans="1:7">
       <c r="A30" t="s">
         <v>33</v>
       </c>
       <c r="B30" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C30" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D30" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F30" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="G30"/>
     </row>
-    <row r="31" spans="1:7" hidden="1">
+    <row r="31" spans="1:7">
       <c r="A31" t="s">
         <v>34</v>
       </c>
       <c r="B31" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C31" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D31" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F31" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="G31"/>
     </row>
-    <row r="32" spans="1:7" hidden="1">
+    <row r="32" spans="1:7">
       <c r="A32" t="s">
         <v>35</v>
       </c>
       <c r="B32" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C32" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D32" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F32" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="G32"/>
     </row>
-    <row r="33" spans="1:7" hidden="1">
+    <row r="33" spans="1:7">
       <c r="A33" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="B33" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C33" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D33" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F33" t="s">
-        <v>280</v>
-      </c>
-      <c r="G33" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" hidden="1">
+        <v>278</v>
+      </c>
+      <c r="G33"/>
+    </row>
+    <row r="34" spans="1:7">
       <c r="A34" t="s">
         <v>36</v>
       </c>
       <c r="B34" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C34" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D34" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F34" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="G34"/>
     </row>
-    <row r="35" spans="1:7" hidden="1">
+    <row r="35" spans="1:7">
       <c r="A35" t="s">
         <v>37</v>
       </c>
       <c r="B35" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C35" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D35" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F35" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="G35"/>
     </row>
-    <row r="36" spans="1:7" hidden="1">
+    <row r="36" spans="1:7">
       <c r="A36" t="s">
         <v>38</v>
       </c>
       <c r="B36" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C36" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D36" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F36" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="G36"/>
     </row>
-    <row r="37" spans="1:7" hidden="1">
+    <row r="37" spans="1:7">
       <c r="A37" t="s">
         <v>39</v>
       </c>
       <c r="B37" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C37" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D37" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F37" t="s">
-        <v>280</v>
-      </c>
-      <c r="G37" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" hidden="1">
+        <v>278</v>
+      </c>
+      <c r="G37"/>
+    </row>
+    <row r="38" spans="1:7">
       <c r="A38" t="s">
         <v>40</v>
       </c>
       <c r="B38" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C38" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D38" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F38" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="G38"/>
     </row>
-    <row r="39" spans="1:7" hidden="1">
+    <row r="39" spans="1:7">
       <c r="A39" t="s">
         <v>41</v>
       </c>
       <c r="B39" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C39" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D39" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F39" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="G39"/>
     </row>
-    <row r="40" spans="1:7" hidden="1">
+    <row r="40" spans="1:7">
       <c r="A40" t="s">
         <v>42</v>
       </c>
       <c r="B40" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C40" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D40" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F40" t="s">
-        <v>280</v>
-      </c>
-      <c r="G40" t="s">
-        <v>281</v>
-      </c>
+        <v>278</v>
+      </c>
+      <c r="G40"/>
     </row>
     <row r="41" spans="1:7" hidden="1">
       <c r="A41" t="s">
         <v>43</v>
       </c>
       <c r="B41" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C41" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="D41" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E41" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F41" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G41"/>
     </row>
@@ -5205,19 +5172,19 @@
         <v>44</v>
       </c>
       <c r="B42" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C42" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="D42" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E42" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F42" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G42"/>
     </row>
@@ -5226,19 +5193,19 @@
         <v>45</v>
       </c>
       <c r="B43" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C43" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="D43" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E43" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F43" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G43"/>
     </row>
@@ -5247,19 +5214,19 @@
         <v>46</v>
       </c>
       <c r="B44" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C44" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="D44" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E44" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F44" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G44"/>
     </row>
@@ -5268,19 +5235,19 @@
         <v>47</v>
       </c>
       <c r="B45" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C45" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="D45" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E45" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F45" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G45"/>
     </row>
@@ -5289,86 +5256,86 @@
         <v>48</v>
       </c>
       <c r="B46" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C46" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="D46" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E46" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F46" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G46"/>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" hidden="1">
       <c r="A47" t="s">
         <v>49</v>
       </c>
       <c r="B47" t="s">
+        <v>299</v>
+      </c>
+      <c r="C47" t="s">
+        <v>299</v>
+      </c>
+      <c r="D47" t="s">
+        <v>261</v>
+      </c>
+      <c r="E47" t="s">
+        <v>302</v>
+      </c>
+      <c r="F47" t="s">
+        <v>260</v>
+      </c>
+      <c r="G47" t="s">
         <v>303</v>
       </c>
-      <c r="C47" t="s">
-        <v>303</v>
-      </c>
-      <c r="D47" t="s">
-        <v>262</v>
-      </c>
-      <c r="E47" t="s">
-        <v>306</v>
-      </c>
-      <c r="F47" t="s">
-        <v>261</v>
-      </c>
-      <c r="G47" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7">
+    </row>
+    <row r="48" spans="1:7" hidden="1">
       <c r="A48" t="s">
         <v>50</v>
       </c>
       <c r="B48" t="s">
+        <v>299</v>
+      </c>
+      <c r="C48" t="s">
+        <v>299</v>
+      </c>
+      <c r="D48" t="s">
+        <v>261</v>
+      </c>
+      <c r="E48" t="s">
+        <v>302</v>
+      </c>
+      <c r="F48" t="s">
+        <v>260</v>
+      </c>
+      <c r="G48" t="s">
         <v>303</v>
       </c>
-      <c r="C48" t="s">
-        <v>303</v>
-      </c>
-      <c r="D48" t="s">
-        <v>262</v>
-      </c>
-      <c r="E48" t="s">
-        <v>306</v>
-      </c>
-      <c r="F48" t="s">
-        <v>261</v>
-      </c>
-      <c r="G48" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7">
+    </row>
+    <row r="49" spans="1:7" hidden="1">
       <c r="A49" t="s">
         <v>51</v>
       </c>
       <c r="B49" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="C49" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="D49" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E49" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="F49" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G49"/>
     </row>
@@ -5377,13 +5344,13 @@
         <v>52</v>
       </c>
       <c r="D50" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E50" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="F50" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="51" spans="1:7" hidden="1">
@@ -5391,13 +5358,13 @@
         <v>53</v>
       </c>
       <c r="D51" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E51" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="F51" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="52" spans="1:7" hidden="1">
@@ -5405,13 +5372,13 @@
         <v>54</v>
       </c>
       <c r="D52" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E52" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="F52" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="53" spans="1:7" ht="40.5" hidden="1">
@@ -5419,16 +5386,16 @@
         <v>55</v>
       </c>
       <c r="D53" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E53" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="F53" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
     </row>
     <row r="54" spans="1:7" hidden="1">
@@ -5436,13 +5403,13 @@
         <v>56</v>
       </c>
       <c r="D54" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E54" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="F54" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="55" spans="1:7" hidden="1">
@@ -5450,13 +5417,13 @@
         <v>57</v>
       </c>
       <c r="D55" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E55" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="F55" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="56" spans="1:7" hidden="1">
@@ -5464,13 +5431,13 @@
         <v>58</v>
       </c>
       <c r="D56" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E56" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="F56" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="57" spans="1:7" hidden="1">
@@ -5478,13 +5445,13 @@
         <v>59</v>
       </c>
       <c r="D57" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E57" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="F57" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="58" spans="1:7" hidden="1">
@@ -5492,13 +5459,13 @@
         <v>60</v>
       </c>
       <c r="D58" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E58" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="F58" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="59" spans="1:7" hidden="1">
@@ -5506,13 +5473,13 @@
         <v>61</v>
       </c>
       <c r="D59" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E59" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="F59" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="60" spans="1:7" hidden="1">
@@ -5520,16 +5487,16 @@
         <v>62</v>
       </c>
       <c r="D60" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E60" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="F60" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
     </row>
     <row r="61" spans="1:7" ht="40.5" hidden="1">
@@ -5537,16 +5504,16 @@
         <v>63</v>
       </c>
       <c r="D61" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E61" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="F61" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
     </row>
     <row r="62" spans="1:7" hidden="1">
@@ -5554,13 +5521,13 @@
         <v>64</v>
       </c>
       <c r="D62" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E62" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="F62" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="63" spans="1:7" hidden="1">
@@ -5568,13 +5535,13 @@
         <v>65</v>
       </c>
       <c r="D63" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E63" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="F63" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="64" spans="1:7" hidden="1">
@@ -5582,13 +5549,13 @@
         <v>66</v>
       </c>
       <c r="D64" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E64" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="F64" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="65" spans="1:7" ht="40.5" hidden="1">
@@ -5596,16 +5563,16 @@
         <v>67</v>
       </c>
       <c r="D65" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E65" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="F65" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
     </row>
     <row r="66" spans="1:7" ht="40.5" hidden="1">
@@ -5613,16 +5580,16 @@
         <v>68</v>
       </c>
       <c r="D66" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E66" t="s">
+        <v>284</v>
+      </c>
+      <c r="F66" t="s">
+        <v>260</v>
+      </c>
+      <c r="G66" s="1" t="s">
         <v>288</v>
-      </c>
-      <c r="F66" t="s">
-        <v>261</v>
-      </c>
-      <c r="G66" s="1" t="s">
-        <v>292</v>
       </c>
     </row>
     <row r="67" spans="1:7" hidden="1">
@@ -5630,13 +5597,13 @@
         <v>69</v>
       </c>
       <c r="D67" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E67" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="F67" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="68" spans="1:7" ht="121.5" hidden="1">
@@ -5644,16 +5611,16 @@
         <v>70</v>
       </c>
       <c r="D68" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E68" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="F68" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
     </row>
     <row r="69" spans="1:7" hidden="1">
@@ -5661,13 +5628,13 @@
         <v>71</v>
       </c>
       <c r="D69" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E69" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="F69" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="70" spans="1:7" hidden="1">
@@ -5675,13 +5642,13 @@
         <v>72</v>
       </c>
       <c r="D70" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E70" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="F70" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="71" spans="1:7" hidden="1">
@@ -5689,13 +5656,13 @@
         <v>73</v>
       </c>
       <c r="D71" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E71" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="F71" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="72" spans="1:7" hidden="1">
@@ -5703,13 +5670,13 @@
         <v>74</v>
       </c>
       <c r="D72" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E72" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="F72" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="73" spans="1:7" hidden="1">
@@ -5717,19 +5684,19 @@
         <v>75</v>
       </c>
       <c r="B73" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C73" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="D73" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E73" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F73" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G73"/>
     </row>
@@ -5738,22 +5705,22 @@
         <v>76</v>
       </c>
       <c r="B74" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C74" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D74" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E74" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="F74" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G74" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="75" spans="1:7" hidden="1">
@@ -5761,22 +5728,22 @@
         <v>77</v>
       </c>
       <c r="B75" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C75" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D75" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E75" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="F75" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G75" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="76" spans="1:7" hidden="1">
@@ -5784,22 +5751,22 @@
         <v>78</v>
       </c>
       <c r="B76" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C76" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D76" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E76" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="F76" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G76" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="77" spans="1:7" hidden="1">
@@ -5807,22 +5774,22 @@
         <v>79</v>
       </c>
       <c r="B77" t="s">
+        <v>266</v>
+      </c>
+      <c r="C77" t="s">
+        <v>266</v>
+      </c>
+      <c r="D77" t="s">
+        <v>262</v>
+      </c>
+      <c r="E77" t="s">
+        <v>266</v>
+      </c>
+      <c r="F77" t="s">
+        <v>260</v>
+      </c>
+      <c r="G77" t="s">
         <v>268</v>
-      </c>
-      <c r="C77" t="s">
-        <v>268</v>
-      </c>
-      <c r="D77" t="s">
-        <v>263</v>
-      </c>
-      <c r="E77" t="s">
-        <v>268</v>
-      </c>
-      <c r="F77" t="s">
-        <v>261</v>
-      </c>
-      <c r="G77" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="78" spans="1:7" hidden="1">
@@ -5830,19 +5797,19 @@
         <v>80</v>
       </c>
       <c r="B78" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C78" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="D78" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E78" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F78" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G78"/>
     </row>
@@ -5851,16 +5818,16 @@
         <v>81</v>
       </c>
       <c r="D79" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E79" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="F79" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
     </row>
     <row r="80" spans="1:7" ht="27" hidden="1">
@@ -5868,13 +5835,13 @@
         <v>82</v>
       </c>
       <c r="D80" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F80" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
     </row>
     <row r="81" spans="1:7" ht="27" hidden="1">
@@ -5882,13 +5849,13 @@
         <v>83</v>
       </c>
       <c r="D81" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F81" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
     </row>
     <row r="82" spans="1:7" ht="27" hidden="1">
@@ -5896,13 +5863,13 @@
         <v>84</v>
       </c>
       <c r="D82" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F82" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
     </row>
     <row r="83" spans="1:7" ht="27" hidden="1">
@@ -5910,13 +5877,13 @@
         <v>85</v>
       </c>
       <c r="D83" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F83" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
     </row>
     <row r="84" spans="1:7" ht="27" hidden="1">
@@ -5924,122 +5891,122 @@
         <v>86</v>
       </c>
       <c r="D84" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F84" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7" hidden="1">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7">
       <c r="A85" t="s">
         <v>87</v>
       </c>
       <c r="B85" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C85" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D85" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F85" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="G85"/>
     </row>
-    <row r="86" spans="1:7" hidden="1">
+    <row r="86" spans="1:7">
       <c r="A86" t="s">
         <v>88</v>
       </c>
       <c r="B86" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C86" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D86" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F86" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="G86"/>
     </row>
-    <row r="87" spans="1:7" hidden="1">
+    <row r="87" spans="1:7">
       <c r="A87" t="s">
         <v>89</v>
       </c>
       <c r="B87" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C87" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D87" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F87" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="G87"/>
     </row>
-    <row r="88" spans="1:7" hidden="1">
+    <row r="88" spans="1:7">
       <c r="A88" t="s">
         <v>90</v>
       </c>
       <c r="B88" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C88" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D88" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F88" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="G88" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7" hidden="1">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7">
       <c r="A89" t="s">
         <v>91</v>
       </c>
       <c r="B89" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C89" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D89" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F89" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="G89"/>
     </row>
-    <row r="90" spans="1:7" hidden="1">
+    <row r="90" spans="1:7">
       <c r="A90" t="s">
         <v>92</v>
       </c>
       <c r="B90" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C90" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D90" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F90" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="G90"/>
     </row>
@@ -6048,13 +6015,13 @@
         <v>93</v>
       </c>
       <c r="D91" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F91" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
     </row>
     <row r="92" spans="1:7" ht="27" hidden="1">
@@ -6062,13 +6029,13 @@
         <v>94</v>
       </c>
       <c r="D92" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F92" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
     </row>
     <row r="93" spans="1:7" ht="27" hidden="1">
@@ -6076,66 +6043,66 @@
         <v>95</v>
       </c>
       <c r="D93" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F93" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7" hidden="1">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7">
       <c r="A94" t="s">
         <v>96</v>
       </c>
       <c r="B94" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C94" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D94" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F94" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="G94"/>
     </row>
-    <row r="95" spans="1:7" hidden="1">
+    <row r="95" spans="1:7">
       <c r="A95" t="s">
         <v>97</v>
       </c>
       <c r="B95" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C95" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D95" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F95" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="G95"/>
     </row>
-    <row r="96" spans="1:7" hidden="1">
+    <row r="96" spans="1:7">
       <c r="A96" t="s">
         <v>98</v>
       </c>
       <c r="B96" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C96" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D96" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F96" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="G96"/>
     </row>
@@ -6144,84 +6111,84 @@
         <v>99</v>
       </c>
       <c r="B97" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C97" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D97" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E97" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="F97" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G97" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="98" spans="1:7" hidden="1">
       <c r="A98" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="E98" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="G98" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="99" spans="1:7" hidden="1">
       <c r="A99" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="E99" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="G99" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="100" spans="1:7" hidden="1">
       <c r="A100" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="E100" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="G100" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="101" spans="1:7" hidden="1">
       <c r="A101" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="E101" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="G101" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="102" spans="1:7" hidden="1">
       <c r="A102" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="E102" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="G102" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="D1:D102">
     <filterColumn colId="0">
       <filters>
-        <filter val="赵小妮"/>
+        <filter val="赵育"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -6243,18 +6210,18 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="B1" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="C1" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -6304,7 +6271,7 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -6359,18 +6326,18 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="B24" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="C24" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -6378,10 +6345,10 @@
         <v>82</v>
       </c>
       <c r="B25" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="C25" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -6389,10 +6356,10 @@
         <v>83</v>
       </c>
       <c r="B26" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="C26" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -6400,10 +6367,10 @@
         <v>84</v>
       </c>
       <c r="B27" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="C27" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -6411,10 +6378,10 @@
         <v>85</v>
       </c>
       <c r="B28" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="C28" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -6422,10 +6389,10 @@
         <v>86</v>
       </c>
       <c r="B29" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="C29" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -6433,10 +6400,10 @@
         <v>87</v>
       </c>
       <c r="B30" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="C30" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -6444,10 +6411,10 @@
         <v>88</v>
       </c>
       <c r="B31" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="C31" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -6455,10 +6422,10 @@
         <v>89</v>
       </c>
       <c r="B32" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="C32" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -6466,10 +6433,10 @@
         <v>90</v>
       </c>
       <c r="B33" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="C33" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -6477,10 +6444,10 @@
         <v>91</v>
       </c>
       <c r="B34" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="C34" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -6488,21 +6455,21 @@
         <v>92</v>
       </c>
       <c r="B35" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="C35" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="B36" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="C36" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -6510,10 +6477,10 @@
         <v>94</v>
       </c>
       <c r="B37" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="C37" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -6521,10 +6488,10 @@
         <v>95</v>
       </c>
       <c r="B38" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="C38" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -6532,10 +6499,10 @@
         <v>96</v>
       </c>
       <c r="B39" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="C39" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -6543,10 +6510,10 @@
         <v>97</v>
       </c>
       <c r="B40" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="C40" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -6554,10 +6521,10 @@
         <v>98</v>
       </c>
       <c r="B41" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="C41" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
     </row>
   </sheetData>

--- a/internal_doc/05.测试设计/story/事务支持RC隔离级别/事务自动化用例跟踪表.xlsx
+++ b/internal_doc/05.测试设计/story/事务支持RC隔离级别/事务自动化用例跟踪表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="2"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="RU" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1468" uniqueCount="313">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1537" uniqueCount="333">
   <si>
     <t>用例编号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1035,6 +1035,83 @@
   </si>
   <si>
     <t>seqDB-17771</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-17826</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-17942</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-17943</t>
+  </si>
+  <si>
+    <t>seqDB-17944</t>
+  </si>
+  <si>
+    <t>seqDB-17945</t>
+  </si>
+  <si>
+    <t>seqDB-17960</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-17114</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-17185</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-17229</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>责任人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>卢伟康</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>赵育</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>尹臻</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-17116</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-17117</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-17080</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-17081</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-17082</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-17083</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>赵小妮</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -6200,15 +6277,16 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C41"/>
+  <dimension ref="A1:D55"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="18.5" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
     <col min="3" max="3" width="29.75" customWidth="1"/>
+    <col min="4" max="4" width="12.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>291</v>
       </c>
@@ -6218,118 +6296,187 @@
       <c r="C1" t="s">
         <v>293</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
+      <c r="D1" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
+      <c r="D2" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="4" spans="1:3">
+      <c r="D3" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="5" spans="1:3">
+      <c r="D4" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="6" spans="1:3">
+      <c r="D5" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
       <c r="A6" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="7" spans="1:3">
+      <c r="D6" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
       <c r="A7" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="8" spans="1:3">
+      <c r="D7" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
       <c r="A8" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="9" spans="1:3">
+      <c r="D8" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
       <c r="A9" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="10" spans="1:3">
+      <c r="D9" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
       <c r="A10" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="11" spans="1:3">
+      <c r="D10" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
       <c r="A11" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="12" spans="1:3">
+      <c r="D11" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
       <c r="A12" t="s">
         <v>295</v>
       </c>
-    </row>
-    <row r="13" spans="1:3">
+      <c r="D12" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
       <c r="A13" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="14" spans="1:3">
+      <c r="D13" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
       <c r="A14" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="15" spans="1:3">
+      <c r="D14" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
       <c r="A15" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="16" spans="1:3">
+      <c r="D15" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
       <c r="A16" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="17" spans="1:3">
+      <c r="D16" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
       <c r="A17" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="18" spans="1:3">
+      <c r="D17" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
       <c r="A18" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="19" spans="1:3">
+      <c r="D18" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
       <c r="A19" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="20" spans="1:3">
+      <c r="D19" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
       <c r="A20" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="21" spans="1:3">
+      <c r="D20" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
       <c r="A21" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="22" spans="1:3">
+      <c r="D21" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
       <c r="A22" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="23" spans="1:3">
+      <c r="D22" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
       <c r="A23" t="s">
         <v>296</v>
       </c>
-    </row>
-    <row r="24" spans="1:3">
+      <c r="D23" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
       <c r="A24" t="s">
         <v>297</v>
       </c>
@@ -6339,8 +6486,11 @@
       <c r="C24" t="s">
         <v>311</v>
       </c>
-    </row>
-    <row r="25" spans="1:3">
+      <c r="D24" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
       <c r="A25" t="s">
         <v>82</v>
       </c>
@@ -6350,8 +6500,11 @@
       <c r="C25" t="s">
         <v>310</v>
       </c>
-    </row>
-    <row r="26" spans="1:3">
+      <c r="D25" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
       <c r="A26" t="s">
         <v>83</v>
       </c>
@@ -6361,8 +6514,11 @@
       <c r="C26" t="s">
         <v>311</v>
       </c>
-    </row>
-    <row r="27" spans="1:3">
+      <c r="D26" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
       <c r="A27" t="s">
         <v>84</v>
       </c>
@@ -6372,8 +6528,11 @@
       <c r="C27" t="s">
         <v>311</v>
       </c>
-    </row>
-    <row r="28" spans="1:3">
+      <c r="D27" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
       <c r="A28" t="s">
         <v>85</v>
       </c>
@@ -6383,8 +6542,11 @@
       <c r="C28" t="s">
         <v>311</v>
       </c>
-    </row>
-    <row r="29" spans="1:3">
+      <c r="D28" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
       <c r="A29" t="s">
         <v>86</v>
       </c>
@@ -6394,8 +6556,11 @@
       <c r="C29" t="s">
         <v>311</v>
       </c>
-    </row>
-    <row r="30" spans="1:3">
+      <c r="D29" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
       <c r="A30" t="s">
         <v>87</v>
       </c>
@@ -6405,8 +6570,11 @@
       <c r="C30" t="s">
         <v>311</v>
       </c>
-    </row>
-    <row r="31" spans="1:3">
+      <c r="D30" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
       <c r="A31" t="s">
         <v>88</v>
       </c>
@@ -6416,8 +6584,11 @@
       <c r="C31" t="s">
         <v>311</v>
       </c>
-    </row>
-    <row r="32" spans="1:3">
+      <c r="D31" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
       <c r="A32" t="s">
         <v>89</v>
       </c>
@@ -6427,8 +6598,11 @@
       <c r="C32" t="s">
         <v>311</v>
       </c>
-    </row>
-    <row r="33" spans="1:3">
+      <c r="D32" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
       <c r="A33" t="s">
         <v>90</v>
       </c>
@@ -6438,8 +6612,11 @@
       <c r="C33" t="s">
         <v>311</v>
       </c>
-    </row>
-    <row r="34" spans="1:3">
+      <c r="D33" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
       <c r="A34" t="s">
         <v>91</v>
       </c>
@@ -6449,8 +6626,11 @@
       <c r="C34" t="s">
         <v>311</v>
       </c>
-    </row>
-    <row r="35" spans="1:3">
+      <c r="D34" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
       <c r="A35" t="s">
         <v>92</v>
       </c>
@@ -6460,8 +6640,11 @@
       <c r="C35" t="s">
         <v>311</v>
       </c>
-    </row>
-    <row r="36" spans="1:3">
+      <c r="D35" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
       <c r="A36" t="s">
         <v>298</v>
       </c>
@@ -6471,8 +6654,11 @@
       <c r="C36" t="s">
         <v>311</v>
       </c>
-    </row>
-    <row r="37" spans="1:3">
+      <c r="D36" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
       <c r="A37" t="s">
         <v>94</v>
       </c>
@@ -6482,8 +6668,11 @@
       <c r="C37" t="s">
         <v>311</v>
       </c>
-    </row>
-    <row r="38" spans="1:3">
+      <c r="D37" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
       <c r="A38" t="s">
         <v>95</v>
       </c>
@@ -6493,8 +6682,11 @@
       <c r="C38" t="s">
         <v>311</v>
       </c>
-    </row>
-    <row r="39" spans="1:3">
+      <c r="D38" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
       <c r="A39" t="s">
         <v>96</v>
       </c>
@@ -6504,8 +6696,11 @@
       <c r="C39" t="s">
         <v>311</v>
       </c>
-    </row>
-    <row r="40" spans="1:3">
+      <c r="D39" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
       <c r="A40" t="s">
         <v>97</v>
       </c>
@@ -6515,16 +6710,134 @@
       <c r="C40" t="s">
         <v>311</v>
       </c>
-    </row>
-    <row r="41" spans="1:3">
+      <c r="D40" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
       <c r="A41" t="s">
-        <v>98</v>
+        <v>313</v>
       </c>
       <c r="B41" t="s">
         <v>309</v>
       </c>
       <c r="C41" t="s">
         <v>311</v>
+      </c>
+      <c r="D41" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" t="s">
+        <v>314</v>
+      </c>
+      <c r="D42" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" t="s">
+        <v>315</v>
+      </c>
+      <c r="D43" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" t="s">
+        <v>316</v>
+      </c>
+      <c r="D44" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4">
+      <c r="A45" t="s">
+        <v>317</v>
+      </c>
+      <c r="D45" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4">
+      <c r="A46" t="s">
+        <v>318</v>
+      </c>
+      <c r="D46" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
+      <c r="A47" t="s">
+        <v>319</v>
+      </c>
+      <c r="D47" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4">
+      <c r="A48" t="s">
+        <v>320</v>
+      </c>
+      <c r="D48" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4">
+      <c r="A49" t="s">
+        <v>321</v>
+      </c>
+      <c r="D49" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4">
+      <c r="A50" t="s">
+        <v>326</v>
+      </c>
+      <c r="D50" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4">
+      <c r="A51" t="s">
+        <v>327</v>
+      </c>
+      <c r="D51" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4">
+      <c r="A52" t="s">
+        <v>328</v>
+      </c>
+      <c r="D52" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4">
+      <c r="A53" t="s">
+        <v>329</v>
+      </c>
+      <c r="D53" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4">
+      <c r="A54" t="s">
+        <v>330</v>
+      </c>
+      <c r="D54" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4">
+      <c r="A55" t="s">
+        <v>331</v>
+      </c>
+      <c r="D55" t="s">
+        <v>332</v>
       </c>
     </row>
   </sheetData>

--- a/internal_doc/05.测试设计/story/事务支持RC隔离级别/事务自动化用例跟踪表.xlsx
+++ b/internal_doc/05.测试设计/story/事务支持RC隔离级别/事务自动化用例跟踪表.xlsx
@@ -4,13 +4,14 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="3"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="RU" sheetId="1" r:id="rId1"/>
     <sheet name="RC等锁" sheetId="2" r:id="rId2"/>
     <sheet name="RC不等锁" sheetId="3" r:id="rId3"/>
     <sheet name="RC不等锁增加逆序索引及逆序查询任务" sheetId="4" r:id="rId4"/>
+    <sheet name="待完成任务" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">RC不等锁!$D$1:$D$102</definedName>
@@ -22,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1537" uniqueCount="333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1539" uniqueCount="335">
   <si>
     <t>用例编号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1112,6 +1113,19 @@
   </si>
   <si>
     <t>赵小妮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>需补充如下测试点：
+1.逆序索引，并发读写操作
+2.正序索引、逆序查询并发写操作
+3.复合索引，并发读写操作---后续根据复合索引的特点单独补充测试用例
+4.同一个索引键上创建多个索引，并发读写操作----需单独补充并发查询的用例
+5.索引分裂后的查询</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>事务基本用例待实现自动化</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1155,9 +1169,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -6845,4 +6862,29 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <cols>
+    <col min="1" max="1" width="75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" ht="81">
+      <c r="A1" s="2" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" t="s">
+        <v>334</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/internal_doc/05.测试设计/story/事务支持RC隔离级别/事务自动化用例跟踪表.xlsx
+++ b/internal_doc/05.测试设计/story/事务支持RC隔离级别/事务自动化用例跟踪表.xlsx
@@ -4,26 +4,30 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="4"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="RU" sheetId="1" r:id="rId1"/>
     <sheet name="RC等锁" sheetId="2" r:id="rId2"/>
     <sheet name="RC不等锁" sheetId="3" r:id="rId3"/>
-    <sheet name="RC不等锁增加逆序索引及逆序查询任务" sheetId="4" r:id="rId4"/>
+    <sheet name="增加逆序索引及逆序查询任务" sheetId="4" r:id="rId4"/>
     <sheet name="待完成任务" sheetId="5" r:id="rId5"/>
+    <sheet name="待开发写入遗留的问题单" sheetId="6" r:id="rId6"/>
+    <sheet name="事务优化自动化用例检视" sheetId="7" r:id="rId7"/>
+    <sheet name="事务支持自动提交、事务失败是否自动回滚、是否支持老版本" sheetId="8" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">RC不等锁!$D$1:$D$102</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">RC等锁!$A$1:$G$67</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">RU!$D$1:$D$94</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">增加逆序索引及逆序查询任务!$A$1:$F$77</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1539" uniqueCount="335">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1789" uniqueCount="405">
   <si>
     <t>用例编号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1027,14 +1031,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>调试通过，待提交</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>调试不通过，问题单4245</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>seqDB-17771</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1104,11 +1100,131 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>seqDB-17083</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>赵小妮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SEQUOIADBMAINSTREAM-4254</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SEQUOIADBMAINSTREAM-4141</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>已提交</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-17171</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-17173</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-17756</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>seqDB-17082</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>seqDB-17083</t>
+    <t>seqDB-18045</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-18046</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>尹臻</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>卢伟康</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>赵育</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-17180</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-17757</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-17211</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-17214</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-17217</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-17226</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-17220</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-17761</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-17765</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-17772</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-17770</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-17773</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-17777</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-17784</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-17782</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ok</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>存在bug后续再调试</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-18047</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1116,16 +1232,154 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>需补充如下测试点：
-1.逆序索引，并发读写操作
-2.正序索引、逆序查询并发写操作
-3.复合索引，并发读写操作---后续根据复合索引的特点单独补充测试用例
-4.同一个索引键上创建多个索引，并发读写操作----需单独补充并发查询的用例
-5.索引分裂后的查询</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>事务基本用例待实现自动化</t>
+    <t>seqDB-18048</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>检视人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>检视结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>update操作为啥使用set，没有使用inc？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>索引查询去掉查询条件
+没有使用批量记录验证</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>同17110</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>需要备注一下为什么没有覆盖正序索引逆序查询等情况</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>需要插入相同的记录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>表扫描死锁，未自动化</t>
+  </si>
+  <si>
+    <t>表扫描死锁，未自动化</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-18211</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-18212</t>
+  </si>
+  <si>
+    <t>seqDB-18213</t>
+  </si>
+  <si>
+    <t>seqDB-18214</t>
+  </si>
+  <si>
+    <t>seqDB-18215</t>
+  </si>
+  <si>
+    <t>seqDB-18216</t>
+  </si>
+  <si>
+    <t>seqDB-18217</t>
+  </si>
+  <si>
+    <t>seqDB-18218</t>
+  </si>
+  <si>
+    <t>seqDB-18219</t>
+  </si>
+  <si>
+    <t>seqDB-18220</t>
+  </si>
+  <si>
+    <t>seqDB-18221</t>
+  </si>
+  <si>
+    <t>seqDB-18222</t>
+  </si>
+  <si>
+    <t>seqDB-18223</t>
+  </si>
+  <si>
+    <t>seqDB-18224</t>
+  </si>
+  <si>
+    <t>用例编号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>责任人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>检视结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>尹臻</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>卢伟康</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ok</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-18226</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-18227</t>
+  </si>
+  <si>
+    <t>seqDB-18228</t>
+  </si>
+  <si>
+    <t>seqDB-18229</t>
+  </si>
+  <si>
+    <t>seqDB-18230</t>
+  </si>
+  <si>
+    <t>seqDB-18231</t>
+  </si>
+  <si>
+    <t>seqDB-18232</t>
+  </si>
+  <si>
+    <t>seqDB-18233</t>
+  </si>
+  <si>
+    <t>seqDB-18234</t>
+  </si>
+  <si>
+    <t>seqDB-18235</t>
+  </si>
+  <si>
+    <t>seqDB-18236</t>
+  </si>
+  <si>
+    <t>seqDB-18237</t>
+  </si>
+  <si>
+    <t>seqDB-18238</t>
+  </si>
+  <si>
+    <t>ok</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1471,7 +1725,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:G94"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
@@ -1501,7 +1754,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7" hidden="1">
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
         <v>168</v>
       </c>
@@ -1521,7 +1774,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="3" spans="1:7" hidden="1">
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>140</v>
       </c>
@@ -1541,7 +1794,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="4" spans="1:7" hidden="1">
+    <row r="4" spans="1:7">
       <c r="A4" t="s">
         <v>141</v>
       </c>
@@ -1561,7 +1814,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="5" spans="1:7" hidden="1">
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
         <v>169</v>
       </c>
@@ -1572,7 +1825,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="6" spans="1:7" hidden="1">
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
         <v>170</v>
       </c>
@@ -1583,7 +1836,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="7" spans="1:7" hidden="1">
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
         <v>171</v>
       </c>
@@ -1594,7 +1847,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="8" spans="1:7" hidden="1">
+    <row r="8" spans="1:7">
       <c r="A8" t="s">
         <v>172</v>
       </c>
@@ -1605,7 +1858,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="9" spans="1:7" hidden="1">
+    <row r="9" spans="1:7">
       <c r="A9" t="s">
         <v>173</v>
       </c>
@@ -1616,7 +1869,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="10" spans="1:7" hidden="1">
+    <row r="10" spans="1:7">
       <c r="A10" t="s">
         <v>174</v>
       </c>
@@ -1627,7 +1880,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="11" spans="1:7" hidden="1">
+    <row r="11" spans="1:7">
       <c r="A11" t="s">
         <v>175</v>
       </c>
@@ -1638,7 +1891,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="12" spans="1:7" hidden="1">
+    <row r="12" spans="1:7">
       <c r="A12" t="s">
         <v>176</v>
       </c>
@@ -1649,7 +1902,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="13" spans="1:7" hidden="1">
+    <row r="13" spans="1:7">
       <c r="A13" t="s">
         <v>177</v>
       </c>
@@ -1660,7 +1913,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="14" spans="1:7" hidden="1">
+    <row r="14" spans="1:7">
       <c r="A14" t="s">
         <v>178</v>
       </c>
@@ -1671,7 +1924,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="15" spans="1:7" hidden="1">
+    <row r="15" spans="1:7">
       <c r="A15" t="s">
         <v>179</v>
       </c>
@@ -1691,7 +1944,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="16" spans="1:7" hidden="1">
+    <row r="16" spans="1:7">
       <c r="A16" t="s">
         <v>180</v>
       </c>
@@ -1711,7 +1964,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="17" spans="1:6" hidden="1">
+    <row r="17" spans="1:6">
       <c r="A17" t="s">
         <v>181</v>
       </c>
@@ -1731,7 +1984,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="18" spans="1:6" hidden="1">
+    <row r="18" spans="1:6">
       <c r="A18" t="s">
         <v>182</v>
       </c>
@@ -1751,7 +2004,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="19" spans="1:6" hidden="1">
+    <row r="19" spans="1:6">
       <c r="A19" t="s">
         <v>183</v>
       </c>
@@ -1762,7 +2015,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="20" spans="1:6" hidden="1">
+    <row r="20" spans="1:6">
       <c r="A20" t="s">
         <v>184</v>
       </c>
@@ -1773,7 +2026,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="21" spans="1:6" hidden="1">
+    <row r="21" spans="1:6">
       <c r="A21" t="s">
         <v>185</v>
       </c>
@@ -1784,7 +2037,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="22" spans="1:6" hidden="1">
+    <row r="22" spans="1:6">
       <c r="A22" t="s">
         <v>186</v>
       </c>
@@ -2155,7 +2408,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="41" spans="1:6" hidden="1">
+    <row r="41" spans="1:6">
       <c r="A41" t="s">
         <v>205</v>
       </c>
@@ -2175,7 +2428,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="42" spans="1:6" hidden="1">
+    <row r="42" spans="1:6">
       <c r="A42" t="s">
         <v>206</v>
       </c>
@@ -2195,7 +2448,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="43" spans="1:6" hidden="1">
+    <row r="43" spans="1:6">
       <c r="A43" t="s">
         <v>207</v>
       </c>
@@ -2215,7 +2468,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="44" spans="1:6" hidden="1">
+    <row r="44" spans="1:6">
       <c r="A44" t="s">
         <v>208</v>
       </c>
@@ -2226,7 +2479,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="45" spans="1:6" hidden="1">
+    <row r="45" spans="1:6">
       <c r="A45" t="s">
         <v>209</v>
       </c>
@@ -2237,7 +2490,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="46" spans="1:6" hidden="1">
+    <row r="46" spans="1:6">
       <c r="A46" t="s">
         <v>210</v>
       </c>
@@ -2257,7 +2510,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="47" spans="1:6" hidden="1">
+    <row r="47" spans="1:6">
       <c r="A47" t="s">
         <v>211</v>
       </c>
@@ -2277,7 +2530,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="48" spans="1:6" hidden="1">
+    <row r="48" spans="1:6">
       <c r="A48" t="s">
         <v>212</v>
       </c>
@@ -2297,7 +2550,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="49" spans="1:6" hidden="1">
+    <row r="49" spans="1:6">
       <c r="A49" t="s">
         <v>213</v>
       </c>
@@ -2308,7 +2561,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="50" spans="1:6" hidden="1">
+    <row r="50" spans="1:6">
       <c r="A50" t="s">
         <v>214</v>
       </c>
@@ -2328,7 +2581,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="51" spans="1:6" hidden="1">
+    <row r="51" spans="1:6">
       <c r="A51" t="s">
         <v>215</v>
       </c>
@@ -2348,7 +2601,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="52" spans="1:6" hidden="1">
+    <row r="52" spans="1:6">
       <c r="A52" t="s">
         <v>216</v>
       </c>
@@ -2368,7 +2621,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="53" spans="1:6" hidden="1">
+    <row r="53" spans="1:6">
       <c r="A53" t="s">
         <v>217</v>
       </c>
@@ -2388,7 +2641,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="54" spans="1:6" hidden="1">
+    <row r="54" spans="1:6">
       <c r="A54" t="s">
         <v>218</v>
       </c>
@@ -2408,7 +2661,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="55" spans="1:6" hidden="1">
+    <row r="55" spans="1:6">
       <c r="A55" t="s">
         <v>219</v>
       </c>
@@ -2428,7 +2681,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="56" spans="1:6" hidden="1">
+    <row r="56" spans="1:6">
       <c r="A56" t="s">
         <v>220</v>
       </c>
@@ -2448,7 +2701,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="57" spans="1:6" hidden="1">
+    <row r="57" spans="1:6">
       <c r="A57" t="s">
         <v>221</v>
       </c>
@@ -2468,7 +2721,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="58" spans="1:6" hidden="1">
+    <row r="58" spans="1:6">
       <c r="A58" t="s">
         <v>222</v>
       </c>
@@ -2488,7 +2741,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="59" spans="1:6" hidden="1">
+    <row r="59" spans="1:6">
       <c r="A59" t="s">
         <v>223</v>
       </c>
@@ -2508,7 +2761,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="60" spans="1:6" hidden="1">
+    <row r="60" spans="1:6">
       <c r="A60" t="s">
         <v>224</v>
       </c>
@@ -2528,7 +2781,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="61" spans="1:6" hidden="1">
+    <row r="61" spans="1:6">
       <c r="A61" t="s">
         <v>225</v>
       </c>
@@ -2548,7 +2801,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="62" spans="1:6" hidden="1">
+    <row r="62" spans="1:6">
       <c r="A62" t="s">
         <v>226</v>
       </c>
@@ -2568,7 +2821,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="63" spans="1:6" hidden="1">
+    <row r="63" spans="1:6">
       <c r="A63" t="s">
         <v>227</v>
       </c>
@@ -2588,7 +2841,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="64" spans="1:6" hidden="1">
+    <row r="64" spans="1:6">
       <c r="A64" t="s">
         <v>228</v>
       </c>
@@ -2608,7 +2861,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="65" spans="1:6" hidden="1">
+    <row r="65" spans="1:6">
       <c r="A65" t="s">
         <v>229</v>
       </c>
@@ -2628,7 +2881,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="66" spans="1:6" hidden="1">
+    <row r="66" spans="1:6">
       <c r="A66" t="s">
         <v>230</v>
       </c>
@@ -2648,7 +2901,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="67" spans="1:6" hidden="1">
+    <row r="67" spans="1:6">
       <c r="A67" t="s">
         <v>231</v>
       </c>
@@ -2668,7 +2921,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="68" spans="1:6" hidden="1">
+    <row r="68" spans="1:6">
       <c r="A68" t="s">
         <v>232</v>
       </c>
@@ -2688,7 +2941,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="69" spans="1:6" hidden="1">
+    <row r="69" spans="1:6">
       <c r="A69" t="s">
         <v>233</v>
       </c>
@@ -2708,7 +2961,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="70" spans="1:6" hidden="1">
+    <row r="70" spans="1:6">
       <c r="A70" t="s">
         <v>234</v>
       </c>
@@ -2728,7 +2981,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="71" spans="1:6" hidden="1">
+    <row r="71" spans="1:6">
       <c r="A71" t="s">
         <v>235</v>
       </c>
@@ -2748,7 +3001,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="72" spans="1:6" hidden="1">
+    <row r="72" spans="1:6">
       <c r="A72" t="s">
         <v>236</v>
       </c>
@@ -2762,7 +3015,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="73" spans="1:6" hidden="1">
+    <row r="73" spans="1:6">
       <c r="A73" t="s">
         <v>237</v>
       </c>
@@ -2776,7 +3029,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="74" spans="1:6" hidden="1">
+    <row r="74" spans="1:6">
       <c r="A74" t="s">
         <v>240</v>
       </c>
@@ -2796,7 +3049,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="75" spans="1:6" hidden="1">
+    <row r="75" spans="1:6">
       <c r="A75" t="s">
         <v>238</v>
       </c>
@@ -2816,7 +3069,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="76" spans="1:6" hidden="1">
+    <row r="76" spans="1:6">
       <c r="A76" t="s">
         <v>239</v>
       </c>
@@ -2836,7 +3089,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="77" spans="1:6" hidden="1">
+    <row r="77" spans="1:6">
       <c r="A77" t="s">
         <v>241</v>
       </c>
@@ -2856,7 +3109,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="78" spans="1:6" hidden="1">
+    <row r="78" spans="1:6">
       <c r="A78" t="s">
         <v>155</v>
       </c>
@@ -2876,7 +3129,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="79" spans="1:6" hidden="1">
+    <row r="79" spans="1:6">
       <c r="A79" t="s">
         <v>242</v>
       </c>
@@ -2896,7 +3149,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="80" spans="1:6" hidden="1">
+    <row r="80" spans="1:6">
       <c r="A80" t="s">
         <v>243</v>
       </c>
@@ -2916,7 +3169,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="81" spans="1:6" hidden="1">
+    <row r="81" spans="1:6">
       <c r="A81" t="s">
         <v>244</v>
       </c>
@@ -2936,7 +3189,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="82" spans="1:6" hidden="1">
+    <row r="82" spans="1:6">
       <c r="A82" t="s">
         <v>245</v>
       </c>
@@ -3076,7 +3329,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="89" spans="1:6" hidden="1">
+    <row r="89" spans="1:6">
       <c r="A89" t="s">
         <v>252</v>
       </c>
@@ -3096,7 +3349,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="90" spans="1:6" hidden="1">
+    <row r="90" spans="1:6">
       <c r="A90" t="s">
         <v>253</v>
       </c>
@@ -3116,7 +3369,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="91" spans="1:6" hidden="1">
+    <row r="91" spans="1:6">
       <c r="A91" t="s">
         <v>254</v>
       </c>
@@ -3198,11 +3451,7 @@
     </row>
   </sheetData>
   <autoFilter ref="D1:D94">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="赵育"/>
-      </filters>
-    </filterColumn>
+    <filterColumn colId="0"/>
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3212,7 +3461,6 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:G67"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
@@ -3242,7 +3490,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7" hidden="1">
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
         <v>100</v>
       </c>
@@ -3253,7 +3501,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="3" spans="1:7" hidden="1">
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>101</v>
       </c>
@@ -3264,7 +3512,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="4" spans="1:7" hidden="1">
+    <row r="4" spans="1:7">
       <c r="A4" t="s">
         <v>102</v>
       </c>
@@ -3275,7 +3523,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="5" spans="1:7" hidden="1">
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
         <v>103</v>
       </c>
@@ -3295,7 +3543,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="6" spans="1:7" hidden="1">
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
         <v>104</v>
       </c>
@@ -3315,7 +3563,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="7" spans="1:7" hidden="1">
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
         <v>105</v>
       </c>
@@ -3335,7 +3583,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="8" spans="1:7" hidden="1">
+    <row r="8" spans="1:7">
       <c r="A8" t="s">
         <v>106</v>
       </c>
@@ -3355,7 +3603,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="9" spans="1:7" hidden="1">
+    <row r="9" spans="1:7">
       <c r="A9" t="s">
         <v>107</v>
       </c>
@@ -3375,7 +3623,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="10" spans="1:7" hidden="1">
+    <row r="10" spans="1:7">
       <c r="A10" t="s">
         <v>108</v>
       </c>
@@ -3395,7 +3643,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="11" spans="1:7" hidden="1">
+    <row r="11" spans="1:7">
       <c r="A11" t="s">
         <v>109</v>
       </c>
@@ -3415,7 +3663,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="12" spans="1:7" hidden="1">
+    <row r="12" spans="1:7">
       <c r="A12" t="s">
         <v>110</v>
       </c>
@@ -3435,7 +3683,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="13" spans="1:7" hidden="1">
+    <row r="13" spans="1:7">
       <c r="A13" t="s">
         <v>111</v>
       </c>
@@ -3455,7 +3703,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="14" spans="1:7" hidden="1">
+    <row r="14" spans="1:7">
       <c r="A14" t="s">
         <v>112</v>
       </c>
@@ -3475,7 +3723,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="15" spans="1:7" hidden="1">
+    <row r="15" spans="1:7">
       <c r="A15" t="s">
         <v>113</v>
       </c>
@@ -3486,7 +3734,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="16" spans="1:7" hidden="1">
+    <row r="16" spans="1:7">
       <c r="A16" t="s">
         <v>114</v>
       </c>
@@ -3497,7 +3745,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="17" spans="1:6" hidden="1">
+    <row r="17" spans="1:6">
       <c r="A17" t="s">
         <v>115</v>
       </c>
@@ -3508,7 +3756,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="18" spans="1:6" hidden="1">
+    <row r="18" spans="1:6">
       <c r="A18" t="s">
         <v>116</v>
       </c>
@@ -3519,7 +3767,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="19" spans="1:6" hidden="1">
+    <row r="19" spans="1:6">
       <c r="A19" t="s">
         <v>117</v>
       </c>
@@ -3539,7 +3787,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="20" spans="1:6" hidden="1">
+    <row r="20" spans="1:6">
       <c r="A20" t="s">
         <v>118</v>
       </c>
@@ -3559,7 +3807,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="21" spans="1:6" hidden="1">
+    <row r="21" spans="1:6">
       <c r="A21" t="s">
         <v>119</v>
       </c>
@@ -3579,7 +3827,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="22" spans="1:6" hidden="1">
+    <row r="22" spans="1:6">
       <c r="A22" t="s">
         <v>120</v>
       </c>
@@ -3599,7 +3847,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="23" spans="1:6" hidden="1">
+    <row r="23" spans="1:6">
       <c r="A23" t="s">
         <v>121</v>
       </c>
@@ -3619,7 +3867,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="24" spans="1:6" hidden="1">
+    <row r="24" spans="1:6">
       <c r="A24" t="s">
         <v>122</v>
       </c>
@@ -3639,7 +3887,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="25" spans="1:6" hidden="1">
+    <row r="25" spans="1:6">
       <c r="A25" t="s">
         <v>123</v>
       </c>
@@ -3659,7 +3907,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="26" spans="1:6" hidden="1">
+    <row r="26" spans="1:6">
       <c r="A26" t="s">
         <v>124</v>
       </c>
@@ -3679,7 +3927,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="27" spans="1:6" hidden="1">
+    <row r="27" spans="1:6">
       <c r="A27" t="s">
         <v>125</v>
       </c>
@@ -3699,7 +3947,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="28" spans="1:6" hidden="1">
+    <row r="28" spans="1:6">
       <c r="A28" t="s">
         <v>126</v>
       </c>
@@ -3719,7 +3967,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="29" spans="1:6" hidden="1">
+    <row r="29" spans="1:6">
       <c r="A29" t="s">
         <v>127</v>
       </c>
@@ -3739,7 +3987,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="30" spans="1:6" hidden="1">
+    <row r="30" spans="1:6">
       <c r="A30" t="s">
         <v>128</v>
       </c>
@@ -3759,7 +4007,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="31" spans="1:6" hidden="1">
+    <row r="31" spans="1:6">
       <c r="A31" t="s">
         <v>129</v>
       </c>
@@ -3779,7 +4027,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="32" spans="1:6" hidden="1">
+    <row r="32" spans="1:6">
       <c r="A32" t="s">
         <v>130</v>
       </c>
@@ -3799,7 +4047,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="33" spans="1:6" hidden="1">
+    <row r="33" spans="1:6">
       <c r="A33" t="s">
         <v>131</v>
       </c>
@@ -3819,7 +4067,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="34" spans="1:6" hidden="1">
+    <row r="34" spans="1:6">
       <c r="A34" t="s">
         <v>132</v>
       </c>
@@ -3830,7 +4078,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="35" spans="1:6" hidden="1">
+    <row r="35" spans="1:6">
       <c r="A35" t="s">
         <v>133</v>
       </c>
@@ -3841,7 +4089,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="36" spans="1:6" hidden="1">
+    <row r="36" spans="1:6">
       <c r="A36" t="s">
         <v>134</v>
       </c>
@@ -3852,7 +4100,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="37" spans="1:6" hidden="1">
+    <row r="37" spans="1:6">
       <c r="A37" t="s">
         <v>135</v>
       </c>
@@ -3863,7 +4111,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="38" spans="1:6" hidden="1">
+    <row r="38" spans="1:6">
       <c r="A38" t="s">
         <v>136</v>
       </c>
@@ -3874,7 +4122,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="39" spans="1:6" hidden="1">
+    <row r="39" spans="1:6">
       <c r="A39" t="s">
         <v>137</v>
       </c>
@@ -3885,7 +4133,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="40" spans="1:6" hidden="1">
+    <row r="40" spans="1:6">
       <c r="A40" t="s">
         <v>138</v>
       </c>
@@ -3905,7 +4153,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="41" spans="1:6" hidden="1">
+    <row r="41" spans="1:6">
       <c r="A41" t="s">
         <v>139</v>
       </c>
@@ -3925,7 +4173,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="42" spans="1:6" hidden="1">
+    <row r="42" spans="1:6">
       <c r="A42" t="s">
         <v>163</v>
       </c>
@@ -3962,7 +4210,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="44" spans="1:6" hidden="1">
+    <row r="44" spans="1:6">
       <c r="A44" t="s">
         <v>165</v>
       </c>
@@ -3999,7 +4247,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="46" spans="1:6" hidden="1">
+    <row r="46" spans="1:6">
       <c r="A46" t="s">
         <v>167</v>
       </c>
@@ -4053,7 +4301,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="49" spans="1:7" hidden="1">
+    <row r="49" spans="1:7">
       <c r="A49" t="s">
         <v>144</v>
       </c>
@@ -4073,7 +4321,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="50" spans="1:7" hidden="1">
+    <row r="50" spans="1:7">
       <c r="A50" t="s">
         <v>145</v>
       </c>
@@ -4093,7 +4341,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="51" spans="1:7" hidden="1">
+    <row r="51" spans="1:7">
       <c r="A51" t="s">
         <v>146</v>
       </c>
@@ -4113,7 +4361,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="52" spans="1:7" hidden="1">
+    <row r="52" spans="1:7">
       <c r="A52" t="s">
         <v>147</v>
       </c>
@@ -4133,7 +4381,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="53" spans="1:7" hidden="1">
+    <row r="53" spans="1:7">
       <c r="A53" t="s">
         <v>148</v>
       </c>
@@ -4153,7 +4401,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="54" spans="1:7" hidden="1">
+    <row r="54" spans="1:7">
       <c r="A54" t="s">
         <v>149</v>
       </c>
@@ -4207,7 +4455,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="57" spans="1:7" hidden="1">
+    <row r="57" spans="1:7">
       <c r="A57" t="s">
         <v>152</v>
       </c>
@@ -4246,7 +4494,7 @@
     </row>
     <row r="59" spans="1:7">
       <c r="A59" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B59" t="s">
         <v>264</v>
@@ -4264,7 +4512,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="60" spans="1:7" hidden="1">
+    <row r="60" spans="1:7">
       <c r="A60" t="s">
         <v>154</v>
       </c>
@@ -4284,7 +4532,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="61" spans="1:7" hidden="1">
+    <row r="61" spans="1:7">
       <c r="A61" t="s">
         <v>156</v>
       </c>
@@ -4304,7 +4552,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="62" spans="1:7" hidden="1">
+    <row r="62" spans="1:7">
       <c r="A62" t="s">
         <v>157</v>
       </c>
@@ -4324,7 +4572,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="63" spans="1:7" hidden="1">
+    <row r="63" spans="1:7">
       <c r="A63" t="s">
         <v>158</v>
       </c>
@@ -4344,7 +4592,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="64" spans="1:7" hidden="1">
+    <row r="64" spans="1:7">
       <c r="A64" t="s">
         <v>159</v>
       </c>
@@ -4364,7 +4612,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="65" spans="1:6" hidden="1">
+    <row r="65" spans="1:6">
       <c r="A65" t="s">
         <v>160</v>
       </c>
@@ -4384,7 +4632,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="66" spans="1:6" hidden="1">
+    <row r="66" spans="1:6">
       <c r="A66" t="s">
         <v>161</v>
       </c>
@@ -4404,7 +4652,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="67" spans="1:6" hidden="1">
+    <row r="67" spans="1:6">
       <c r="A67" t="s">
         <v>162</v>
       </c>
@@ -4426,16 +4674,8 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:G67">
-    <filterColumn colId="2">
-      <filters>
-        <filter val="否"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="3">
-      <filters>
-        <filter val="赵育"/>
-      </filters>
-    </filterColumn>
+    <filterColumn colId="2"/>
+    <filterColumn colId="3"/>
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6064,9 +6304,7 @@
       <c r="F88" t="s">
         <v>278</v>
       </c>
-      <c r="G88" t="s">
-        <v>277</v>
-      </c>
+      <c r="G88"/>
     </row>
     <row r="89" spans="1:7">
       <c r="A89" t="s">
@@ -6294,16 +6532,19 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D55"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:F77"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="18.5" customWidth="1"/>
+    <col min="1" max="1" width="31.625" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
     <col min="3" max="3" width="29.75" customWidth="1"/>
     <col min="4" max="4" width="12.875" customWidth="1"/>
+    <col min="5" max="5" width="15.75" customWidth="1"/>
+    <col min="6" max="6" width="27.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>291</v>
       </c>
@@ -6314,186 +6555,324 @@
         <v>293</v>
       </c>
       <c r="D1" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
+        <v>320</v>
+      </c>
+      <c r="E1" t="s">
+        <v>362</v>
+      </c>
+      <c r="F1" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" hidden="1">
       <c r="A2" t="s">
         <v>294</v>
       </c>
       <c r="D2" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+        <v>321</v>
+      </c>
+      <c r="E2" t="s">
+        <v>341</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" hidden="1">
       <c r="A3" t="s">
         <v>27</v>
       </c>
       <c r="D3" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+        <v>321</v>
+      </c>
+      <c r="E3" t="s">
+        <v>341</v>
+      </c>
+      <c r="F3" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" hidden="1">
       <c r="A4" t="s">
         <v>28</v>
       </c>
       <c r="D4" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+        <v>321</v>
+      </c>
+      <c r="E4" t="s">
+        <v>341</v>
+      </c>
+      <c r="F4" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" hidden="1">
       <c r="A5" t="s">
         <v>29</v>
       </c>
       <c r="D5" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
+        <v>321</v>
+      </c>
+      <c r="E5" t="s">
+        <v>341</v>
+      </c>
+      <c r="F5" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" hidden="1">
       <c r="A6" t="s">
         <v>30</v>
       </c>
       <c r="D6" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
+        <v>321</v>
+      </c>
+      <c r="E6" t="s">
+        <v>341</v>
+      </c>
+      <c r="F6" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" hidden="1">
       <c r="A7" t="s">
         <v>31</v>
       </c>
       <c r="D7" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
+        <v>321</v>
+      </c>
+      <c r="E7" t="s">
+        <v>341</v>
+      </c>
+      <c r="F7" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" hidden="1">
       <c r="A8" t="s">
         <v>32</v>
       </c>
       <c r="D8" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
+        <v>321</v>
+      </c>
+      <c r="E8" t="s">
+        <v>341</v>
+      </c>
+      <c r="F8" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" hidden="1">
       <c r="A9" t="s">
         <v>33</v>
       </c>
       <c r="D9" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
+        <v>321</v>
+      </c>
+      <c r="E9" t="s">
+        <v>341</v>
+      </c>
+      <c r="F9" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" hidden="1">
       <c r="A10" t="s">
         <v>34</v>
       </c>
       <c r="D10" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
+        <v>321</v>
+      </c>
+      <c r="E10" t="s">
+        <v>341</v>
+      </c>
+      <c r="F10" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" hidden="1">
       <c r="A11" t="s">
         <v>35</v>
       </c>
       <c r="D11" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
+        <v>321</v>
+      </c>
+      <c r="E11" t="s">
+        <v>341</v>
+      </c>
+      <c r="F11" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" hidden="1">
       <c r="A12" t="s">
         <v>295</v>
       </c>
       <c r="D12" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
+        <v>321</v>
+      </c>
+      <c r="E12" t="s">
+        <v>341</v>
+      </c>
+      <c r="F12" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" hidden="1">
       <c r="A13" t="s">
         <v>36</v>
       </c>
       <c r="D13" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
+        <v>321</v>
+      </c>
+      <c r="E13" t="s">
+        <v>341</v>
+      </c>
+      <c r="F13" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" hidden="1">
       <c r="A14" t="s">
         <v>37</v>
       </c>
       <c r="D14" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
+        <v>321</v>
+      </c>
+      <c r="E14" t="s">
+        <v>341</v>
+      </c>
+      <c r="F14" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" hidden="1">
       <c r="A15" t="s">
         <v>38</v>
       </c>
       <c r="D15" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
+        <v>321</v>
+      </c>
+      <c r="E15" t="s">
+        <v>341</v>
+      </c>
+      <c r="F15" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" hidden="1">
       <c r="A16" t="s">
         <v>39</v>
       </c>
       <c r="D16" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
+        <v>321</v>
+      </c>
+      <c r="E16" t="s">
+        <v>341</v>
+      </c>
+      <c r="F16" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" hidden="1">
       <c r="A17" t="s">
         <v>40</v>
       </c>
       <c r="D17" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
+        <v>321</v>
+      </c>
+      <c r="E17" t="s">
+        <v>341</v>
+      </c>
+      <c r="F17" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" hidden="1">
       <c r="A18" t="s">
         <v>41</v>
       </c>
       <c r="D18" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
+        <v>321</v>
+      </c>
+      <c r="E18" t="s">
+        <v>341</v>
+      </c>
+      <c r="F18" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" hidden="1">
       <c r="A19" t="s">
         <v>42</v>
       </c>
       <c r="D19" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
+        <v>321</v>
+      </c>
+      <c r="E19" t="s">
+        <v>341</v>
+      </c>
+      <c r="F19" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="27" hidden="1">
       <c r="A20" t="s">
         <v>43</v>
       </c>
       <c r="D20" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
+        <v>321</v>
+      </c>
+      <c r="E20" t="s">
+        <v>341</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" hidden="1">
       <c r="A21" t="s">
         <v>44</v>
       </c>
       <c r="D21" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4">
+        <v>321</v>
+      </c>
+      <c r="E21" t="s">
+        <v>341</v>
+      </c>
+      <c r="F21" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" hidden="1">
       <c r="A22" t="s">
         <v>45</v>
       </c>
       <c r="D22" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
+        <v>321</v>
+      </c>
+      <c r="E22" t="s">
+        <v>341</v>
+      </c>
+      <c r="F22" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" hidden="1">
       <c r="A23" t="s">
         <v>296</v>
       </c>
       <c r="D23" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4">
+        <v>321</v>
+      </c>
+      <c r="E23" t="s">
+        <v>341</v>
+      </c>
+      <c r="F23" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" hidden="1">
       <c r="A24" t="s">
         <v>297</v>
       </c>
@@ -6501,13 +6880,16 @@
         <v>309</v>
       </c>
       <c r="C24" t="s">
-        <v>311</v>
+        <v>332</v>
       </c>
       <c r="D24" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4">
+        <v>322</v>
+      </c>
+      <c r="E24" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" hidden="1">
       <c r="A25" t="s">
         <v>82</v>
       </c>
@@ -6515,13 +6897,16 @@
         <v>309</v>
       </c>
       <c r="C25" t="s">
-        <v>310</v>
+        <v>332</v>
       </c>
       <c r="D25" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4">
+        <v>322</v>
+      </c>
+      <c r="E25" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" hidden="1">
       <c r="A26" t="s">
         <v>83</v>
       </c>
@@ -6529,13 +6914,16 @@
         <v>309</v>
       </c>
       <c r="C26" t="s">
-        <v>311</v>
+        <v>332</v>
       </c>
       <c r="D26" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4">
+        <v>322</v>
+      </c>
+      <c r="E26" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" hidden="1">
       <c r="A27" t="s">
         <v>84</v>
       </c>
@@ -6543,13 +6931,16 @@
         <v>309</v>
       </c>
       <c r="C27" t="s">
-        <v>311</v>
+        <v>332</v>
       </c>
       <c r="D27" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4">
+        <v>322</v>
+      </c>
+      <c r="E27" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" hidden="1">
       <c r="A28" t="s">
         <v>85</v>
       </c>
@@ -6557,13 +6948,16 @@
         <v>309</v>
       </c>
       <c r="C28" t="s">
-        <v>311</v>
+        <v>332</v>
       </c>
       <c r="D28" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4">
+        <v>322</v>
+      </c>
+      <c r="E28" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" hidden="1">
       <c r="A29" t="s">
         <v>86</v>
       </c>
@@ -6571,13 +6965,16 @@
         <v>309</v>
       </c>
       <c r="C29" t="s">
-        <v>311</v>
+        <v>332</v>
       </c>
       <c r="D29" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4">
+        <v>322</v>
+      </c>
+      <c r="E29" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" hidden="1">
       <c r="A30" t="s">
         <v>87</v>
       </c>
@@ -6585,13 +6982,16 @@
         <v>309</v>
       </c>
       <c r="C30" t="s">
-        <v>311</v>
+        <v>332</v>
       </c>
       <c r="D30" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4">
+        <v>322</v>
+      </c>
+      <c r="E30" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" hidden="1">
       <c r="A31" t="s">
         <v>88</v>
       </c>
@@ -6599,13 +6999,16 @@
         <v>309</v>
       </c>
       <c r="C31" t="s">
-        <v>311</v>
+        <v>332</v>
       </c>
       <c r="D31" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4">
+        <v>322</v>
+      </c>
+      <c r="E31" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" hidden="1">
       <c r="A32" t="s">
         <v>89</v>
       </c>
@@ -6613,13 +7016,16 @@
         <v>309</v>
       </c>
       <c r="C32" t="s">
-        <v>311</v>
+        <v>332</v>
       </c>
       <c r="D32" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4">
+        <v>322</v>
+      </c>
+      <c r="E32" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" hidden="1">
       <c r="A33" t="s">
         <v>90</v>
       </c>
@@ -6627,13 +7033,16 @@
         <v>309</v>
       </c>
       <c r="C33" t="s">
-        <v>311</v>
+        <v>332</v>
       </c>
       <c r="D33" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4">
+        <v>322</v>
+      </c>
+      <c r="E33" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" hidden="1">
       <c r="A34" t="s">
         <v>91</v>
       </c>
@@ -6641,13 +7050,16 @@
         <v>309</v>
       </c>
       <c r="C34" t="s">
-        <v>311</v>
+        <v>332</v>
       </c>
       <c r="D34" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4">
+        <v>322</v>
+      </c>
+      <c r="E34" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" hidden="1">
       <c r="A35" t="s">
         <v>92</v>
       </c>
@@ -6655,13 +7067,16 @@
         <v>309</v>
       </c>
       <c r="C35" t="s">
-        <v>311</v>
+        <v>332</v>
       </c>
       <c r="D35" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4">
+        <v>322</v>
+      </c>
+      <c r="E35" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" hidden="1">
       <c r="A36" t="s">
         <v>298</v>
       </c>
@@ -6669,13 +7084,16 @@
         <v>309</v>
       </c>
       <c r="C36" t="s">
-        <v>311</v>
+        <v>332</v>
       </c>
       <c r="D36" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4">
+        <v>322</v>
+      </c>
+      <c r="E36" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" hidden="1">
       <c r="A37" t="s">
         <v>94</v>
       </c>
@@ -6683,13 +7101,16 @@
         <v>309</v>
       </c>
       <c r="C37" t="s">
-        <v>311</v>
+        <v>332</v>
       </c>
       <c r="D37" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4">
+        <v>322</v>
+      </c>
+      <c r="E37" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" hidden="1">
       <c r="A38" t="s">
         <v>95</v>
       </c>
@@ -6697,13 +7118,16 @@
         <v>309</v>
       </c>
       <c r="C38" t="s">
-        <v>311</v>
+        <v>332</v>
       </c>
       <c r="D38" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4">
+        <v>322</v>
+      </c>
+      <c r="E38" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" hidden="1">
       <c r="A39" t="s">
         <v>96</v>
       </c>
@@ -6711,13 +7135,16 @@
         <v>309</v>
       </c>
       <c r="C39" t="s">
-        <v>311</v>
+        <v>332</v>
       </c>
       <c r="D39" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4">
+        <v>322</v>
+      </c>
+      <c r="E39" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" hidden="1">
       <c r="A40" t="s">
         <v>97</v>
       </c>
@@ -6725,139 +7152,540 @@
         <v>309</v>
       </c>
       <c r="C40" t="s">
+        <v>332</v>
+      </c>
+      <c r="D40" t="s">
+        <v>322</v>
+      </c>
+      <c r="E40" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" hidden="1">
+      <c r="A41" t="s">
         <v>311</v>
-      </c>
-      <c r="D40" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4">
-      <c r="A41" t="s">
-        <v>313</v>
       </c>
       <c r="B41" t="s">
         <v>309</v>
       </c>
       <c r="C41" t="s">
-        <v>311</v>
+        <v>332</v>
       </c>
       <c r="D41" t="s">
+        <v>322</v>
+      </c>
+      <c r="E41" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" hidden="1">
+      <c r="A42" t="s">
+        <v>312</v>
+      </c>
+      <c r="D42" t="s">
+        <v>323</v>
+      </c>
+      <c r="E42" t="s">
+        <v>341</v>
+      </c>
+      <c r="F42" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" hidden="1">
+      <c r="A43" t="s">
+        <v>313</v>
+      </c>
+      <c r="D43" t="s">
+        <v>323</v>
+      </c>
+      <c r="E43" t="s">
+        <v>341</v>
+      </c>
+      <c r="F43" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" hidden="1">
+      <c r="A44" t="s">
+        <v>314</v>
+      </c>
+      <c r="D44" t="s">
+        <v>323</v>
+      </c>
+      <c r="E44" t="s">
+        <v>341</v>
+      </c>
+      <c r="F44" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" hidden="1">
+      <c r="A45" t="s">
+        <v>315</v>
+      </c>
+      <c r="D45" t="s">
+        <v>323</v>
+      </c>
+      <c r="E45" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" hidden="1">
+      <c r="A46" t="s">
+        <v>316</v>
+      </c>
+      <c r="D46" t="s">
+        <v>323</v>
+      </c>
+      <c r="E46" t="s">
+        <v>341</v>
+      </c>
+      <c r="F46" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" hidden="1">
+      <c r="A47" t="s">
+        <v>317</v>
+      </c>
+      <c r="D47" t="s">
+        <v>323</v>
+      </c>
+      <c r="E47" t="s">
+        <v>341</v>
+      </c>
+      <c r="F47" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" hidden="1">
+      <c r="A48" t="s">
+        <v>318</v>
+      </c>
+      <c r="D48" t="s">
+        <v>323</v>
+      </c>
+      <c r="E48" t="s">
+        <v>341</v>
+      </c>
+      <c r="F48" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" hidden="1">
+      <c r="A49" t="s">
+        <v>319</v>
+      </c>
+      <c r="D49" t="s">
+        <v>323</v>
+      </c>
+      <c r="E49" t="s">
+        <v>341</v>
+      </c>
+      <c r="F49" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6">
+      <c r="A50" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="42" spans="1:4">
-      <c r="A42" t="s">
-        <v>314</v>
-      </c>
-      <c r="D42" t="s">
+      <c r="D50" t="s">
+        <v>329</v>
+      </c>
+      <c r="E50" t="s">
+        <v>341</v>
+      </c>
+      <c r="F50" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6">
+      <c r="A51" t="s">
         <v>325</v>
       </c>
-    </row>
-    <row r="43" spans="1:4">
-      <c r="A43" t="s">
-        <v>315</v>
-      </c>
-      <c r="D43" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4">
-      <c r="A44" t="s">
-        <v>316</v>
-      </c>
-      <c r="D44" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4">
-      <c r="A45" t="s">
-        <v>317</v>
-      </c>
-      <c r="D45" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4">
-      <c r="A46" t="s">
-        <v>318</v>
-      </c>
-      <c r="D46" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4">
-      <c r="A47" t="s">
-        <v>319</v>
-      </c>
-      <c r="D47" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4">
-      <c r="A48" t="s">
-        <v>320</v>
-      </c>
-      <c r="D48" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4">
-      <c r="A49" t="s">
-        <v>321</v>
-      </c>
-      <c r="D49" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4">
-      <c r="A50" t="s">
+      <c r="D51" t="s">
+        <v>329</v>
+      </c>
+      <c r="E51" t="s">
+        <v>341</v>
+      </c>
+      <c r="F51" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6">
+      <c r="A52" t="s">
         <v>326</v>
       </c>
-      <c r="D50" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4">
-      <c r="A51" t="s">
+      <c r="D52" t="s">
+        <v>329</v>
+      </c>
+      <c r="E52" t="s">
+        <v>341</v>
+      </c>
+      <c r="F52" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6">
+      <c r="A53" t="s">
         <v>327</v>
       </c>
-      <c r="D51" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4">
-      <c r="A52" t="s">
+      <c r="D53" t="s">
+        <v>329</v>
+      </c>
+      <c r="E53" t="s">
+        <v>341</v>
+      </c>
+      <c r="F53" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6">
+      <c r="A54" t="s">
+        <v>336</v>
+      </c>
+      <c r="D54" t="s">
+        <v>329</v>
+      </c>
+      <c r="E54" t="s">
+        <v>341</v>
+      </c>
+      <c r="F54" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6">
+      <c r="A55" t="s">
         <v>328</v>
       </c>
-      <c r="D52" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4">
-      <c r="A53" t="s">
+      <c r="D55" t="s">
         <v>329</v>
       </c>
-      <c r="D53" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4">
-      <c r="A54" t="s">
-        <v>330</v>
-      </c>
-      <c r="D54" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4">
-      <c r="A55" t="s">
-        <v>331</v>
-      </c>
-      <c r="D55" t="s">
-        <v>332</v>
+      <c r="E55" t="s">
+        <v>341</v>
+      </c>
+      <c r="F55" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" hidden="1">
+      <c r="A56" t="s">
+        <v>333</v>
+      </c>
+      <c r="D56" t="s">
+        <v>340</v>
+      </c>
+      <c r="E56" t="s">
+        <v>341</v>
+      </c>
+      <c r="F56" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" hidden="1">
+      <c r="A57" t="s">
+        <v>334</v>
+      </c>
+      <c r="D57" t="s">
+        <v>340</v>
+      </c>
+      <c r="E57" t="s">
+        <v>341</v>
+      </c>
+      <c r="F57" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" hidden="1">
+      <c r="A58" t="s">
+        <v>335</v>
+      </c>
+      <c r="D58" t="s">
+        <v>340</v>
+      </c>
+      <c r="E58" t="s">
+        <v>341</v>
+      </c>
+      <c r="F58" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" hidden="1">
+      <c r="A59" t="s">
+        <v>342</v>
+      </c>
+      <c r="D59" t="s">
+        <v>340</v>
+      </c>
+      <c r="E59" t="s">
+        <v>341</v>
+      </c>
+      <c r="F59" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" hidden="1">
+      <c r="A60" t="s">
+        <v>343</v>
+      </c>
+      <c r="D60" t="s">
+        <v>340</v>
+      </c>
+      <c r="E60" t="s">
+        <v>341</v>
+      </c>
+      <c r="F60" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" hidden="1">
+      <c r="A61" t="s">
+        <v>344</v>
+      </c>
+      <c r="D61" t="s">
+        <v>340</v>
+      </c>
+      <c r="E61" t="s">
+        <v>341</v>
+      </c>
+      <c r="F61" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" hidden="1">
+      <c r="A62" t="s">
+        <v>345</v>
+      </c>
+      <c r="D62" t="s">
+        <v>340</v>
+      </c>
+      <c r="E62" t="s">
+        <v>341</v>
+      </c>
+      <c r="F62" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" hidden="1">
+      <c r="A63" t="s">
+        <v>346</v>
+      </c>
+      <c r="D63" t="s">
+        <v>340</v>
+      </c>
+      <c r="E63" t="s">
+        <v>341</v>
+      </c>
+      <c r="F63" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" hidden="1">
+      <c r="A64" t="s">
+        <v>347</v>
+      </c>
+      <c r="D64" t="s">
+        <v>340</v>
+      </c>
+      <c r="E64" t="s">
+        <v>341</v>
+      </c>
+      <c r="F64" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" hidden="1">
+      <c r="A65" t="s">
+        <v>348</v>
+      </c>
+      <c r="D65" t="s">
+        <v>340</v>
+      </c>
+      <c r="E65" t="s">
+        <v>341</v>
+      </c>
+      <c r="F65" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" hidden="1">
+      <c r="A66" t="s">
+        <v>349</v>
+      </c>
+      <c r="C66" t="s">
+        <v>357</v>
+      </c>
+      <c r="D66" t="s">
+        <v>341</v>
+      </c>
+      <c r="E66" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" hidden="1">
+      <c r="A67" t="s">
+        <v>350</v>
+      </c>
+      <c r="C67" t="s">
+        <v>358</v>
+      </c>
+      <c r="D67" t="s">
+        <v>341</v>
+      </c>
+      <c r="E67" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" hidden="1">
+      <c r="A68" t="s">
+        <v>351</v>
+      </c>
+      <c r="C68" t="s">
+        <v>357</v>
+      </c>
+      <c r="D68" t="s">
+        <v>341</v>
+      </c>
+      <c r="E68" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" hidden="1">
+      <c r="A69" t="s">
+        <v>352</v>
+      </c>
+      <c r="C69" t="s">
+        <v>357</v>
+      </c>
+      <c r="D69" t="s">
+        <v>341</v>
+      </c>
+      <c r="E69" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" hidden="1">
+      <c r="A70" t="s">
+        <v>353</v>
+      </c>
+      <c r="C70" t="s">
+        <v>357</v>
+      </c>
+      <c r="D70" t="s">
+        <v>341</v>
+      </c>
+      <c r="E70" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" hidden="1">
+      <c r="A71" t="s">
+        <v>354</v>
+      </c>
+      <c r="C71" t="s">
+        <v>357</v>
+      </c>
+      <c r="D71" t="s">
+        <v>341</v>
+      </c>
+      <c r="E71" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" hidden="1">
+      <c r="A72" t="s">
+        <v>355</v>
+      </c>
+      <c r="C72" t="s">
+        <v>357</v>
+      </c>
+      <c r="D72" t="s">
+        <v>341</v>
+      </c>
+      <c r="E72" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" hidden="1">
+      <c r="A73" t="s">
+        <v>356</v>
+      </c>
+      <c r="C73" t="s">
+        <v>357</v>
+      </c>
+      <c r="D73" t="s">
+        <v>341</v>
+      </c>
+      <c r="E73" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" hidden="1">
+      <c r="A74" t="s">
+        <v>337</v>
+      </c>
+      <c r="D74" t="s">
+        <v>339</v>
+      </c>
+      <c r="E74" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" hidden="1">
+      <c r="A75" t="s">
+        <v>338</v>
+      </c>
+      <c r="D75" t="s">
+        <v>339</v>
+      </c>
+      <c r="E75" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6">
+      <c r="A76" t="s">
+        <v>359</v>
+      </c>
+      <c r="D76" t="s">
+        <v>360</v>
+      </c>
+      <c r="E76" t="s">
+        <v>341</v>
+      </c>
+      <c r="F76" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6">
+      <c r="A77" t="s">
+        <v>361</v>
+      </c>
+      <c r="D77" t="s">
+        <v>360</v>
+      </c>
+      <c r="E77" t="s">
+        <v>341</v>
+      </c>
+      <c r="F77" t="s">
+        <v>357</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:F77">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="赵小妮"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="4">
+      <filters>
+        <filter val="赵育"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -6866,25 +7694,355 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="81">
-      <c r="A1" s="2" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1">
-      <c r="A2" t="s">
-        <v>334</v>
-      </c>
+    <row r="1" spans="1:1">
+      <c r="A1" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A7:A8"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <cols>
+    <col min="1" max="1" width="38.125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" s="2" t="s">
+        <v>331</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C15"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <cols>
+    <col min="1" max="1" width="20.375" customWidth="1"/>
+    <col min="2" max="2" width="14.375" customWidth="1"/>
+    <col min="3" max="3" width="65" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
+        <v>385</v>
+      </c>
+      <c r="B1" t="s">
+        <v>386</v>
+      </c>
+      <c r="C1" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>371</v>
+      </c>
+      <c r="B2" t="s">
+        <v>388</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>372</v>
+      </c>
+      <c r="B3" t="s">
+        <v>388</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>373</v>
+      </c>
+      <c r="B4" t="s">
+        <v>388</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>374</v>
+      </c>
+      <c r="B5" t="s">
+        <v>388</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>375</v>
+      </c>
+      <c r="B6" t="s">
+        <v>329</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>376</v>
+      </c>
+      <c r="B7" t="s">
+        <v>329</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>377</v>
+      </c>
+      <c r="B8" t="s">
+        <v>329</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>378</v>
+      </c>
+      <c r="B9" t="s">
+        <v>329</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>379</v>
+      </c>
+      <c r="B10" t="s">
+        <v>329</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>380</v>
+      </c>
+      <c r="B11" t="s">
+        <v>329</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>381</v>
+      </c>
+      <c r="B12" t="s">
+        <v>389</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>382</v>
+      </c>
+      <c r="B13" t="s">
+        <v>389</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>383</v>
+      </c>
+      <c r="B14" t="s">
+        <v>389</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
+        <v>384</v>
+      </c>
+      <c r="B15" t="s">
+        <v>389</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>390</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <cols>
+    <col min="1" max="1" width="15.75" customWidth="1"/>
+    <col min="2" max="2" width="13" customWidth="1"/>
+    <col min="3" max="3" width="24.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
+        <v>385</v>
+      </c>
+      <c r="B1" t="s">
+        <v>386</v>
+      </c>
+      <c r="C1" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>391</v>
+      </c>
+      <c r="B2" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>392</v>
+      </c>
+      <c r="B3" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>393</v>
+      </c>
+      <c r="B4" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>394</v>
+      </c>
+      <c r="B5" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>395</v>
+      </c>
+      <c r="B6" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>396</v>
+      </c>
+      <c r="B7" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>397</v>
+      </c>
+      <c r="B8" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>398</v>
+      </c>
+      <c r="B9" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>399</v>
+      </c>
+      <c r="B10" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>400</v>
+      </c>
+      <c r="B11" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>401</v>
+      </c>
+      <c r="B12" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>402</v>
+      </c>
+      <c r="B13" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>403</v>
+      </c>
+      <c r="B14" t="s">
+        <v>389</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/internal_doc/05.测试设计/story/事务支持RC隔离级别/事务自动化用例跟踪表.xlsx
+++ b/internal_doc/05.测试设计/story/事务支持RC隔离级别/事务自动化用例跟踪表.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1789" uniqueCount="405">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1792" uniqueCount="407">
   <si>
     <t>用例编号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1377,6 +1377,14 @@
   </si>
   <si>
     <t>seqDB-18238</t>
+  </si>
+  <si>
+    <t>ok</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ok</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>ok</t>
@@ -6564,7 +6572,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="2" spans="1:6" hidden="1">
+    <row r="2" spans="1:6">
       <c r="A2" t="s">
         <v>294</v>
       </c>
@@ -6578,7 +6586,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="3" spans="1:6" hidden="1">
+    <row r="3" spans="1:6">
       <c r="A3" t="s">
         <v>27</v>
       </c>
@@ -6592,7 +6600,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="4" spans="1:6" hidden="1">
+    <row r="4" spans="1:6">
       <c r="A4" t="s">
         <v>28</v>
       </c>
@@ -6606,7 +6614,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="5" spans="1:6" hidden="1">
+    <row r="5" spans="1:6">
       <c r="A5" t="s">
         <v>29</v>
       </c>
@@ -6620,7 +6628,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="6" spans="1:6" hidden="1">
+    <row r="6" spans="1:6">
       <c r="A6" t="s">
         <v>30</v>
       </c>
@@ -6634,7 +6642,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="7" spans="1:6" hidden="1">
+    <row r="7" spans="1:6">
       <c r="A7" t="s">
         <v>31</v>
       </c>
@@ -6648,7 +6656,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="8" spans="1:6" hidden="1">
+    <row r="8" spans="1:6">
       <c r="A8" t="s">
         <v>32</v>
       </c>
@@ -6662,7 +6670,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="9" spans="1:6" hidden="1">
+    <row r="9" spans="1:6">
       <c r="A9" t="s">
         <v>33</v>
       </c>
@@ -6676,7 +6684,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="10" spans="1:6" hidden="1">
+    <row r="10" spans="1:6">
       <c r="A10" t="s">
         <v>34</v>
       </c>
@@ -6690,7 +6698,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="11" spans="1:6" hidden="1">
+    <row r="11" spans="1:6">
       <c r="A11" t="s">
         <v>35</v>
       </c>
@@ -6704,7 +6712,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="12" spans="1:6" hidden="1">
+    <row r="12" spans="1:6">
       <c r="A12" t="s">
         <v>295</v>
       </c>
@@ -6718,7 +6726,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="13" spans="1:6" hidden="1">
+    <row r="13" spans="1:6">
       <c r="A13" t="s">
         <v>36</v>
       </c>
@@ -6732,7 +6740,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="14" spans="1:6" hidden="1">
+    <row r="14" spans="1:6">
       <c r="A14" t="s">
         <v>37</v>
       </c>
@@ -6746,7 +6754,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="15" spans="1:6" hidden="1">
+    <row r="15" spans="1:6">
       <c r="A15" t="s">
         <v>38</v>
       </c>
@@ -6760,7 +6768,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="16" spans="1:6" hidden="1">
+    <row r="16" spans="1:6">
       <c r="A16" t="s">
         <v>39</v>
       </c>
@@ -6774,7 +6782,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="17" spans="1:6" hidden="1">
+    <row r="17" spans="1:6">
       <c r="A17" t="s">
         <v>40</v>
       </c>
@@ -6788,7 +6796,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="18" spans="1:6" hidden="1">
+    <row r="18" spans="1:6">
       <c r="A18" t="s">
         <v>41</v>
       </c>
@@ -6802,7 +6810,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="19" spans="1:6" hidden="1">
+    <row r="19" spans="1:6">
       <c r="A19" t="s">
         <v>42</v>
       </c>
@@ -6816,7 +6824,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="27" hidden="1">
+    <row r="20" spans="1:6" ht="27">
       <c r="A20" t="s">
         <v>43</v>
       </c>
@@ -6830,7 +6838,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="21" spans="1:6" hidden="1">
+    <row r="21" spans="1:6">
       <c r="A21" t="s">
         <v>44</v>
       </c>
@@ -6844,7 +6852,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="22" spans="1:6" hidden="1">
+    <row r="22" spans="1:6">
       <c r="A22" t="s">
         <v>45</v>
       </c>
@@ -6858,7 +6866,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="23" spans="1:6" hidden="1">
+    <row r="23" spans="1:6">
       <c r="A23" t="s">
         <v>296</v>
       </c>
@@ -7178,7 +7186,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="42" spans="1:6" hidden="1">
+    <row r="42" spans="1:6">
       <c r="A42" t="s">
         <v>312</v>
       </c>
@@ -7192,7 +7200,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="43" spans="1:6" hidden="1">
+    <row r="43" spans="1:6">
       <c r="A43" t="s">
         <v>313</v>
       </c>
@@ -7206,7 +7214,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="44" spans="1:6" hidden="1">
+    <row r="44" spans="1:6">
       <c r="A44" t="s">
         <v>314</v>
       </c>
@@ -7220,7 +7228,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="45" spans="1:6" hidden="1">
+    <row r="45" spans="1:6">
       <c r="A45" t="s">
         <v>315</v>
       </c>
@@ -7230,8 +7238,11 @@
       <c r="E45" t="s">
         <v>341</v>
       </c>
-    </row>
-    <row r="46" spans="1:6" hidden="1">
+      <c r="F45" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6">
       <c r="A46" t="s">
         <v>316</v>
       </c>
@@ -7245,7 +7256,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="47" spans="1:6" hidden="1">
+    <row r="47" spans="1:6">
       <c r="A47" t="s">
         <v>317</v>
       </c>
@@ -7259,7 +7270,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="48" spans="1:6" hidden="1">
+    <row r="48" spans="1:6">
       <c r="A48" t="s">
         <v>318</v>
       </c>
@@ -7273,7 +7284,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="49" spans="1:6" hidden="1">
+    <row r="49" spans="1:6">
       <c r="A49" t="s">
         <v>319</v>
       </c>
@@ -7371,7 +7382,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="56" spans="1:6" hidden="1">
+    <row r="56" spans="1:6">
       <c r="A56" t="s">
         <v>333</v>
       </c>
@@ -7385,7 +7396,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="57" spans="1:6" hidden="1">
+    <row r="57" spans="1:6">
       <c r="A57" t="s">
         <v>334</v>
       </c>
@@ -7399,7 +7410,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="58" spans="1:6" hidden="1">
+    <row r="58" spans="1:6">
       <c r="A58" t="s">
         <v>335</v>
       </c>
@@ -7413,7 +7424,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="59" spans="1:6" hidden="1">
+    <row r="59" spans="1:6">
       <c r="A59" t="s">
         <v>342</v>
       </c>
@@ -7427,7 +7438,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="60" spans="1:6" hidden="1">
+    <row r="60" spans="1:6">
       <c r="A60" t="s">
         <v>343</v>
       </c>
@@ -7441,7 +7452,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="61" spans="1:6" hidden="1">
+    <row r="61" spans="1:6">
       <c r="A61" t="s">
         <v>344</v>
       </c>
@@ -7455,7 +7466,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="62" spans="1:6" hidden="1">
+    <row r="62" spans="1:6">
       <c r="A62" t="s">
         <v>345</v>
       </c>
@@ -7469,7 +7480,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="63" spans="1:6" hidden="1">
+    <row r="63" spans="1:6">
       <c r="A63" t="s">
         <v>346</v>
       </c>
@@ -7483,7 +7494,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="64" spans="1:6" hidden="1">
+    <row r="64" spans="1:6">
       <c r="A64" t="s">
         <v>347</v>
       </c>
@@ -7497,7 +7508,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="65" spans="1:6" hidden="1">
+    <row r="65" spans="1:6">
       <c r="A65" t="s">
         <v>348</v>
       </c>
@@ -7623,7 +7634,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="74" spans="1:6" hidden="1">
+    <row r="74" spans="1:6">
       <c r="A74" t="s">
         <v>337</v>
       </c>
@@ -7633,8 +7644,11 @@
       <c r="E74" t="s">
         <v>341</v>
       </c>
-    </row>
-    <row r="75" spans="1:6" hidden="1">
+      <c r="F74" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6">
       <c r="A75" t="s">
         <v>338</v>
       </c>
@@ -7643,6 +7657,9 @@
       </c>
       <c r="E75" t="s">
         <v>341</v>
+      </c>
+      <c r="F75" t="s">
+        <v>406</v>
       </c>
     </row>
     <row r="76" spans="1:6">
@@ -7675,11 +7692,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:F77">
-    <filterColumn colId="3">
-      <filters>
-        <filter val="赵小妮"/>
-      </filters>
-    </filterColumn>
+    <filterColumn colId="3"/>
     <filterColumn colId="4">
       <filters>
         <filter val="赵育"/>
